--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3B23C3-1039-4AF9-9339-B86FAEAD7BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86023DB-02D9-4121-ADAA-4E3332CDB1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="42">
   <si>
     <t>Data</t>
   </si>
@@ -158,6 +158,9 @@
   <si>
     <t>18.10.2026</t>
   </si>
+  <si>
+    <t>20.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -260,6 +263,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -267,15 +279,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -553,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1010"/>
+  <dimension ref="A1:C1067"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -562,18 +565,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -606,17 +609,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7">
         <f>B4-B5</f>
         <v>862</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -627,18 +630,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -671,31 +674,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="A15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="7">
         <f>B13-B14</f>
         <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
+      <c r="A18" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -728,31 +731,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="4">
+      <c r="A23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="7">
         <f>B21-B22</f>
         <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
+      <c r="A26" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -785,31 +788,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="4">
+      <c r="A31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="7">
         <f>B29-B30</f>
         <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="7"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
+      <c r="A34" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -842,31 +845,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="4">
+      <c r="A39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="7">
         <f>B37-B38</f>
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="3"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="7"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
+      <c r="A42" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -899,31 +902,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="4">
+      <c r="A47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="7">
         <f>B45-B46</f>
         <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="3"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="7"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
+      <c r="A50" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="5"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -956,31 +959,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="4">
+      <c r="A55" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="7">
         <f>B53-B54</f>
         <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="3"/>
-      <c r="B56" s="4"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="7"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
+      <c r="A58" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="8"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -1013,17 +1016,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="4">
+      <c r="A63" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="7">
         <f>B61-B62</f>
         <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1034,18 +1037,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
+      <c r="A67" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1078,31 +1081,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="4">
+      <c r="A72" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="7">
         <f>B70-B71</f>
         <v>37</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="3"/>
-      <c r="B73" s="4"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="7"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="8"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="5"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1135,31 +1138,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="4">
+      <c r="A80" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="7">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="3"/>
-      <c r="B81" s="4"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="7"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
+      <c r="A83" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="8"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="5"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1192,31 +1195,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="4">
+      <c r="A88" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="7">
         <f>B86-B87</f>
         <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="3"/>
-      <c r="B89" s="4"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="7"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
+      <c r="A91" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="8"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1249,31 +1252,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="4">
+      <c r="A96" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="7">
         <f>B94-B95</f>
         <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="3"/>
-      <c r="B97" s="4"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="7"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
+      <c r="A99" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="8"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1306,17 +1309,17 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="4">
+      <c r="A104" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="7">
         <f>B102-B103</f>
         <v>583</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="4"/>
+      <c r="A105" s="6"/>
+      <c r="B105" s="7"/>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="1" t="s">
@@ -1327,18 +1330,18 @@
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
+      <c r="A108" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B109" s="7"/>
-      <c r="C109" s="8"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="1" t="s">
@@ -1371,31 +1374,31 @@
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B113" s="4">
+      <c r="A113" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B113" s="7">
         <f>B111-B112</f>
         <v>451</v>
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="3"/>
-      <c r="B114" s="4"/>
+      <c r="A114" s="6"/>
+      <c r="B114" s="7"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
+      <c r="A116" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B117" s="7"/>
-      <c r="C117" s="8"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="1" t="s">
@@ -1428,31 +1431,31 @@
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B121" s="4">
+      <c r="A121" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B121" s="7">
         <f>B119-B120</f>
         <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="3"/>
-      <c r="B122" s="4"/>
+      <c r="A122" s="6"/>
+      <c r="B122" s="7"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
+      <c r="A124" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B125" s="7"/>
-      <c r="C125" s="8"/>
+      <c r="B125" s="4"/>
+      <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="1" t="s">
@@ -1485,31 +1488,31 @@
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B129" s="4">
+      <c r="A129" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129" s="7">
         <f>B127-B128</f>
         <v>142</v>
       </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="3"/>
-      <c r="B130" s="4"/>
+      <c r="A130" s="6"/>
+      <c r="B130" s="7"/>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
+      <c r="A132" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B133" s="7"/>
-      <c r="C133" s="8"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1542,31 +1545,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="4">
+      <c r="A137" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="7">
         <f>B135-B136</f>
         <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="3"/>
-      <c r="B138" s="4"/>
+      <c r="A138" s="6"/>
+      <c r="B138" s="7"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
+      <c r="A140" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B141" s="7"/>
-      <c r="C141" s="8"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1599,31 +1602,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="4">
+      <c r="A145" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="7">
         <f>B143-B144</f>
         <v>49</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="3"/>
-      <c r="B146" s="4"/>
+      <c r="A146" s="6"/>
+      <c r="B146" s="7"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
+      <c r="A148" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="8"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1656,31 +1659,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="4">
+      <c r="A153" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="7">
         <f>B151-B152</f>
         <v>153</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="3"/>
-      <c r="B154" s="4"/>
+      <c r="A154" s="6"/>
+      <c r="B154" s="7"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
+      <c r="A156" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="7"/>
-      <c r="C157" s="8"/>
+      <c r="B157" s="4"/>
+      <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1713,17 +1716,17 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="4">
+      <c r="A161" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="7">
         <f>B159-B160</f>
         <v>475</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="3"/>
-      <c r="B162" s="4"/>
+      <c r="A162" s="6"/>
+      <c r="B162" s="7"/>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="1" t="s">
@@ -1734,18 +1737,18 @@
       </c>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B165" s="5"/>
-      <c r="C165" s="5"/>
+      <c r="A165" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B165" s="8"/>
+      <c r="C165" s="8"/>
     </row>
     <row r="166" spans="1:3">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B166" s="7"/>
-      <c r="C166" s="8"/>
+      <c r="B166" s="4"/>
+      <c r="C166" s="5"/>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="1" t="s">
@@ -1778,31 +1781,31 @@
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B170" s="4">
+      <c r="A170" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B170" s="7">
         <f>B168-B169</f>
         <v>185</v>
       </c>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171" s="3"/>
-      <c r="B171" s="4"/>
+      <c r="A171" s="6"/>
+      <c r="B171" s="7"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="5"/>
+      <c r="A173" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B173" s="8"/>
+      <c r="C173" s="8"/>
     </row>
     <row r="174" spans="1:3">
-      <c r="A174" s="6" t="s">
+      <c r="A174" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B174" s="7"/>
-      <c r="C174" s="8"/>
+      <c r="B174" s="4"/>
+      <c r="C174" s="5"/>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="1" t="s">
@@ -1835,31 +1838,31 @@
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B178" s="4">
+      <c r="A178" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B178" s="7">
         <f>B176-B177</f>
         <v>137</v>
       </c>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179" s="3"/>
-      <c r="B179" s="4"/>
+      <c r="A179" s="6"/>
+      <c r="B179" s="7"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
+      <c r="A181" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B181" s="8"/>
+      <c r="C181" s="8"/>
     </row>
     <row r="182" spans="1:3">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B182" s="7"/>
-      <c r="C182" s="8"/>
+      <c r="B182" s="4"/>
+      <c r="C182" s="5"/>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="1" t="s">
@@ -1892,31 +1895,31 @@
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B186" s="4">
+      <c r="A186" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B186" s="7">
         <f>B184-B185</f>
         <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:3">
-      <c r="A187" s="3"/>
-      <c r="B187" s="4"/>
+      <c r="A187" s="6"/>
+      <c r="B187" s="7"/>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="5"/>
-      <c r="C189" s="5"/>
+      <c r="A189" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B190" s="7"/>
-      <c r="C190" s="8"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="5"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1949,31 +1952,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="4">
+      <c r="A194" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="7">
         <f>B192-B193</f>
         <v>16</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="3"/>
-      <c r="B195" s="4"/>
+      <c r="A195" s="6"/>
+      <c r="B195" s="7"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="5"/>
-      <c r="C197" s="5"/>
+      <c r="A197" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="6" t="s">
+      <c r="A198" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B198" s="7"/>
-      <c r="C198" s="8"/>
+      <c r="B198" s="4"/>
+      <c r="C198" s="5"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -2006,31 +2009,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="4">
+      <c r="A202" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="7">
         <f>B200-B201</f>
         <v>976</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="3"/>
-      <c r="B203" s="4"/>
+      <c r="A203" s="6"/>
+      <c r="B203" s="7"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
+      <c r="A205" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="8"/>
+      <c r="C205" s="8"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="6" t="s">
+      <c r="A206" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B206" s="7"/>
-      <c r="C206" s="8"/>
+      <c r="B206" s="4"/>
+      <c r="C206" s="5"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2063,31 +2066,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="4">
+      <c r="A210" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="7">
         <f>B208-B209</f>
         <v>540</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="3"/>
-      <c r="B211" s="4"/>
+      <c r="A211" s="6"/>
+      <c r="B211" s="7"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
+      <c r="A213" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="7"/>
-      <c r="C214" s="8"/>
+      <c r="B214" s="4"/>
+      <c r="C214" s="5"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2120,17 +2123,17 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="4">
+      <c r="A218" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="7">
         <f>B216-B217</f>
         <v>193</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="3"/>
-      <c r="B219" s="4"/>
+      <c r="A219" s="6"/>
+      <c r="B219" s="7"/>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="1" t="s">
@@ -2141,18 +2144,18 @@
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B222" s="5"/>
-      <c r="C222" s="5"/>
+      <c r="A222" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B222" s="8"/>
+      <c r="C222" s="8"/>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="6" t="s">
+      <c r="A223" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B223" s="7"/>
-      <c r="C223" s="8"/>
+      <c r="B223" s="4"/>
+      <c r="C223" s="5"/>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="1" t="s">
@@ -2185,31 +2188,31 @@
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B227" s="4">
+      <c r="A227" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B227" s="7">
         <f>B225-B226</f>
         <v>172</v>
       </c>
     </row>
     <row r="228" spans="1:3">
-      <c r="A228" s="3"/>
-      <c r="B228" s="4"/>
+      <c r="A228" s="6"/>
+      <c r="B228" s="7"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B230" s="5"/>
-      <c r="C230" s="5"/>
+      <c r="A230" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B230" s="8"/>
+      <c r="C230" s="8"/>
     </row>
     <row r="231" spans="1:3">
-      <c r="A231" s="6" t="s">
+      <c r="A231" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B231" s="7"/>
-      <c r="C231" s="8"/>
+      <c r="B231" s="4"/>
+      <c r="C231" s="5"/>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="1" t="s">
@@ -2242,31 +2245,31 @@
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B235" s="4">
+      <c r="A235" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B235" s="7">
         <f>B233-B234</f>
         <v>234</v>
       </c>
     </row>
     <row r="236" spans="1:3">
-      <c r="A236" s="3"/>
-      <c r="B236" s="4"/>
+      <c r="A236" s="6"/>
+      <c r="B236" s="7"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
+      <c r="A238" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
     </row>
     <row r="239" spans="1:3">
-      <c r="A239" s="6" t="s">
+      <c r="A239" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B239" s="7"/>
-      <c r="C239" s="8"/>
+      <c r="B239" s="4"/>
+      <c r="C239" s="5"/>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="1" t="s">
@@ -2299,31 +2302,31 @@
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B243" s="4">
+      <c r="A243" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B243" s="7">
         <f>B241-B242</f>
         <v>576</v>
       </c>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244" s="3"/>
-      <c r="B244" s="4"/>
+      <c r="A244" s="6"/>
+      <c r="B244" s="7"/>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
+      <c r="A246" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="6" t="s">
+      <c r="A247" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B247" s="7"/>
-      <c r="C247" s="8"/>
+      <c r="B247" s="4"/>
+      <c r="C247" s="5"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2356,31 +2359,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="4">
+      <c r="A251" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="7">
         <f>B249-B250</f>
         <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="3"/>
-      <c r="B252" s="4"/>
+      <c r="A252" s="6"/>
+      <c r="B252" s="7"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
+      <c r="A254" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="6" t="s">
+      <c r="A255" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B255" s="7"/>
-      <c r="C255" s="8"/>
+      <c r="B255" s="4"/>
+      <c r="C255" s="5"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2413,31 +2416,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="4">
+      <c r="A259" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="7">
         <f>B257-B258</f>
         <v>35</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="3"/>
-      <c r="B260" s="4"/>
+      <c r="A260" s="6"/>
+      <c r="B260" s="7"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5"/>
+      <c r="A262" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="8"/>
+      <c r="C262" s="8"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="6" t="s">
+      <c r="A263" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B263" s="7"/>
-      <c r="C263" s="8"/>
+      <c r="B263" s="4"/>
+      <c r="C263" s="5"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2470,31 +2473,31 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="4">
+      <c r="A267" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="7">
         <f>B265-B266</f>
         <v>81</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="3"/>
-      <c r="B268" s="4"/>
+      <c r="A268" s="6"/>
+      <c r="B268" s="7"/>
     </row>
     <row r="270" spans="1:3">
-      <c r="A270" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B270" s="5"/>
-      <c r="C270" s="5"/>
+      <c r="A270" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B270" s="8"/>
+      <c r="C270" s="8"/>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="6" t="s">
+      <c r="A271" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B271" s="7"/>
-      <c r="C271" s="8"/>
+      <c r="B271" s="4"/>
+      <c r="C271" s="5"/>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" s="1" t="s">
@@ -2527,17 +2530,17 @@
       </c>
     </row>
     <row r="275" spans="1:3">
-      <c r="A275" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B275" s="4">
+      <c r="A275" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B275" s="7">
         <f>B273-B274</f>
         <v>417</v>
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="3"/>
-      <c r="B276" s="4"/>
+      <c r="A276" s="6"/>
+      <c r="B276" s="7"/>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" s="1" t="s">
@@ -2548,18 +2551,18 @@
       </c>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="5"/>
-      <c r="C279" s="5"/>
+      <c r="A279" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="8"/>
+      <c r="C279" s="8"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B280" s="7"/>
-      <c r="C280" s="8"/>
+      <c r="B280" s="4"/>
+      <c r="C280" s="5"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2592,31 +2595,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="4">
+      <c r="A284" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="7">
         <f>B282-B283</f>
         <v>14</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="3"/>
-      <c r="B285" s="4"/>
+      <c r="A285" s="6"/>
+      <c r="B285" s="7"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="5"/>
-      <c r="C287" s="5"/>
+      <c r="A287" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="8"/>
+      <c r="C287" s="8"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="6" t="s">
+      <c r="A288" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B288" s="7"/>
-      <c r="C288" s="8"/>
+      <c r="B288" s="4"/>
+      <c r="C288" s="5"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2649,31 +2652,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="4">
+      <c r="A292" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="7">
         <f>B290-B291</f>
         <v>387</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="3"/>
-      <c r="B293" s="4"/>
+      <c r="A293" s="6"/>
+      <c r="B293" s="7"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="5"/>
-      <c r="C295" s="5"/>
+      <c r="A295" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="8"/>
+      <c r="C295" s="8"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="6" t="s">
+      <c r="A296" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B296" s="7"/>
-      <c r="C296" s="8"/>
+      <c r="B296" s="4"/>
+      <c r="C296" s="5"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2706,31 +2709,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="4">
+      <c r="A300" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="7">
         <f>B298-B299</f>
         <v>524</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="3"/>
-      <c r="B301" s="4"/>
+      <c r="A301" s="6"/>
+      <c r="B301" s="7"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="5"/>
-      <c r="C303" s="5"/>
+      <c r="A303" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="8"/>
+      <c r="C303" s="8"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="6" t="s">
+      <c r="A304" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B304" s="7"/>
-      <c r="C304" s="8"/>
+      <c r="B304" s="4"/>
+      <c r="C304" s="5"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2763,31 +2766,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="4">
+      <c r="A308" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="7">
         <f>B306-B307</f>
         <v>99</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="3"/>
-      <c r="B309" s="4"/>
+      <c r="A309" s="6"/>
+      <c r="B309" s="7"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="5"/>
-      <c r="C311" s="5"/>
+      <c r="A311" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="8"/>
+      <c r="C311" s="8"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="6" t="s">
+      <c r="A312" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B312" s="7"/>
-      <c r="C312" s="8"/>
+      <c r="B312" s="4"/>
+      <c r="C312" s="5"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2820,31 +2823,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="4">
+      <c r="A316" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="7">
         <f>B314-B315</f>
         <v>308</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="3"/>
-      <c r="B317" s="4"/>
+      <c r="A317" s="6"/>
+      <c r="B317" s="7"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="5"/>
-      <c r="C319" s="5"/>
+      <c r="A319" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="8"/>
+      <c r="C319" s="8"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="6" t="s">
+      <c r="A320" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B320" s="7"/>
-      <c r="C320" s="8"/>
+      <c r="B320" s="4"/>
+      <c r="C320" s="5"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2877,31 +2880,31 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="4">
+      <c r="A324" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="7">
         <f>B322-B323</f>
         <v>166</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="3"/>
-      <c r="B325" s="4"/>
+      <c r="A325" s="6"/>
+      <c r="B325" s="7"/>
     </row>
     <row r="327" spans="1:3">
-      <c r="A327" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B327" s="5"/>
-      <c r="C327" s="5"/>
+      <c r="A327" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B327" s="8"/>
+      <c r="C327" s="8"/>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="6" t="s">
+      <c r="A328" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B328" s="7"/>
-      <c r="C328" s="8"/>
+      <c r="B328" s="4"/>
+      <c r="C328" s="5"/>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" s="1" t="s">
@@ -2934,17 +2937,17 @@
       </c>
     </row>
     <row r="332" spans="1:3">
-      <c r="A332" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B332" s="4">
+      <c r="A332" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B332" s="7">
         <f>B330-B331</f>
         <v>168</v>
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="3"/>
-      <c r="B333" s="4"/>
+      <c r="A333" s="6"/>
+      <c r="B333" s="7"/>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" s="1" t="s">
@@ -2955,18 +2958,18 @@
       </c>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="5"/>
-      <c r="C336" s="5"/>
+      <c r="A336" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="8"/>
+      <c r="C336" s="8"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="6" t="s">
+      <c r="A337" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B337" s="7"/>
-      <c r="C337" s="8"/>
+      <c r="B337" s="4"/>
+      <c r="C337" s="5"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2999,31 +3002,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="4">
+      <c r="A341" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="7">
         <f>B339-B340</f>
         <v>322</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="3"/>
-      <c r="B342" s="4"/>
+      <c r="A342" s="6"/>
+      <c r="B342" s="7"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="5"/>
-      <c r="C344" s="5"/>
+      <c r="A344" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="8"/>
+      <c r="C344" s="8"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="6" t="s">
+      <c r="A345" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B345" s="7"/>
-      <c r="C345" s="8"/>
+      <c r="B345" s="4"/>
+      <c r="C345" s="5"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3056,31 +3059,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="4">
+      <c r="A349" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="7">
         <f>B347-B348</f>
         <v>255</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="3"/>
-      <c r="B350" s="4"/>
+      <c r="A350" s="6"/>
+      <c r="B350" s="7"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="5"/>
-      <c r="C352" s="5"/>
+      <c r="A352" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="8"/>
+      <c r="C352" s="8"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="6" t="s">
+      <c r="A353" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B353" s="7"/>
-      <c r="C353" s="8"/>
+      <c r="B353" s="4"/>
+      <c r="C353" s="5"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3113,31 +3116,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="4">
+      <c r="A357" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="7">
         <f>B355-B356</f>
         <v>486</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="3"/>
-      <c r="B358" s="4"/>
+      <c r="A358" s="6"/>
+      <c r="B358" s="7"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="5"/>
-      <c r="C360" s="5"/>
+      <c r="A360" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="8"/>
+      <c r="C360" s="8"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="6" t="s">
+      <c r="A361" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B361" s="7"/>
-      <c r="C361" s="8"/>
+      <c r="B361" s="4"/>
+      <c r="C361" s="5"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3170,31 +3173,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="4">
+      <c r="A365" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="7">
         <f>B363-B364</f>
         <v>9</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="3"/>
-      <c r="B366" s="4"/>
+      <c r="A366" s="6"/>
+      <c r="B366" s="7"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="5"/>
-      <c r="C368" s="5"/>
+      <c r="A368" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="8"/>
+      <c r="C368" s="8"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="6" t="s">
+      <c r="A369" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B369" s="7"/>
-      <c r="C369" s="8"/>
+      <c r="B369" s="4"/>
+      <c r="C369" s="5"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3227,31 +3230,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="4">
+      <c r="A373" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="7">
         <f>B371-B372</f>
         <v>161</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="3"/>
-      <c r="B374" s="4"/>
+      <c r="A374" s="6"/>
+      <c r="B374" s="7"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="5"/>
-      <c r="C376" s="5"/>
+      <c r="A376" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="8"/>
+      <c r="C376" s="8"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="6" t="s">
+      <c r="A377" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B377" s="7"/>
-      <c r="C377" s="8"/>
+      <c r="B377" s="4"/>
+      <c r="C377" s="5"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3284,17 +3287,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="4">
+      <c r="A381" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="7">
         <f>B379-B380</f>
         <v>220</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="3"/>
-      <c r="B382" s="4"/>
+      <c r="A382" s="6"/>
+      <c r="B382" s="7"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3305,18 +3308,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="5"/>
-      <c r="C385" s="5"/>
+      <c r="A385" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="8"/>
+      <c r="C385" s="8"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="6" t="s">
+      <c r="A386" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B386" s="7"/>
-      <c r="C386" s="8"/>
+      <c r="B386" s="4"/>
+      <c r="C386" s="5"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3349,31 +3352,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="4">
+      <c r="A390" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="7">
         <f>B388-B389</f>
         <v>698</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="3"/>
-      <c r="B391" s="4"/>
+      <c r="A391" s="6"/>
+      <c r="B391" s="7"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="5"/>
-      <c r="C393" s="5"/>
+      <c r="A393" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="8"/>
+      <c r="C393" s="8"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="6" t="s">
+      <c r="A394" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B394" s="7"/>
-      <c r="C394" s="8"/>
+      <c r="B394" s="4"/>
+      <c r="C394" s="5"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3406,31 +3409,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="4">
+      <c r="A398" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="7">
         <f>B396-B397</f>
         <v>164</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="3"/>
-      <c r="B399" s="4"/>
+      <c r="A399" s="6"/>
+      <c r="B399" s="7"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="5"/>
-      <c r="C401" s="5"/>
+      <c r="A401" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="8"/>
+      <c r="C401" s="8"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="6" t="s">
+      <c r="A402" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B402" s="7"/>
-      <c r="C402" s="8"/>
+      <c r="B402" s="4"/>
+      <c r="C402" s="5"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3463,31 +3466,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="4">
+      <c r="A406" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="7">
         <f>B404-B405</f>
         <v>400</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="3"/>
-      <c r="B407" s="4"/>
+      <c r="A407" s="6"/>
+      <c r="B407" s="7"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="5"/>
-      <c r="C409" s="5"/>
+      <c r="A409" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="8"/>
+      <c r="C409" s="8"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="6" t="s">
+      <c r="A410" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B410" s="7"/>
-      <c r="C410" s="8"/>
+      <c r="B410" s="4"/>
+      <c r="C410" s="5"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3520,31 +3523,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="4">
+      <c r="A414" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="7">
         <f>B412-B413</f>
         <v>14</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="3"/>
-      <c r="B415" s="4"/>
+      <c r="A415" s="6"/>
+      <c r="B415" s="7"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="5"/>
-      <c r="C417" s="5"/>
+      <c r="A417" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="8"/>
+      <c r="C417" s="8"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="6" t="s">
+      <c r="A418" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B418" s="7"/>
-      <c r="C418" s="8"/>
+      <c r="B418" s="4"/>
+      <c r="C418" s="5"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3577,31 +3580,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="4">
+      <c r="A422" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="7">
         <f>B420-B421</f>
         <v>5</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="3"/>
-      <c r="B423" s="4"/>
+      <c r="A423" s="6"/>
+      <c r="B423" s="7"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="5"/>
-      <c r="C425" s="5"/>
+      <c r="A425" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="8"/>
+      <c r="C425" s="8"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="6" t="s">
+      <c r="A426" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B426" s="7"/>
-      <c r="C426" s="8"/>
+      <c r="B426" s="4"/>
+      <c r="C426" s="5"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3634,31 +3637,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="4">
+      <c r="A430" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="7">
         <f>B428-B429</f>
         <v>60</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="3"/>
-      <c r="B431" s="4"/>
+      <c r="A431" s="6"/>
+      <c r="B431" s="7"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="5"/>
-      <c r="C433" s="5"/>
+      <c r="A433" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="8"/>
+      <c r="C433" s="8"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="6" t="s">
+      <c r="A434" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B434" s="7"/>
-      <c r="C434" s="8"/>
+      <c r="B434" s="4"/>
+      <c r="C434" s="5"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3691,17 +3694,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="4">
+      <c r="A438" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="7">
         <f>B436-B437</f>
         <v>558</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="3"/>
-      <c r="B439" s="4"/>
+      <c r="A439" s="6"/>
+      <c r="B439" s="7"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3712,18 +3715,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="5"/>
-      <c r="C442" s="5"/>
+      <c r="A442" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="8"/>
+      <c r="C442" s="8"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="6" t="s">
+      <c r="A443" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B443" s="7"/>
-      <c r="C443" s="8"/>
+      <c r="B443" s="4"/>
+      <c r="C443" s="5"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3756,31 +3759,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="4">
+      <c r="A447" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="7">
         <f>B445-B446</f>
         <v>32</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="3"/>
-      <c r="B448" s="4"/>
+      <c r="A448" s="6"/>
+      <c r="B448" s="7"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="5"/>
-      <c r="C450" s="5"/>
+      <c r="A450" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="8"/>
+      <c r="C450" s="8"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="6" t="s">
+      <c r="A451" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B451" s="7"/>
-      <c r="C451" s="8"/>
+      <c r="B451" s="4"/>
+      <c r="C451" s="5"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3813,31 +3816,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="4">
+      <c r="A455" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="7">
         <f>B453-B454</f>
         <v>613</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="3"/>
-      <c r="B456" s="4"/>
+      <c r="A456" s="6"/>
+      <c r="B456" s="7"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="5"/>
-      <c r="C458" s="5"/>
+      <c r="A458" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="8"/>
+      <c r="C458" s="8"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="6" t="s">
+      <c r="A459" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B459" s="7"/>
-      <c r="C459" s="8"/>
+      <c r="B459" s="4"/>
+      <c r="C459" s="5"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3870,31 +3873,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="4">
+      <c r="A463" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="7">
         <f>B461-B462</f>
         <v>257</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="3"/>
-      <c r="B464" s="4"/>
+      <c r="A464" s="6"/>
+      <c r="B464" s="7"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="5"/>
-      <c r="C466" s="5"/>
+      <c r="A466" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="8"/>
+      <c r="C466" s="8"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="6" t="s">
+      <c r="A467" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B467" s="7"/>
-      <c r="C467" s="8"/>
+      <c r="B467" s="4"/>
+      <c r="C467" s="5"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3927,31 +3930,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="4">
+      <c r="A471" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="7">
         <f>B469-B470</f>
         <v>502</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="3"/>
-      <c r="B472" s="4"/>
+      <c r="A472" s="6"/>
+      <c r="B472" s="7"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="5"/>
-      <c r="C474" s="5"/>
+      <c r="A474" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="8"/>
+      <c r="C474" s="8"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="6" t="s">
+      <c r="A475" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B475" s="7"/>
-      <c r="C475" s="8"/>
+      <c r="B475" s="4"/>
+      <c r="C475" s="5"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3984,31 +3987,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="4">
+      <c r="A479" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="7">
         <f>B477-B478</f>
         <v>470</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="3"/>
-      <c r="B480" s="4"/>
+      <c r="A480" s="6"/>
+      <c r="B480" s="7"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="5"/>
-      <c r="C482" s="5"/>
+      <c r="A482" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="8"/>
+      <c r="C482" s="8"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="6" t="s">
+      <c r="A483" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B483" s="7"/>
-      <c r="C483" s="8"/>
+      <c r="B483" s="4"/>
+      <c r="C483" s="5"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4041,31 +4044,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="4">
+      <c r="A487" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="7">
         <f>B485-B486</f>
         <v>53</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="3"/>
-      <c r="B488" s="4"/>
+      <c r="A488" s="6"/>
+      <c r="B488" s="7"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="5"/>
-      <c r="C490" s="5"/>
+      <c r="A490" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="8"/>
+      <c r="C490" s="8"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="6" t="s">
+      <c r="A491" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B491" s="7"/>
-      <c r="C491" s="8"/>
+      <c r="B491" s="4"/>
+      <c r="C491" s="5"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4098,17 +4101,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="4">
+      <c r="A495" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="7">
         <f>B493-B494</f>
         <v>1309</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="3"/>
-      <c r="B496" s="4"/>
+      <c r="A496" s="6"/>
+      <c r="B496" s="7"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4119,18 +4122,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="5"/>
-      <c r="C499" s="5"/>
+      <c r="A499" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="8"/>
+      <c r="C499" s="8"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="6" t="s">
+      <c r="A500" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B500" s="7"/>
-      <c r="C500" s="8"/>
+      <c r="B500" s="4"/>
+      <c r="C500" s="5"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4163,31 +4166,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="4">
+      <c r="A504" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="7">
         <f>B502-B503</f>
         <v>241</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="3"/>
-      <c r="B505" s="4"/>
+      <c r="A505" s="6"/>
+      <c r="B505" s="7"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="5"/>
-      <c r="C507" s="5"/>
+      <c r="A507" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="8"/>
+      <c r="C507" s="8"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="6" t="s">
+      <c r="A508" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B508" s="7"/>
-      <c r="C508" s="8"/>
+      <c r="B508" s="4"/>
+      <c r="C508" s="5"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4220,31 +4223,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="4">
+      <c r="A512" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="7">
         <f>B510-B511</f>
         <v>10</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="3"/>
-      <c r="B513" s="4"/>
+      <c r="A513" s="6"/>
+      <c r="B513" s="7"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="5"/>
-      <c r="C515" s="5"/>
+      <c r="A515" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="8"/>
+      <c r="C515" s="8"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="6" t="s">
+      <c r="A516" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B516" s="7"/>
-      <c r="C516" s="8"/>
+      <c r="B516" s="4"/>
+      <c r="C516" s="5"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4277,31 +4280,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="4">
+      <c r="A520" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="7">
         <f>B518-B519</f>
         <v>258</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="3"/>
-      <c r="B521" s="4"/>
+      <c r="A521" s="6"/>
+      <c r="B521" s="7"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="5"/>
-      <c r="C523" s="5"/>
+      <c r="A523" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="8"/>
+      <c r="C523" s="8"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="6" t="s">
+      <c r="A524" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B524" s="7"/>
-      <c r="C524" s="8"/>
+      <c r="B524" s="4"/>
+      <c r="C524" s="5"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4334,31 +4337,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="4">
+      <c r="A528" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="7">
         <f>B526-B527</f>
         <v>74</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="3"/>
-      <c r="B529" s="4"/>
+      <c r="A529" s="6"/>
+      <c r="B529" s="7"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="5"/>
-      <c r="C531" s="5"/>
+      <c r="A531" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="8"/>
+      <c r="C531" s="8"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="6" t="s">
+      <c r="A532" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B532" s="7"/>
-      <c r="C532" s="8"/>
+      <c r="B532" s="4"/>
+      <c r="C532" s="5"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4391,31 +4394,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="4">
+      <c r="A536" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="7">
         <f>B534-B535</f>
         <v>100</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="3"/>
-      <c r="B537" s="4"/>
+      <c r="A537" s="6"/>
+      <c r="B537" s="7"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="5"/>
-      <c r="C539" s="5"/>
+      <c r="A539" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="8"/>
+      <c r="C539" s="8"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="6" t="s">
+      <c r="A540" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B540" s="7"/>
-      <c r="C540" s="8"/>
+      <c r="B540" s="4"/>
+      <c r="C540" s="5"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4448,31 +4451,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="4">
+      <c r="A544" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="7">
         <f>B542-B543</f>
         <v>701</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="3"/>
-      <c r="B545" s="4"/>
+      <c r="A545" s="6"/>
+      <c r="B545" s="7"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="5"/>
-      <c r="C547" s="5"/>
+      <c r="A547" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="8"/>
+      <c r="C547" s="8"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="6" t="s">
+      <c r="A548" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B548" s="7"/>
-      <c r="C548" s="8"/>
+      <c r="B548" s="4"/>
+      <c r="C548" s="5"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4505,31 +4508,31 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="4">
+      <c r="A552" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="7">
         <f>B550-B551</f>
         <v>33</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="3"/>
-      <c r="B553" s="4"/>
+      <c r="A553" s="6"/>
+      <c r="B553" s="7"/>
     </row>
     <row r="555" spans="1:3">
-      <c r="A555" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B555" s="5"/>
-      <c r="C555" s="5"/>
+      <c r="A555" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B555" s="8"/>
+      <c r="C555" s="8"/>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="6" t="s">
+      <c r="A556" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B556" s="7"/>
-      <c r="C556" s="8"/>
+      <c r="B556" s="4"/>
+      <c r="C556" s="5"/>
     </row>
     <row r="557" spans="1:3">
       <c r="A557" s="1" t="s">
@@ -4562,17 +4565,17 @@
       </c>
     </row>
     <row r="560" spans="1:3">
-      <c r="A560" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B560" s="4">
+      <c r="A560" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B560" s="7">
         <f>B558-B559</f>
         <v>277</v>
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="3"/>
-      <c r="B561" s="4"/>
+      <c r="A561" s="6"/>
+      <c r="B561" s="7"/>
     </row>
     <row r="562" spans="1:3">
       <c r="A562" s="1" t="s">
@@ -4583,18 +4586,18 @@
       </c>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="5"/>
-      <c r="C564" s="5"/>
+      <c r="A564" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="8"/>
+      <c r="C564" s="8"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="6" t="s">
+      <c r="A565" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B565" s="7"/>
-      <c r="C565" s="8"/>
+      <c r="B565" s="4"/>
+      <c r="C565" s="5"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4627,31 +4630,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="4">
+      <c r="A569" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="7">
         <f>B567-B568</f>
         <v>241</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="3"/>
-      <c r="B570" s="4"/>
+      <c r="A570" s="6"/>
+      <c r="B570" s="7"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="5"/>
-      <c r="C572" s="5"/>
+      <c r="A572" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="8"/>
+      <c r="C572" s="8"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="6" t="s">
+      <c r="A573" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B573" s="7"/>
-      <c r="C573" s="8"/>
+      <c r="B573" s="4"/>
+      <c r="C573" s="5"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4684,31 +4687,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="4">
+      <c r="A577" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="7">
         <f>B575-B576</f>
         <v>1445</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="3"/>
-      <c r="B578" s="4"/>
+      <c r="A578" s="6"/>
+      <c r="B578" s="7"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="5"/>
-      <c r="C580" s="5"/>
+      <c r="A580" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="8"/>
+      <c r="C580" s="8"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="6" t="s">
+      <c r="A581" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B581" s="7"/>
-      <c r="C581" s="8"/>
+      <c r="B581" s="4"/>
+      <c r="C581" s="5"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4741,31 +4744,31 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="4">
+      <c r="A585" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="7">
         <f>B583-B584</f>
         <v>46</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="3"/>
-      <c r="B586" s="4"/>
+      <c r="A586" s="6"/>
+      <c r="B586" s="7"/>
     </row>
     <row r="588" spans="1:3">
-      <c r="A588" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B588" s="5"/>
-      <c r="C588" s="5"/>
+      <c r="A588" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B588" s="8"/>
+      <c r="C588" s="8"/>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="6" t="s">
+      <c r="A589" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B589" s="7"/>
-      <c r="C589" s="8"/>
+      <c r="B589" s="4"/>
+      <c r="C589" s="5"/>
     </row>
     <row r="590" spans="1:3">
       <c r="A590" s="1" t="s">
@@ -4798,31 +4801,31 @@
       </c>
     </row>
     <row r="593" spans="1:3">
-      <c r="A593" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B593" s="4">
+      <c r="A593" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B593" s="7">
         <f>B591-B592</f>
         <v>52</v>
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="3"/>
-      <c r="B594" s="4"/>
+      <c r="A594" s="6"/>
+      <c r="B594" s="7"/>
     </row>
     <row r="596" spans="1:3">
-      <c r="A596" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B596" s="5"/>
-      <c r="C596" s="5"/>
+      <c r="A596" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B596" s="8"/>
+      <c r="C596" s="8"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="6" t="s">
+      <c r="A597" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B597" s="7"/>
-      <c r="C597" s="8"/>
+      <c r="B597" s="4"/>
+      <c r="C597" s="5"/>
     </row>
     <row r="598" spans="1:3">
       <c r="A598" s="1" t="s">
@@ -4855,31 +4858,31 @@
       </c>
     </row>
     <row r="601" spans="1:3">
-      <c r="A601" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B601" s="4">
+      <c r="A601" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B601" s="7">
         <f>B599-B600</f>
         <v>402</v>
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="3"/>
-      <c r="B602" s="4"/>
+      <c r="A602" s="6"/>
+      <c r="B602" s="7"/>
     </row>
     <row r="604" spans="1:3">
-      <c r="A604" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B604" s="5"/>
-      <c r="C604" s="5"/>
+      <c r="A604" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B604" s="8"/>
+      <c r="C604" s="8"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="6" t="s">
+      <c r="A605" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B605" s="7"/>
-      <c r="C605" s="8"/>
+      <c r="B605" s="4"/>
+      <c r="C605" s="5"/>
     </row>
     <row r="606" spans="1:3">
       <c r="A606" s="1" t="s">
@@ -4912,31 +4915,31 @@
       </c>
     </row>
     <row r="609" spans="1:3">
-      <c r="A609" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B609" s="4">
+      <c r="A609" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B609" s="7">
         <f>B607-B608</f>
         <v>15</v>
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="3"/>
-      <c r="B610" s="4"/>
+      <c r="A610" s="6"/>
+      <c r="B610" s="7"/>
     </row>
     <row r="612" spans="1:3">
-      <c r="A612" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B612" s="5"/>
-      <c r="C612" s="5"/>
+      <c r="A612" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B612" s="8"/>
+      <c r="C612" s="8"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="6" t="s">
+      <c r="A613" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B613" s="7"/>
-      <c r="C613" s="8"/>
+      <c r="B613" s="4"/>
+      <c r="C613" s="5"/>
     </row>
     <row r="614" spans="1:3">
       <c r="A614" s="1" t="s">
@@ -4969,17 +4972,17 @@
       </c>
     </row>
     <row r="617" spans="1:3">
-      <c r="A617" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B617" s="4">
+      <c r="A617" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B617" s="7">
         <f>B615-B616</f>
         <v>581</v>
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="3"/>
-      <c r="B618" s="4"/>
+      <c r="A618" s="6"/>
+      <c r="B618" s="7"/>
     </row>
     <row r="619" spans="1:3">
       <c r="A619" s="1" t="s">
@@ -4990,18 +4993,18 @@
       </c>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="5"/>
-      <c r="C621" s="5"/>
+      <c r="A621" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="8"/>
+      <c r="C621" s="8"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="6" t="s">
+      <c r="A622" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B622" s="7"/>
-      <c r="C622" s="8"/>
+      <c r="B622" s="4"/>
+      <c r="C622" s="5"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5034,31 +5037,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="4">
+      <c r="A626" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="7">
         <f>B624-B625</f>
         <v>0</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="3"/>
-      <c r="B627" s="4"/>
+      <c r="A627" s="6"/>
+      <c r="B627" s="7"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="5"/>
-      <c r="C629" s="5"/>
+      <c r="A629" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="8"/>
+      <c r="C629" s="8"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="6" t="s">
+      <c r="A630" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B630" s="7"/>
-      <c r="C630" s="8"/>
+      <c r="B630" s="4"/>
+      <c r="C630" s="5"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5091,31 +5094,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="4">
+      <c r="A634" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="7">
         <f>B632-B633</f>
         <v>416</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="3"/>
-      <c r="B635" s="4"/>
+      <c r="A635" s="6"/>
+      <c r="B635" s="7"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="5"/>
-      <c r="C637" s="5"/>
+      <c r="A637" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="8"/>
+      <c r="C637" s="8"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="6" t="s">
+      <c r="A638" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B638" s="7"/>
-      <c r="C638" s="8"/>
+      <c r="B638" s="4"/>
+      <c r="C638" s="5"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5148,31 +5151,31 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="4">
+      <c r="A642" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="7">
         <f>B640-B641</f>
         <v>148</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="3"/>
-      <c r="B643" s="4"/>
+      <c r="A643" s="6"/>
+      <c r="B643" s="7"/>
     </row>
     <row r="645" spans="1:3">
-      <c r="A645" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B645" s="5"/>
-      <c r="C645" s="5"/>
+      <c r="A645" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B645" s="8"/>
+      <c r="C645" s="8"/>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="6" t="s">
+      <c r="A646" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B646" s="7"/>
-      <c r="C646" s="8"/>
+      <c r="B646" s="4"/>
+      <c r="C646" s="5"/>
     </row>
     <row r="647" spans="1:3">
       <c r="A647" s="1" t="s">
@@ -5205,31 +5208,31 @@
       </c>
     </row>
     <row r="650" spans="1:3">
-      <c r="A650" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B650" s="4">
+      <c r="A650" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B650" s="7">
         <f>B648-B649</f>
         <v>329</v>
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="3"/>
-      <c r="B651" s="4"/>
+      <c r="A651" s="6"/>
+      <c r="B651" s="7"/>
     </row>
     <row r="653" spans="1:3">
-      <c r="A653" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B653" s="5"/>
-      <c r="C653" s="5"/>
+      <c r="A653" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B653" s="8"/>
+      <c r="C653" s="8"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="6" t="s">
+      <c r="A654" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B654" s="7"/>
-      <c r="C654" s="8"/>
+      <c r="B654" s="4"/>
+      <c r="C654" s="5"/>
     </row>
     <row r="655" spans="1:3">
       <c r="A655" s="1" t="s">
@@ -5262,31 +5265,31 @@
       </c>
     </row>
     <row r="658" spans="1:3">
-      <c r="A658" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B658" s="4">
+      <c r="A658" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B658" s="7">
         <f>B656-B657</f>
         <v>299</v>
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="3"/>
-      <c r="B659" s="4"/>
+      <c r="A659" s="6"/>
+      <c r="B659" s="7"/>
     </row>
     <row r="661" spans="1:3">
-      <c r="A661" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B661" s="5"/>
-      <c r="C661" s="5"/>
+      <c r="A661" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B661" s="8"/>
+      <c r="C661" s="8"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="6" t="s">
+      <c r="A662" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B662" s="7"/>
-      <c r="C662" s="8"/>
+      <c r="B662" s="4"/>
+      <c r="C662" s="5"/>
     </row>
     <row r="663" spans="1:3">
       <c r="A663" s="1" t="s">
@@ -5319,31 +5322,31 @@
       </c>
     </row>
     <row r="666" spans="1:3">
-      <c r="A666" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B666" s="4">
+      <c r="A666" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B666" s="7">
         <f>B664-B665</f>
         <v>382</v>
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="3"/>
-      <c r="B667" s="4"/>
+      <c r="A667" s="6"/>
+      <c r="B667" s="7"/>
     </row>
     <row r="669" spans="1:3">
-      <c r="A669" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B669" s="5"/>
-      <c r="C669" s="5"/>
+      <c r="A669" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B669" s="8"/>
+      <c r="C669" s="8"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="6" t="s">
+      <c r="A670" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B670" s="7"/>
-      <c r="C670" s="8"/>
+      <c r="B670" s="4"/>
+      <c r="C670" s="5"/>
     </row>
     <row r="671" spans="1:3">
       <c r="A671" s="1" t="s">
@@ -5376,17 +5379,17 @@
       </c>
     </row>
     <row r="674" spans="1:3">
-      <c r="A674" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B674" s="4">
+      <c r="A674" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B674" s="7">
         <f>B672-B673</f>
         <v>617</v>
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="3"/>
-      <c r="B675" s="4"/>
+      <c r="A675" s="6"/>
+      <c r="B675" s="7"/>
     </row>
     <row r="676" spans="1:3">
       <c r="A676" s="1" t="s">
@@ -5397,18 +5400,18 @@
       </c>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="5"/>
-      <c r="C678" s="5"/>
+      <c r="A678" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="8"/>
+      <c r="C678" s="8"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="6" t="s">
+      <c r="A679" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B679" s="7"/>
-      <c r="C679" s="8"/>
+      <c r="B679" s="4"/>
+      <c r="C679" s="5"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5441,31 +5444,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="4">
+      <c r="A683" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="7">
         <f>B681-B682</f>
         <v>196</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="3"/>
-      <c r="B684" s="4"/>
+      <c r="A684" s="6"/>
+      <c r="B684" s="7"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="5"/>
-      <c r="C686" s="5"/>
+      <c r="A686" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="8"/>
+      <c r="C686" s="8"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="6" t="s">
+      <c r="A687" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B687" s="7"/>
-      <c r="C687" s="8"/>
+      <c r="B687" s="4"/>
+      <c r="C687" s="5"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5498,31 +5501,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="4">
+      <c r="A691" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="7">
         <f>B689-B690</f>
         <v>7</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="3"/>
-      <c r="B692" s="4"/>
+      <c r="A692" s="6"/>
+      <c r="B692" s="7"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="5"/>
-      <c r="C694" s="5"/>
+      <c r="A694" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="8"/>
+      <c r="C694" s="8"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="6" t="s">
+      <c r="A695" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="7"/>
-      <c r="C695" s="8"/>
+      <c r="B695" s="4"/>
+      <c r="C695" s="5"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5555,17 +5558,17 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="4">
+      <c r="A699" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="7">
         <f>B697-B698</f>
         <v>757</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="3"/>
-      <c r="B700" s="4"/>
+      <c r="A700" s="6"/>
+      <c r="B700" s="7"/>
     </row>
     <row r="701" spans="1:3">
       <c r="A701" s="1" t="s">
@@ -5576,18 +5579,18 @@
       </c>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B703" s="5"/>
-      <c r="C703" s="5"/>
+      <c r="A703" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B703" s="8"/>
+      <c r="C703" s="8"/>
     </row>
     <row r="704" spans="1:3">
-      <c r="A704" s="6" t="s">
+      <c r="A704" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B704" s="7"/>
-      <c r="C704" s="8"/>
+      <c r="B704" s="4"/>
+      <c r="C704" s="5"/>
     </row>
     <row r="705" spans="1:3">
       <c r="A705" s="1" t="s">
@@ -5620,31 +5623,31 @@
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B708" s="4">
+      <c r="A708" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B708" s="7">
         <f>B706-B707</f>
         <v>244</v>
       </c>
     </row>
     <row r="709" spans="1:3">
-      <c r="A709" s="3"/>
-      <c r="B709" s="4"/>
+      <c r="A709" s="6"/>
+      <c r="B709" s="7"/>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B711" s="5"/>
-      <c r="C711" s="5"/>
+      <c r="A711" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="8"/>
+      <c r="C711" s="8"/>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="6" t="s">
+      <c r="A712" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B712" s="7"/>
-      <c r="C712" s="8"/>
+      <c r="B712" s="4"/>
+      <c r="C712" s="5"/>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" s="1" t="s">
@@ -5677,31 +5680,31 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B716" s="4">
+      <c r="A716" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="7">
         <f>B714-B715</f>
         <v>167</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="3"/>
-      <c r="B717" s="4"/>
+      <c r="A717" s="6"/>
+      <c r="B717" s="7"/>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B719" s="5"/>
-      <c r="C719" s="5"/>
+      <c r="A719" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="8"/>
+      <c r="C719" s="8"/>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="6" t="s">
+      <c r="A720" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B720" s="7"/>
-      <c r="C720" s="8"/>
+      <c r="B720" s="4"/>
+      <c r="C720" s="5"/>
     </row>
     <row r="721" spans="1:3">
       <c r="A721" s="1" t="s">
@@ -5734,31 +5737,31 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B724" s="4">
+      <c r="A724" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="7">
         <f>B722-B723</f>
         <v>401</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="3"/>
-      <c r="B725" s="4"/>
+      <c r="A725" s="6"/>
+      <c r="B725" s="7"/>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B727" s="5"/>
-      <c r="C727" s="5"/>
+      <c r="A727" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="8"/>
+      <c r="C727" s="8"/>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="6" t="s">
+      <c r="A728" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B728" s="7"/>
-      <c r="C728" s="8"/>
+      <c r="B728" s="4"/>
+      <c r="C728" s="5"/>
     </row>
     <row r="729" spans="1:3">
       <c r="A729" s="1" t="s">
@@ -5791,31 +5794,31 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B732" s="4">
+      <c r="A732" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="7">
         <f>B730-B731</f>
         <v>20</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="3"/>
-      <c r="B733" s="4"/>
+      <c r="A733" s="6"/>
+      <c r="B733" s="7"/>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B735" s="5"/>
-      <c r="C735" s="5"/>
+      <c r="A735" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="8"/>
+      <c r="C735" s="8"/>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="6" t="s">
+      <c r="A736" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B736" s="7"/>
-      <c r="C736" s="8"/>
+      <c r="B736" s="4"/>
+      <c r="C736" s="5"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="1" t="s">
@@ -5848,31 +5851,31 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B740" s="4">
+      <c r="A740" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="7">
         <f>B738-B739</f>
         <v>0</v>
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="3"/>
-      <c r="B741" s="4"/>
+      <c r="A741" s="6"/>
+      <c r="B741" s="7"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B743" s="5"/>
-      <c r="C743" s="5"/>
+      <c r="A743" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="8"/>
+      <c r="C743" s="8"/>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="6" t="s">
+      <c r="A744" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B744" s="7"/>
-      <c r="C744" s="8"/>
+      <c r="B744" s="4"/>
+      <c r="C744" s="5"/>
     </row>
     <row r="745" spans="1:3">
       <c r="A745" s="1" t="s">
@@ -5905,31 +5908,31 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B748" s="4">
+      <c r="A748" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="7">
         <f>B746-B747</f>
         <v>0</v>
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="3"/>
-      <c r="B749" s="4"/>
+      <c r="A749" s="6"/>
+      <c r="B749" s="7"/>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B751" s="5"/>
-      <c r="C751" s="5"/>
+      <c r="A751" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="8"/>
+      <c r="C751" s="8"/>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="6" t="s">
+      <c r="A752" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B752" s="7"/>
-      <c r="C752" s="8"/>
+      <c r="B752" s="4"/>
+      <c r="C752" s="5"/>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" s="1" t="s">
@@ -5962,17 +5965,17 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="4">
+      <c r="A756" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="7">
         <f>B754-B755</f>
         <v>282</v>
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="3"/>
-      <c r="B757" s="4"/>
+      <c r="A757" s="6"/>
+      <c r="B757" s="7"/>
     </row>
     <row r="758" spans="1:3">
       <c r="A758" s="1" t="s">
@@ -5983,18 +5986,18 @@
       </c>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B760" s="5"/>
-      <c r="C760" s="5"/>
+      <c r="A760" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B760" s="8"/>
+      <c r="C760" s="8"/>
     </row>
     <row r="761" spans="1:3">
-      <c r="A761" s="6" t="s">
+      <c r="A761" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B761" s="7"/>
-      <c r="C761" s="8"/>
+      <c r="B761" s="4"/>
+      <c r="C761" s="5"/>
     </row>
     <row r="762" spans="1:3">
       <c r="A762" s="1" t="s">
@@ -6027,31 +6030,31 @@
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B765" s="4">
+      <c r="A765" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B765" s="7">
         <f>B763-B764</f>
         <v>2453</v>
       </c>
     </row>
     <row r="766" spans="1:3">
-      <c r="A766" s="3"/>
-      <c r="B766" s="4"/>
+      <c r="A766" s="6"/>
+      <c r="B766" s="7"/>
     </row>
     <row r="768" spans="1:3">
-      <c r="A768" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B768" s="5"/>
-      <c r="C768" s="5"/>
+      <c r="A768" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B768" s="8"/>
+      <c r="C768" s="8"/>
     </row>
     <row r="769" spans="1:3">
-      <c r="A769" s="6" t="s">
+      <c r="A769" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B769" s="7"/>
-      <c r="C769" s="8"/>
+      <c r="B769" s="4"/>
+      <c r="C769" s="5"/>
     </row>
     <row r="770" spans="1:3">
       <c r="A770" s="1" t="s">
@@ -6084,31 +6087,31 @@
       </c>
     </row>
     <row r="773" spans="1:3">
-      <c r="A773" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B773" s="4">
+      <c r="A773" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B773" s="7">
         <f>B771-B772</f>
         <v>1173</v>
       </c>
     </row>
     <row r="774" spans="1:3">
-      <c r="A774" s="3"/>
-      <c r="B774" s="4"/>
+      <c r="A774" s="6"/>
+      <c r="B774" s="7"/>
     </row>
     <row r="776" spans="1:3">
-      <c r="A776" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B776" s="5"/>
-      <c r="C776" s="5"/>
+      <c r="A776" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B776" s="8"/>
+      <c r="C776" s="8"/>
     </row>
     <row r="777" spans="1:3">
-      <c r="A777" s="6" t="s">
+      <c r="A777" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B777" s="7"/>
-      <c r="C777" s="8"/>
+      <c r="B777" s="4"/>
+      <c r="C777" s="5"/>
     </row>
     <row r="778" spans="1:3">
       <c r="A778" s="1" t="s">
@@ -6141,31 +6144,31 @@
       </c>
     </row>
     <row r="781" spans="1:3">
-      <c r="A781" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B781" s="4">
+      <c r="A781" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781" s="7">
         <f>B779-B780</f>
         <v>1136</v>
       </c>
     </row>
     <row r="782" spans="1:3">
-      <c r="A782" s="3"/>
-      <c r="B782" s="4"/>
+      <c r="A782" s="6"/>
+      <c r="B782" s="7"/>
     </row>
     <row r="784" spans="1:3">
-      <c r="A784" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B784" s="5"/>
-      <c r="C784" s="5"/>
+      <c r="A784" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B784" s="8"/>
+      <c r="C784" s="8"/>
     </row>
     <row r="785" spans="1:3">
-      <c r="A785" s="6" t="s">
+      <c r="A785" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B785" s="7"/>
-      <c r="C785" s="8"/>
+      <c r="B785" s="4"/>
+      <c r="C785" s="5"/>
     </row>
     <row r="786" spans="1:3">
       <c r="A786" s="1" t="s">
@@ -6198,31 +6201,31 @@
       </c>
     </row>
     <row r="789" spans="1:3">
-      <c r="A789" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B789" s="4">
+      <c r="A789" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789" s="7">
         <f>B787-B788</f>
         <v>136</v>
       </c>
     </row>
     <row r="790" spans="1:3">
-      <c r="A790" s="3"/>
-      <c r="B790" s="4"/>
+      <c r="A790" s="6"/>
+      <c r="B790" s="7"/>
     </row>
     <row r="792" spans="1:3">
-      <c r="A792" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B792" s="5"/>
-      <c r="C792" s="5"/>
+      <c r="A792" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B792" s="8"/>
+      <c r="C792" s="8"/>
     </row>
     <row r="793" spans="1:3">
-      <c r="A793" s="6" t="s">
+      <c r="A793" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B793" s="7"/>
-      <c r="C793" s="8"/>
+      <c r="B793" s="4"/>
+      <c r="C793" s="5"/>
     </row>
     <row r="794" spans="1:3">
       <c r="A794" s="1" t="s">
@@ -6255,31 +6258,31 @@
       </c>
     </row>
     <row r="797" spans="1:3">
-      <c r="A797" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B797" s="4">
+      <c r="A797" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797" s="7">
         <f>B795-B796</f>
         <v>549</v>
       </c>
     </row>
     <row r="798" spans="1:3">
-      <c r="A798" s="3"/>
-      <c r="B798" s="4"/>
+      <c r="A798" s="6"/>
+      <c r="B798" s="7"/>
     </row>
     <row r="800" spans="1:3">
-      <c r="A800" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B800" s="5"/>
-      <c r="C800" s="5"/>
+      <c r="A800" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B800" s="8"/>
+      <c r="C800" s="8"/>
     </row>
     <row r="801" spans="1:3">
-      <c r="A801" s="6" t="s">
+      <c r="A801" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B801" s="7"/>
-      <c r="C801" s="8"/>
+      <c r="B801" s="4"/>
+      <c r="C801" s="5"/>
     </row>
     <row r="802" spans="1:3">
       <c r="A802" s="1" t="s">
@@ -6312,31 +6315,31 @@
       </c>
     </row>
     <row r="805" spans="1:3">
-      <c r="A805" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B805" s="4">
+      <c r="A805" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805" s="7">
         <f>B803-B804</f>
         <v>84</v>
       </c>
     </row>
     <row r="806" spans="1:3">
-      <c r="A806" s="3"/>
-      <c r="B806" s="4"/>
+      <c r="A806" s="6"/>
+      <c r="B806" s="7"/>
     </row>
     <row r="808" spans="1:3">
-      <c r="A808" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B808" s="5"/>
-      <c r="C808" s="5"/>
+      <c r="A808" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B808" s="8"/>
+      <c r="C808" s="8"/>
     </row>
     <row r="809" spans="1:3">
-      <c r="A809" s="6" t="s">
+      <c r="A809" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B809" s="7"/>
-      <c r="C809" s="8"/>
+      <c r="B809" s="4"/>
+      <c r="C809" s="5"/>
     </row>
     <row r="810" spans="1:3">
       <c r="A810" s="1" t="s">
@@ -6369,17 +6372,17 @@
       </c>
     </row>
     <row r="813" spans="1:3">
-      <c r="A813" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B813" s="4">
+      <c r="A813" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813" s="7">
         <f>B811-B812</f>
         <v>325</v>
       </c>
     </row>
     <row r="814" spans="1:3">
-      <c r="A814" s="3"/>
-      <c r="B814" s="4"/>
+      <c r="A814" s="6"/>
+      <c r="B814" s="7"/>
     </row>
     <row r="815" spans="1:3">
       <c r="A815" s="1" t="s">
@@ -6390,18 +6393,18 @@
       </c>
     </row>
     <row r="817" spans="1:3">
-      <c r="A817" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B817" s="5"/>
-      <c r="C817" s="5"/>
+      <c r="A817" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B817" s="8"/>
+      <c r="C817" s="8"/>
     </row>
     <row r="818" spans="1:3">
-      <c r="A818" s="6" t="s">
+      <c r="A818" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B818" s="7"/>
-      <c r="C818" s="8"/>
+      <c r="B818" s="4"/>
+      <c r="C818" s="5"/>
     </row>
     <row r="819" spans="1:3">
       <c r="A819" s="1" t="s">
@@ -6434,31 +6437,31 @@
       </c>
     </row>
     <row r="822" spans="1:3">
-      <c r="A822" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B822" s="4">
+      <c r="A822" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B822" s="7">
         <f>B820-B821</f>
         <v>31</v>
       </c>
     </row>
     <row r="823" spans="1:3">
-      <c r="A823" s="3"/>
-      <c r="B823" s="4"/>
+      <c r="A823" s="6"/>
+      <c r="B823" s="7"/>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B825" s="5"/>
-      <c r="C825" s="5"/>
+      <c r="A825" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B825" s="8"/>
+      <c r="C825" s="8"/>
     </row>
     <row r="826" spans="1:3">
-      <c r="A826" s="6" t="s">
+      <c r="A826" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B826" s="7"/>
-      <c r="C826" s="8"/>
+      <c r="B826" s="4"/>
+      <c r="C826" s="5"/>
     </row>
     <row r="827" spans="1:3">
       <c r="A827" s="1" t="s">
@@ -6491,31 +6494,31 @@
       </c>
     </row>
     <row r="830" spans="1:3">
-      <c r="A830" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B830" s="4">
+      <c r="A830" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B830" s="7">
         <f>B828-B829</f>
         <v>637</v>
       </c>
     </row>
     <row r="831" spans="1:3">
-      <c r="A831" s="3"/>
-      <c r="B831" s="4"/>
+      <c r="A831" s="6"/>
+      <c r="B831" s="7"/>
     </row>
     <row r="833" spans="1:3">
-      <c r="A833" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B833" s="5"/>
-      <c r="C833" s="5"/>
+      <c r="A833" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B833" s="8"/>
+      <c r="C833" s="8"/>
     </row>
     <row r="834" spans="1:3">
-      <c r="A834" s="6" t="s">
+      <c r="A834" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B834" s="7"/>
-      <c r="C834" s="8"/>
+      <c r="B834" s="4"/>
+      <c r="C834" s="5"/>
     </row>
     <row r="835" spans="1:3">
       <c r="A835" s="1" t="s">
@@ -6548,31 +6551,31 @@
       </c>
     </row>
     <row r="838" spans="1:3">
-      <c r="A838" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B838" s="4">
+      <c r="A838" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B838" s="7">
         <f>B836-B837</f>
         <v>58</v>
       </c>
     </row>
     <row r="839" spans="1:3">
-      <c r="A839" s="3"/>
-      <c r="B839" s="4"/>
+      <c r="A839" s="6"/>
+      <c r="B839" s="7"/>
     </row>
     <row r="841" spans="1:3">
-      <c r="A841" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B841" s="5"/>
-      <c r="C841" s="5"/>
+      <c r="A841" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B841" s="8"/>
+      <c r="C841" s="8"/>
     </row>
     <row r="842" spans="1:3">
-      <c r="A842" s="6" t="s">
+      <c r="A842" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B842" s="7"/>
-      <c r="C842" s="8"/>
+      <c r="B842" s="4"/>
+      <c r="C842" s="5"/>
     </row>
     <row r="843" spans="1:3">
       <c r="A843" s="1" t="s">
@@ -6605,31 +6608,31 @@
       </c>
     </row>
     <row r="846" spans="1:3">
-      <c r="A846" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B846" s="4">
+      <c r="A846" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846" s="7">
         <f>B844-B845</f>
         <v>1579</v>
       </c>
     </row>
     <row r="847" spans="1:3">
-      <c r="A847" s="3"/>
-      <c r="B847" s="4"/>
+      <c r="A847" s="6"/>
+      <c r="B847" s="7"/>
     </row>
     <row r="849" spans="1:3">
-      <c r="A849" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B849" s="5"/>
-      <c r="C849" s="5"/>
+      <c r="A849" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B849" s="8"/>
+      <c r="C849" s="8"/>
     </row>
     <row r="850" spans="1:3">
-      <c r="A850" s="6" t="s">
+      <c r="A850" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B850" s="7"/>
-      <c r="C850" s="8"/>
+      <c r="B850" s="4"/>
+      <c r="C850" s="5"/>
     </row>
     <row r="851" spans="1:3">
       <c r="A851" s="1" t="s">
@@ -6662,31 +6665,31 @@
       </c>
     </row>
     <row r="854" spans="1:3">
-      <c r="A854" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B854" s="4">
+      <c r="A854" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854" s="7">
         <f>B852-B853</f>
         <v>201</v>
       </c>
     </row>
     <row r="855" spans="1:3">
-      <c r="A855" s="3"/>
-      <c r="B855" s="4"/>
+      <c r="A855" s="6"/>
+      <c r="B855" s="7"/>
     </row>
     <row r="857" spans="1:3">
-      <c r="A857" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B857" s="5"/>
-      <c r="C857" s="5"/>
+      <c r="A857" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B857" s="8"/>
+      <c r="C857" s="8"/>
     </row>
     <row r="858" spans="1:3">
-      <c r="A858" s="6" t="s">
+      <c r="A858" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B858" s="7"/>
-      <c r="C858" s="8"/>
+      <c r="B858" s="4"/>
+      <c r="C858" s="5"/>
     </row>
     <row r="859" spans="1:3">
       <c r="A859" s="1" t="s">
@@ -6719,31 +6722,31 @@
       </c>
     </row>
     <row r="862" spans="1:3">
-      <c r="A862" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B862" s="4">
+      <c r="A862" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862" s="7">
         <f>B860-B861</f>
         <v>788</v>
       </c>
     </row>
     <row r="863" spans="1:3">
-      <c r="A863" s="3"/>
-      <c r="B863" s="4"/>
+      <c r="A863" s="6"/>
+      <c r="B863" s="7"/>
     </row>
     <row r="865" spans="1:3">
-      <c r="A865" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B865" s="5"/>
-      <c r="C865" s="5"/>
+      <c r="A865" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B865" s="8"/>
+      <c r="C865" s="8"/>
     </row>
     <row r="866" spans="1:3">
-      <c r="A866" s="6" t="s">
+      <c r="A866" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B866" s="7"/>
-      <c r="C866" s="8"/>
+      <c r="B866" s="4"/>
+      <c r="C866" s="5"/>
     </row>
     <row r="867" spans="1:3">
       <c r="A867" s="1" t="s">
@@ -6776,17 +6779,17 @@
       </c>
     </row>
     <row r="870" spans="1:3">
-      <c r="A870" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B870" s="4">
+      <c r="A870" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870" s="7">
         <f>B868-B869</f>
         <v>2041</v>
       </c>
     </row>
     <row r="871" spans="1:3">
-      <c r="A871" s="3"/>
-      <c r="B871" s="4"/>
+      <c r="A871" s="6"/>
+      <c r="B871" s="7"/>
     </row>
     <row r="872" spans="1:3">
       <c r="A872" s="1" t="s">
@@ -6797,18 +6800,18 @@
       </c>
     </row>
     <row r="874" spans="1:3">
-      <c r="A874" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B874" s="5"/>
-      <c r="C874" s="5"/>
+      <c r="A874" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B874" s="8"/>
+      <c r="C874" s="8"/>
     </row>
     <row r="875" spans="1:3">
-      <c r="A875" s="6" t="s">
+      <c r="A875" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B875" s="7"/>
-      <c r="C875" s="8"/>
+      <c r="B875" s="4"/>
+      <c r="C875" s="5"/>
     </row>
     <row r="876" spans="1:3">
       <c r="A876" s="1" t="s">
@@ -6841,31 +6844,31 @@
       </c>
     </row>
     <row r="879" spans="1:3">
-      <c r="A879" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B879" s="4">
+      <c r="A879" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B879" s="7">
         <f>B877-B878</f>
         <v>37</v>
       </c>
     </row>
     <row r="880" spans="1:3">
-      <c r="A880" s="3"/>
-      <c r="B880" s="4"/>
+      <c r="A880" s="6"/>
+      <c r="B880" s="7"/>
     </row>
     <row r="882" spans="1:3">
-      <c r="A882" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B882" s="5"/>
-      <c r="C882" s="5"/>
+      <c r="A882" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B882" s="8"/>
+      <c r="C882" s="8"/>
     </row>
     <row r="883" spans="1:3">
-      <c r="A883" s="6" t="s">
+      <c r="A883" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B883" s="7"/>
-      <c r="C883" s="8"/>
+      <c r="B883" s="4"/>
+      <c r="C883" s="5"/>
     </row>
     <row r="884" spans="1:3">
       <c r="A884" s="1" t="s">
@@ -6898,31 +6901,31 @@
       </c>
     </row>
     <row r="887" spans="1:3">
-      <c r="A887" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B887" s="4">
+      <c r="A887" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B887" s="7">
         <f>B885-B886</f>
         <v>746</v>
       </c>
     </row>
     <row r="888" spans="1:3">
-      <c r="A888" s="3"/>
-      <c r="B888" s="4"/>
+      <c r="A888" s="6"/>
+      <c r="B888" s="7"/>
     </row>
     <row r="890" spans="1:3">
-      <c r="A890" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B890" s="5"/>
-      <c r="C890" s="5"/>
+      <c r="A890" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B890" s="8"/>
+      <c r="C890" s="8"/>
     </row>
     <row r="891" spans="1:3">
-      <c r="A891" s="6" t="s">
+      <c r="A891" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B891" s="7"/>
-      <c r="C891" s="8"/>
+      <c r="B891" s="4"/>
+      <c r="C891" s="5"/>
     </row>
     <row r="892" spans="1:3">
       <c r="A892" s="1" t="s">
@@ -6955,31 +6958,31 @@
       </c>
     </row>
     <row r="895" spans="1:3">
-      <c r="A895" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B895" s="4">
+      <c r="A895" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B895" s="7">
         <f>B893-B894</f>
         <v>65</v>
       </c>
     </row>
     <row r="896" spans="1:3">
-      <c r="A896" s="3"/>
-      <c r="B896" s="4"/>
+      <c r="A896" s="6"/>
+      <c r="B896" s="7"/>
     </row>
     <row r="898" spans="1:3">
-      <c r="A898" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B898" s="5"/>
-      <c r="C898" s="5"/>
+      <c r="A898" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B898" s="8"/>
+      <c r="C898" s="8"/>
     </row>
     <row r="899" spans="1:3">
-      <c r="A899" s="6" t="s">
+      <c r="A899" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B899" s="7"/>
-      <c r="C899" s="8"/>
+      <c r="B899" s="4"/>
+      <c r="C899" s="5"/>
     </row>
     <row r="900" spans="1:3">
       <c r="A900" s="1" t="s">
@@ -7012,31 +7015,31 @@
       </c>
     </row>
     <row r="903" spans="1:3">
-      <c r="A903" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B903" s="4">
+      <c r="A903" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B903" s="7">
         <f>B901-B902</f>
         <v>888</v>
       </c>
     </row>
     <row r="904" spans="1:3">
-      <c r="A904" s="3"/>
-      <c r="B904" s="4"/>
+      <c r="A904" s="6"/>
+      <c r="B904" s="7"/>
     </row>
     <row r="906" spans="1:3">
-      <c r="A906" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B906" s="5"/>
-      <c r="C906" s="5"/>
+      <c r="A906" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B906" s="8"/>
+      <c r="C906" s="8"/>
     </row>
     <row r="907" spans="1:3">
-      <c r="A907" s="6" t="s">
+      <c r="A907" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B907" s="7"/>
-      <c r="C907" s="8"/>
+      <c r="B907" s="4"/>
+      <c r="C907" s="5"/>
     </row>
     <row r="908" spans="1:3">
       <c r="A908" s="1" t="s">
@@ -7069,31 +7072,31 @@
       </c>
     </row>
     <row r="911" spans="1:3">
-      <c r="A911" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B911" s="4">
+      <c r="A911" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B911" s="7">
         <f>B909-B910</f>
         <v>363</v>
       </c>
     </row>
     <row r="912" spans="1:3">
-      <c r="A912" s="3"/>
-      <c r="B912" s="4"/>
+      <c r="A912" s="6"/>
+      <c r="B912" s="7"/>
     </row>
     <row r="914" spans="1:3">
-      <c r="A914" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B914" s="5"/>
-      <c r="C914" s="5"/>
+      <c r="A914" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B914" s="8"/>
+      <c r="C914" s="8"/>
     </row>
     <row r="915" spans="1:3">
-      <c r="A915" s="6" t="s">
+      <c r="A915" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B915" s="7"/>
-      <c r="C915" s="8"/>
+      <c r="B915" s="4"/>
+      <c r="C915" s="5"/>
     </row>
     <row r="916" spans="1:3">
       <c r="A916" s="1" t="s">
@@ -7126,31 +7129,31 @@
       </c>
     </row>
     <row r="919" spans="1:3">
-      <c r="A919" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B919" s="4">
+      <c r="A919" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B919" s="7">
         <f>B917-B918</f>
         <v>379</v>
       </c>
     </row>
     <row r="920" spans="1:3">
-      <c r="A920" s="3"/>
-      <c r="B920" s="4"/>
+      <c r="A920" s="6"/>
+      <c r="B920" s="7"/>
     </row>
     <row r="922" spans="1:3">
-      <c r="A922" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B922" s="5"/>
-      <c r="C922" s="5"/>
+      <c r="A922" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B922" s="8"/>
+      <c r="C922" s="8"/>
     </row>
     <row r="923" spans="1:3">
-      <c r="A923" s="6" t="s">
+      <c r="A923" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B923" s="7"/>
-      <c r="C923" s="8"/>
+      <c r="B923" s="4"/>
+      <c r="C923" s="5"/>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" s="1" t="s">
@@ -7183,17 +7186,17 @@
       </c>
     </row>
     <row r="927" spans="1:3">
-      <c r="A927" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B927" s="4">
+      <c r="A927" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B927" s="7">
         <f>B925-B926</f>
         <v>260</v>
       </c>
     </row>
     <row r="928" spans="1:3">
-      <c r="A928" s="3"/>
-      <c r="B928" s="4"/>
+      <c r="A928" s="6"/>
+      <c r="B928" s="7"/>
     </row>
     <row r="929" spans="1:3">
       <c r="A929" s="1" t="s">
@@ -7204,18 +7207,18 @@
       </c>
     </row>
     <row r="931" spans="1:3">
-      <c r="A931" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B931" s="5"/>
-      <c r="C931" s="5"/>
+      <c r="A931" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B931" s="8"/>
+      <c r="C931" s="8"/>
     </row>
     <row r="932" spans="1:3">
-      <c r="A932" s="6" t="s">
+      <c r="A932" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B932" s="7"/>
-      <c r="C932" s="8"/>
+      <c r="B932" s="4"/>
+      <c r="C932" s="5"/>
     </row>
     <row r="933" spans="1:3">
       <c r="A933" s="1" t="s">
@@ -7248,31 +7251,31 @@
       </c>
     </row>
     <row r="936" spans="1:3">
-      <c r="A936" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B936" s="4">
+      <c r="A936" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B936" s="7">
         <f>B934-B935</f>
         <v>471</v>
       </c>
     </row>
     <row r="937" spans="1:3">
-      <c r="A937" s="3"/>
-      <c r="B937" s="4"/>
+      <c r="A937" s="6"/>
+      <c r="B937" s="7"/>
     </row>
     <row r="939" spans="1:3">
-      <c r="A939" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B939" s="5"/>
-      <c r="C939" s="5"/>
+      <c r="A939" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B939" s="8"/>
+      <c r="C939" s="8"/>
     </row>
     <row r="940" spans="1:3">
-      <c r="A940" s="6" t="s">
+      <c r="A940" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B940" s="7"/>
-      <c r="C940" s="8"/>
+      <c r="B940" s="4"/>
+      <c r="C940" s="5"/>
     </row>
     <row r="941" spans="1:3">
       <c r="A941" s="1" t="s">
@@ -7305,31 +7308,31 @@
       </c>
     </row>
     <row r="944" spans="1:3">
-      <c r="A944" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B944" s="4">
+      <c r="A944" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B944" s="7">
         <f>B942-B943</f>
         <v>391</v>
       </c>
     </row>
     <row r="945" spans="1:3">
-      <c r="A945" s="3"/>
-      <c r="B945" s="4"/>
+      <c r="A945" s="6"/>
+      <c r="B945" s="7"/>
     </row>
     <row r="947" spans="1:3">
-      <c r="A947" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B947" s="5"/>
-      <c r="C947" s="5"/>
+      <c r="A947" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B947" s="8"/>
+      <c r="C947" s="8"/>
     </row>
     <row r="948" spans="1:3">
-      <c r="A948" s="6" t="s">
+      <c r="A948" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B948" s="7"/>
-      <c r="C948" s="8"/>
+      <c r="B948" s="4"/>
+      <c r="C948" s="5"/>
     </row>
     <row r="949" spans="1:3">
       <c r="A949" s="1" t="s">
@@ -7362,31 +7365,31 @@
       </c>
     </row>
     <row r="952" spans="1:3">
-      <c r="A952" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B952" s="4">
+      <c r="A952" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B952" s="7">
         <f>B950-B951</f>
         <v>1654</v>
       </c>
     </row>
     <row r="953" spans="1:3">
-      <c r="A953" s="3"/>
-      <c r="B953" s="4"/>
+      <c r="A953" s="6"/>
+      <c r="B953" s="7"/>
     </row>
     <row r="955" spans="1:3">
-      <c r="A955" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B955" s="5"/>
-      <c r="C955" s="5"/>
+      <c r="A955" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B955" s="8"/>
+      <c r="C955" s="8"/>
     </row>
     <row r="956" spans="1:3">
-      <c r="A956" s="6" t="s">
+      <c r="A956" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B956" s="7"/>
-      <c r="C956" s="8"/>
+      <c r="B956" s="4"/>
+      <c r="C956" s="5"/>
     </row>
     <row r="957" spans="1:3">
       <c r="A957" s="1" t="s">
@@ -7419,31 +7422,31 @@
       </c>
     </row>
     <row r="960" spans="1:3">
-      <c r="A960" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B960" s="4">
+      <c r="A960" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B960" s="7">
         <f>B958-B959</f>
         <v>1076</v>
       </c>
     </row>
     <row r="961" spans="1:3">
-      <c r="A961" s="3"/>
-      <c r="B961" s="4"/>
+      <c r="A961" s="6"/>
+      <c r="B961" s="7"/>
     </row>
     <row r="963" spans="1:3">
-      <c r="A963" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B963" s="5"/>
-      <c r="C963" s="5"/>
+      <c r="A963" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B963" s="8"/>
+      <c r="C963" s="8"/>
     </row>
     <row r="964" spans="1:3">
-      <c r="A964" s="6" t="s">
+      <c r="A964" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B964" s="7"/>
-      <c r="C964" s="8"/>
+      <c r="B964" s="4"/>
+      <c r="C964" s="5"/>
     </row>
     <row r="965" spans="1:3">
       <c r="A965" s="1" t="s">
@@ -7476,31 +7479,31 @@
       </c>
     </row>
     <row r="968" spans="1:3">
-      <c r="A968" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B968" s="4">
+      <c r="A968" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B968" s="7">
         <f>B966-B967</f>
         <v>0</v>
       </c>
     </row>
     <row r="969" spans="1:3">
-      <c r="A969" s="3"/>
-      <c r="B969" s="4"/>
+      <c r="A969" s="6"/>
+      <c r="B969" s="7"/>
     </row>
     <row r="971" spans="1:3">
-      <c r="A971" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B971" s="5"/>
-      <c r="C971" s="5"/>
+      <c r="A971" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B971" s="8"/>
+      <c r="C971" s="8"/>
     </row>
     <row r="972" spans="1:3">
-      <c r="A972" s="6" t="s">
+      <c r="A972" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B972" s="7"/>
-      <c r="C972" s="8"/>
+      <c r="B972" s="4"/>
+      <c r="C972" s="5"/>
     </row>
     <row r="973" spans="1:3">
       <c r="A973" s="1" t="s">
@@ -7533,31 +7536,31 @@
       </c>
     </row>
     <row r="976" spans="1:3">
-      <c r="A976" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B976" s="4">
+      <c r="A976" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B976" s="7">
         <f>B974-B975</f>
         <v>207</v>
       </c>
     </row>
     <row r="977" spans="1:3">
-      <c r="A977" s="3"/>
-      <c r="B977" s="4"/>
+      <c r="A977" s="6"/>
+      <c r="B977" s="7"/>
     </row>
     <row r="979" spans="1:3">
-      <c r="A979" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B979" s="5"/>
-      <c r="C979" s="5"/>
+      <c r="A979" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B979" s="8"/>
+      <c r="C979" s="8"/>
     </row>
     <row r="980" spans="1:3">
-      <c r="A980" s="6" t="s">
+      <c r="A980" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B980" s="7"/>
-      <c r="C980" s="8"/>
+      <c r="B980" s="4"/>
+      <c r="C980" s="5"/>
     </row>
     <row r="981" spans="1:3">
       <c r="A981" s="1" t="s">
@@ -7590,17 +7593,17 @@
       </c>
     </row>
     <row r="984" spans="1:3">
-      <c r="A984" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B984" s="4">
+      <c r="A984" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B984" s="7">
         <f>B982-B983</f>
         <v>12</v>
       </c>
     </row>
     <row r="985" spans="1:3">
-      <c r="A985" s="3"/>
-      <c r="B985" s="4"/>
+      <c r="A985" s="6"/>
+      <c r="B985" s="7"/>
     </row>
     <row r="986" spans="1:3">
       <c r="A986" s="1" t="s">
@@ -7611,18 +7614,18 @@
       </c>
     </row>
     <row r="988" spans="1:3">
-      <c r="A988" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B988" s="5"/>
-      <c r="C988" s="5"/>
+      <c r="A988" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B988" s="8"/>
+      <c r="C988" s="8"/>
     </row>
     <row r="989" spans="1:3">
-      <c r="A989" s="6" t="s">
+      <c r="A989" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B989" s="7"/>
-      <c r="C989" s="8"/>
+      <c r="B989" s="4"/>
+      <c r="C989" s="5"/>
     </row>
     <row r="990" spans="1:3">
       <c r="A990" s="1" t="s">
@@ -7655,31 +7658,31 @@
       </c>
     </row>
     <row r="993" spans="1:3">
-      <c r="A993" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B993" s="4">
+      <c r="A993" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B993" s="7">
         <f>B991-B992</f>
         <v>923</v>
       </c>
     </row>
     <row r="994" spans="1:3">
-      <c r="A994" s="3"/>
-      <c r="B994" s="4"/>
+      <c r="A994" s="6"/>
+      <c r="B994" s="7"/>
     </row>
     <row r="996" spans="1:3">
-      <c r="A996" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B996" s="5"/>
-      <c r="C996" s="5"/>
+      <c r="A996" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B996" s="8"/>
+      <c r="C996" s="8"/>
     </row>
     <row r="997" spans="1:3">
-      <c r="A997" s="6" t="s">
+      <c r="A997" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B997" s="7"/>
-      <c r="C997" s="8"/>
+      <c r="B997" s="4"/>
+      <c r="C997" s="5"/>
     </row>
     <row r="998" spans="1:3">
       <c r="A998" s="1" t="s">
@@ -7712,31 +7715,31 @@
       </c>
     </row>
     <row r="1001" spans="1:3">
-      <c r="A1001" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1001" s="4">
+      <c r="A1001" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1001" s="7">
         <f>B999-B1000</f>
         <v>149</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
-      <c r="A1002" s="3"/>
-      <c r="B1002" s="4"/>
+      <c r="A1002" s="6"/>
+      <c r="B1002" s="7"/>
     </row>
     <row r="1004" spans="1:3">
-      <c r="A1004" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1004" s="5"/>
-      <c r="C1004" s="5"/>
+      <c r="A1004" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1004" s="8"/>
+      <c r="C1004" s="8"/>
     </row>
     <row r="1005" spans="1:3">
-      <c r="A1005" s="6" t="s">
+      <c r="A1005" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B1005" s="7"/>
-      <c r="C1005" s="8"/>
+      <c r="B1005" s="4"/>
+      <c r="C1005" s="5"/>
     </row>
     <row r="1006" spans="1:3">
       <c r="A1006" s="1" t="s">
@@ -7768,106 +7771,843 @@
         <v>202</v>
       </c>
     </row>
-    <row r="1009" spans="1:2">
-      <c r="A1009" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1009" s="4">
+    <row r="1009" spans="1:3">
+      <c r="A1009" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1009" s="7">
         <f>B1007-B1008</f>
         <v>26</v>
       </c>
     </row>
-    <row r="1010" spans="1:2">
-      <c r="A1010" s="3"/>
-      <c r="B1010" s="4"/>
+    <row r="1010" spans="1:3">
+      <c r="A1010" s="6"/>
+      <c r="B1010" s="7"/>
+    </row>
+    <row r="1012" spans="1:3">
+      <c r="A1012" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1012" s="8"/>
+      <c r="C1012" s="8"/>
+    </row>
+    <row r="1013" spans="1:3">
+      <c r="A1013" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1013" s="4"/>
+      <c r="C1013" s="5"/>
+    </row>
+    <row r="1014" spans="1:3">
+      <c r="A1014" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1014" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3">
+      <c r="A1015" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1015" s="2">
+        <v>2234</v>
+      </c>
+      <c r="C1015" s="2">
+        <v>8856</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3">
+      <c r="A1016" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1016" s="2">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3">
+      <c r="A1017" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1017" s="7">
+        <f>B1015-B1016</f>
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3">
+      <c r="A1018" s="6"/>
+      <c r="B1018" s="7"/>
+    </row>
+    <row r="1019" spans="1:3">
+      <c r="A1019" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1019" s="2">
+        <v>80706</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3">
+      <c r="A1021" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1021" s="8"/>
+      <c r="C1021" s="8"/>
+    </row>
+    <row r="1022" spans="1:3">
+      <c r="A1022" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1022" s="4"/>
+      <c r="C1022" s="5"/>
+    </row>
+    <row r="1023" spans="1:3">
+      <c r="A1023" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1023" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1023" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3">
+      <c r="A1024" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1024" s="2">
+        <v>925</v>
+      </c>
+      <c r="C1024" s="2">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3">
+      <c r="A1025" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1025" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3">
+      <c r="A1026" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1026" s="7">
+        <f>B1024-B1025</f>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3">
+      <c r="A1027" s="6"/>
+      <c r="B1027" s="7"/>
+    </row>
+    <row r="1029" spans="1:3">
+      <c r="A1029" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1029" s="8"/>
+      <c r="C1029" s="8"/>
+    </row>
+    <row r="1030" spans="1:3">
+      <c r="A1030" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1030" s="4"/>
+      <c r="C1030" s="5"/>
+    </row>
+    <row r="1031" spans="1:3">
+      <c r="A1031" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1031" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1031" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3">
+      <c r="A1032" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1032" s="2">
+        <v>2884</v>
+      </c>
+      <c r="C1032" s="2">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3">
+      <c r="A1033" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1033" s="2">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3">
+      <c r="A1034" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1034" s="7">
+        <f>B1032-B1033</f>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:3">
+      <c r="A1035" s="6"/>
+      <c r="B1035" s="7"/>
+    </row>
+    <row r="1037" spans="1:3">
+      <c r="A1037" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1037" s="8"/>
+      <c r="C1037" s="8"/>
+    </row>
+    <row r="1038" spans="1:3">
+      <c r="A1038" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1038" s="4"/>
+      <c r="C1038" s="5"/>
+    </row>
+    <row r="1039" spans="1:3">
+      <c r="A1039" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1039" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1039" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3">
+      <c r="A1040" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1040" s="2">
+        <v>2037</v>
+      </c>
+      <c r="C1040" s="2">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3">
+      <c r="A1041" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1041" s="2">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3">
+      <c r="A1042" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1042" s="7">
+        <f>B1040-B1041</f>
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:3">
+      <c r="A1043" s="6"/>
+      <c r="B1043" s="7"/>
+    </row>
+    <row r="1045" spans="1:3">
+      <c r="A1045" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1045" s="8"/>
+      <c r="C1045" s="8"/>
+    </row>
+    <row r="1046" spans="1:3">
+      <c r="A1046" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1046" s="4"/>
+      <c r="C1046" s="5"/>
+    </row>
+    <row r="1047" spans="1:3">
+      <c r="A1047" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1047" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1047" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3">
+      <c r="A1048" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1048" s="2">
+        <v>432</v>
+      </c>
+      <c r="C1048" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3">
+      <c r="A1049" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1049" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3">
+      <c r="A1050" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1050" s="7">
+        <f>B1048-B1049</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3">
+      <c r="A1051" s="6"/>
+      <c r="B1051" s="7"/>
+    </row>
+    <row r="1053" spans="1:3">
+      <c r="A1053" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1053" s="8"/>
+      <c r="C1053" s="8"/>
+    </row>
+    <row r="1054" spans="1:3">
+      <c r="A1054" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1054" s="4"/>
+      <c r="C1054" s="5"/>
+    </row>
+    <row r="1055" spans="1:3">
+      <c r="A1055" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1055" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1055" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3">
+      <c r="A1056" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1056" s="2">
+        <v>41</v>
+      </c>
+      <c r="C1056" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3">
+      <c r="A1057" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1057" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3">
+      <c r="A1058" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1058" s="7">
+        <f>B1056-B1057</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:3">
+      <c r="A1059" s="6"/>
+      <c r="B1059" s="7"/>
+    </row>
+    <row r="1061" spans="1:3">
+      <c r="A1061" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1061" s="8"/>
+      <c r="C1061" s="8"/>
+    </row>
+    <row r="1062" spans="1:3">
+      <c r="A1062" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1062" s="4"/>
+      <c r="C1062" s="5"/>
+    </row>
+    <row r="1063" spans="1:3">
+      <c r="A1063" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1063" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1063" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3">
+      <c r="A1064" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1064" s="2">
+        <v>148</v>
+      </c>
+      <c r="C1064" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3">
+      <c r="A1065" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1065" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3">
+      <c r="A1066" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1066" s="7">
+        <f>B1064-B1065</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3">
+      <c r="A1067" s="6"/>
+      <c r="B1067" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="496">
-    <mergeCell ref="A997:C997"/>
-    <mergeCell ref="A1001:A1002"/>
-    <mergeCell ref="B1001:B1002"/>
-    <mergeCell ref="A1004:C1004"/>
-    <mergeCell ref="A1005:C1005"/>
-    <mergeCell ref="A1009:A1010"/>
-    <mergeCell ref="B1009:B1010"/>
-    <mergeCell ref="A979:C979"/>
-    <mergeCell ref="A980:C980"/>
-    <mergeCell ref="A984:A985"/>
-    <mergeCell ref="B984:B985"/>
-    <mergeCell ref="A988:C988"/>
-    <mergeCell ref="A989:C989"/>
-    <mergeCell ref="A993:A994"/>
-    <mergeCell ref="B993:B994"/>
-    <mergeCell ref="A996:C996"/>
-    <mergeCell ref="A903:A904"/>
-    <mergeCell ref="B903:B904"/>
-    <mergeCell ref="A906:C906"/>
-    <mergeCell ref="A907:C907"/>
-    <mergeCell ref="A911:A912"/>
-    <mergeCell ref="B911:B912"/>
-    <mergeCell ref="A914:C914"/>
-    <mergeCell ref="A915:C915"/>
-    <mergeCell ref="A919:A920"/>
-    <mergeCell ref="B919:B920"/>
-    <mergeCell ref="A883:C883"/>
-    <mergeCell ref="A887:A888"/>
-    <mergeCell ref="B887:B888"/>
-    <mergeCell ref="A890:C890"/>
-    <mergeCell ref="A891:C891"/>
-    <mergeCell ref="A895:A896"/>
-    <mergeCell ref="B895:B896"/>
-    <mergeCell ref="A898:C898"/>
-    <mergeCell ref="A899:C899"/>
-    <mergeCell ref="A865:C865"/>
-    <mergeCell ref="A866:C866"/>
-    <mergeCell ref="A870:A871"/>
-    <mergeCell ref="B870:B871"/>
-    <mergeCell ref="A874:C874"/>
-    <mergeCell ref="A875:C875"/>
-    <mergeCell ref="A879:A880"/>
-    <mergeCell ref="B879:B880"/>
-    <mergeCell ref="A882:C882"/>
-    <mergeCell ref="A776:C776"/>
-    <mergeCell ref="A777:C777"/>
-    <mergeCell ref="A781:A782"/>
-    <mergeCell ref="B781:B782"/>
-    <mergeCell ref="A784:C784"/>
-    <mergeCell ref="A805:A806"/>
-    <mergeCell ref="B805:B806"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="A789:A790"/>
-    <mergeCell ref="B789:B790"/>
-    <mergeCell ref="A792:C792"/>
-    <mergeCell ref="A793:C793"/>
-    <mergeCell ref="A797:A798"/>
-    <mergeCell ref="B797:B798"/>
-    <mergeCell ref="A800:C800"/>
-    <mergeCell ref="A801:C801"/>
-    <mergeCell ref="A760:C760"/>
-    <mergeCell ref="A761:C761"/>
-    <mergeCell ref="A765:A766"/>
-    <mergeCell ref="B765:B766"/>
-    <mergeCell ref="A748:A749"/>
-    <mergeCell ref="A768:C768"/>
-    <mergeCell ref="A769:C769"/>
-    <mergeCell ref="A773:A774"/>
-    <mergeCell ref="B773:B774"/>
-    <mergeCell ref="B716:B717"/>
-    <mergeCell ref="B724:B725"/>
-    <mergeCell ref="B732:B733"/>
-    <mergeCell ref="B740:B741"/>
-    <mergeCell ref="B748:B749"/>
-    <mergeCell ref="A751:C751"/>
-    <mergeCell ref="A752:C752"/>
-    <mergeCell ref="A756:A757"/>
-    <mergeCell ref="B756:B757"/>
-    <mergeCell ref="A744:C744"/>
-    <mergeCell ref="A719:C719"/>
-    <mergeCell ref="A720:C720"/>
-    <mergeCell ref="A727:C727"/>
-    <mergeCell ref="A728:C728"/>
-    <mergeCell ref="A735:C735"/>
-    <mergeCell ref="A736:C736"/>
+  <mergeCells count="524">
+    <mergeCell ref="A1062:C1062"/>
+    <mergeCell ref="A1066:A1067"/>
+    <mergeCell ref="B1066:B1067"/>
+    <mergeCell ref="A1045:C1045"/>
+    <mergeCell ref="A1046:C1046"/>
+    <mergeCell ref="A1050:A1051"/>
+    <mergeCell ref="B1050:B1051"/>
+    <mergeCell ref="A1053:C1053"/>
+    <mergeCell ref="A1054:C1054"/>
+    <mergeCell ref="A1058:A1059"/>
+    <mergeCell ref="B1058:B1059"/>
+    <mergeCell ref="A1061:C1061"/>
+    <mergeCell ref="A1026:A1027"/>
+    <mergeCell ref="B1026:B1027"/>
+    <mergeCell ref="A1029:C1029"/>
+    <mergeCell ref="A1030:C1030"/>
+    <mergeCell ref="A1034:A1035"/>
+    <mergeCell ref="B1034:B1035"/>
+    <mergeCell ref="A1037:C1037"/>
+    <mergeCell ref="A1038:C1038"/>
+    <mergeCell ref="A1042:A1043"/>
+    <mergeCell ref="B1042:B1043"/>
+    <mergeCell ref="A972:C972"/>
+    <mergeCell ref="A976:A977"/>
+    <mergeCell ref="B976:B977"/>
+    <mergeCell ref="A1012:C1012"/>
+    <mergeCell ref="A1013:C1013"/>
+    <mergeCell ref="A1017:A1018"/>
+    <mergeCell ref="B1017:B1018"/>
+    <mergeCell ref="A1021:C1021"/>
+    <mergeCell ref="A1022:C1022"/>
+    <mergeCell ref="A955:C955"/>
+    <mergeCell ref="A956:C956"/>
+    <mergeCell ref="A960:A961"/>
+    <mergeCell ref="B960:B961"/>
+    <mergeCell ref="A963:C963"/>
+    <mergeCell ref="A964:C964"/>
+    <mergeCell ref="A968:A969"/>
+    <mergeCell ref="B968:B969"/>
+    <mergeCell ref="A971:C971"/>
+    <mergeCell ref="A936:A937"/>
+    <mergeCell ref="B936:B937"/>
+    <mergeCell ref="A939:C939"/>
+    <mergeCell ref="A940:C940"/>
+    <mergeCell ref="A944:A945"/>
+    <mergeCell ref="B944:B945"/>
+    <mergeCell ref="A947:C947"/>
+    <mergeCell ref="A948:C948"/>
+    <mergeCell ref="A952:A953"/>
+    <mergeCell ref="B952:B953"/>
+    <mergeCell ref="A858:C858"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="B862:B863"/>
+    <mergeCell ref="A922:C922"/>
+    <mergeCell ref="A923:C923"/>
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="B927:B928"/>
+    <mergeCell ref="A931:C931"/>
+    <mergeCell ref="A932:C932"/>
+    <mergeCell ref="A841:C841"/>
+    <mergeCell ref="A842:C842"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="B846:B847"/>
+    <mergeCell ref="A849:C849"/>
+    <mergeCell ref="A850:C850"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="B854:B855"/>
+    <mergeCell ref="A857:C857"/>
+    <mergeCell ref="A822:A823"/>
+    <mergeCell ref="B822:B823"/>
+    <mergeCell ref="A825:C825"/>
+    <mergeCell ref="A826:C826"/>
+    <mergeCell ref="A830:A831"/>
+    <mergeCell ref="B830:B831"/>
+    <mergeCell ref="A833:C833"/>
+    <mergeCell ref="A834:C834"/>
+    <mergeCell ref="A838:A839"/>
+    <mergeCell ref="B838:B839"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A808:C808"/>
+    <mergeCell ref="A809:C809"/>
+    <mergeCell ref="A813:A814"/>
+    <mergeCell ref="B813:B814"/>
+    <mergeCell ref="A817:C817"/>
+    <mergeCell ref="A818:C818"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A231:C231"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A239:C239"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A270:C270"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A327:C327"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A450:C450"/>
+    <mergeCell ref="A451:C451"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A443:C443"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A458:C458"/>
+    <mergeCell ref="A459:C459"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A482:C482"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A490:C490"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="A491:C491"/>
+    <mergeCell ref="A499:C499"/>
+    <mergeCell ref="A500:C500"/>
+    <mergeCell ref="A507:C507"/>
+    <mergeCell ref="A508:C508"/>
+    <mergeCell ref="A515:C515"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="B674:B675"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A596:C596"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A547:C547"/>
+    <mergeCell ref="A548:C548"/>
+    <mergeCell ref="A555:C555"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A564:C564"/>
+    <mergeCell ref="B560:B561"/>
+    <mergeCell ref="B569:B570"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="B593:B594"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="A650:A651"/>
+    <mergeCell ref="A658:A659"/>
+    <mergeCell ref="A666:A667"/>
+    <mergeCell ref="A674:A675"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A704:C704"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A708:A709"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="B708:B709"/>
+    <mergeCell ref="A669:C669"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A604:C604"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A223:C223"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A243:A244"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A275:A276"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="B235:B236"/>
+    <mergeCell ref="B243:B244"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B275:B276"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="A332:A333"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="A447:A448"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
+    <mergeCell ref="A433:C433"/>
+    <mergeCell ref="A434:C434"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="B447:B448"/>
+    <mergeCell ref="A442:C442"/>
+    <mergeCell ref="B601:B602"/>
+    <mergeCell ref="B609:B610"/>
+    <mergeCell ref="B617:B618"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="B650:B651"/>
+    <mergeCell ref="B658:B659"/>
+    <mergeCell ref="B666:B667"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A645:C645"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A653:C653"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A661:C661"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A612:C612"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="A552:A553"/>
+    <mergeCell ref="A560:A561"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="A593:A594"/>
+    <mergeCell ref="A565:C565"/>
+    <mergeCell ref="A572:C572"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A588:C588"/>
+    <mergeCell ref="A589:C589"/>
     <mergeCell ref="B691:B692"/>
     <mergeCell ref="B699:B700"/>
     <mergeCell ref="A601:A602"/>
@@ -7892,393 +8632,91 @@
     <mergeCell ref="B536:B537"/>
     <mergeCell ref="B544:B545"/>
     <mergeCell ref="B552:B553"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="A552:A553"/>
-    <mergeCell ref="A560:A561"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="A593:A594"/>
-    <mergeCell ref="A565:C565"/>
-    <mergeCell ref="A572:C572"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A588:C588"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="B601:B602"/>
-    <mergeCell ref="B609:B610"/>
-    <mergeCell ref="B617:B618"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="B650:B651"/>
-    <mergeCell ref="B658:B659"/>
-    <mergeCell ref="B666:B667"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A645:C645"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A653:C653"/>
-    <mergeCell ref="A654:C654"/>
-    <mergeCell ref="A661:C661"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="A447:A448"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A433:C433"/>
-    <mergeCell ref="A434:C434"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="B447:B448"/>
-    <mergeCell ref="A442:C442"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="A332:A333"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="B332:B333"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A243:A244"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A275:A276"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="B235:B236"/>
-    <mergeCell ref="B243:B244"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="B275:B276"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A223:C223"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A703:C703"/>
-    <mergeCell ref="A704:C704"/>
-    <mergeCell ref="A711:C711"/>
-    <mergeCell ref="A708:A709"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="A732:A733"/>
-    <mergeCell ref="A740:A741"/>
-    <mergeCell ref="A712:C712"/>
-    <mergeCell ref="B708:B709"/>
-    <mergeCell ref="A669:C669"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A604:C604"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A612:C612"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A629:C629"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="A650:A651"/>
-    <mergeCell ref="A658:A659"/>
-    <mergeCell ref="A666:A667"/>
-    <mergeCell ref="A674:A675"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B674:B675"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A596:C596"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A547:C547"/>
-    <mergeCell ref="A548:C548"/>
-    <mergeCell ref="A555:C555"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A564:C564"/>
-    <mergeCell ref="B560:B561"/>
-    <mergeCell ref="B569:B570"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="B593:B594"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A458:C458"/>
-    <mergeCell ref="A459:C459"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A490:C490"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="A491:C491"/>
-    <mergeCell ref="A499:C499"/>
-    <mergeCell ref="A500:C500"/>
-    <mergeCell ref="A507:C507"/>
-    <mergeCell ref="A508:C508"/>
-    <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A450:C450"/>
-    <mergeCell ref="A451:C451"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A443:C443"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A327:C327"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A239:C239"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A270:C270"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A231:C231"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A166:C166"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A182:C182"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A808:C808"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="A813:A814"/>
-    <mergeCell ref="B813:B814"/>
-    <mergeCell ref="A817:C817"/>
-    <mergeCell ref="A818:C818"/>
-    <mergeCell ref="A822:A823"/>
-    <mergeCell ref="B822:B823"/>
-    <mergeCell ref="A825:C825"/>
-    <mergeCell ref="A826:C826"/>
-    <mergeCell ref="A830:A831"/>
-    <mergeCell ref="B830:B831"/>
-    <mergeCell ref="A833:C833"/>
-    <mergeCell ref="A834:C834"/>
-    <mergeCell ref="A838:A839"/>
-    <mergeCell ref="B838:B839"/>
-    <mergeCell ref="A841:C841"/>
-    <mergeCell ref="A842:C842"/>
-    <mergeCell ref="A846:A847"/>
-    <mergeCell ref="B846:B847"/>
-    <mergeCell ref="A849:C849"/>
-    <mergeCell ref="A850:C850"/>
-    <mergeCell ref="A854:A855"/>
-    <mergeCell ref="B854:B855"/>
-    <mergeCell ref="A857:C857"/>
-    <mergeCell ref="A858:C858"/>
-    <mergeCell ref="A862:A863"/>
-    <mergeCell ref="B862:B863"/>
-    <mergeCell ref="A922:C922"/>
-    <mergeCell ref="A923:C923"/>
-    <mergeCell ref="A927:A928"/>
-    <mergeCell ref="B927:B928"/>
-    <mergeCell ref="A931:C931"/>
-    <mergeCell ref="A932:C932"/>
-    <mergeCell ref="A936:A937"/>
-    <mergeCell ref="B936:B937"/>
-    <mergeCell ref="A939:C939"/>
-    <mergeCell ref="A940:C940"/>
-    <mergeCell ref="A944:A945"/>
-    <mergeCell ref="B944:B945"/>
-    <mergeCell ref="A947:C947"/>
-    <mergeCell ref="A948:C948"/>
-    <mergeCell ref="A952:A953"/>
-    <mergeCell ref="B952:B953"/>
-    <mergeCell ref="A955:C955"/>
-    <mergeCell ref="A956:C956"/>
-    <mergeCell ref="A960:A961"/>
-    <mergeCell ref="B960:B961"/>
-    <mergeCell ref="A963:C963"/>
-    <mergeCell ref="A964:C964"/>
-    <mergeCell ref="A968:A969"/>
-    <mergeCell ref="B968:B969"/>
-    <mergeCell ref="A971:C971"/>
-    <mergeCell ref="A972:C972"/>
-    <mergeCell ref="A976:A977"/>
-    <mergeCell ref="B976:B977"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A761:C761"/>
+    <mergeCell ref="A765:A766"/>
+    <mergeCell ref="B765:B766"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="A768:C768"/>
+    <mergeCell ref="A769:C769"/>
+    <mergeCell ref="A773:A774"/>
+    <mergeCell ref="B773:B774"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A777:C777"/>
+    <mergeCell ref="A781:A782"/>
+    <mergeCell ref="B781:B782"/>
+    <mergeCell ref="A784:C784"/>
+    <mergeCell ref="A805:A806"/>
+    <mergeCell ref="B805:B806"/>
+    <mergeCell ref="A785:C785"/>
+    <mergeCell ref="A789:A790"/>
+    <mergeCell ref="B789:B790"/>
+    <mergeCell ref="A792:C792"/>
+    <mergeCell ref="A793:C793"/>
+    <mergeCell ref="A797:A798"/>
+    <mergeCell ref="B797:B798"/>
+    <mergeCell ref="A800:C800"/>
+    <mergeCell ref="A801:C801"/>
+    <mergeCell ref="A865:C865"/>
+    <mergeCell ref="A866:C866"/>
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="B870:B871"/>
+    <mergeCell ref="A874:C874"/>
+    <mergeCell ref="A875:C875"/>
+    <mergeCell ref="A879:A880"/>
+    <mergeCell ref="B879:B880"/>
+    <mergeCell ref="A882:C882"/>
+    <mergeCell ref="A883:C883"/>
+    <mergeCell ref="A887:A888"/>
+    <mergeCell ref="B887:B888"/>
+    <mergeCell ref="A890:C890"/>
+    <mergeCell ref="A891:C891"/>
+    <mergeCell ref="A895:A896"/>
+    <mergeCell ref="B895:B896"/>
+    <mergeCell ref="A898:C898"/>
+    <mergeCell ref="A899:C899"/>
+    <mergeCell ref="A903:A904"/>
+    <mergeCell ref="B903:B904"/>
+    <mergeCell ref="A906:C906"/>
+    <mergeCell ref="A907:C907"/>
+    <mergeCell ref="A911:A912"/>
+    <mergeCell ref="B911:B912"/>
+    <mergeCell ref="A914:C914"/>
+    <mergeCell ref="A915:C915"/>
+    <mergeCell ref="A919:A920"/>
+    <mergeCell ref="B919:B920"/>
+    <mergeCell ref="A997:C997"/>
+    <mergeCell ref="A1001:A1002"/>
+    <mergeCell ref="B1001:B1002"/>
+    <mergeCell ref="A1004:C1004"/>
+    <mergeCell ref="A1005:C1005"/>
+    <mergeCell ref="A1009:A1010"/>
+    <mergeCell ref="B1009:B1010"/>
+    <mergeCell ref="A979:C979"/>
+    <mergeCell ref="A980:C980"/>
+    <mergeCell ref="A984:A985"/>
+    <mergeCell ref="B984:B985"/>
+    <mergeCell ref="A988:C988"/>
+    <mergeCell ref="A989:C989"/>
+    <mergeCell ref="A993:A994"/>
+    <mergeCell ref="B993:B994"/>
+    <mergeCell ref="A996:C996"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED78C315-6D4F-4663-88ED-CB09D1FAF49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0A3D02-1620-4BC9-AA92-10633EEB0F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,6 +242,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -255,9 +258,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -544,18 +544,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -588,17 +588,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -609,18 +609,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -653,31 +653,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="A15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -710,31 +710,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="7">
+      <c r="A23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="8">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -767,31 +767,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="7">
+      <c r="A31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="8">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
+      <c r="A34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -824,31 +824,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="7">
+      <c r="A39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
+      <c r="A42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -881,31 +881,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="7">
+      <c r="A47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="8">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="8"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
+      <c r="A50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -938,31 +938,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="7">
+      <c r="A55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="8">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
+      <c r="A58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -995,17 +995,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="7">
+      <c r="A63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="8">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="6"/>
-      <c r="B64" s="7"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="8"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1016,18 +1016,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
+      <c r="A67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1060,31 +1060,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="7">
+      <c r="A72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="8">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="7"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="8"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
+      <c r="A75" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="6"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1117,31 +1117,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7">
+      <c r="A80" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="8">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="8"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
+      <c r="A83" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="6"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1174,31 +1174,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="7">
+      <c r="A88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="8">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="6"/>
-      <c r="B89" s="7"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="8"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
+      <c r="A91" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="6"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1231,31 +1231,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="7">
+      <c r="A96" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="8">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="7"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="8"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
+      <c r="A99" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="4"/>
-      <c r="C100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="6"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1288,31 +1288,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="7">
+      <c r="A104" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="8">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="7"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="8"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
+      <c r="A107" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="4"/>
-      <c r="C108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="6"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1345,31 +1345,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="7">
+      <c r="A112" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="8">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="7"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="8"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
+      <c r="A115" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="4"/>
-      <c r="C116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="6"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1402,31 +1402,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="7">
+      <c r="A120" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="8">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="6"/>
-      <c r="B121" s="7"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="8"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
+      <c r="A123" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="4"/>
-      <c r="C124" s="5"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="6"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1459,17 +1459,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="7">
+      <c r="A128" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="8">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="6"/>
-      <c r="B129" s="7"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="8"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1480,18 +1480,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
+      <c r="A132" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="4"/>
-      <c r="C133" s="5"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="6"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1524,31 +1524,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="7">
+      <c r="A137" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="8">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="6"/>
-      <c r="B138" s="7"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="8"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
+      <c r="A140" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="3" t="s">
+      <c r="A141" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="4"/>
-      <c r="C141" s="5"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="6"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1581,31 +1581,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="7">
+      <c r="A145" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="8">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="6"/>
-      <c r="B146" s="7"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="8"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="8"/>
-      <c r="C148" s="8"/>
+      <c r="A148" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="3" t="s">
+      <c r="A149" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="4"/>
-      <c r="C149" s="5"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="6"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1638,31 +1638,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="7">
+      <c r="A153" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="8">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="6"/>
-      <c r="B154" s="7"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="8"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
+      <c r="A156" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="3" t="s">
+      <c r="A157" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="4"/>
-      <c r="C157" s="5"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="6"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1695,31 +1695,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="7">
+      <c r="A161" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="8">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="6"/>
-      <c r="B162" s="7"/>
+      <c r="A162" s="7"/>
+      <c r="B162" s="8"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
+      <c r="A164" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="3" t="s">
+      <c r="A165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="4"/>
-      <c r="C165" s="5"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="6"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1752,31 +1752,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="7">
+      <c r="A169" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="8">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="6"/>
-      <c r="B170" s="7"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="8"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="8"/>
-      <c r="C172" s="8"/>
+      <c r="A172" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="3" t="s">
+      <c r="A173" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="4"/>
-      <c r="C173" s="5"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="6"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1809,31 +1809,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="7">
+      <c r="A177" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="8">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="6"/>
-      <c r="B178" s="7"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="8"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
+      <c r="A180" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="3" t="s">
+      <c r="A181" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="4"/>
-      <c r="C181" s="5"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="6"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1866,17 +1866,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="7">
+      <c r="A185" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="8">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="6"/>
-      <c r="B186" s="7"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="8"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1887,18 +1887,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
+      <c r="A189" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="3" t="s">
+      <c r="A190" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="4"/>
-      <c r="C190" s="5"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="6"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1931,31 +1931,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="7">
+      <c r="A194" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="8">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="6"/>
-      <c r="B195" s="7"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="8"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
+      <c r="A197" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="3" t="s">
+      <c r="A198" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="4"/>
-      <c r="C198" s="5"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="6"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -1988,31 +1988,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="7">
+      <c r="A202" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="8">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="6"/>
-      <c r="B203" s="7"/>
+      <c r="A203" s="7"/>
+      <c r="B203" s="8"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="8"/>
-      <c r="C205" s="8"/>
+      <c r="A205" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="3" t="s">
+      <c r="A206" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="4"/>
-      <c r="C206" s="5"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="6"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2045,31 +2045,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="7">
+      <c r="A210" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="8">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="6"/>
-      <c r="B211" s="7"/>
+      <c r="A211" s="7"/>
+      <c r="B211" s="8"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
+      <c r="A213" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="3" t="s">
+      <c r="A214" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="4"/>
-      <c r="C214" s="5"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="6"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2102,31 +2102,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="7">
+      <c r="A218" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="8">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="6"/>
-      <c r="B219" s="7"/>
+      <c r="A219" s="7"/>
+      <c r="B219" s="8"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
+      <c r="A221" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="3" t="s">
+      <c r="A222" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="4"/>
-      <c r="C222" s="5"/>
+      <c r="B222" s="5"/>
+      <c r="C222" s="6"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2159,31 +2159,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="7">
+      <c r="A226" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="8">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="6"/>
-      <c r="B227" s="7"/>
+      <c r="A227" s="7"/>
+      <c r="B227" s="8"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
+      <c r="A229" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="3" t="s">
+      <c r="A230" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="4"/>
-      <c r="C230" s="5"/>
+      <c r="B230" s="5"/>
+      <c r="C230" s="6"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2216,31 +2216,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="7">
+      <c r="A234" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="8">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="6"/>
-      <c r="B235" s="7"/>
+      <c r="A235" s="7"/>
+      <c r="B235" s="8"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="8"/>
-      <c r="C237" s="8"/>
+      <c r="A237" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="3" t="s">
+      <c r="A238" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="4"/>
-      <c r="C238" s="5"/>
+      <c r="B238" s="5"/>
+      <c r="C238" s="6"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2273,17 +2273,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="7">
+      <c r="A242" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="8">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="6"/>
-      <c r="B243" s="7"/>
+      <c r="A243" s="7"/>
+      <c r="B243" s="8"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2294,18 +2294,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="8"/>
-      <c r="C246" s="8"/>
+      <c r="A246" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="3" t="s">
+      <c r="A247" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="4"/>
-      <c r="C247" s="5"/>
+      <c r="B247" s="5"/>
+      <c r="C247" s="6"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2338,31 +2338,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="7">
+      <c r="A251" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="8">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="6"/>
-      <c r="B252" s="7"/>
+      <c r="A252" s="7"/>
+      <c r="B252" s="8"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="8"/>
-      <c r="C254" s="8"/>
+      <c r="A254" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="3" t="s">
+      <c r="A255" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="4"/>
-      <c r="C255" s="5"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="6"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2395,31 +2395,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="7">
+      <c r="A259" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="8">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="6"/>
-      <c r="B260" s="7"/>
+      <c r="A260" s="7"/>
+      <c r="B260" s="8"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="8"/>
-      <c r="C262" s="8"/>
+      <c r="A262" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="3" t="s">
+      <c r="A263" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="4"/>
-      <c r="C263" s="5"/>
+      <c r="B263" s="5"/>
+      <c r="C263" s="6"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2452,17 +2452,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="7">
+      <c r="A267" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="8">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="6"/>
-      <c r="B268" s="7"/>
+      <c r="A268" s="7"/>
+      <c r="B268" s="8"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2473,18 +2473,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="8"/>
-      <c r="C271" s="8"/>
+      <c r="A271" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="3" t="s">
+      <c r="A272" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="4"/>
-      <c r="C272" s="5"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="6"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2517,31 +2517,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="7">
+      <c r="A276" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="8">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="6"/>
-      <c r="B277" s="7"/>
+      <c r="A277" s="7"/>
+      <c r="B277" s="8"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
+      <c r="A279" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="3" t="s">
+      <c r="A280" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="4"/>
-      <c r="C280" s="5"/>
+      <c r="B280" s="5"/>
+      <c r="C280" s="6"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2574,31 +2574,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="7">
+      <c r="A284" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="8">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="6"/>
-      <c r="B285" s="7"/>
+      <c r="A285" s="7"/>
+      <c r="B285" s="8"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="8"/>
-      <c r="C287" s="8"/>
+      <c r="A287" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="3"/>
+      <c r="C287" s="3"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="3" t="s">
+      <c r="A288" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="4"/>
-      <c r="C288" s="5"/>
+      <c r="B288" s="5"/>
+      <c r="C288" s="6"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2631,31 +2631,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="7">
+      <c r="A292" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="8">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="6"/>
-      <c r="B293" s="7"/>
+      <c r="A293" s="7"/>
+      <c r="B293" s="8"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="8"/>
-      <c r="C295" s="8"/>
+      <c r="A295" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="3" t="s">
+      <c r="A296" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="4"/>
-      <c r="C296" s="5"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="6"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2688,31 +2688,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="7">
+      <c r="A300" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="8">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="6"/>
-      <c r="B301" s="7"/>
+      <c r="A301" s="7"/>
+      <c r="B301" s="8"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="8"/>
-      <c r="C303" s="8"/>
+      <c r="A303" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="3" t="s">
+      <c r="A304" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="4"/>
-      <c r="C304" s="5"/>
+      <c r="B304" s="5"/>
+      <c r="C304" s="6"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2745,31 +2745,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="7">
+      <c r="A308" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="8">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="6"/>
-      <c r="B309" s="7"/>
+      <c r="A309" s="7"/>
+      <c r="B309" s="8"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="8"/>
-      <c r="C311" s="8"/>
+      <c r="A311" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="3"/>
+      <c r="C311" s="3"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="3" t="s">
+      <c r="A312" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="4"/>
-      <c r="C312" s="5"/>
+      <c r="B312" s="5"/>
+      <c r="C312" s="6"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2802,31 +2802,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="7">
+      <c r="A316" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="8">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="6"/>
-      <c r="B317" s="7"/>
+      <c r="A317" s="7"/>
+      <c r="B317" s="8"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="8"/>
-      <c r="C319" s="8"/>
+      <c r="A319" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="3"/>
+      <c r="C319" s="3"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="3" t="s">
+      <c r="A320" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="4"/>
-      <c r="C320" s="5"/>
+      <c r="B320" s="5"/>
+      <c r="C320" s="6"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2859,17 +2859,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="7">
+      <c r="A324" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="8">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="6"/>
-      <c r="B325" s="7"/>
+      <c r="A325" s="7"/>
+      <c r="B325" s="8"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2880,18 +2880,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="8"/>
-      <c r="C328" s="8"/>
+      <c r="A328" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="3" t="s">
+      <c r="A329" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="4"/>
-      <c r="C329" s="5"/>
+      <c r="B329" s="5"/>
+      <c r="C329" s="6"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2924,31 +2924,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="7">
+      <c r="A333" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="8">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="6"/>
-      <c r="B334" s="7"/>
+      <c r="A334" s="7"/>
+      <c r="B334" s="8"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="8"/>
-      <c r="C336" s="8"/>
+      <c r="A336" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="3"/>
+      <c r="C336" s="3"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="3" t="s">
+      <c r="A337" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="4"/>
-      <c r="C337" s="5"/>
+      <c r="B337" s="5"/>
+      <c r="C337" s="6"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2981,31 +2981,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="7">
+      <c r="A341" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="8">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="6"/>
-      <c r="B342" s="7"/>
+      <c r="A342" s="7"/>
+      <c r="B342" s="8"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="8"/>
-      <c r="C344" s="8"/>
+      <c r="A344" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="3"/>
+      <c r="C344" s="3"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="3" t="s">
+      <c r="A345" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="4"/>
-      <c r="C345" s="5"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="6"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3038,31 +3038,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="7">
+      <c r="A349" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="8">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="6"/>
-      <c r="B350" s="7"/>
+      <c r="A350" s="7"/>
+      <c r="B350" s="8"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="8"/>
-      <c r="C352" s="8"/>
+      <c r="A352" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="3"/>
+      <c r="C352" s="3"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="3" t="s">
+      <c r="A353" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="4"/>
-      <c r="C353" s="5"/>
+      <c r="B353" s="5"/>
+      <c r="C353" s="6"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3095,31 +3095,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="7">
+      <c r="A357" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="8">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="6"/>
-      <c r="B358" s="7"/>
+      <c r="A358" s="7"/>
+      <c r="B358" s="8"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="8"/>
-      <c r="C360" s="8"/>
+      <c r="A360" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="3"/>
+      <c r="C360" s="3"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="3" t="s">
+      <c r="A361" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="4"/>
-      <c r="C361" s="5"/>
+      <c r="B361" s="5"/>
+      <c r="C361" s="6"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3152,31 +3152,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="7">
+      <c r="A365" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="8">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="6"/>
-      <c r="B366" s="7"/>
+      <c r="A366" s="7"/>
+      <c r="B366" s="8"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="8"/>
-      <c r="C368" s="8"/>
+      <c r="A368" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="3"/>
+      <c r="C368" s="3"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="3" t="s">
+      <c r="A369" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="4"/>
-      <c r="C369" s="5"/>
+      <c r="B369" s="5"/>
+      <c r="C369" s="6"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3209,31 +3209,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="7">
+      <c r="A373" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="8">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="6"/>
-      <c r="B374" s="7"/>
+      <c r="A374" s="7"/>
+      <c r="B374" s="8"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="8"/>
-      <c r="C376" s="8"/>
+      <c r="A376" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="3"/>
+      <c r="C376" s="3"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="3" t="s">
+      <c r="A377" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="4"/>
-      <c r="C377" s="5"/>
+      <c r="B377" s="5"/>
+      <c r="C377" s="6"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3266,17 +3266,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="7">
+      <c r="A381" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="8">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="6"/>
-      <c r="B382" s="7"/>
+      <c r="A382" s="7"/>
+      <c r="B382" s="8"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3287,18 +3287,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="8"/>
-      <c r="C385" s="8"/>
+      <c r="A385" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="3"/>
+      <c r="C385" s="3"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="3" t="s">
+      <c r="A386" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="4"/>
-      <c r="C386" s="5"/>
+      <c r="B386" s="5"/>
+      <c r="C386" s="6"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3331,31 +3331,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="7">
+      <c r="A390" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="8">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="6"/>
-      <c r="B391" s="7"/>
+      <c r="A391" s="7"/>
+      <c r="B391" s="8"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="8"/>
-      <c r="C393" s="8"/>
+      <c r="A393" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="3"/>
+      <c r="C393" s="3"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="3" t="s">
+      <c r="A394" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="4"/>
-      <c r="C394" s="5"/>
+      <c r="B394" s="5"/>
+      <c r="C394" s="6"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3388,31 +3388,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="7">
+      <c r="A398" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="8">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="6"/>
-      <c r="B399" s="7"/>
+      <c r="A399" s="7"/>
+      <c r="B399" s="8"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="8"/>
-      <c r="C401" s="8"/>
+      <c r="A401" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="3"/>
+      <c r="C401" s="3"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="3" t="s">
+      <c r="A402" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="4"/>
-      <c r="C402" s="5"/>
+      <c r="B402" s="5"/>
+      <c r="C402" s="6"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3445,31 +3445,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="7">
+      <c r="A406" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="8">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="6"/>
-      <c r="B407" s="7"/>
+      <c r="A407" s="7"/>
+      <c r="B407" s="8"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="8"/>
-      <c r="C409" s="8"/>
+      <c r="A409" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="3"/>
+      <c r="C409" s="3"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="3" t="s">
+      <c r="A410" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="4"/>
-      <c r="C410" s="5"/>
+      <c r="B410" s="5"/>
+      <c r="C410" s="6"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3502,31 +3502,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="7">
+      <c r="A414" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="8">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="6"/>
-      <c r="B415" s="7"/>
+      <c r="A415" s="7"/>
+      <c r="B415" s="8"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="8"/>
-      <c r="C417" s="8"/>
+      <c r="A417" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="3"/>
+      <c r="C417" s="3"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="3" t="s">
+      <c r="A418" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="4"/>
-      <c r="C418" s="5"/>
+      <c r="B418" s="5"/>
+      <c r="C418" s="6"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3559,31 +3559,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="7">
+      <c r="A422" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="8">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="6"/>
-      <c r="B423" s="7"/>
+      <c r="A423" s="7"/>
+      <c r="B423" s="8"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="8"/>
-      <c r="C425" s="8"/>
+      <c r="A425" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="3" t="s">
+      <c r="A426" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="4"/>
-      <c r="C426" s="5"/>
+      <c r="B426" s="5"/>
+      <c r="C426" s="6"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3616,31 +3616,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="7">
+      <c r="A430" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="8">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="6"/>
-      <c r="B431" s="7"/>
+      <c r="A431" s="7"/>
+      <c r="B431" s="8"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="8"/>
-      <c r="C433" s="8"/>
+      <c r="A433" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="3" t="s">
+      <c r="A434" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="4"/>
-      <c r="C434" s="5"/>
+      <c r="B434" s="5"/>
+      <c r="C434" s="6"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3673,17 +3673,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="7">
+      <c r="A438" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="8">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="6"/>
-      <c r="B439" s="7"/>
+      <c r="A439" s="7"/>
+      <c r="B439" s="8"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3694,18 +3694,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="8"/>
-      <c r="C442" s="8"/>
+      <c r="A442" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="3" t="s">
+      <c r="A443" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="4"/>
-      <c r="C443" s="5"/>
+      <c r="B443" s="5"/>
+      <c r="C443" s="6"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3738,31 +3738,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="7">
+      <c r="A447" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="8">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="6"/>
-      <c r="B448" s="7"/>
+      <c r="A448" s="7"/>
+      <c r="B448" s="8"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="8"/>
-      <c r="C450" s="8"/>
+      <c r="A450" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="3"/>
+      <c r="C450" s="3"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="3" t="s">
+      <c r="A451" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="4"/>
-      <c r="C451" s="5"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="6"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3795,31 +3795,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="7">
+      <c r="A455" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="8">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="6"/>
-      <c r="B456" s="7"/>
+      <c r="A456" s="7"/>
+      <c r="B456" s="8"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="8"/>
-      <c r="C458" s="8"/>
+      <c r="A458" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="3" t="s">
+      <c r="A459" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="4"/>
-      <c r="C459" s="5"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="6"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3852,31 +3852,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="7">
+      <c r="A463" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="8">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="6"/>
-      <c r="B464" s="7"/>
+      <c r="A464" s="7"/>
+      <c r="B464" s="8"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="8"/>
-      <c r="C466" s="8"/>
+      <c r="A466" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="3"/>
+      <c r="C466" s="3"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="3" t="s">
+      <c r="A467" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="4"/>
-      <c r="C467" s="5"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="6"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3909,31 +3909,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="7">
+      <c r="A471" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="8">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="6"/>
-      <c r="B472" s="7"/>
+      <c r="A472" s="7"/>
+      <c r="B472" s="8"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="8"/>
-      <c r="C474" s="8"/>
+      <c r="A474" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="3"/>
+      <c r="C474" s="3"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="3" t="s">
+      <c r="A475" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="4"/>
-      <c r="C475" s="5"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="6"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3966,31 +3966,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="7">
+      <c r="A479" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="8">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="6"/>
-      <c r="B480" s="7"/>
+      <c r="A480" s="7"/>
+      <c r="B480" s="8"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="8"/>
-      <c r="C482" s="8"/>
+      <c r="A482" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="3"/>
+      <c r="C482" s="3"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="3" t="s">
+      <c r="A483" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="4"/>
-      <c r="C483" s="5"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="6"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4023,31 +4023,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="7">
+      <c r="A487" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="8">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="6"/>
-      <c r="B488" s="7"/>
+      <c r="A488" s="7"/>
+      <c r="B488" s="8"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="8"/>
-      <c r="C490" s="8"/>
+      <c r="A490" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="3"/>
+      <c r="C490" s="3"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="3" t="s">
+      <c r="A491" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="4"/>
-      <c r="C491" s="5"/>
+      <c r="B491" s="5"/>
+      <c r="C491" s="6"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4080,17 +4080,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="7">
+      <c r="A495" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="8">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="6"/>
-      <c r="B496" s="7"/>
+      <c r="A496" s="7"/>
+      <c r="B496" s="8"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4101,18 +4101,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="8"/>
-      <c r="C499" s="8"/>
+      <c r="A499" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="3"/>
+      <c r="C499" s="3"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="3" t="s">
+      <c r="A500" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="4"/>
-      <c r="C500" s="5"/>
+      <c r="B500" s="5"/>
+      <c r="C500" s="6"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4145,31 +4145,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="7">
+      <c r="A504" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="8">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="6"/>
-      <c r="B505" s="7"/>
+      <c r="A505" s="7"/>
+      <c r="B505" s="8"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="8"/>
-      <c r="C507" s="8"/>
+      <c r="A507" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="3"/>
+      <c r="C507" s="3"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="3" t="s">
+      <c r="A508" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="4"/>
-      <c r="C508" s="5"/>
+      <c r="B508" s="5"/>
+      <c r="C508" s="6"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4202,31 +4202,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="7">
+      <c r="A512" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="8">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="6"/>
-      <c r="B513" s="7"/>
+      <c r="A513" s="7"/>
+      <c r="B513" s="8"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="8"/>
-      <c r="C515" s="8"/>
+      <c r="A515" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="3"/>
+      <c r="C515" s="3"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="3" t="s">
+      <c r="A516" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="4"/>
-      <c r="C516" s="5"/>
+      <c r="B516" s="5"/>
+      <c r="C516" s="6"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4259,31 +4259,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="7">
+      <c r="A520" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="8">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="6"/>
-      <c r="B521" s="7"/>
+      <c r="A521" s="7"/>
+      <c r="B521" s="8"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="8"/>
-      <c r="C523" s="8"/>
+      <c r="A523" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="3"/>
+      <c r="C523" s="3"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="3" t="s">
+      <c r="A524" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="4"/>
-      <c r="C524" s="5"/>
+      <c r="B524" s="5"/>
+      <c r="C524" s="6"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4316,31 +4316,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="7">
+      <c r="A528" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="8">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="6"/>
-      <c r="B529" s="7"/>
+      <c r="A529" s="7"/>
+      <c r="B529" s="8"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="8"/>
-      <c r="C531" s="8"/>
+      <c r="A531" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="3"/>
+      <c r="C531" s="3"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="3" t="s">
+      <c r="A532" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="4"/>
-      <c r="C532" s="5"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="6"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4373,31 +4373,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="7">
+      <c r="A536" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="8">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="6"/>
-      <c r="B537" s="7"/>
+      <c r="A537" s="7"/>
+      <c r="B537" s="8"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="8"/>
-      <c r="C539" s="8"/>
+      <c r="A539" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="3"/>
+      <c r="C539" s="3"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="3" t="s">
+      <c r="A540" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="4"/>
-      <c r="C540" s="5"/>
+      <c r="B540" s="5"/>
+      <c r="C540" s="6"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4430,31 +4430,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="7">
+      <c r="A544" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="8">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="6"/>
-      <c r="B545" s="7"/>
+      <c r="A545" s="7"/>
+      <c r="B545" s="8"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="8"/>
-      <c r="C547" s="8"/>
+      <c r="A547" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="3"/>
+      <c r="C547" s="3"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="3" t="s">
+      <c r="A548" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="4"/>
-      <c r="C548" s="5"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="6"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4487,17 +4487,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="7">
+      <c r="A552" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="8">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="6"/>
-      <c r="B553" s="7"/>
+      <c r="A553" s="7"/>
+      <c r="B553" s="8"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4508,18 +4508,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="8"/>
-      <c r="C556" s="8"/>
+      <c r="A556" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="3"/>
+      <c r="C556" s="3"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="3" t="s">
+      <c r="A557" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="4"/>
-      <c r="C557" s="5"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="6"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4552,31 +4552,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="7">
+      <c r="A561" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="8">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="6"/>
-      <c r="B562" s="7"/>
+      <c r="A562" s="7"/>
+      <c r="B562" s="8"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="8"/>
-      <c r="C564" s="8"/>
+      <c r="A564" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="3"/>
+      <c r="C564" s="3"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="3" t="s">
+      <c r="A565" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="4"/>
-      <c r="C565" s="5"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="6"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4609,31 +4609,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="7">
+      <c r="A569" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="8">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="6"/>
-      <c r="B570" s="7"/>
+      <c r="A570" s="7"/>
+      <c r="B570" s="8"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="8"/>
-      <c r="C572" s="8"/>
+      <c r="A572" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="3"/>
+      <c r="C572" s="3"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="3" t="s">
+      <c r="A573" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="4"/>
-      <c r="C573" s="5"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="6"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4666,31 +4666,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="7">
+      <c r="A577" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="8">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="6"/>
-      <c r="B578" s="7"/>
+      <c r="A578" s="7"/>
+      <c r="B578" s="8"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="8"/>
-      <c r="C580" s="8"/>
+      <c r="A580" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="3"/>
+      <c r="C580" s="3"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="3" t="s">
+      <c r="A581" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="4"/>
-      <c r="C581" s="5"/>
+      <c r="B581" s="5"/>
+      <c r="C581" s="6"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4723,17 +4723,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="7">
+      <c r="A585" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="8">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="6"/>
-      <c r="B586" s="7"/>
+      <c r="A586" s="7"/>
+      <c r="B586" s="8"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4744,18 +4744,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="8"/>
-      <c r="C589" s="8"/>
+      <c r="A589" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="3"/>
+      <c r="C589" s="3"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="3" t="s">
+      <c r="A590" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="4"/>
-      <c r="C590" s="5"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="6"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4788,31 +4788,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="7">
+      <c r="A594" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="8">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="6"/>
-      <c r="B595" s="7"/>
+      <c r="A595" s="7"/>
+      <c r="B595" s="8"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="8"/>
-      <c r="C597" s="8"/>
+      <c r="A597" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="3"/>
+      <c r="C597" s="3"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="3" t="s">
+      <c r="A598" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="4"/>
-      <c r="C598" s="5"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="6"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4845,31 +4845,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="7">
+      <c r="A602" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="8">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="6"/>
-      <c r="B603" s="7"/>
+      <c r="A603" s="7"/>
+      <c r="B603" s="8"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="8"/>
-      <c r="C605" s="8"/>
+      <c r="A605" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="3"/>
+      <c r="C605" s="3"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="3" t="s">
+      <c r="A606" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="4"/>
-      <c r="C606" s="5"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="6"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4902,31 +4902,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="7">
+      <c r="A610" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="8">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="6"/>
-      <c r="B611" s="7"/>
+      <c r="A611" s="7"/>
+      <c r="B611" s="8"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="8"/>
-      <c r="C613" s="8"/>
+      <c r="A613" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="3"/>
+      <c r="C613" s="3"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="3" t="s">
+      <c r="A614" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="4"/>
-      <c r="C614" s="5"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="6"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4959,31 +4959,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="7">
+      <c r="A618" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="8">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="6"/>
-      <c r="B619" s="7"/>
+      <c r="A619" s="7"/>
+      <c r="B619" s="8"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="8"/>
-      <c r="C621" s="8"/>
+      <c r="A621" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="3"/>
+      <c r="C621" s="3"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="3" t="s">
+      <c r="A622" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="4"/>
-      <c r="C622" s="5"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="6"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5016,31 +5016,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="7">
+      <c r="A626" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="8">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="6"/>
-      <c r="B627" s="7"/>
+      <c r="A627" s="7"/>
+      <c r="B627" s="8"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="8"/>
-      <c r="C629" s="8"/>
+      <c r="A629" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="3"/>
+      <c r="C629" s="3"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="3" t="s">
+      <c r="A630" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="4"/>
-      <c r="C630" s="5"/>
+      <c r="B630" s="5"/>
+      <c r="C630" s="6"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5073,31 +5073,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="7">
+      <c r="A634" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="8">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="6"/>
-      <c r="B635" s="7"/>
+      <c r="A635" s="7"/>
+      <c r="B635" s="8"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="8"/>
-      <c r="C637" s="8"/>
+      <c r="A637" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="3"/>
+      <c r="C637" s="3"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="3" t="s">
+      <c r="A638" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="4"/>
-      <c r="C638" s="5"/>
+      <c r="B638" s="5"/>
+      <c r="C638" s="6"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5130,39 +5130,39 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="7">
+      <c r="A642" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="8">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="6"/>
-      <c r="B643" s="7"/>
+      <c r="A643" s="7"/>
+      <c r="B643" s="8"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B644" s="2">
-        <v>80706</v>
+        <v>73794</v>
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="8"/>
-      <c r="C646" s="8"/>
+      <c r="A646" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="3"/>
+      <c r="C646" s="3"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="3" t="s">
+      <c r="A647" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="4"/>
-      <c r="C647" s="5"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="6"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5195,31 +5195,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="7">
+      <c r="A651" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="8">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="6"/>
-      <c r="B652" s="7"/>
+      <c r="A652" s="7"/>
+      <c r="B652" s="8"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="8"/>
-      <c r="C654" s="8"/>
+      <c r="A654" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="3"/>
+      <c r="C654" s="3"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="3" t="s">
+      <c r="A655" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="4"/>
-      <c r="C655" s="5"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="6"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5252,31 +5252,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="7">
+      <c r="A659" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="8">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="6"/>
-      <c r="B660" s="7"/>
+      <c r="A660" s="7"/>
+      <c r="B660" s="8"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="8"/>
-      <c r="C662" s="8"/>
+      <c r="A662" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="3"/>
+      <c r="C662" s="3"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="3" t="s">
+      <c r="A663" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="4"/>
-      <c r="C663" s="5"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="6"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5309,31 +5309,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="7">
+      <c r="A667" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="8">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="6"/>
-      <c r="B668" s="7"/>
+      <c r="A668" s="7"/>
+      <c r="B668" s="8"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="8"/>
-      <c r="C670" s="8"/>
+      <c r="A670" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="3"/>
+      <c r="C670" s="3"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="3" t="s">
+      <c r="A671" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="4"/>
-      <c r="C671" s="5"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="6"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5366,31 +5366,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="7">
+      <c r="A675" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="8">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="6"/>
-      <c r="B676" s="7"/>
+      <c r="A676" s="7"/>
+      <c r="B676" s="8"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="8"/>
-      <c r="C678" s="8"/>
+      <c r="A678" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="3"/>
+      <c r="C678" s="3"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="3" t="s">
+      <c r="A679" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="4"/>
-      <c r="C679" s="5"/>
+      <c r="B679" s="5"/>
+      <c r="C679" s="6"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5423,31 +5423,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="7">
+      <c r="A683" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="8">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="6"/>
-      <c r="B684" s="7"/>
+      <c r="A684" s="7"/>
+      <c r="B684" s="8"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="8"/>
-      <c r="C686" s="8"/>
+      <c r="A686" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="3"/>
+      <c r="C686" s="3"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="3" t="s">
+      <c r="A687" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="4"/>
-      <c r="C687" s="5"/>
+      <c r="B687" s="5"/>
+      <c r="C687" s="6"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5480,31 +5480,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="7">
+      <c r="A691" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="8">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="6"/>
-      <c r="B692" s="7"/>
+      <c r="A692" s="7"/>
+      <c r="B692" s="8"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="8"/>
-      <c r="C694" s="8"/>
+      <c r="A694" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="3"/>
+      <c r="C694" s="3"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="3" t="s">
+      <c r="A695" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="4"/>
-      <c r="C695" s="5"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="6"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5537,120 +5537,234 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="7">
+      <c r="A699" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="8">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="6"/>
-      <c r="B700" s="7"/>
+      <c r="A700" s="7"/>
+      <c r="B700" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="344">
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A487:A488"/>
-    <mergeCell ref="B487:B488"/>
-    <mergeCell ref="A565:C565"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="B569:B570"/>
-    <mergeCell ref="A572:C572"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A547:C547"/>
-    <mergeCell ref="A548:C548"/>
-    <mergeCell ref="A552:A553"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A557:C557"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="B561:B562"/>
-    <mergeCell ref="A564:C564"/>
-    <mergeCell ref="B463:B464"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A515:C515"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A490:C490"/>
+    <mergeCell ref="A491:C491"/>
+    <mergeCell ref="A495:A496"/>
+    <mergeCell ref="B495:B496"/>
+    <mergeCell ref="A499:C499"/>
+    <mergeCell ref="A500:C500"/>
+    <mergeCell ref="A433:C433"/>
+    <mergeCell ref="A434:C434"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:C442"/>
+    <mergeCell ref="A443:C443"/>
+    <mergeCell ref="A447:A448"/>
+    <mergeCell ref="B447:B448"/>
+    <mergeCell ref="A450:C450"/>
+    <mergeCell ref="A451:C451"/>
+    <mergeCell ref="A455:A456"/>
+    <mergeCell ref="B455:B456"/>
+    <mergeCell ref="A458:C458"/>
+    <mergeCell ref="A459:C459"/>
+    <mergeCell ref="A463:A464"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A157:C157"/>
     <mergeCell ref="B259:B260"/>
     <mergeCell ref="B267:B268"/>
     <mergeCell ref="A169:A170"/>
@@ -5675,226 +5789,112 @@
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="B112:B113"/>
     <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A490:C490"/>
-    <mergeCell ref="A491:C491"/>
-    <mergeCell ref="A495:A496"/>
-    <mergeCell ref="B495:B496"/>
-    <mergeCell ref="A499:C499"/>
-    <mergeCell ref="A500:C500"/>
-    <mergeCell ref="A433:C433"/>
-    <mergeCell ref="A434:C434"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A442:C442"/>
-    <mergeCell ref="A443:C443"/>
-    <mergeCell ref="A447:A448"/>
-    <mergeCell ref="B447:B448"/>
-    <mergeCell ref="A450:C450"/>
-    <mergeCell ref="A451:C451"/>
-    <mergeCell ref="A455:A456"/>
-    <mergeCell ref="B455:B456"/>
-    <mergeCell ref="A458:C458"/>
-    <mergeCell ref="A459:C459"/>
-    <mergeCell ref="A463:A464"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="B463:B464"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A487:A488"/>
+    <mergeCell ref="B487:B488"/>
+    <mergeCell ref="A565:C565"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="B569:B570"/>
+    <mergeCell ref="A572:C572"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A547:C547"/>
+    <mergeCell ref="A548:C548"/>
+    <mergeCell ref="A552:A553"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A557:C557"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="B561:B562"/>
+    <mergeCell ref="A564:C564"/>
     <mergeCell ref="A504:A505"/>
     <mergeCell ref="B504:B505"/>
     <mergeCell ref="A507:C507"/>
     <mergeCell ref="A508:C508"/>
     <mergeCell ref="A512:A513"/>
     <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0A3D02-1620-4BC9-AA92-10633EEB0F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A313110-35B8-4B14-BB59-E33446C6894C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="36">
   <si>
     <t>Data</t>
   </si>
@@ -140,6 +140,9 @@
   <si>
     <t>21.10.2026</t>
   </si>
+  <si>
+    <t>22.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -242,9 +245,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -258,6 +258,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -535,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C700"/>
+  <dimension ref="A1:C765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -544,18 +547,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -588,17 +591,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -609,18 +612,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="A10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -653,31 +656,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="7">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="A18" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -710,31 +713,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="7">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -767,31 +770,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="7">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="7"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="A34" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -824,31 +827,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="7">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="7"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="A42" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -881,31 +884,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="7">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="7"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
+      <c r="A50" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="5"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -938,31 +941,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="7">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="7"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="A58" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -995,17 +998,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="7">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1016,18 +1019,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
+      <c r="A67" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1060,31 +1063,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="8">
+      <c r="A72" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="7">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="7"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
+      <c r="A75" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="6"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="5"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1117,31 +1120,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="8">
+      <c r="A80" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="7">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="7"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="A83" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="6"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="5"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1174,31 +1177,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="8">
+      <c r="A88" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="7">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="7"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
+      <c r="A91" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="6"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1231,31 +1234,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="8">
+      <c r="A96" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="7">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="7"/>
-      <c r="B97" s="8"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="7"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="A99" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="6"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1288,31 +1291,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="8">
+      <c r="A104" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="7">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="7"/>
-      <c r="B105" s="8"/>
+      <c r="A105" s="6"/>
+      <c r="B105" s="7"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="A107" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="6"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1345,31 +1348,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="8">
+      <c r="A112" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="7">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="7"/>
-      <c r="B113" s="8"/>
+      <c r="A113" s="6"/>
+      <c r="B113" s="7"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="A115" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="6"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1402,31 +1405,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="8">
+      <c r="A120" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="7">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="7"/>
-      <c r="B121" s="8"/>
+      <c r="A121" s="6"/>
+      <c r="B121" s="7"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="A123" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="6"/>
+      <c r="B124" s="4"/>
+      <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1459,17 +1462,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="8">
+      <c r="A128" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="7">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="7"/>
-      <c r="B129" s="8"/>
+      <c r="A129" s="6"/>
+      <c r="B129" s="7"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1480,18 +1483,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="A132" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="5"/>
-      <c r="C133" s="6"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1524,31 +1527,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="8">
+      <c r="A137" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="7">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="7"/>
-      <c r="B138" s="8"/>
+      <c r="A138" s="6"/>
+      <c r="B138" s="7"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
+      <c r="A140" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="5"/>
-      <c r="C141" s="6"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1581,31 +1584,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="8">
+      <c r="A145" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="7">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="7"/>
-      <c r="B146" s="8"/>
+      <c r="A146" s="6"/>
+      <c r="B146" s="7"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
+      <c r="A148" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="6"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1638,31 +1641,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="8">
+      <c r="A153" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="7">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="7"/>
-      <c r="B154" s="8"/>
+      <c r="A154" s="6"/>
+      <c r="B154" s="7"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
+      <c r="A156" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="5"/>
-      <c r="C157" s="6"/>
+      <c r="B157" s="4"/>
+      <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1695,31 +1698,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="8">
+      <c r="A161" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="7">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="7"/>
-      <c r="B162" s="8"/>
+      <c r="A162" s="6"/>
+      <c r="B162" s="7"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
+      <c r="A164" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="5"/>
-      <c r="C165" s="6"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="5"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1752,31 +1755,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="8">
+      <c r="A169" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="7">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="7"/>
-      <c r="B170" s="8"/>
+      <c r="A170" s="6"/>
+      <c r="B170" s="7"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
+      <c r="A172" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="8"/>
+      <c r="C172" s="8"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="6"/>
+      <c r="B173" s="4"/>
+      <c r="C173" s="5"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1809,31 +1812,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="8">
+      <c r="A177" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="7">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="7"/>
-      <c r="B178" s="8"/>
+      <c r="A178" s="6"/>
+      <c r="B178" s="7"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
+      <c r="A180" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="8"/>
+      <c r="C180" s="8"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="6"/>
+      <c r="B181" s="4"/>
+      <c r="C181" s="5"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1866,17 +1869,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="8">
+      <c r="A185" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="7">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="7"/>
-      <c r="B186" s="8"/>
+      <c r="A186" s="6"/>
+      <c r="B186" s="7"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1887,18 +1890,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
+      <c r="A189" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="5"/>
-      <c r="C190" s="6"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="5"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1931,31 +1934,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="8">
+      <c r="A194" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="7">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="7"/>
-      <c r="B195" s="8"/>
+      <c r="A195" s="6"/>
+      <c r="B195" s="7"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
+      <c r="A197" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="5"/>
-      <c r="C198" s="6"/>
+      <c r="B198" s="4"/>
+      <c r="C198" s="5"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -1988,31 +1991,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="8">
+      <c r="A202" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="7">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="7"/>
-      <c r="B203" s="8"/>
+      <c r="A203" s="6"/>
+      <c r="B203" s="7"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="3"/>
-      <c r="C205" s="3"/>
+      <c r="A205" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="8"/>
+      <c r="C205" s="8"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="5"/>
-      <c r="C206" s="6"/>
+      <c r="B206" s="4"/>
+      <c r="C206" s="5"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2045,31 +2048,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="8">
+      <c r="A210" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="7">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="7"/>
-      <c r="B211" s="8"/>
+      <c r="A211" s="6"/>
+      <c r="B211" s="7"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="3"/>
-      <c r="C213" s="3"/>
+      <c r="A213" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="6"/>
+      <c r="B214" s="4"/>
+      <c r="C214" s="5"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2102,31 +2105,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="8">
+      <c r="A218" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="7">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="7"/>
-      <c r="B219" s="8"/>
+      <c r="A219" s="6"/>
+      <c r="B219" s="7"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="3"/>
-      <c r="C221" s="3"/>
+      <c r="A221" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="5"/>
-      <c r="C222" s="6"/>
+      <c r="B222" s="4"/>
+      <c r="C222" s="5"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2159,31 +2162,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="8">
+      <c r="A226" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="7">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="7"/>
-      <c r="B227" s="8"/>
+      <c r="A227" s="6"/>
+      <c r="B227" s="7"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="3"/>
-      <c r="C229" s="3"/>
+      <c r="A229" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="5"/>
-      <c r="C230" s="6"/>
+      <c r="B230" s="4"/>
+      <c r="C230" s="5"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2216,31 +2219,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="8">
+      <c r="A234" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="7">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="7"/>
-      <c r="B235" s="8"/>
+      <c r="A235" s="6"/>
+      <c r="B235" s="7"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="3"/>
-      <c r="C237" s="3"/>
+      <c r="A237" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="6"/>
+      <c r="B238" s="4"/>
+      <c r="C238" s="5"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2273,17 +2276,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="8">
+      <c r="A242" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="7">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="7"/>
-      <c r="B243" s="8"/>
+      <c r="A243" s="6"/>
+      <c r="B243" s="7"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2294,18 +2297,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="3"/>
-      <c r="C246" s="3"/>
+      <c r="A246" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="4" t="s">
+      <c r="A247" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="5"/>
-      <c r="C247" s="6"/>
+      <c r="B247" s="4"/>
+      <c r="C247" s="5"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2338,31 +2341,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="8">
+      <c r="A251" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="7">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="7"/>
-      <c r="B252" s="8"/>
+      <c r="A252" s="6"/>
+      <c r="B252" s="7"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="3"/>
-      <c r="C254" s="3"/>
+      <c r="A254" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="5"/>
-      <c r="C255" s="6"/>
+      <c r="B255" s="4"/>
+      <c r="C255" s="5"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2395,31 +2398,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="8">
+      <c r="A259" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="7">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="7"/>
-      <c r="B260" s="8"/>
+      <c r="A260" s="6"/>
+      <c r="B260" s="7"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="3"/>
-      <c r="C262" s="3"/>
+      <c r="A262" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="8"/>
+      <c r="C262" s="8"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="4" t="s">
+      <c r="A263" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="5"/>
-      <c r="C263" s="6"/>
+      <c r="B263" s="4"/>
+      <c r="C263" s="5"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2452,17 +2455,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="8">
+      <c r="A267" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="7">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="7"/>
-      <c r="B268" s="8"/>
+      <c r="A268" s="6"/>
+      <c r="B268" s="7"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2473,18 +2476,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="3"/>
-      <c r="C271" s="3"/>
+      <c r="A271" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="8"/>
+      <c r="C271" s="8"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="5"/>
-      <c r="C272" s="6"/>
+      <c r="B272" s="4"/>
+      <c r="C272" s="5"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2517,31 +2520,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="8">
+      <c r="A276" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="7">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="7"/>
-      <c r="B277" s="8"/>
+      <c r="A277" s="6"/>
+      <c r="B277" s="7"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="3"/>
-      <c r="C279" s="3"/>
+      <c r="A279" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="8"/>
+      <c r="C279" s="8"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="5"/>
-      <c r="C280" s="6"/>
+      <c r="B280" s="4"/>
+      <c r="C280" s="5"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2574,31 +2577,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="8">
+      <c r="A284" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="7">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="7"/>
-      <c r="B285" s="8"/>
+      <c r="A285" s="6"/>
+      <c r="B285" s="7"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="3"/>
-      <c r="C287" s="3"/>
+      <c r="A287" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="8"/>
+      <c r="C287" s="8"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="4" t="s">
+      <c r="A288" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="5"/>
-      <c r="C288" s="6"/>
+      <c r="B288" s="4"/>
+      <c r="C288" s="5"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2631,31 +2634,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="8">
+      <c r="A292" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="7">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="7"/>
-      <c r="B293" s="8"/>
+      <c r="A293" s="6"/>
+      <c r="B293" s="7"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="3"/>
-      <c r="C295" s="3"/>
+      <c r="A295" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="8"/>
+      <c r="C295" s="8"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="5"/>
-      <c r="C296" s="6"/>
+      <c r="B296" s="4"/>
+      <c r="C296" s="5"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2688,31 +2691,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="8">
+      <c r="A300" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="7">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="7"/>
-      <c r="B301" s="8"/>
+      <c r="A301" s="6"/>
+      <c r="B301" s="7"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="3"/>
-      <c r="C303" s="3"/>
+      <c r="A303" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="8"/>
+      <c r="C303" s="8"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="4" t="s">
+      <c r="A304" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="5"/>
-      <c r="C304" s="6"/>
+      <c r="B304" s="4"/>
+      <c r="C304" s="5"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2745,31 +2748,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="8">
+      <c r="A308" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="7">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="7"/>
-      <c r="B309" s="8"/>
+      <c r="A309" s="6"/>
+      <c r="B309" s="7"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="3"/>
-      <c r="C311" s="3"/>
+      <c r="A311" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="8"/>
+      <c r="C311" s="8"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="4" t="s">
+      <c r="A312" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="5"/>
-      <c r="C312" s="6"/>
+      <c r="B312" s="4"/>
+      <c r="C312" s="5"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2802,31 +2805,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="8">
+      <c r="A316" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="7">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="7"/>
-      <c r="B317" s="8"/>
+      <c r="A317" s="6"/>
+      <c r="B317" s="7"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="3"/>
-      <c r="C319" s="3"/>
+      <c r="A319" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="8"/>
+      <c r="C319" s="8"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="4" t="s">
+      <c r="A320" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="5"/>
-      <c r="C320" s="6"/>
+      <c r="B320" s="4"/>
+      <c r="C320" s="5"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2859,17 +2862,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="8">
+      <c r="A324" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="7">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="7"/>
-      <c r="B325" s="8"/>
+      <c r="A325" s="6"/>
+      <c r="B325" s="7"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2880,18 +2883,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="3"/>
-      <c r="C328" s="3"/>
+      <c r="A328" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="8"/>
+      <c r="C328" s="8"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="4" t="s">
+      <c r="A329" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="5"/>
-      <c r="C329" s="6"/>
+      <c r="B329" s="4"/>
+      <c r="C329" s="5"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2924,31 +2927,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="8">
+      <c r="A333" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="7">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="7"/>
-      <c r="B334" s="8"/>
+      <c r="A334" s="6"/>
+      <c r="B334" s="7"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="3"/>
-      <c r="C336" s="3"/>
+      <c r="A336" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="8"/>
+      <c r="C336" s="8"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="5"/>
-      <c r="C337" s="6"/>
+      <c r="B337" s="4"/>
+      <c r="C337" s="5"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2981,31 +2984,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="8">
+      <c r="A341" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="7">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="7"/>
-      <c r="B342" s="8"/>
+      <c r="A342" s="6"/>
+      <c r="B342" s="7"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="3"/>
-      <c r="C344" s="3"/>
+      <c r="A344" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="8"/>
+      <c r="C344" s="8"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="5"/>
-      <c r="C345" s="6"/>
+      <c r="B345" s="4"/>
+      <c r="C345" s="5"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3038,31 +3041,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="8">
+      <c r="A349" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="7">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="7"/>
-      <c r="B350" s="8"/>
+      <c r="A350" s="6"/>
+      <c r="B350" s="7"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="3"/>
-      <c r="C352" s="3"/>
+      <c r="A352" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="8"/>
+      <c r="C352" s="8"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="4" t="s">
+      <c r="A353" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="5"/>
-      <c r="C353" s="6"/>
+      <c r="B353" s="4"/>
+      <c r="C353" s="5"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3095,31 +3098,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="8">
+      <c r="A357" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="7">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="7"/>
-      <c r="B358" s="8"/>
+      <c r="A358" s="6"/>
+      <c r="B358" s="7"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="3"/>
-      <c r="C360" s="3"/>
+      <c r="A360" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="8"/>
+      <c r="C360" s="8"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="5"/>
-      <c r="C361" s="6"/>
+      <c r="B361" s="4"/>
+      <c r="C361" s="5"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3152,31 +3155,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="8">
+      <c r="A365" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="7">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="7"/>
-      <c r="B366" s="8"/>
+      <c r="A366" s="6"/>
+      <c r="B366" s="7"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="3"/>
-      <c r="C368" s="3"/>
+      <c r="A368" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="8"/>
+      <c r="C368" s="8"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="4" t="s">
+      <c r="A369" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="5"/>
-      <c r="C369" s="6"/>
+      <c r="B369" s="4"/>
+      <c r="C369" s="5"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3209,31 +3212,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="8">
+      <c r="A373" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="7">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="7"/>
-      <c r="B374" s="8"/>
+      <c r="A374" s="6"/>
+      <c r="B374" s="7"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="3"/>
-      <c r="C376" s="3"/>
+      <c r="A376" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="8"/>
+      <c r="C376" s="8"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="4" t="s">
+      <c r="A377" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="5"/>
-      <c r="C377" s="6"/>
+      <c r="B377" s="4"/>
+      <c r="C377" s="5"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3266,17 +3269,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="8">
+      <c r="A381" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="7">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="7"/>
-      <c r="B382" s="8"/>
+      <c r="A382" s="6"/>
+      <c r="B382" s="7"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3287,18 +3290,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="3"/>
-      <c r="C385" s="3"/>
+      <c r="A385" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="8"/>
+      <c r="C385" s="8"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="5"/>
-      <c r="C386" s="6"/>
+      <c r="B386" s="4"/>
+      <c r="C386" s="5"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3331,31 +3334,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="8">
+      <c r="A390" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="7">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="7"/>
-      <c r="B391" s="8"/>
+      <c r="A391" s="6"/>
+      <c r="B391" s="7"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="3"/>
-      <c r="C393" s="3"/>
+      <c r="A393" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="8"/>
+      <c r="C393" s="8"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="4" t="s">
+      <c r="A394" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="5"/>
-      <c r="C394" s="6"/>
+      <c r="B394" s="4"/>
+      <c r="C394" s="5"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3388,31 +3391,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="8">
+      <c r="A398" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="7">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="7"/>
-      <c r="B399" s="8"/>
+      <c r="A399" s="6"/>
+      <c r="B399" s="7"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="3"/>
-      <c r="C401" s="3"/>
+      <c r="A401" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="8"/>
+      <c r="C401" s="8"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="4" t="s">
+      <c r="A402" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="5"/>
-      <c r="C402" s="6"/>
+      <c r="B402" s="4"/>
+      <c r="C402" s="5"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3445,31 +3448,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="8">
+      <c r="A406" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="7">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="7"/>
-      <c r="B407" s="8"/>
+      <c r="A407" s="6"/>
+      <c r="B407" s="7"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="3"/>
-      <c r="C409" s="3"/>
+      <c r="A409" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="8"/>
+      <c r="C409" s="8"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="4" t="s">
+      <c r="A410" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="5"/>
-      <c r="C410" s="6"/>
+      <c r="B410" s="4"/>
+      <c r="C410" s="5"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3502,31 +3505,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="8">
+      <c r="A414" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="7">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="7"/>
-      <c r="B415" s="8"/>
+      <c r="A415" s="6"/>
+      <c r="B415" s="7"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="3"/>
-      <c r="C417" s="3"/>
+      <c r="A417" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="8"/>
+      <c r="C417" s="8"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="4" t="s">
+      <c r="A418" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="5"/>
-      <c r="C418" s="6"/>
+      <c r="B418" s="4"/>
+      <c r="C418" s="5"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3559,31 +3562,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="8">
+      <c r="A422" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="7">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="7"/>
-      <c r="B423" s="8"/>
+      <c r="A423" s="6"/>
+      <c r="B423" s="7"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="3"/>
-      <c r="C425" s="3"/>
+      <c r="A425" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="8"/>
+      <c r="C425" s="8"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="4" t="s">
+      <c r="A426" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="5"/>
-      <c r="C426" s="6"/>
+      <c r="B426" s="4"/>
+      <c r="C426" s="5"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3616,31 +3619,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="8">
+      <c r="A430" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="7">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="7"/>
-      <c r="B431" s="8"/>
+      <c r="A431" s="6"/>
+      <c r="B431" s="7"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
+      <c r="A433" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="8"/>
+      <c r="C433" s="8"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="4" t="s">
+      <c r="A434" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="5"/>
-      <c r="C434" s="6"/>
+      <c r="B434" s="4"/>
+      <c r="C434" s="5"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3673,17 +3676,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="8">
+      <c r="A438" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="7">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="7"/>
-      <c r="B439" s="8"/>
+      <c r="A439" s="6"/>
+      <c r="B439" s="7"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3694,18 +3697,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
+      <c r="A442" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="8"/>
+      <c r="C442" s="8"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="4" t="s">
+      <c r="A443" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="5"/>
-      <c r="C443" s="6"/>
+      <c r="B443" s="4"/>
+      <c r="C443" s="5"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3738,31 +3741,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="8">
+      <c r="A447" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="7">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="7"/>
-      <c r="B448" s="8"/>
+      <c r="A448" s="6"/>
+      <c r="B448" s="7"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="3"/>
-      <c r="C450" s="3"/>
+      <c r="A450" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="8"/>
+      <c r="C450" s="8"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="5"/>
-      <c r="C451" s="6"/>
+      <c r="B451" s="4"/>
+      <c r="C451" s="5"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3795,31 +3798,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="8">
+      <c r="A455" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="7">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="7"/>
-      <c r="B456" s="8"/>
+      <c r="A456" s="6"/>
+      <c r="B456" s="7"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
+      <c r="A458" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="8"/>
+      <c r="C458" s="8"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="4" t="s">
+      <c r="A459" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="5"/>
-      <c r="C459" s="6"/>
+      <c r="B459" s="4"/>
+      <c r="C459" s="5"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3852,31 +3855,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="8">
+      <c r="A463" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="7">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="7"/>
-      <c r="B464" s="8"/>
+      <c r="A464" s="6"/>
+      <c r="B464" s="7"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="3"/>
-      <c r="C466" s="3"/>
+      <c r="A466" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="8"/>
+      <c r="C466" s="8"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="4" t="s">
+      <c r="A467" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="5"/>
-      <c r="C467" s="6"/>
+      <c r="B467" s="4"/>
+      <c r="C467" s="5"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3909,31 +3912,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="8">
+      <c r="A471" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="7">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="7"/>
-      <c r="B472" s="8"/>
+      <c r="A472" s="6"/>
+      <c r="B472" s="7"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="3"/>
-      <c r="C474" s="3"/>
+      <c r="A474" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="8"/>
+      <c r="C474" s="8"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="4" t="s">
+      <c r="A475" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="5"/>
-      <c r="C475" s="6"/>
+      <c r="B475" s="4"/>
+      <c r="C475" s="5"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3966,31 +3969,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="8">
+      <c r="A479" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="7">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="7"/>
-      <c r="B480" s="8"/>
+      <c r="A480" s="6"/>
+      <c r="B480" s="7"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="3"/>
-      <c r="C482" s="3"/>
+      <c r="A482" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="8"/>
+      <c r="C482" s="8"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="4" t="s">
+      <c r="A483" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="5"/>
-      <c r="C483" s="6"/>
+      <c r="B483" s="4"/>
+      <c r="C483" s="5"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4023,31 +4026,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="8">
+      <c r="A487" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="7">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="7"/>
-      <c r="B488" s="8"/>
+      <c r="A488" s="6"/>
+      <c r="B488" s="7"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="3"/>
-      <c r="C490" s="3"/>
+      <c r="A490" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="8"/>
+      <c r="C490" s="8"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="4" t="s">
+      <c r="A491" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="5"/>
-      <c r="C491" s="6"/>
+      <c r="B491" s="4"/>
+      <c r="C491" s="5"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4080,17 +4083,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="8">
+      <c r="A495" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="7">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="7"/>
-      <c r="B496" s="8"/>
+      <c r="A496" s="6"/>
+      <c r="B496" s="7"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4101,18 +4104,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="3"/>
-      <c r="C499" s="3"/>
+      <c r="A499" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="8"/>
+      <c r="C499" s="8"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="4" t="s">
+      <c r="A500" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="5"/>
-      <c r="C500" s="6"/>
+      <c r="B500" s="4"/>
+      <c r="C500" s="5"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4145,31 +4148,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="8">
+      <c r="A504" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="7">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="7"/>
-      <c r="B505" s="8"/>
+      <c r="A505" s="6"/>
+      <c r="B505" s="7"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="3"/>
-      <c r="C507" s="3"/>
+      <c r="A507" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="8"/>
+      <c r="C507" s="8"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="4" t="s">
+      <c r="A508" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="5"/>
-      <c r="C508" s="6"/>
+      <c r="B508" s="4"/>
+      <c r="C508" s="5"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4202,31 +4205,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="8">
+      <c r="A512" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="7">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="7"/>
-      <c r="B513" s="8"/>
+      <c r="A513" s="6"/>
+      <c r="B513" s="7"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="3"/>
-      <c r="C515" s="3"/>
+      <c r="A515" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="8"/>
+      <c r="C515" s="8"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="4" t="s">
+      <c r="A516" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="5"/>
-      <c r="C516" s="6"/>
+      <c r="B516" s="4"/>
+      <c r="C516" s="5"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4259,31 +4262,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="8">
+      <c r="A520" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="7">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="7"/>
-      <c r="B521" s="8"/>
+      <c r="A521" s="6"/>
+      <c r="B521" s="7"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="3"/>
-      <c r="C523" s="3"/>
+      <c r="A523" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="8"/>
+      <c r="C523" s="8"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="4" t="s">
+      <c r="A524" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="5"/>
-      <c r="C524" s="6"/>
+      <c r="B524" s="4"/>
+      <c r="C524" s="5"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4316,31 +4319,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="8">
+      <c r="A528" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="7">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="7"/>
-      <c r="B529" s="8"/>
+      <c r="A529" s="6"/>
+      <c r="B529" s="7"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="3"/>
-      <c r="C531" s="3"/>
+      <c r="A531" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="8"/>
+      <c r="C531" s="8"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="4" t="s">
+      <c r="A532" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="5"/>
-      <c r="C532" s="6"/>
+      <c r="B532" s="4"/>
+      <c r="C532" s="5"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4373,31 +4376,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="8">
+      <c r="A536" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="7">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="7"/>
-      <c r="B537" s="8"/>
+      <c r="A537" s="6"/>
+      <c r="B537" s="7"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="3"/>
-      <c r="C539" s="3"/>
+      <c r="A539" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="8"/>
+      <c r="C539" s="8"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="4" t="s">
+      <c r="A540" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="5"/>
-      <c r="C540" s="6"/>
+      <c r="B540" s="4"/>
+      <c r="C540" s="5"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4430,31 +4433,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="8">
+      <c r="A544" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="7">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="7"/>
-      <c r="B545" s="8"/>
+      <c r="A545" s="6"/>
+      <c r="B545" s="7"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="3"/>
-      <c r="C547" s="3"/>
+      <c r="A547" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="8"/>
+      <c r="C547" s="8"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="4" t="s">
+      <c r="A548" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="5"/>
-      <c r="C548" s="6"/>
+      <c r="B548" s="4"/>
+      <c r="C548" s="5"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4487,17 +4490,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="8">
+      <c r="A552" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="7">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="7"/>
-      <c r="B553" s="8"/>
+      <c r="A553" s="6"/>
+      <c r="B553" s="7"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4508,18 +4511,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="3"/>
-      <c r="C556" s="3"/>
+      <c r="A556" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="8"/>
+      <c r="C556" s="8"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="4" t="s">
+      <c r="A557" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="5"/>
-      <c r="C557" s="6"/>
+      <c r="B557" s="4"/>
+      <c r="C557" s="5"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4552,31 +4555,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="8">
+      <c r="A561" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="7">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="7"/>
-      <c r="B562" s="8"/>
+      <c r="A562" s="6"/>
+      <c r="B562" s="7"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="3"/>
-      <c r="C564" s="3"/>
+      <c r="A564" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="8"/>
+      <c r="C564" s="8"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="4" t="s">
+      <c r="A565" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="5"/>
-      <c r="C565" s="6"/>
+      <c r="B565" s="4"/>
+      <c r="C565" s="5"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4609,31 +4612,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="8">
+      <c r="A569" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="7">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="7"/>
-      <c r="B570" s="8"/>
+      <c r="A570" s="6"/>
+      <c r="B570" s="7"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="3"/>
-      <c r="C572" s="3"/>
+      <c r="A572" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="8"/>
+      <c r="C572" s="8"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="4" t="s">
+      <c r="A573" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="5"/>
-      <c r="C573" s="6"/>
+      <c r="B573" s="4"/>
+      <c r="C573" s="5"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4666,31 +4669,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="8">
+      <c r="A577" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="7">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="7"/>
-      <c r="B578" s="8"/>
+      <c r="A578" s="6"/>
+      <c r="B578" s="7"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="3"/>
-      <c r="C580" s="3"/>
+      <c r="A580" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="8"/>
+      <c r="C580" s="8"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="4" t="s">
+      <c r="A581" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="5"/>
-      <c r="C581" s="6"/>
+      <c r="B581" s="4"/>
+      <c r="C581" s="5"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4723,17 +4726,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="8">
+      <c r="A585" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="7">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="7"/>
-      <c r="B586" s="8"/>
+      <c r="A586" s="6"/>
+      <c r="B586" s="7"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4744,18 +4747,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="3"/>
-      <c r="C589" s="3"/>
+      <c r="A589" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="8"/>
+      <c r="C589" s="8"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="4" t="s">
+      <c r="A590" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="5"/>
-      <c r="C590" s="6"/>
+      <c r="B590" s="4"/>
+      <c r="C590" s="5"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4788,31 +4791,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="8">
+      <c r="A594" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="7">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="7"/>
-      <c r="B595" s="8"/>
+      <c r="A595" s="6"/>
+      <c r="B595" s="7"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="3"/>
-      <c r="C597" s="3"/>
+      <c r="A597" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="8"/>
+      <c r="C597" s="8"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="4" t="s">
+      <c r="A598" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="5"/>
-      <c r="C598" s="6"/>
+      <c r="B598" s="4"/>
+      <c r="C598" s="5"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4845,31 +4848,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="8">
+      <c r="A602" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="7">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="7"/>
-      <c r="B603" s="8"/>
+      <c r="A603" s="6"/>
+      <c r="B603" s="7"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="3"/>
-      <c r="C605" s="3"/>
+      <c r="A605" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="8"/>
+      <c r="C605" s="8"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="4" t="s">
+      <c r="A606" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="5"/>
-      <c r="C606" s="6"/>
+      <c r="B606" s="4"/>
+      <c r="C606" s="5"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4902,31 +4905,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="8">
+      <c r="A610" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="7">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="7"/>
-      <c r="B611" s="8"/>
+      <c r="A611" s="6"/>
+      <c r="B611" s="7"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="3"/>
-      <c r="C613" s="3"/>
+      <c r="A613" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="8"/>
+      <c r="C613" s="8"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="4" t="s">
+      <c r="A614" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="5"/>
-      <c r="C614" s="6"/>
+      <c r="B614" s="4"/>
+      <c r="C614" s="5"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4959,31 +4962,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="8">
+      <c r="A618" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="7">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="7"/>
-      <c r="B619" s="8"/>
+      <c r="A619" s="6"/>
+      <c r="B619" s="7"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="3"/>
-      <c r="C621" s="3"/>
+      <c r="A621" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="8"/>
+      <c r="C621" s="8"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="4" t="s">
+      <c r="A622" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="5"/>
-      <c r="C622" s="6"/>
+      <c r="B622" s="4"/>
+      <c r="C622" s="5"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5016,31 +5019,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="8">
+      <c r="A626" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="7">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="7"/>
-      <c r="B627" s="8"/>
+      <c r="A627" s="6"/>
+      <c r="B627" s="7"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="3"/>
-      <c r="C629" s="3"/>
+      <c r="A629" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="8"/>
+      <c r="C629" s="8"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="4" t="s">
+      <c r="A630" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="5"/>
-      <c r="C630" s="6"/>
+      <c r="B630" s="4"/>
+      <c r="C630" s="5"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5073,31 +5076,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="8">
+      <c r="A634" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="7">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="7"/>
-      <c r="B635" s="8"/>
+      <c r="A635" s="6"/>
+      <c r="B635" s="7"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="3"/>
-      <c r="C637" s="3"/>
+      <c r="A637" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="8"/>
+      <c r="C637" s="8"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="4" t="s">
+      <c r="A638" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="5"/>
-      <c r="C638" s="6"/>
+      <c r="B638" s="4"/>
+      <c r="C638" s="5"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5130,17 +5133,17 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="8">
+      <c r="A642" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="7">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="7"/>
-      <c r="B643" s="8"/>
+      <c r="A643" s="6"/>
+      <c r="B643" s="7"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
@@ -5151,18 +5154,18 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="3"/>
-      <c r="C646" s="3"/>
+      <c r="A646" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="8"/>
+      <c r="C646" s="8"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="4" t="s">
+      <c r="A647" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="5"/>
-      <c r="C647" s="6"/>
+      <c r="B647" s="4"/>
+      <c r="C647" s="5"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5195,31 +5198,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="8">
+      <c r="A651" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="7">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="7"/>
-      <c r="B652" s="8"/>
+      <c r="A652" s="6"/>
+      <c r="B652" s="7"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="3"/>
-      <c r="C654" s="3"/>
+      <c r="A654" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="8"/>
+      <c r="C654" s="8"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="4" t="s">
+      <c r="A655" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="5"/>
-      <c r="C655" s="6"/>
+      <c r="B655" s="4"/>
+      <c r="C655" s="5"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5252,31 +5255,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="8">
+      <c r="A659" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="7">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="7"/>
-      <c r="B660" s="8"/>
+      <c r="A660" s="6"/>
+      <c r="B660" s="7"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="3"/>
-      <c r="C662" s="3"/>
+      <c r="A662" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="8"/>
+      <c r="C662" s="8"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="4" t="s">
+      <c r="A663" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="5"/>
-      <c r="C663" s="6"/>
+      <c r="B663" s="4"/>
+      <c r="C663" s="5"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5309,31 +5312,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="8">
+      <c r="A667" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="7">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="7"/>
-      <c r="B668" s="8"/>
+      <c r="A668" s="6"/>
+      <c r="B668" s="7"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="3"/>
-      <c r="C670" s="3"/>
+      <c r="A670" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="8"/>
+      <c r="C670" s="8"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="4" t="s">
+      <c r="A671" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="5"/>
-      <c r="C671" s="6"/>
+      <c r="B671" s="4"/>
+      <c r="C671" s="5"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5366,31 +5369,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="8">
+      <c r="A675" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="7">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="7"/>
-      <c r="B676" s="8"/>
+      <c r="A676" s="6"/>
+      <c r="B676" s="7"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="3"/>
-      <c r="C678" s="3"/>
+      <c r="A678" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="8"/>
+      <c r="C678" s="8"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="4" t="s">
+      <c r="A679" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="5"/>
-      <c r="C679" s="6"/>
+      <c r="B679" s="4"/>
+      <c r="C679" s="5"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5423,31 +5426,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="8">
+      <c r="A683" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="7">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="7"/>
-      <c r="B684" s="8"/>
+      <c r="A684" s="6"/>
+      <c r="B684" s="7"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="3"/>
-      <c r="C686" s="3"/>
+      <c r="A686" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="8"/>
+      <c r="C686" s="8"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="4" t="s">
+      <c r="A687" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="5"/>
-      <c r="C687" s="6"/>
+      <c r="B687" s="4"/>
+      <c r="C687" s="5"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5480,31 +5483,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="8">
+      <c r="A691" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="7">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="7"/>
-      <c r="B692" s="8"/>
+      <c r="A692" s="6"/>
+      <c r="B692" s="7"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="3"/>
-      <c r="C694" s="3"/>
+      <c r="A694" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="8"/>
+      <c r="C694" s="8"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="4" t="s">
+      <c r="A695" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="5"/>
-      <c r="C695" s="6"/>
+      <c r="B695" s="4"/>
+      <c r="C695" s="5"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5537,107 +5540,748 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="8">
+      <c r="A699" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="7">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="7"/>
-      <c r="B700" s="8"/>
+      <c r="A700" s="6"/>
+      <c r="B700" s="7"/>
+    </row>
+    <row r="702" spans="1:3">
+      <c r="A702" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B702" s="8"/>
+      <c r="C702" s="8"/>
+    </row>
+    <row r="703" spans="1:3">
+      <c r="A703" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B703" s="4"/>
+      <c r="C703" s="5"/>
+    </row>
+    <row r="704" spans="1:3">
+      <c r="A704" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3">
+      <c r="A705" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B705" s="2">
+        <v>593</v>
+      </c>
+      <c r="C705" s="2">
+        <v>5705</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3">
+      <c r="A706" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B706" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3">
+      <c r="A707" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="7">
+        <f>B705-B706</f>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3">
+      <c r="A708" s="6"/>
+      <c r="B708" s="7"/>
+    </row>
+    <row r="709" spans="1:3">
+      <c r="A709" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B709" s="2">
+        <v>72509</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3">
+      <c r="A711" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="8"/>
+      <c r="C711" s="8"/>
+    </row>
+    <row r="712" spans="1:3">
+      <c r="A712" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B712" s="4"/>
+      <c r="C712" s="5"/>
+    </row>
+    <row r="713" spans="1:3">
+      <c r="A713" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C713" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3">
+      <c r="A714" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B714" s="2">
+        <v>42</v>
+      </c>
+      <c r="C714" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3">
+      <c r="A715" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B715" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3">
+      <c r="A716" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="7">
+        <f>B714-B715</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3">
+      <c r="A717" s="6"/>
+      <c r="B717" s="7"/>
+    </row>
+    <row r="719" spans="1:3">
+      <c r="A719" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="8"/>
+      <c r="C719" s="8"/>
+    </row>
+    <row r="720" spans="1:3">
+      <c r="A720" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B720" s="4"/>
+      <c r="C720" s="5"/>
+    </row>
+    <row r="721" spans="1:3">
+      <c r="A721" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C721" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3">
+      <c r="A722" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B722" s="2">
+        <v>581</v>
+      </c>
+      <c r="C722" s="2">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3">
+      <c r="A723" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B723" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3">
+      <c r="A724" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="7">
+        <f>B722-B723</f>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3">
+      <c r="A725" s="6"/>
+      <c r="B725" s="7"/>
+    </row>
+    <row r="727" spans="1:3">
+      <c r="A727" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="8"/>
+      <c r="C727" s="8"/>
+    </row>
+    <row r="728" spans="1:3">
+      <c r="A728" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B728" s="4"/>
+      <c r="C728" s="5"/>
+    </row>
+    <row r="729" spans="1:3">
+      <c r="A729" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C729" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3">
+      <c r="A730" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B730" s="2">
+        <v>1559</v>
+      </c>
+      <c r="C730" s="2">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3">
+      <c r="A731" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B731" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3">
+      <c r="A732" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="7">
+        <f>B730-B731</f>
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3">
+      <c r="A733" s="6"/>
+      <c r="B733" s="7"/>
+    </row>
+    <row r="735" spans="1:3">
+      <c r="A735" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="8"/>
+      <c r="C735" s="8"/>
+    </row>
+    <row r="736" spans="1:3">
+      <c r="A736" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B736" s="4"/>
+      <c r="C736" s="5"/>
+    </row>
+    <row r="737" spans="1:3">
+      <c r="A737" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C737" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3">
+      <c r="A738" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B738" s="2">
+        <v>303</v>
+      </c>
+      <c r="C738" s="2">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3">
+      <c r="A739" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B739" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3">
+      <c r="A740" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="7">
+        <f>B738-B739</f>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3">
+      <c r="A741" s="6"/>
+      <c r="B741" s="7"/>
+    </row>
+    <row r="743" spans="1:3">
+      <c r="A743" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="8"/>
+      <c r="C743" s="8"/>
+    </row>
+    <row r="744" spans="1:3">
+      <c r="A744" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B744" s="4"/>
+      <c r="C744" s="5"/>
+    </row>
+    <row r="745" spans="1:3">
+      <c r="A745" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B745" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C745" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3">
+      <c r="A746" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B746" s="2">
+        <v>1326</v>
+      </c>
+      <c r="C746" s="2">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3">
+      <c r="A747" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B747" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3">
+      <c r="A748" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="7">
+        <f>B746-B747</f>
+        <v>961</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3">
+      <c r="A749" s="6"/>
+      <c r="B749" s="7"/>
+    </row>
+    <row r="751" spans="1:3">
+      <c r="A751" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="8"/>
+      <c r="C751" s="8"/>
+    </row>
+    <row r="752" spans="1:3">
+      <c r="A752" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B752" s="4"/>
+      <c r="C752" s="5"/>
+    </row>
+    <row r="753" spans="1:3">
+      <c r="A753" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B753" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C753" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3">
+      <c r="A754" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B754" s="2">
+        <v>10</v>
+      </c>
+      <c r="C754" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3">
+      <c r="A755" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B755" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3">
+      <c r="A756" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="7">
+        <f>B754-B755</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3">
+      <c r="A757" s="6"/>
+      <c r="B757" s="7"/>
+    </row>
+    <row r="759" spans="1:3">
+      <c r="A759" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B759" s="8"/>
+      <c r="C759" s="8"/>
+    </row>
+    <row r="760" spans="1:3">
+      <c r="A760" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B760" s="4"/>
+      <c r="C760" s="5"/>
+    </row>
+    <row r="761" spans="1:3">
+      <c r="A761" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B761" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C761" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3">
+      <c r="A762" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B762" s="2">
+        <v>840</v>
+      </c>
+      <c r="C762" s="2">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3">
+      <c r="A763" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B763" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3">
+      <c r="A764" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764" s="7">
+        <f>B762-B763</f>
+        <v>616</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3">
+      <c r="A765" s="6"/>
+      <c r="B765" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="344">
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A490:C490"/>
-    <mergeCell ref="A491:C491"/>
-    <mergeCell ref="A495:A496"/>
-    <mergeCell ref="B495:B496"/>
-    <mergeCell ref="A499:C499"/>
-    <mergeCell ref="A500:C500"/>
-    <mergeCell ref="A433:C433"/>
-    <mergeCell ref="A434:C434"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A442:C442"/>
-    <mergeCell ref="A443:C443"/>
-    <mergeCell ref="A447:A448"/>
-    <mergeCell ref="B447:B448"/>
-    <mergeCell ref="A450:C450"/>
-    <mergeCell ref="A451:C451"/>
-    <mergeCell ref="A455:A456"/>
-    <mergeCell ref="B455:B456"/>
-    <mergeCell ref="A458:C458"/>
-    <mergeCell ref="A459:C459"/>
-    <mergeCell ref="A463:A464"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
+  <mergeCells count="376">
+    <mergeCell ref="A759:C759"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A764:A765"/>
+    <mergeCell ref="B764:B765"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A702:C702"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A707:A708"/>
+    <mergeCell ref="B707:B708"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A487:A488"/>
+    <mergeCell ref="B487:B488"/>
+    <mergeCell ref="A565:C565"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="B569:B570"/>
+    <mergeCell ref="A572:C572"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A547:C547"/>
+    <mergeCell ref="A548:C548"/>
+    <mergeCell ref="A552:A553"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A557:C557"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="B561:B562"/>
+    <mergeCell ref="A564:C564"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A507:C507"/>
+    <mergeCell ref="A508:C508"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A376:C376"/>
     <mergeCell ref="A377:C377"/>
@@ -5662,239 +6306,94 @@
     <mergeCell ref="A164:C164"/>
     <mergeCell ref="A165:C165"/>
     <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A490:C490"/>
+    <mergeCell ref="A491:C491"/>
+    <mergeCell ref="A495:A496"/>
+    <mergeCell ref="B495:B496"/>
+    <mergeCell ref="A499:C499"/>
+    <mergeCell ref="A500:C500"/>
+    <mergeCell ref="A433:C433"/>
+    <mergeCell ref="A434:C434"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:C442"/>
+    <mergeCell ref="A443:C443"/>
+    <mergeCell ref="A447:A448"/>
+    <mergeCell ref="B447:B448"/>
+    <mergeCell ref="A450:C450"/>
+    <mergeCell ref="A451:C451"/>
+    <mergeCell ref="A455:A456"/>
+    <mergeCell ref="B455:B456"/>
+    <mergeCell ref="A458:C458"/>
+    <mergeCell ref="A459:C459"/>
+    <mergeCell ref="A463:A464"/>
     <mergeCell ref="B463:B464"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A487:A488"/>
-    <mergeCell ref="B487:B488"/>
-    <mergeCell ref="A565:C565"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="B569:B570"/>
-    <mergeCell ref="A572:C572"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A547:C547"/>
-    <mergeCell ref="A548:C548"/>
-    <mergeCell ref="A552:A553"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A557:C557"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="B561:B562"/>
-    <mergeCell ref="A564:C564"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A507:C507"/>
-    <mergeCell ref="A508:C508"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A515:C515"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A313110-35B8-4B14-BB59-E33446C6894C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA7B5EA-0B27-487C-A7DE-7021FDDF04DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="37">
   <si>
     <t>Data</t>
   </si>
@@ -143,6 +143,9 @@
   <si>
     <t>22.10.2026</t>
   </si>
+  <si>
+    <t>23.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -245,6 +248,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -258,9 +264,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -538,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C765"/>
+  <dimension ref="A1:C830"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -547,18 +550,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -591,17 +594,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -612,18 +615,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -656,31 +659,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="7">
+      <c r="A15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -713,31 +716,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="7">
+      <c r="A23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="8">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -770,31 +773,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="7">
+      <c r="A31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="8">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
+      <c r="A34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -827,31 +830,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="7">
+      <c r="A39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
+      <c r="A42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -884,31 +887,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="7">
+      <c r="A47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="8">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="8"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
+      <c r="A50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -941,31 +944,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="7">
+      <c r="A55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="8">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
+      <c r="A58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -998,17 +1001,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="7">
+      <c r="A63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="8">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="6"/>
-      <c r="B64" s="7"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="8"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1019,18 +1022,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
+      <c r="A67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1063,31 +1066,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="7">
+      <c r="A72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="8">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="7"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="8"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
+      <c r="A75" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="6"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1120,31 +1123,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="7">
+      <c r="A80" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="8">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="8"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
+      <c r="A83" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="6"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1177,31 +1180,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="7">
+      <c r="A88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="8">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="6"/>
-      <c r="B89" s="7"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="8"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
+      <c r="A91" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="6"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1234,31 +1237,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="7">
+      <c r="A96" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="8">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="7"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="8"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
+      <c r="A99" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="4"/>
-      <c r="C100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="6"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1291,31 +1294,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="7">
+      <c r="A104" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="8">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="7"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="8"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
+      <c r="A107" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="4"/>
-      <c r="C108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="6"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1348,31 +1351,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="7">
+      <c r="A112" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="8">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="7"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="8"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
+      <c r="A115" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="4"/>
-      <c r="C116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="6"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1405,31 +1408,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="7">
+      <c r="A120" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="8">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="6"/>
-      <c r="B121" s="7"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="8"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
+      <c r="A123" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="4"/>
-      <c r="C124" s="5"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="6"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1462,17 +1465,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="7">
+      <c r="A128" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="8">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="6"/>
-      <c r="B129" s="7"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="8"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1483,18 +1486,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
+      <c r="A132" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="3" t="s">
+      <c r="A133" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="4"/>
-      <c r="C133" s="5"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="6"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1527,31 +1530,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="7">
+      <c r="A137" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="8">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="6"/>
-      <c r="B138" s="7"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="8"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
+      <c r="A140" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="3" t="s">
+      <c r="A141" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="4"/>
-      <c r="C141" s="5"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="6"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1584,31 +1587,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="7">
+      <c r="A145" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="8">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="6"/>
-      <c r="B146" s="7"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="8"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="8"/>
-      <c r="C148" s="8"/>
+      <c r="A148" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="3" t="s">
+      <c r="A149" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="4"/>
-      <c r="C149" s="5"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="6"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1641,31 +1644,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="7">
+      <c r="A153" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="8">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="6"/>
-      <c r="B154" s="7"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="8"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
+      <c r="A156" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="3" t="s">
+      <c r="A157" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="4"/>
-      <c r="C157" s="5"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="6"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1698,31 +1701,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="7">
+      <c r="A161" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="8">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="6"/>
-      <c r="B162" s="7"/>
+      <c r="A162" s="7"/>
+      <c r="B162" s="8"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
+      <c r="A164" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="3" t="s">
+      <c r="A165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="4"/>
-      <c r="C165" s="5"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="6"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1755,31 +1758,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="7">
+      <c r="A169" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="8">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="6"/>
-      <c r="B170" s="7"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="8"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="8"/>
-      <c r="C172" s="8"/>
+      <c r="A172" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="3" t="s">
+      <c r="A173" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="4"/>
-      <c r="C173" s="5"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="6"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1812,31 +1815,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="7">
+      <c r="A177" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="8">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="6"/>
-      <c r="B178" s="7"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="8"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
+      <c r="A180" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="3" t="s">
+      <c r="A181" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="4"/>
-      <c r="C181" s="5"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="6"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1869,17 +1872,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="7">
+      <c r="A185" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="8">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="6"/>
-      <c r="B186" s="7"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="8"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1890,18 +1893,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
+      <c r="A189" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="3" t="s">
+      <c r="A190" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="4"/>
-      <c r="C190" s="5"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="6"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1934,31 +1937,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="7">
+      <c r="A194" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="8">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="6"/>
-      <c r="B195" s="7"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="8"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
+      <c r="A197" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="3" t="s">
+      <c r="A198" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="4"/>
-      <c r="C198" s="5"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="6"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -1991,31 +1994,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="7">
+      <c r="A202" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="8">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="6"/>
-      <c r="B203" s="7"/>
+      <c r="A203" s="7"/>
+      <c r="B203" s="8"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="8"/>
-      <c r="C205" s="8"/>
+      <c r="A205" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="3" t="s">
+      <c r="A206" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="4"/>
-      <c r="C206" s="5"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="6"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2048,31 +2051,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="7">
+      <c r="A210" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="8">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="6"/>
-      <c r="B211" s="7"/>
+      <c r="A211" s="7"/>
+      <c r="B211" s="8"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
+      <c r="A213" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="3" t="s">
+      <c r="A214" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="4"/>
-      <c r="C214" s="5"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="6"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2105,31 +2108,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="7">
+      <c r="A218" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="8">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="6"/>
-      <c r="B219" s="7"/>
+      <c r="A219" s="7"/>
+      <c r="B219" s="8"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
+      <c r="A221" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="3" t="s">
+      <c r="A222" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="4"/>
-      <c r="C222" s="5"/>
+      <c r="B222" s="5"/>
+      <c r="C222" s="6"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2162,31 +2165,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="7">
+      <c r="A226" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="8">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="6"/>
-      <c r="B227" s="7"/>
+      <c r="A227" s="7"/>
+      <c r="B227" s="8"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
+      <c r="A229" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="3" t="s">
+      <c r="A230" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="4"/>
-      <c r="C230" s="5"/>
+      <c r="B230" s="5"/>
+      <c r="C230" s="6"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2219,31 +2222,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="7">
+      <c r="A234" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="8">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="6"/>
-      <c r="B235" s="7"/>
+      <c r="A235" s="7"/>
+      <c r="B235" s="8"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="8"/>
-      <c r="C237" s="8"/>
+      <c r="A237" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="3" t="s">
+      <c r="A238" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="4"/>
-      <c r="C238" s="5"/>
+      <c r="B238" s="5"/>
+      <c r="C238" s="6"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2276,17 +2279,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="7">
+      <c r="A242" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="8">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="6"/>
-      <c r="B243" s="7"/>
+      <c r="A243" s="7"/>
+      <c r="B243" s="8"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2297,18 +2300,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="8"/>
-      <c r="C246" s="8"/>
+      <c r="A246" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="3" t="s">
+      <c r="A247" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="4"/>
-      <c r="C247" s="5"/>
+      <c r="B247" s="5"/>
+      <c r="C247" s="6"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2341,31 +2344,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="7">
+      <c r="A251" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="8">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="6"/>
-      <c r="B252" s="7"/>
+      <c r="A252" s="7"/>
+      <c r="B252" s="8"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="8"/>
-      <c r="C254" s="8"/>
+      <c r="A254" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="3" t="s">
+      <c r="A255" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="4"/>
-      <c r="C255" s="5"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="6"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2398,31 +2401,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="7">
+      <c r="A259" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="8">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="6"/>
-      <c r="B260" s="7"/>
+      <c r="A260" s="7"/>
+      <c r="B260" s="8"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="8"/>
-      <c r="C262" s="8"/>
+      <c r="A262" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="3" t="s">
+      <c r="A263" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="4"/>
-      <c r="C263" s="5"/>
+      <c r="B263" s="5"/>
+      <c r="C263" s="6"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2455,17 +2458,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="7">
+      <c r="A267" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="8">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="6"/>
-      <c r="B268" s="7"/>
+      <c r="A268" s="7"/>
+      <c r="B268" s="8"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2476,18 +2479,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="8"/>
-      <c r="C271" s="8"/>
+      <c r="A271" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="3" t="s">
+      <c r="A272" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="4"/>
-      <c r="C272" s="5"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="6"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2520,31 +2523,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="7">
+      <c r="A276" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="8">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="6"/>
-      <c r="B277" s="7"/>
+      <c r="A277" s="7"/>
+      <c r="B277" s="8"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
+      <c r="A279" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="3" t="s">
+      <c r="A280" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="4"/>
-      <c r="C280" s="5"/>
+      <c r="B280" s="5"/>
+      <c r="C280" s="6"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2577,31 +2580,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="7">
+      <c r="A284" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="8">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="6"/>
-      <c r="B285" s="7"/>
+      <c r="A285" s="7"/>
+      <c r="B285" s="8"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="8"/>
-      <c r="C287" s="8"/>
+      <c r="A287" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="3"/>
+      <c r="C287" s="3"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="3" t="s">
+      <c r="A288" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="4"/>
-      <c r="C288" s="5"/>
+      <c r="B288" s="5"/>
+      <c r="C288" s="6"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2634,31 +2637,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="7">
+      <c r="A292" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="8">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="6"/>
-      <c r="B293" s="7"/>
+      <c r="A293" s="7"/>
+      <c r="B293" s="8"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="8"/>
-      <c r="C295" s="8"/>
+      <c r="A295" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="3" t="s">
+      <c r="A296" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="4"/>
-      <c r="C296" s="5"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="6"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2691,31 +2694,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="7">
+      <c r="A300" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="8">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="6"/>
-      <c r="B301" s="7"/>
+      <c r="A301" s="7"/>
+      <c r="B301" s="8"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="8"/>
-      <c r="C303" s="8"/>
+      <c r="A303" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="3" t="s">
+      <c r="A304" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="4"/>
-      <c r="C304" s="5"/>
+      <c r="B304" s="5"/>
+      <c r="C304" s="6"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2748,31 +2751,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="7">
+      <c r="A308" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="8">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="6"/>
-      <c r="B309" s="7"/>
+      <c r="A309" s="7"/>
+      <c r="B309" s="8"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="8"/>
-      <c r="C311" s="8"/>
+      <c r="A311" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="3"/>
+      <c r="C311" s="3"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="3" t="s">
+      <c r="A312" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="4"/>
-      <c r="C312" s="5"/>
+      <c r="B312" s="5"/>
+      <c r="C312" s="6"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2805,31 +2808,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="7">
+      <c r="A316" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="8">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="6"/>
-      <c r="B317" s="7"/>
+      <c r="A317" s="7"/>
+      <c r="B317" s="8"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="8"/>
-      <c r="C319" s="8"/>
+      <c r="A319" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="3"/>
+      <c r="C319" s="3"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="3" t="s">
+      <c r="A320" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="4"/>
-      <c r="C320" s="5"/>
+      <c r="B320" s="5"/>
+      <c r="C320" s="6"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2862,17 +2865,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="7">
+      <c r="A324" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="8">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="6"/>
-      <c r="B325" s="7"/>
+      <c r="A325" s="7"/>
+      <c r="B325" s="8"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2883,18 +2886,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="8"/>
-      <c r="C328" s="8"/>
+      <c r="A328" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="3" t="s">
+      <c r="A329" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="4"/>
-      <c r="C329" s="5"/>
+      <c r="B329" s="5"/>
+      <c r="C329" s="6"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2927,31 +2930,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="7">
+      <c r="A333" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="8">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="6"/>
-      <c r="B334" s="7"/>
+      <c r="A334" s="7"/>
+      <c r="B334" s="8"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="8"/>
-      <c r="C336" s="8"/>
+      <c r="A336" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="3"/>
+      <c r="C336" s="3"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="3" t="s">
+      <c r="A337" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="4"/>
-      <c r="C337" s="5"/>
+      <c r="B337" s="5"/>
+      <c r="C337" s="6"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2984,31 +2987,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="7">
+      <c r="A341" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="8">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="6"/>
-      <c r="B342" s="7"/>
+      <c r="A342" s="7"/>
+      <c r="B342" s="8"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="8"/>
-      <c r="C344" s="8"/>
+      <c r="A344" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="3"/>
+      <c r="C344" s="3"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="3" t="s">
+      <c r="A345" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="4"/>
-      <c r="C345" s="5"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="6"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3041,31 +3044,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="7">
+      <c r="A349" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="8">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="6"/>
-      <c r="B350" s="7"/>
+      <c r="A350" s="7"/>
+      <c r="B350" s="8"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="8"/>
-      <c r="C352" s="8"/>
+      <c r="A352" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="3"/>
+      <c r="C352" s="3"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="3" t="s">
+      <c r="A353" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="4"/>
-      <c r="C353" s="5"/>
+      <c r="B353" s="5"/>
+      <c r="C353" s="6"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3098,31 +3101,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="7">
+      <c r="A357" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="8">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="6"/>
-      <c r="B358" s="7"/>
+      <c r="A358" s="7"/>
+      <c r="B358" s="8"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="8"/>
-      <c r="C360" s="8"/>
+      <c r="A360" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="3"/>
+      <c r="C360" s="3"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="3" t="s">
+      <c r="A361" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="4"/>
-      <c r="C361" s="5"/>
+      <c r="B361" s="5"/>
+      <c r="C361" s="6"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3155,31 +3158,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="7">
+      <c r="A365" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="8">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="6"/>
-      <c r="B366" s="7"/>
+      <c r="A366" s="7"/>
+      <c r="B366" s="8"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="8"/>
-      <c r="C368" s="8"/>
+      <c r="A368" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="3"/>
+      <c r="C368" s="3"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="3" t="s">
+      <c r="A369" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="4"/>
-      <c r="C369" s="5"/>
+      <c r="B369" s="5"/>
+      <c r="C369" s="6"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3212,31 +3215,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="7">
+      <c r="A373" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="8">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="6"/>
-      <c r="B374" s="7"/>
+      <c r="A374" s="7"/>
+      <c r="B374" s="8"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="8"/>
-      <c r="C376" s="8"/>
+      <c r="A376" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="3"/>
+      <c r="C376" s="3"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="3" t="s">
+      <c r="A377" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="4"/>
-      <c r="C377" s="5"/>
+      <c r="B377" s="5"/>
+      <c r="C377" s="6"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3269,17 +3272,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="7">
+      <c r="A381" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="8">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="6"/>
-      <c r="B382" s="7"/>
+      <c r="A382" s="7"/>
+      <c r="B382" s="8"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3290,18 +3293,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="8"/>
-      <c r="C385" s="8"/>
+      <c r="A385" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="3"/>
+      <c r="C385" s="3"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="3" t="s">
+      <c r="A386" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="4"/>
-      <c r="C386" s="5"/>
+      <c r="B386" s="5"/>
+      <c r="C386" s="6"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3334,31 +3337,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="7">
+      <c r="A390" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="8">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="6"/>
-      <c r="B391" s="7"/>
+      <c r="A391" s="7"/>
+      <c r="B391" s="8"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="8"/>
-      <c r="C393" s="8"/>
+      <c r="A393" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="3"/>
+      <c r="C393" s="3"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="3" t="s">
+      <c r="A394" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="4"/>
-      <c r="C394" s="5"/>
+      <c r="B394" s="5"/>
+      <c r="C394" s="6"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3391,31 +3394,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="7">
+      <c r="A398" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="8">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="6"/>
-      <c r="B399" s="7"/>
+      <c r="A399" s="7"/>
+      <c r="B399" s="8"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="8"/>
-      <c r="C401" s="8"/>
+      <c r="A401" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="3"/>
+      <c r="C401" s="3"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="3" t="s">
+      <c r="A402" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="4"/>
-      <c r="C402" s="5"/>
+      <c r="B402" s="5"/>
+      <c r="C402" s="6"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3448,31 +3451,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="7">
+      <c r="A406" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="8">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="6"/>
-      <c r="B407" s="7"/>
+      <c r="A407" s="7"/>
+      <c r="B407" s="8"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="8"/>
-      <c r="C409" s="8"/>
+      <c r="A409" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="3"/>
+      <c r="C409" s="3"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="3" t="s">
+      <c r="A410" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="4"/>
-      <c r="C410" s="5"/>
+      <c r="B410" s="5"/>
+      <c r="C410" s="6"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3505,31 +3508,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="7">
+      <c r="A414" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="8">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="6"/>
-      <c r="B415" s="7"/>
+      <c r="A415" s="7"/>
+      <c r="B415" s="8"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="8"/>
-      <c r="C417" s="8"/>
+      <c r="A417" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="3"/>
+      <c r="C417" s="3"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="3" t="s">
+      <c r="A418" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="4"/>
-      <c r="C418" s="5"/>
+      <c r="B418" s="5"/>
+      <c r="C418" s="6"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3562,31 +3565,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="7">
+      <c r="A422" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="8">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="6"/>
-      <c r="B423" s="7"/>
+      <c r="A423" s="7"/>
+      <c r="B423" s="8"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="8"/>
-      <c r="C425" s="8"/>
+      <c r="A425" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="3" t="s">
+      <c r="A426" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="4"/>
-      <c r="C426" s="5"/>
+      <c r="B426" s="5"/>
+      <c r="C426" s="6"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3619,31 +3622,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="7">
+      <c r="A430" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="8">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="6"/>
-      <c r="B431" s="7"/>
+      <c r="A431" s="7"/>
+      <c r="B431" s="8"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="8"/>
-      <c r="C433" s="8"/>
+      <c r="A433" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="3" t="s">
+      <c r="A434" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="4"/>
-      <c r="C434" s="5"/>
+      <c r="B434" s="5"/>
+      <c r="C434" s="6"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3676,17 +3679,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="7">
+      <c r="A438" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="8">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="6"/>
-      <c r="B439" s="7"/>
+      <c r="A439" s="7"/>
+      <c r="B439" s="8"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3697,18 +3700,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="8"/>
-      <c r="C442" s="8"/>
+      <c r="A442" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="3" t="s">
+      <c r="A443" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="4"/>
-      <c r="C443" s="5"/>
+      <c r="B443" s="5"/>
+      <c r="C443" s="6"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3741,31 +3744,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="7">
+      <c r="A447" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="8">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="6"/>
-      <c r="B448" s="7"/>
+      <c r="A448" s="7"/>
+      <c r="B448" s="8"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="8"/>
-      <c r="C450" s="8"/>
+      <c r="A450" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="3"/>
+      <c r="C450" s="3"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="3" t="s">
+      <c r="A451" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="4"/>
-      <c r="C451" s="5"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="6"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3798,31 +3801,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="7">
+      <c r="A455" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="8">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="6"/>
-      <c r="B456" s="7"/>
+      <c r="A456" s="7"/>
+      <c r="B456" s="8"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="8"/>
-      <c r="C458" s="8"/>
+      <c r="A458" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="3" t="s">
+      <c r="A459" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="4"/>
-      <c r="C459" s="5"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="6"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3855,31 +3858,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="7">
+      <c r="A463" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="8">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="6"/>
-      <c r="B464" s="7"/>
+      <c r="A464" s="7"/>
+      <c r="B464" s="8"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="8"/>
-      <c r="C466" s="8"/>
+      <c r="A466" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="3"/>
+      <c r="C466" s="3"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="3" t="s">
+      <c r="A467" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="4"/>
-      <c r="C467" s="5"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="6"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3912,31 +3915,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="7">
+      <c r="A471" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="8">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="6"/>
-      <c r="B472" s="7"/>
+      <c r="A472" s="7"/>
+      <c r="B472" s="8"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="8"/>
-      <c r="C474" s="8"/>
+      <c r="A474" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="3"/>
+      <c r="C474" s="3"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="3" t="s">
+      <c r="A475" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="4"/>
-      <c r="C475" s="5"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="6"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3969,31 +3972,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="7">
+      <c r="A479" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="8">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="6"/>
-      <c r="B480" s="7"/>
+      <c r="A480" s="7"/>
+      <c r="B480" s="8"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="8"/>
-      <c r="C482" s="8"/>
+      <c r="A482" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="3"/>
+      <c r="C482" s="3"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="3" t="s">
+      <c r="A483" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="4"/>
-      <c r="C483" s="5"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="6"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4026,31 +4029,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="7">
+      <c r="A487" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="8">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="6"/>
-      <c r="B488" s="7"/>
+      <c r="A488" s="7"/>
+      <c r="B488" s="8"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="8"/>
-      <c r="C490" s="8"/>
+      <c r="A490" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="3"/>
+      <c r="C490" s="3"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="3" t="s">
+      <c r="A491" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="4"/>
-      <c r="C491" s="5"/>
+      <c r="B491" s="5"/>
+      <c r="C491" s="6"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4083,17 +4086,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="7">
+      <c r="A495" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="8">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="6"/>
-      <c r="B496" s="7"/>
+      <c r="A496" s="7"/>
+      <c r="B496" s="8"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4104,18 +4107,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="8"/>
-      <c r="C499" s="8"/>
+      <c r="A499" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="3"/>
+      <c r="C499" s="3"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="3" t="s">
+      <c r="A500" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="4"/>
-      <c r="C500" s="5"/>
+      <c r="B500" s="5"/>
+      <c r="C500" s="6"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4148,31 +4151,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="7">
+      <c r="A504" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="8">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="6"/>
-      <c r="B505" s="7"/>
+      <c r="A505" s="7"/>
+      <c r="B505" s="8"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="8"/>
-      <c r="C507" s="8"/>
+      <c r="A507" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="3"/>
+      <c r="C507" s="3"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="3" t="s">
+      <c r="A508" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="4"/>
-      <c r="C508" s="5"/>
+      <c r="B508" s="5"/>
+      <c r="C508" s="6"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4205,31 +4208,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="7">
+      <c r="A512" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="8">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="6"/>
-      <c r="B513" s="7"/>
+      <c r="A513" s="7"/>
+      <c r="B513" s="8"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="8"/>
-      <c r="C515" s="8"/>
+      <c r="A515" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="3"/>
+      <c r="C515" s="3"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="3" t="s">
+      <c r="A516" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="4"/>
-      <c r="C516" s="5"/>
+      <c r="B516" s="5"/>
+      <c r="C516" s="6"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4262,31 +4265,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="7">
+      <c r="A520" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="8">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="6"/>
-      <c r="B521" s="7"/>
+      <c r="A521" s="7"/>
+      <c r="B521" s="8"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="8"/>
-      <c r="C523" s="8"/>
+      <c r="A523" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="3"/>
+      <c r="C523" s="3"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="3" t="s">
+      <c r="A524" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="4"/>
-      <c r="C524" s="5"/>
+      <c r="B524" s="5"/>
+      <c r="C524" s="6"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4319,31 +4322,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="7">
+      <c r="A528" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="8">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="6"/>
-      <c r="B529" s="7"/>
+      <c r="A529" s="7"/>
+      <c r="B529" s="8"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="8"/>
-      <c r="C531" s="8"/>
+      <c r="A531" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="3"/>
+      <c r="C531" s="3"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="3" t="s">
+      <c r="A532" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="4"/>
-      <c r="C532" s="5"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="6"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4376,31 +4379,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="7">
+      <c r="A536" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="8">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="6"/>
-      <c r="B537" s="7"/>
+      <c r="A537" s="7"/>
+      <c r="B537" s="8"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="8"/>
-      <c r="C539" s="8"/>
+      <c r="A539" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="3"/>
+      <c r="C539" s="3"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="3" t="s">
+      <c r="A540" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="4"/>
-      <c r="C540" s="5"/>
+      <c r="B540" s="5"/>
+      <c r="C540" s="6"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4433,31 +4436,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="7">
+      <c r="A544" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="8">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="6"/>
-      <c r="B545" s="7"/>
+      <c r="A545" s="7"/>
+      <c r="B545" s="8"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="8"/>
-      <c r="C547" s="8"/>
+      <c r="A547" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="3"/>
+      <c r="C547" s="3"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="3" t="s">
+      <c r="A548" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="4"/>
-      <c r="C548" s="5"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="6"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4490,17 +4493,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="7">
+      <c r="A552" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="8">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="6"/>
-      <c r="B553" s="7"/>
+      <c r="A553" s="7"/>
+      <c r="B553" s="8"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4511,18 +4514,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="8"/>
-      <c r="C556" s="8"/>
+      <c r="A556" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="3"/>
+      <c r="C556" s="3"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="3" t="s">
+      <c r="A557" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="4"/>
-      <c r="C557" s="5"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="6"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4555,31 +4558,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="7">
+      <c r="A561" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="8">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="6"/>
-      <c r="B562" s="7"/>
+      <c r="A562" s="7"/>
+      <c r="B562" s="8"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="8"/>
-      <c r="C564" s="8"/>
+      <c r="A564" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="3"/>
+      <c r="C564" s="3"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="3" t="s">
+      <c r="A565" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="4"/>
-      <c r="C565" s="5"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="6"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4612,31 +4615,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="7">
+      <c r="A569" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="8">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="6"/>
-      <c r="B570" s="7"/>
+      <c r="A570" s="7"/>
+      <c r="B570" s="8"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="8"/>
-      <c r="C572" s="8"/>
+      <c r="A572" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="3"/>
+      <c r="C572" s="3"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="3" t="s">
+      <c r="A573" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="4"/>
-      <c r="C573" s="5"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="6"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4669,31 +4672,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="7">
+      <c r="A577" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="8">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="6"/>
-      <c r="B578" s="7"/>
+      <c r="A578" s="7"/>
+      <c r="B578" s="8"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="8"/>
-      <c r="C580" s="8"/>
+      <c r="A580" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="3"/>
+      <c r="C580" s="3"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="3" t="s">
+      <c r="A581" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="4"/>
-      <c r="C581" s="5"/>
+      <c r="B581" s="5"/>
+      <c r="C581" s="6"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4726,17 +4729,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="7">
+      <c r="A585" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="8">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="6"/>
-      <c r="B586" s="7"/>
+      <c r="A586" s="7"/>
+      <c r="B586" s="8"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4747,18 +4750,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="8"/>
-      <c r="C589" s="8"/>
+      <c r="A589" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="3"/>
+      <c r="C589" s="3"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="3" t="s">
+      <c r="A590" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="4"/>
-      <c r="C590" s="5"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="6"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4791,31 +4794,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="7">
+      <c r="A594" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="8">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="6"/>
-      <c r="B595" s="7"/>
+      <c r="A595" s="7"/>
+      <c r="B595" s="8"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="8"/>
-      <c r="C597" s="8"/>
+      <c r="A597" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="3"/>
+      <c r="C597" s="3"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="3" t="s">
+      <c r="A598" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="4"/>
-      <c r="C598" s="5"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="6"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4848,31 +4851,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="7">
+      <c r="A602" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="8">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="6"/>
-      <c r="B603" s="7"/>
+      <c r="A603" s="7"/>
+      <c r="B603" s="8"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="8"/>
-      <c r="C605" s="8"/>
+      <c r="A605" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="3"/>
+      <c r="C605" s="3"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="3" t="s">
+      <c r="A606" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="4"/>
-      <c r="C606" s="5"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="6"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4905,31 +4908,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="7">
+      <c r="A610" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="8">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="6"/>
-      <c r="B611" s="7"/>
+      <c r="A611" s="7"/>
+      <c r="B611" s="8"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="8"/>
-      <c r="C613" s="8"/>
+      <c r="A613" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="3"/>
+      <c r="C613" s="3"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="3" t="s">
+      <c r="A614" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="4"/>
-      <c r="C614" s="5"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="6"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4962,31 +4965,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="7">
+      <c r="A618" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="8">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="6"/>
-      <c r="B619" s="7"/>
+      <c r="A619" s="7"/>
+      <c r="B619" s="8"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="8"/>
-      <c r="C621" s="8"/>
+      <c r="A621" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="3"/>
+      <c r="C621" s="3"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="3" t="s">
+      <c r="A622" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="4"/>
-      <c r="C622" s="5"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="6"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5019,31 +5022,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="7">
+      <c r="A626" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="8">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="6"/>
-      <c r="B627" s="7"/>
+      <c r="A627" s="7"/>
+      <c r="B627" s="8"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="8"/>
-      <c r="C629" s="8"/>
+      <c r="A629" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="3"/>
+      <c r="C629" s="3"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="3" t="s">
+      <c r="A630" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="4"/>
-      <c r="C630" s="5"/>
+      <c r="B630" s="5"/>
+      <c r="C630" s="6"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5076,31 +5079,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="7">
+      <c r="A634" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="8">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="6"/>
-      <c r="B635" s="7"/>
+      <c r="A635" s="7"/>
+      <c r="B635" s="8"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="8"/>
-      <c r="C637" s="8"/>
+      <c r="A637" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="3"/>
+      <c r="C637" s="3"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="3" t="s">
+      <c r="A638" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="4"/>
-      <c r="C638" s="5"/>
+      <c r="B638" s="5"/>
+      <c r="C638" s="6"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5133,17 +5136,17 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="7">
+      <c r="A642" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="8">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="6"/>
-      <c r="B643" s="7"/>
+      <c r="A643" s="7"/>
+      <c r="B643" s="8"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
@@ -5154,18 +5157,18 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="8"/>
-      <c r="C646" s="8"/>
+      <c r="A646" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="3"/>
+      <c r="C646" s="3"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="3" t="s">
+      <c r="A647" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="4"/>
-      <c r="C647" s="5"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="6"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5198,31 +5201,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="7">
+      <c r="A651" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="8">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="6"/>
-      <c r="B652" s="7"/>
+      <c r="A652" s="7"/>
+      <c r="B652" s="8"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="8"/>
-      <c r="C654" s="8"/>
+      <c r="A654" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="3"/>
+      <c r="C654" s="3"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="3" t="s">
+      <c r="A655" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="4"/>
-      <c r="C655" s="5"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="6"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5255,31 +5258,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="7">
+      <c r="A659" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="8">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="6"/>
-      <c r="B660" s="7"/>
+      <c r="A660" s="7"/>
+      <c r="B660" s="8"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="8"/>
-      <c r="C662" s="8"/>
+      <c r="A662" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="3"/>
+      <c r="C662" s="3"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="3" t="s">
+      <c r="A663" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="4"/>
-      <c r="C663" s="5"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="6"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5312,31 +5315,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="7">
+      <c r="A667" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="8">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="6"/>
-      <c r="B668" s="7"/>
+      <c r="A668" s="7"/>
+      <c r="B668" s="8"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="8"/>
-      <c r="C670" s="8"/>
+      <c r="A670" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="3"/>
+      <c r="C670" s="3"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="3" t="s">
+      <c r="A671" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="4"/>
-      <c r="C671" s="5"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="6"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5369,31 +5372,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="7">
+      <c r="A675" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="8">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="6"/>
-      <c r="B676" s="7"/>
+      <c r="A676" s="7"/>
+      <c r="B676" s="8"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="8"/>
-      <c r="C678" s="8"/>
+      <c r="A678" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="3"/>
+      <c r="C678" s="3"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="3" t="s">
+      <c r="A679" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="4"/>
-      <c r="C679" s="5"/>
+      <c r="B679" s="5"/>
+      <c r="C679" s="6"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5426,31 +5429,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="7">
+      <c r="A683" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="8">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="6"/>
-      <c r="B684" s="7"/>
+      <c r="A684" s="7"/>
+      <c r="B684" s="8"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="8"/>
-      <c r="C686" s="8"/>
+      <c r="A686" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="3"/>
+      <c r="C686" s="3"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="3" t="s">
+      <c r="A687" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="4"/>
-      <c r="C687" s="5"/>
+      <c r="B687" s="5"/>
+      <c r="C687" s="6"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5483,31 +5486,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="7">
+      <c r="A691" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="8">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="6"/>
-      <c r="B692" s="7"/>
+      <c r="A692" s="7"/>
+      <c r="B692" s="8"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="8"/>
-      <c r="C694" s="8"/>
+      <c r="A694" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="3"/>
+      <c r="C694" s="3"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="3" t="s">
+      <c r="A695" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="4"/>
-      <c r="C695" s="5"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="6"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5540,31 +5543,31 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="7">
+      <c r="A699" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="8">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="6"/>
-      <c r="B700" s="7"/>
+      <c r="A700" s="7"/>
+      <c r="B700" s="8"/>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B702" s="8"/>
-      <c r="C702" s="8"/>
+      <c r="A702" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B702" s="3"/>
+      <c r="C702" s="3"/>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="3" t="s">
+      <c r="A703" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B703" s="4"/>
-      <c r="C703" s="5"/>
+      <c r="B703" s="5"/>
+      <c r="C703" s="6"/>
     </row>
     <row r="704" spans="1:3">
       <c r="A704" s="1" t="s">
@@ -5597,17 +5600,17 @@
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B707" s="7">
+      <c r="A707" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="8">
         <f>B705-B706</f>
         <v>448</v>
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="6"/>
-      <c r="B708" s="7"/>
+      <c r="A708" s="7"/>
+      <c r="B708" s="8"/>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" s="1" t="s">
@@ -5618,18 +5621,18 @@
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B711" s="8"/>
-      <c r="C711" s="8"/>
+      <c r="A711" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="3"/>
+      <c r="C711" s="3"/>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="3" t="s">
+      <c r="A712" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B712" s="4"/>
-      <c r="C712" s="5"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="6"/>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" s="1" t="s">
@@ -5662,31 +5665,31 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B716" s="7">
+      <c r="A716" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="8">
         <f>B714-B715</f>
         <v>27</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="6"/>
-      <c r="B717" s="7"/>
+      <c r="A717" s="7"/>
+      <c r="B717" s="8"/>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B719" s="8"/>
-      <c r="C719" s="8"/>
+      <c r="A719" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="3"/>
+      <c r="C719" s="3"/>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="3" t="s">
+      <c r="A720" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B720" s="4"/>
-      <c r="C720" s="5"/>
+      <c r="B720" s="5"/>
+      <c r="C720" s="6"/>
     </row>
     <row r="721" spans="1:3">
       <c r="A721" s="1" t="s">
@@ -5719,31 +5722,31 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B724" s="7">
+      <c r="A724" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="8">
         <f>B722-B723</f>
         <v>386</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="6"/>
-      <c r="B725" s="7"/>
+      <c r="A725" s="7"/>
+      <c r="B725" s="8"/>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B727" s="8"/>
-      <c r="C727" s="8"/>
+      <c r="A727" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="3"/>
+      <c r="C727" s="3"/>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="3" t="s">
+      <c r="A728" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B728" s="4"/>
-      <c r="C728" s="5"/>
+      <c r="B728" s="5"/>
+      <c r="C728" s="6"/>
     </row>
     <row r="729" spans="1:3">
       <c r="A729" s="1" t="s">
@@ -5776,31 +5779,31 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B732" s="7">
+      <c r="A732" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="8">
         <f>B730-B731</f>
         <v>1256</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="6"/>
-      <c r="B733" s="7"/>
+      <c r="A733" s="7"/>
+      <c r="B733" s="8"/>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B735" s="8"/>
-      <c r="C735" s="8"/>
+      <c r="A735" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="3"/>
+      <c r="C735" s="3"/>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="3" t="s">
+      <c r="A736" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B736" s="4"/>
-      <c r="C736" s="5"/>
+      <c r="B736" s="5"/>
+      <c r="C736" s="6"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="1" t="s">
@@ -5833,31 +5836,31 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B740" s="7">
+      <c r="A740" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="8">
         <f>B738-B739</f>
         <v>227</v>
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="6"/>
-      <c r="B741" s="7"/>
+      <c r="A741" s="7"/>
+      <c r="B741" s="8"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B743" s="8"/>
-      <c r="C743" s="8"/>
+      <c r="A743" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="3"/>
+      <c r="C743" s="3"/>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="3" t="s">
+      <c r="A744" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B744" s="4"/>
-      <c r="C744" s="5"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="6"/>
     </row>
     <row r="745" spans="1:3">
       <c r="A745" s="1" t="s">
@@ -5890,31 +5893,31 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B748" s="7">
+      <c r="A748" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="8">
         <f>B746-B747</f>
         <v>961</v>
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="6"/>
-      <c r="B749" s="7"/>
+      <c r="A749" s="7"/>
+      <c r="B749" s="8"/>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B751" s="8"/>
-      <c r="C751" s="8"/>
+      <c r="A751" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="3"/>
+      <c r="C751" s="3"/>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="3" t="s">
+      <c r="A752" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B752" s="4"/>
-      <c r="C752" s="5"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="6"/>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" s="1" t="s">
@@ -5947,31 +5950,31 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="7">
+      <c r="A756" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="8">
         <f>B754-B755</f>
         <v>6</v>
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="6"/>
-      <c r="B757" s="7"/>
+      <c r="A757" s="7"/>
+      <c r="B757" s="8"/>
     </row>
     <row r="759" spans="1:3">
-      <c r="A759" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B759" s="8"/>
-      <c r="C759" s="8"/>
+      <c r="A759" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B759" s="3"/>
+      <c r="C759" s="3"/>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="3" t="s">
+      <c r="A760" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B760" s="4"/>
-      <c r="C760" s="5"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="6"/>
     </row>
     <row r="761" spans="1:3">
       <c r="A761" s="1" t="s">
@@ -6004,165 +6007,722 @@
       </c>
     </row>
     <row r="764" spans="1:3">
-      <c r="A764" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B764" s="7">
+      <c r="A764" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764" s="8">
         <f>B762-B763</f>
         <v>616</v>
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="6"/>
-      <c r="B765" s="7"/>
+      <c r="A765" s="7"/>
+      <c r="B765" s="8"/>
+    </row>
+    <row r="767" spans="1:3">
+      <c r="A767" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B767" s="3"/>
+      <c r="C767" s="3"/>
+    </row>
+    <row r="768" spans="1:3">
+      <c r="A768" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B768" s="5"/>
+      <c r="C768" s="6"/>
+    </row>
+    <row r="769" spans="1:3">
+      <c r="A769" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B769" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C769" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3">
+      <c r="A770" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B770" s="2">
+        <v>2299</v>
+      </c>
+      <c r="C770" s="2">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3">
+      <c r="A771" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B771" s="2">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3">
+      <c r="A772" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B772" s="8">
+        <f>B770-B771</f>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3">
+      <c r="A773" s="7"/>
+      <c r="B773" s="8"/>
+    </row>
+    <row r="774" spans="1:3">
+      <c r="A774" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B774" s="2">
+        <v>74429</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3">
+      <c r="A776" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B776" s="3"/>
+      <c r="C776" s="3"/>
+    </row>
+    <row r="777" spans="1:3">
+      <c r="A777" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B777" s="5"/>
+      <c r="C777" s="6"/>
+    </row>
+    <row r="778" spans="1:3">
+      <c r="A778" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C778" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3">
+      <c r="A779" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B779" s="2">
+        <v>521</v>
+      </c>
+      <c r="C779" s="2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3">
+      <c r="A780" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B780" s="2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3">
+      <c r="A781" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781" s="8">
+        <f>B779-B780</f>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3">
+      <c r="A782" s="7"/>
+      <c r="B782" s="8"/>
+    </row>
+    <row r="784" spans="1:3">
+      <c r="A784" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B784" s="3"/>
+      <c r="C784" s="3"/>
+    </row>
+    <row r="785" spans="1:3">
+      <c r="A785" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B785" s="5"/>
+      <c r="C785" s="6"/>
+    </row>
+    <row r="786" spans="1:3">
+      <c r="A786" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B786" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C786" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3">
+      <c r="A787" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B787" s="2">
+        <v>8639</v>
+      </c>
+      <c r="C787" s="2">
+        <v>8648</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3">
+      <c r="A788" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B788" s="2">
+        <v>8043</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3">
+      <c r="A789" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789" s="8">
+        <f>B787-B788</f>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3">
+      <c r="A790" s="7"/>
+      <c r="B790" s="8"/>
+    </row>
+    <row r="792" spans="1:3">
+      <c r="A792" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B792" s="3"/>
+      <c r="C792" s="3"/>
+    </row>
+    <row r="793" spans="1:3">
+      <c r="A793" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B793" s="5"/>
+      <c r="C793" s="6"/>
+    </row>
+    <row r="794" spans="1:3">
+      <c r="A794" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B794" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C794" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3">
+      <c r="A795" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B795" s="2">
+        <v>328</v>
+      </c>
+      <c r="C795" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3">
+      <c r="A796" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B796" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3">
+      <c r="A797" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797" s="8">
+        <f>B795-B796</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3">
+      <c r="A798" s="7"/>
+      <c r="B798" s="8"/>
+    </row>
+    <row r="800" spans="1:3">
+      <c r="A800" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B800" s="3"/>
+      <c r="C800" s="3"/>
+    </row>
+    <row r="801" spans="1:3">
+      <c r="A801" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B801" s="5"/>
+      <c r="C801" s="6"/>
+    </row>
+    <row r="802" spans="1:3">
+      <c r="A802" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B802" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C802" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3">
+      <c r="A803" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B803" s="2">
+        <v>540</v>
+      </c>
+      <c r="C803" s="2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3">
+      <c r="A804" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B804" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3">
+      <c r="A805" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805" s="8">
+        <f>B803-B804</f>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3">
+      <c r="A806" s="7"/>
+      <c r="B806" s="8"/>
+    </row>
+    <row r="808" spans="1:3">
+      <c r="A808" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B808" s="3"/>
+      <c r="C808" s="3"/>
+    </row>
+    <row r="809" spans="1:3">
+      <c r="A809" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B809" s="5"/>
+      <c r="C809" s="6"/>
+    </row>
+    <row r="810" spans="1:3">
+      <c r="A810" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B810" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C810" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3">
+      <c r="A811" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B811" s="2">
+        <v>1769</v>
+      </c>
+      <c r="C811" s="2">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3">
+      <c r="A812" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B812" s="2">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3">
+      <c r="A813" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813" s="8">
+        <f>B811-B812</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3">
+      <c r="A814" s="7"/>
+      <c r="B814" s="8"/>
+    </row>
+    <row r="816" spans="1:3">
+      <c r="A816" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B816" s="3"/>
+      <c r="C816" s="3"/>
+    </row>
+    <row r="817" spans="1:3">
+      <c r="A817" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B817" s="5"/>
+      <c r="C817" s="6"/>
+    </row>
+    <row r="818" spans="1:3">
+      <c r="A818" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B818" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C818" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3">
+      <c r="A819" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B819" s="2">
+        <v>77</v>
+      </c>
+      <c r="C819" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3">
+      <c r="A820" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B820" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3">
+      <c r="A821" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B821" s="8">
+        <f>B819-B820</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3">
+      <c r="A822" s="7"/>
+      <c r="B822" s="8"/>
+    </row>
+    <row r="824" spans="1:3">
+      <c r="A824" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B824" s="3"/>
+      <c r="C824" s="3"/>
+    </row>
+    <row r="825" spans="1:3">
+      <c r="A825" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B825" s="5"/>
+      <c r="C825" s="6"/>
+    </row>
+    <row r="826" spans="1:3">
+      <c r="A826" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B826" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3">
+      <c r="A827" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B827" s="2">
+        <v>134</v>
+      </c>
+      <c r="C827" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3">
+      <c r="A828" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B828" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3">
+      <c r="A829" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B829" s="8">
+        <f>B827-B828</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3">
+      <c r="A830" s="7"/>
+      <c r="B830" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="376">
-    <mergeCell ref="A759:C759"/>
-    <mergeCell ref="A760:C760"/>
-    <mergeCell ref="A764:A765"/>
-    <mergeCell ref="B764:B765"/>
-    <mergeCell ref="A740:A741"/>
-    <mergeCell ref="B740:B741"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A744:C744"/>
-    <mergeCell ref="A748:A749"/>
-    <mergeCell ref="B748:B749"/>
-    <mergeCell ref="A751:C751"/>
-    <mergeCell ref="A752:C752"/>
-    <mergeCell ref="A756:A757"/>
-    <mergeCell ref="B756:B757"/>
-    <mergeCell ref="A720:C720"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="B724:B725"/>
-    <mergeCell ref="A727:C727"/>
-    <mergeCell ref="A728:C728"/>
-    <mergeCell ref="A732:A733"/>
-    <mergeCell ref="B732:B733"/>
-    <mergeCell ref="A735:C735"/>
-    <mergeCell ref="A736:C736"/>
-    <mergeCell ref="A702:C702"/>
-    <mergeCell ref="A703:C703"/>
-    <mergeCell ref="A707:A708"/>
-    <mergeCell ref="B707:B708"/>
-    <mergeCell ref="A711:C711"/>
-    <mergeCell ref="A712:C712"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="B716:B717"/>
-    <mergeCell ref="A719:C719"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A487:A488"/>
-    <mergeCell ref="B487:B488"/>
-    <mergeCell ref="A565:C565"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="B569:B570"/>
-    <mergeCell ref="A572:C572"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A547:C547"/>
-    <mergeCell ref="A548:C548"/>
-    <mergeCell ref="A552:A553"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A557:C557"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="B561:B562"/>
-    <mergeCell ref="A564:C564"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A507:C507"/>
-    <mergeCell ref="A508:C508"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B88:B89"/>
+  <mergeCells count="408">
+    <mergeCell ref="A824:C824"/>
+    <mergeCell ref="A825:C825"/>
+    <mergeCell ref="A829:A830"/>
+    <mergeCell ref="B829:B830"/>
+    <mergeCell ref="A805:A806"/>
+    <mergeCell ref="B805:B806"/>
+    <mergeCell ref="A808:C808"/>
+    <mergeCell ref="A809:C809"/>
+    <mergeCell ref="A813:A814"/>
+    <mergeCell ref="B813:B814"/>
+    <mergeCell ref="A816:C816"/>
+    <mergeCell ref="A817:C817"/>
+    <mergeCell ref="A821:A822"/>
+    <mergeCell ref="B821:B822"/>
+    <mergeCell ref="A785:C785"/>
+    <mergeCell ref="A789:A790"/>
+    <mergeCell ref="B789:B790"/>
+    <mergeCell ref="A792:C792"/>
+    <mergeCell ref="A793:C793"/>
+    <mergeCell ref="A797:A798"/>
+    <mergeCell ref="B797:B798"/>
+    <mergeCell ref="A800:C800"/>
+    <mergeCell ref="A801:C801"/>
+    <mergeCell ref="A767:C767"/>
+    <mergeCell ref="A768:C768"/>
+    <mergeCell ref="A772:A773"/>
+    <mergeCell ref="B772:B773"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A777:C777"/>
+    <mergeCell ref="A781:A782"/>
+    <mergeCell ref="B781:B782"/>
+    <mergeCell ref="A784:C784"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A490:C490"/>
+    <mergeCell ref="A491:C491"/>
+    <mergeCell ref="A495:A496"/>
+    <mergeCell ref="B495:B496"/>
+    <mergeCell ref="A499:C499"/>
+    <mergeCell ref="A500:C500"/>
+    <mergeCell ref="A433:C433"/>
+    <mergeCell ref="A434:C434"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:C442"/>
+    <mergeCell ref="A443:C443"/>
+    <mergeCell ref="A447:A448"/>
+    <mergeCell ref="B447:B448"/>
+    <mergeCell ref="A450:C450"/>
+    <mergeCell ref="A451:C451"/>
+    <mergeCell ref="A455:A456"/>
+    <mergeCell ref="B455:B456"/>
+    <mergeCell ref="A458:C458"/>
+    <mergeCell ref="A459:C459"/>
+    <mergeCell ref="A463:A464"/>
+    <mergeCell ref="B463:B464"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A169:A170"/>
     <mergeCell ref="A177:A178"/>
     <mergeCell ref="A185:A186"/>
@@ -6187,213 +6747,152 @@
     <mergeCell ref="A148:C148"/>
     <mergeCell ref="A149:C149"/>
     <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A490:C490"/>
-    <mergeCell ref="A491:C491"/>
-    <mergeCell ref="A495:A496"/>
-    <mergeCell ref="B495:B496"/>
-    <mergeCell ref="A499:C499"/>
-    <mergeCell ref="A500:C500"/>
-    <mergeCell ref="A433:C433"/>
-    <mergeCell ref="A434:C434"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A442:C442"/>
-    <mergeCell ref="A443:C443"/>
-    <mergeCell ref="A447:A448"/>
-    <mergeCell ref="B447:B448"/>
-    <mergeCell ref="A450:C450"/>
-    <mergeCell ref="A451:C451"/>
-    <mergeCell ref="A455:A456"/>
-    <mergeCell ref="B455:B456"/>
-    <mergeCell ref="A458:C458"/>
-    <mergeCell ref="A459:C459"/>
-    <mergeCell ref="A463:A464"/>
-    <mergeCell ref="B463:B464"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A487:A488"/>
+    <mergeCell ref="B487:B488"/>
+    <mergeCell ref="A565:C565"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="B569:B570"/>
+    <mergeCell ref="A572:C572"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A547:C547"/>
+    <mergeCell ref="A548:C548"/>
+    <mergeCell ref="A552:A553"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A557:C557"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="B561:B562"/>
+    <mergeCell ref="A564:C564"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A507:C507"/>
+    <mergeCell ref="A508:C508"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
     <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A702:C702"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A707:A708"/>
+    <mergeCell ref="B707:B708"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A759:C759"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A764:A765"/>
+    <mergeCell ref="B764:B765"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA7B5EA-0B27-487C-A7DE-7021FDDF04DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD641FE-A3BE-4D08-87F8-72804B5C996B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="38">
   <si>
     <t>Data</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>23.10.2026</t>
+  </si>
+  <si>
+    <t>24.10.2026</t>
   </si>
 </sst>
 </file>
@@ -541,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C830"/>
+  <dimension ref="A1:C887"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -6483,85 +6486,750 @@
       <c r="A830" s="7"/>
       <c r="B830" s="8"/>
     </row>
+    <row r="832" spans="1:3">
+      <c r="A832" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B832" s="3"/>
+      <c r="C832" s="3"/>
+    </row>
+    <row r="833" spans="1:3">
+      <c r="A833" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B833" s="5"/>
+      <c r="C833" s="6"/>
+    </row>
+    <row r="834" spans="1:3">
+      <c r="A834" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B834" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C834" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3">
+      <c r="A835" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B835" s="2">
+        <v>1</v>
+      </c>
+      <c r="C835" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3">
+      <c r="A836" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B836" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3">
+      <c r="A837" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B837" s="8">
+        <f>B835-B836</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3">
+      <c r="A838" s="7"/>
+      <c r="B838" s="8"/>
+    </row>
+    <row r="839" spans="1:3">
+      <c r="A839" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B839" s="2">
+        <v>61011</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3">
+      <c r="A841" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B841" s="3"/>
+      <c r="C841" s="3"/>
+    </row>
+    <row r="842" spans="1:3">
+      <c r="A842" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B842" s="5"/>
+      <c r="C842" s="6"/>
+    </row>
+    <row r="843" spans="1:3">
+      <c r="A843" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C843" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3">
+      <c r="A844" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B844" s="2">
+        <v>6698</v>
+      </c>
+      <c r="C844" s="2">
+        <v>6698</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3">
+      <c r="A845" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B845" s="2">
+        <v>5981</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3">
+      <c r="A846" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846" s="8">
+        <f>B844-B845</f>
+        <v>717</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3">
+      <c r="A847" s="7"/>
+      <c r="B847" s="8"/>
+    </row>
+    <row r="849" spans="1:3">
+      <c r="A849" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B849" s="3"/>
+      <c r="C849" s="3"/>
+    </row>
+    <row r="850" spans="1:3">
+      <c r="A850" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B850" s="5"/>
+      <c r="C850" s="6"/>
+    </row>
+    <row r="851" spans="1:3">
+      <c r="A851" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B851" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C851" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3">
+      <c r="A852" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B852" s="2">
+        <v>11</v>
+      </c>
+      <c r="C852" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3">
+      <c r="A853" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B853" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3">
+      <c r="A854" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854" s="8">
+        <f>B852-B853</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3">
+      <c r="A855" s="7"/>
+      <c r="B855" s="8"/>
+    </row>
+    <row r="857" spans="1:3">
+      <c r="A857" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B857" s="3"/>
+      <c r="C857" s="3"/>
+    </row>
+    <row r="858" spans="1:3">
+      <c r="A858" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B858" s="5"/>
+      <c r="C858" s="6"/>
+    </row>
+    <row r="859" spans="1:3">
+      <c r="A859" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B859" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C859" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3">
+      <c r="A860" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B860" s="2">
+        <v>291</v>
+      </c>
+      <c r="C860" s="2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3">
+      <c r="A861" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B861" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3">
+      <c r="A862" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862" s="8">
+        <f>B860-B861</f>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3">
+      <c r="A863" s="7"/>
+      <c r="B863" s="8"/>
+    </row>
+    <row r="865" spans="1:3">
+      <c r="A865" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B865" s="3"/>
+      <c r="C865" s="3"/>
+    </row>
+    <row r="866" spans="1:3">
+      <c r="A866" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B866" s="5"/>
+      <c r="C866" s="6"/>
+    </row>
+    <row r="867" spans="1:3">
+      <c r="A867" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B867" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C867" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3">
+      <c r="A868" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B868" s="2">
+        <v>188</v>
+      </c>
+      <c r="C868" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3">
+      <c r="A869" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B869" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3">
+      <c r="A870" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870" s="8">
+        <f>B868-B869</f>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3">
+      <c r="A871" s="7"/>
+      <c r="B871" s="8"/>
+    </row>
+    <row r="873" spans="1:3">
+      <c r="A873" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B873" s="3"/>
+      <c r="C873" s="3"/>
+    </row>
+    <row r="874" spans="1:3">
+      <c r="A874" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B874" s="5"/>
+      <c r="C874" s="6"/>
+    </row>
+    <row r="875" spans="1:3">
+      <c r="A875" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B875" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C875" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3">
+      <c r="A876" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B876" s="2">
+        <v>775</v>
+      </c>
+      <c r="C876" s="2">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3">
+      <c r="A877" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B877" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3">
+      <c r="A878" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B878" s="8">
+        <f>B876-B877</f>
+        <v>449</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3">
+      <c r="A879" s="7"/>
+      <c r="B879" s="8"/>
+    </row>
+    <row r="881" spans="1:3">
+      <c r="A881" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B881" s="3"/>
+      <c r="C881" s="3"/>
+    </row>
+    <row r="882" spans="1:3">
+      <c r="A882" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B882" s="5"/>
+      <c r="C882" s="6"/>
+    </row>
+    <row r="883" spans="1:3">
+      <c r="A883" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B883" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C883" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3">
+      <c r="A884" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B884" s="2">
+        <v>1071</v>
+      </c>
+      <c r="C884" s="2">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="885" spans="1:3">
+      <c r="A885" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B885" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="886" spans="1:3">
+      <c r="A886" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B886" s="8">
+        <f>B884-B885</f>
+        <v>821</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3">
+      <c r="A887" s="7"/>
+      <c r="B887" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="408">
-    <mergeCell ref="A824:C824"/>
-    <mergeCell ref="A825:C825"/>
-    <mergeCell ref="A829:A830"/>
-    <mergeCell ref="B829:B830"/>
-    <mergeCell ref="A805:A806"/>
-    <mergeCell ref="B805:B806"/>
-    <mergeCell ref="A808:C808"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="A813:A814"/>
-    <mergeCell ref="B813:B814"/>
-    <mergeCell ref="A816:C816"/>
-    <mergeCell ref="A817:C817"/>
-    <mergeCell ref="A821:A822"/>
-    <mergeCell ref="B821:B822"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="A789:A790"/>
-    <mergeCell ref="B789:B790"/>
-    <mergeCell ref="A792:C792"/>
-    <mergeCell ref="A793:C793"/>
-    <mergeCell ref="A797:A798"/>
-    <mergeCell ref="B797:B798"/>
-    <mergeCell ref="A800:C800"/>
-    <mergeCell ref="A801:C801"/>
-    <mergeCell ref="A767:C767"/>
-    <mergeCell ref="A768:C768"/>
-    <mergeCell ref="A772:A773"/>
-    <mergeCell ref="B772:B773"/>
-    <mergeCell ref="A776:C776"/>
-    <mergeCell ref="A777:C777"/>
-    <mergeCell ref="A781:A782"/>
-    <mergeCell ref="B781:B782"/>
-    <mergeCell ref="A784:C784"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
+  <mergeCells count="436">
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="B870:B871"/>
+    <mergeCell ref="A873:C873"/>
+    <mergeCell ref="A874:C874"/>
+    <mergeCell ref="A878:A879"/>
+    <mergeCell ref="B878:B879"/>
+    <mergeCell ref="A881:C881"/>
+    <mergeCell ref="A882:C882"/>
+    <mergeCell ref="A886:A887"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="A850:C850"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="B854:B855"/>
+    <mergeCell ref="A857:C857"/>
+    <mergeCell ref="A858:C858"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="B862:B863"/>
+    <mergeCell ref="A865:C865"/>
+    <mergeCell ref="A866:C866"/>
+    <mergeCell ref="A832:C832"/>
+    <mergeCell ref="A833:C833"/>
+    <mergeCell ref="A837:A838"/>
+    <mergeCell ref="B837:B838"/>
+    <mergeCell ref="A841:C841"/>
+    <mergeCell ref="A842:C842"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="B846:B847"/>
+    <mergeCell ref="A849:C849"/>
+    <mergeCell ref="A759:C759"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A764:A765"/>
+    <mergeCell ref="B764:B765"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A702:C702"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A707:A708"/>
+    <mergeCell ref="B707:B708"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A487:A488"/>
+    <mergeCell ref="B487:B488"/>
+    <mergeCell ref="A565:C565"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="B569:B570"/>
+    <mergeCell ref="A572:C572"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A547:C547"/>
+    <mergeCell ref="A548:C548"/>
+    <mergeCell ref="A552:A553"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A557:C557"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="B561:B562"/>
+    <mergeCell ref="A564:C564"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A507:C507"/>
+    <mergeCell ref="A508:C508"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
+    <mergeCell ref="A515:C515"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
     <mergeCell ref="A430:A431"/>
     <mergeCell ref="B430:B431"/>
     <mergeCell ref="A490:C490"/>
@@ -6586,313 +7254,83 @@
     <mergeCell ref="A459:C459"/>
     <mergeCell ref="A463:A464"/>
     <mergeCell ref="B463:B464"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A487:A488"/>
-    <mergeCell ref="B487:B488"/>
-    <mergeCell ref="A565:C565"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="B569:B570"/>
-    <mergeCell ref="A572:C572"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A547:C547"/>
-    <mergeCell ref="A548:C548"/>
-    <mergeCell ref="A552:A553"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A557:C557"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="B561:B562"/>
-    <mergeCell ref="A564:C564"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A507:C507"/>
-    <mergeCell ref="A508:C508"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
-    <mergeCell ref="A702:C702"/>
-    <mergeCell ref="A703:C703"/>
-    <mergeCell ref="A707:A708"/>
-    <mergeCell ref="B707:B708"/>
-    <mergeCell ref="A711:C711"/>
-    <mergeCell ref="A712:C712"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="B716:B717"/>
-    <mergeCell ref="A719:C719"/>
-    <mergeCell ref="A720:C720"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="B724:B725"/>
-    <mergeCell ref="A727:C727"/>
-    <mergeCell ref="A728:C728"/>
-    <mergeCell ref="A732:A733"/>
-    <mergeCell ref="B732:B733"/>
-    <mergeCell ref="A735:C735"/>
-    <mergeCell ref="A736:C736"/>
-    <mergeCell ref="A759:C759"/>
-    <mergeCell ref="A760:C760"/>
-    <mergeCell ref="A764:A765"/>
-    <mergeCell ref="B764:B765"/>
-    <mergeCell ref="A740:A741"/>
-    <mergeCell ref="B740:B741"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A744:C744"/>
-    <mergeCell ref="A748:A749"/>
-    <mergeCell ref="B748:B749"/>
-    <mergeCell ref="A751:C751"/>
-    <mergeCell ref="A752:C752"/>
-    <mergeCell ref="A756:A757"/>
-    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A767:C767"/>
+    <mergeCell ref="A768:C768"/>
+    <mergeCell ref="A772:A773"/>
+    <mergeCell ref="B772:B773"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A777:C777"/>
+    <mergeCell ref="A781:A782"/>
+    <mergeCell ref="B781:B782"/>
+    <mergeCell ref="A784:C784"/>
+    <mergeCell ref="A785:C785"/>
+    <mergeCell ref="A789:A790"/>
+    <mergeCell ref="B789:B790"/>
+    <mergeCell ref="A792:C792"/>
+    <mergeCell ref="A793:C793"/>
+    <mergeCell ref="A797:A798"/>
+    <mergeCell ref="B797:B798"/>
+    <mergeCell ref="A800:C800"/>
+    <mergeCell ref="A801:C801"/>
+    <mergeCell ref="A824:C824"/>
+    <mergeCell ref="A825:C825"/>
+    <mergeCell ref="A829:A830"/>
+    <mergeCell ref="B829:B830"/>
+    <mergeCell ref="A805:A806"/>
+    <mergeCell ref="B805:B806"/>
+    <mergeCell ref="A808:C808"/>
+    <mergeCell ref="A809:C809"/>
+    <mergeCell ref="A813:A814"/>
+    <mergeCell ref="B813:B814"/>
+    <mergeCell ref="A816:C816"/>
+    <mergeCell ref="A817:C817"/>
+    <mergeCell ref="A821:A822"/>
+    <mergeCell ref="B821:B822"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD641FE-A3BE-4D08-87F8-72804B5C996B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7D225E-6A4C-4E45-8FD4-34A2C602371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="39">
   <si>
     <t>Data</t>
   </si>
@@ -149,6 +149,9 @@
   <si>
     <t>24.10.2026</t>
   </si>
+  <si>
+    <t>26.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -252,6 +255,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -261,12 +270,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -544,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C887"/>
+  <dimension ref="A1:C936"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -553,18 +556,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -597,17 +600,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -618,18 +621,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -662,31 +665,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="A18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -719,31 +722,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -776,31 +779,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="A34" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -833,31 +836,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="4">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="A42" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -890,31 +893,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="4">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="4"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
+      <c r="A50" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -947,31 +950,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="4">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="A58" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -1004,17 +1007,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="4">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1025,18 +1028,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
+      <c r="A67" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1069,31 +1072,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="8">
+      <c r="A72" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="4">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
+      <c r="A75" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="6"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1126,31 +1129,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="8">
+      <c r="A80" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="4">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="4"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="A83" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="6"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="8"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1183,31 +1186,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="8">
+      <c r="A88" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="4">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="4"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
+      <c r="A91" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="6"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1240,31 +1243,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="8">
+      <c r="A96" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="4">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="7"/>
-      <c r="B97" s="8"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="4"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="A99" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="6"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="8"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1297,31 +1300,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="8">
+      <c r="A104" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="4">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="7"/>
-      <c r="B105" s="8"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="4"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="A107" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="6"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="8"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1354,31 +1357,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="8">
+      <c r="A112" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="4">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="7"/>
-      <c r="B113" s="8"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="4"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="A115" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="6"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="8"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1411,31 +1414,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="8">
+      <c r="A120" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="4">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="7"/>
-      <c r="B121" s="8"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="4"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="A123" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="6"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="8"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1468,17 +1471,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="8">
+      <c r="A128" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="4">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="7"/>
-      <c r="B129" s="8"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="4"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1489,18 +1492,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="A132" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="5"/>
-      <c r="C133" s="6"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="8"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1533,31 +1536,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="8">
+      <c r="A137" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="4">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="7"/>
-      <c r="B138" s="8"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="4"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
+      <c r="A140" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="5"/>
-      <c r="C141" s="6"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="8"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1590,31 +1593,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="8">
+      <c r="A145" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="4">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="7"/>
-      <c r="B146" s="8"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="4"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
+      <c r="A148" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="6"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="8"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1647,31 +1650,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="8">
+      <c r="A153" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="4">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="7"/>
-      <c r="B154" s="8"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="4"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
+      <c r="A156" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="5"/>
-      <c r="C157" s="6"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="8"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1704,31 +1707,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="8">
+      <c r="A161" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="4">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="7"/>
-      <c r="B162" s="8"/>
+      <c r="A162" s="3"/>
+      <c r="B162" s="4"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
+      <c r="A164" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="5"/>
-      <c r="C165" s="6"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1761,31 +1764,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="8">
+      <c r="A169" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="4">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="7"/>
-      <c r="B170" s="8"/>
+      <c r="A170" s="3"/>
+      <c r="B170" s="4"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
+      <c r="A172" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="6"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="8"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1818,31 +1821,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="8">
+      <c r="A177" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="4">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="7"/>
-      <c r="B178" s="8"/>
+      <c r="A178" s="3"/>
+      <c r="B178" s="4"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
+      <c r="A180" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="6"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="8"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1875,17 +1878,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="8">
+      <c r="A185" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="4">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="7"/>
-      <c r="B186" s="8"/>
+      <c r="A186" s="3"/>
+      <c r="B186" s="4"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1896,18 +1899,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
+      <c r="A189" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="5"/>
-      <c r="C190" s="6"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="8"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1940,31 +1943,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="8">
+      <c r="A194" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="4">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="7"/>
-      <c r="B195" s="8"/>
+      <c r="A195" s="3"/>
+      <c r="B195" s="4"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
+      <c r="A197" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="5"/>
+      <c r="C197" s="5"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="5"/>
-      <c r="C198" s="6"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="8"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -1997,31 +2000,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="8">
+      <c r="A202" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="4">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="7"/>
-      <c r="B203" s="8"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="4"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="3"/>
-      <c r="C205" s="3"/>
+      <c r="A205" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="5"/>
-      <c r="C206" s="6"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="8"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2054,31 +2057,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="8">
+      <c r="A210" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="4">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="7"/>
-      <c r="B211" s="8"/>
+      <c r="A211" s="3"/>
+      <c r="B211" s="4"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="3"/>
-      <c r="C213" s="3"/>
+      <c r="A213" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="5"/>
+      <c r="C213" s="5"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="6"/>
+      <c r="B214" s="7"/>
+      <c r="C214" s="8"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2111,31 +2114,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="8">
+      <c r="A218" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="4">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="7"/>
-      <c r="B219" s="8"/>
+      <c r="A219" s="3"/>
+      <c r="B219" s="4"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="3"/>
-      <c r="C221" s="3"/>
+      <c r="A221" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="5"/>
+      <c r="C221" s="5"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="5"/>
-      <c r="C222" s="6"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="8"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2168,31 +2171,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="8">
+      <c r="A226" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="4">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="7"/>
-      <c r="B227" s="8"/>
+      <c r="A227" s="3"/>
+      <c r="B227" s="4"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="3"/>
-      <c r="C229" s="3"/>
+      <c r="A229" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="5"/>
+      <c r="C229" s="5"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="5"/>
-      <c r="C230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="8"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2225,31 +2228,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="8">
+      <c r="A234" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="4">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="7"/>
-      <c r="B235" s="8"/>
+      <c r="A235" s="3"/>
+      <c r="B235" s="4"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="3"/>
-      <c r="C237" s="3"/>
+      <c r="A237" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="5"/>
+      <c r="C237" s="5"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="6"/>
+      <c r="B238" s="7"/>
+      <c r="C238" s="8"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2282,17 +2285,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="8">
+      <c r="A242" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="4">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="7"/>
-      <c r="B243" s="8"/>
+      <c r="A243" s="3"/>
+      <c r="B243" s="4"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2303,18 +2306,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="3"/>
-      <c r="C246" s="3"/>
+      <c r="A246" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="5"/>
+      <c r="C246" s="5"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="4" t="s">
+      <c r="A247" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="5"/>
-      <c r="C247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="8"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2347,31 +2350,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="8">
+      <c r="A251" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="4">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="7"/>
-      <c r="B252" s="8"/>
+      <c r="A252" s="3"/>
+      <c r="B252" s="4"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="3"/>
-      <c r="C254" s="3"/>
+      <c r="A254" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="5"/>
+      <c r="C254" s="5"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="5"/>
-      <c r="C255" s="6"/>
+      <c r="B255" s="7"/>
+      <c r="C255" s="8"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2404,31 +2407,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="8">
+      <c r="A259" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="4">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="7"/>
-      <c r="B260" s="8"/>
+      <c r="A260" s="3"/>
+      <c r="B260" s="4"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="3"/>
-      <c r="C262" s="3"/>
+      <c r="A262" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="5"/>
+      <c r="C262" s="5"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="4" t="s">
+      <c r="A263" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="5"/>
-      <c r="C263" s="6"/>
+      <c r="B263" s="7"/>
+      <c r="C263" s="8"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2461,17 +2464,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="8">
+      <c r="A267" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="4">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="7"/>
-      <c r="B268" s="8"/>
+      <c r="A268" s="3"/>
+      <c r="B268" s="4"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2482,18 +2485,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="3"/>
-      <c r="C271" s="3"/>
+      <c r="A271" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="5"/>
+      <c r="C271" s="5"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="5"/>
-      <c r="C272" s="6"/>
+      <c r="B272" s="7"/>
+      <c r="C272" s="8"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2526,31 +2529,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="8">
+      <c r="A276" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="4">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="7"/>
-      <c r="B277" s="8"/>
+      <c r="A277" s="3"/>
+      <c r="B277" s="4"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="3"/>
-      <c r="C279" s="3"/>
+      <c r="A279" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="5"/>
+      <c r="C279" s="5"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="5"/>
-      <c r="C280" s="6"/>
+      <c r="B280" s="7"/>
+      <c r="C280" s="8"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2583,31 +2586,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="8">
+      <c r="A284" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="4">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="7"/>
-      <c r="B285" s="8"/>
+      <c r="A285" s="3"/>
+      <c r="B285" s="4"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="3"/>
-      <c r="C287" s="3"/>
+      <c r="A287" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="5"/>
+      <c r="C287" s="5"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="4" t="s">
+      <c r="A288" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="5"/>
-      <c r="C288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="8"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2640,31 +2643,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="8">
+      <c r="A292" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="4">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="7"/>
-      <c r="B293" s="8"/>
+      <c r="A293" s="3"/>
+      <c r="B293" s="4"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="3"/>
-      <c r="C295" s="3"/>
+      <c r="A295" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="5"/>
+      <c r="C295" s="5"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="5"/>
-      <c r="C296" s="6"/>
+      <c r="B296" s="7"/>
+      <c r="C296" s="8"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2697,31 +2700,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="8">
+      <c r="A300" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="4">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="7"/>
-      <c r="B301" s="8"/>
+      <c r="A301" s="3"/>
+      <c r="B301" s="4"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="3"/>
-      <c r="C303" s="3"/>
+      <c r="A303" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="5"/>
+      <c r="C303" s="5"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="4" t="s">
+      <c r="A304" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="5"/>
-      <c r="C304" s="6"/>
+      <c r="B304" s="7"/>
+      <c r="C304" s="8"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2754,31 +2757,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="8">
+      <c r="A308" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="4">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="7"/>
-      <c r="B309" s="8"/>
+      <c r="A309" s="3"/>
+      <c r="B309" s="4"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="3"/>
-      <c r="C311" s="3"/>
+      <c r="A311" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="5"/>
+      <c r="C311" s="5"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="4" t="s">
+      <c r="A312" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="5"/>
-      <c r="C312" s="6"/>
+      <c r="B312" s="7"/>
+      <c r="C312" s="8"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2811,31 +2814,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="8">
+      <c r="A316" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="4">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="7"/>
-      <c r="B317" s="8"/>
+      <c r="A317" s="3"/>
+      <c r="B317" s="4"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="3"/>
-      <c r="C319" s="3"/>
+      <c r="A319" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="5"/>
+      <c r="C319" s="5"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="4" t="s">
+      <c r="A320" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="5"/>
-      <c r="C320" s="6"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="8"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2868,17 +2871,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="8">
+      <c r="A324" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="4">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="7"/>
-      <c r="B325" s="8"/>
+      <c r="A325" s="3"/>
+      <c r="B325" s="4"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2889,18 +2892,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="3"/>
-      <c r="C328" s="3"/>
+      <c r="A328" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="5"/>
+      <c r="C328" s="5"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="4" t="s">
+      <c r="A329" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="5"/>
-      <c r="C329" s="6"/>
+      <c r="B329" s="7"/>
+      <c r="C329" s="8"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2933,31 +2936,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="8">
+      <c r="A333" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="4">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="7"/>
-      <c r="B334" s="8"/>
+      <c r="A334" s="3"/>
+      <c r="B334" s="4"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="3"/>
-      <c r="C336" s="3"/>
+      <c r="A336" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="5"/>
+      <c r="C336" s="5"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="5"/>
-      <c r="C337" s="6"/>
+      <c r="B337" s="7"/>
+      <c r="C337" s="8"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2990,31 +2993,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="8">
+      <c r="A341" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="4">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="7"/>
-      <c r="B342" s="8"/>
+      <c r="A342" s="3"/>
+      <c r="B342" s="4"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="3"/>
-      <c r="C344" s="3"/>
+      <c r="A344" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="5"/>
+      <c r="C344" s="5"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="5"/>
-      <c r="C345" s="6"/>
+      <c r="B345" s="7"/>
+      <c r="C345" s="8"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3047,31 +3050,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="8">
+      <c r="A349" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="4">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="7"/>
-      <c r="B350" s="8"/>
+      <c r="A350" s="3"/>
+      <c r="B350" s="4"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="3"/>
-      <c r="C352" s="3"/>
+      <c r="A352" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="5"/>
+      <c r="C352" s="5"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="4" t="s">
+      <c r="A353" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="5"/>
-      <c r="C353" s="6"/>
+      <c r="B353" s="7"/>
+      <c r="C353" s="8"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3104,31 +3107,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="8">
+      <c r="A357" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="4">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="7"/>
-      <c r="B358" s="8"/>
+      <c r="A358" s="3"/>
+      <c r="B358" s="4"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="3"/>
-      <c r="C360" s="3"/>
+      <c r="A360" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="5"/>
+      <c r="C360" s="5"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="5"/>
-      <c r="C361" s="6"/>
+      <c r="B361" s="7"/>
+      <c r="C361" s="8"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3161,31 +3164,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="8">
+      <c r="A365" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="4">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="7"/>
-      <c r="B366" s="8"/>
+      <c r="A366" s="3"/>
+      <c r="B366" s="4"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="3"/>
-      <c r="C368" s="3"/>
+      <c r="A368" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="5"/>
+      <c r="C368" s="5"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="4" t="s">
+      <c r="A369" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="5"/>
-      <c r="C369" s="6"/>
+      <c r="B369" s="7"/>
+      <c r="C369" s="8"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3218,31 +3221,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="8">
+      <c r="A373" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="4">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="7"/>
-      <c r="B374" s="8"/>
+      <c r="A374" s="3"/>
+      <c r="B374" s="4"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="3"/>
-      <c r="C376" s="3"/>
+      <c r="A376" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="5"/>
+      <c r="C376" s="5"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="4" t="s">
+      <c r="A377" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="5"/>
-      <c r="C377" s="6"/>
+      <c r="B377" s="7"/>
+      <c r="C377" s="8"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3275,17 +3278,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="8">
+      <c r="A381" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="4">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="7"/>
-      <c r="B382" s="8"/>
+      <c r="A382" s="3"/>
+      <c r="B382" s="4"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3296,18 +3299,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="3"/>
-      <c r="C385" s="3"/>
+      <c r="A385" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="5"/>
+      <c r="C385" s="5"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="5"/>
-      <c r="C386" s="6"/>
+      <c r="B386" s="7"/>
+      <c r="C386" s="8"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3340,31 +3343,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="8">
+      <c r="A390" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="4">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="7"/>
-      <c r="B391" s="8"/>
+      <c r="A391" s="3"/>
+      <c r="B391" s="4"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="3"/>
-      <c r="C393" s="3"/>
+      <c r="A393" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="5"/>
+      <c r="C393" s="5"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="4" t="s">
+      <c r="A394" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="5"/>
-      <c r="C394" s="6"/>
+      <c r="B394" s="7"/>
+      <c r="C394" s="8"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3397,31 +3400,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="8">
+      <c r="A398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="4">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="7"/>
-      <c r="B399" s="8"/>
+      <c r="A399" s="3"/>
+      <c r="B399" s="4"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="3"/>
-      <c r="C401" s="3"/>
+      <c r="A401" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="5"/>
+      <c r="C401" s="5"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="4" t="s">
+      <c r="A402" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="5"/>
-      <c r="C402" s="6"/>
+      <c r="B402" s="7"/>
+      <c r="C402" s="8"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3454,31 +3457,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="8">
+      <c r="A406" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="4">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="7"/>
-      <c r="B407" s="8"/>
+      <c r="A407" s="3"/>
+      <c r="B407" s="4"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="3"/>
-      <c r="C409" s="3"/>
+      <c r="A409" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="5"/>
+      <c r="C409" s="5"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="4" t="s">
+      <c r="A410" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="5"/>
-      <c r="C410" s="6"/>
+      <c r="B410" s="7"/>
+      <c r="C410" s="8"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3511,31 +3514,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="8">
+      <c r="A414" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="4">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="7"/>
-      <c r="B415" s="8"/>
+      <c r="A415" s="3"/>
+      <c r="B415" s="4"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="3"/>
-      <c r="C417" s="3"/>
+      <c r="A417" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="5"/>
+      <c r="C417" s="5"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="4" t="s">
+      <c r="A418" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="5"/>
-      <c r="C418" s="6"/>
+      <c r="B418" s="7"/>
+      <c r="C418" s="8"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3568,31 +3571,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="8">
+      <c r="A422" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="4">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="7"/>
-      <c r="B423" s="8"/>
+      <c r="A423" s="3"/>
+      <c r="B423" s="4"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="3"/>
-      <c r="C425" s="3"/>
+      <c r="A425" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="5"/>
+      <c r="C425" s="5"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="4" t="s">
+      <c r="A426" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="5"/>
-      <c r="C426" s="6"/>
+      <c r="B426" s="7"/>
+      <c r="C426" s="8"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3625,31 +3628,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="8">
+      <c r="A430" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="4">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="7"/>
-      <c r="B431" s="8"/>
+      <c r="A431" s="3"/>
+      <c r="B431" s="4"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
+      <c r="A433" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="5"/>
+      <c r="C433" s="5"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="4" t="s">
+      <c r="A434" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="5"/>
-      <c r="C434" s="6"/>
+      <c r="B434" s="7"/>
+      <c r="C434" s="8"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3682,17 +3685,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="8">
+      <c r="A438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="4">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="7"/>
-      <c r="B439" s="8"/>
+      <c r="A439" s="3"/>
+      <c r="B439" s="4"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3703,18 +3706,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
+      <c r="A442" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="5"/>
+      <c r="C442" s="5"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="4" t="s">
+      <c r="A443" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="5"/>
-      <c r="C443" s="6"/>
+      <c r="B443" s="7"/>
+      <c r="C443" s="8"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3747,31 +3750,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="8">
+      <c r="A447" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="4">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="7"/>
-      <c r="B448" s="8"/>
+      <c r="A448" s="3"/>
+      <c r="B448" s="4"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="3"/>
-      <c r="C450" s="3"/>
+      <c r="A450" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="5"/>
+      <c r="C450" s="5"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="5"/>
-      <c r="C451" s="6"/>
+      <c r="B451" s="7"/>
+      <c r="C451" s="8"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3804,31 +3807,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="8">
+      <c r="A455" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="4">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="7"/>
-      <c r="B456" s="8"/>
+      <c r="A456" s="3"/>
+      <c r="B456" s="4"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
+      <c r="A458" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="5"/>
+      <c r="C458" s="5"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="4" t="s">
+      <c r="A459" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="5"/>
-      <c r="C459" s="6"/>
+      <c r="B459" s="7"/>
+      <c r="C459" s="8"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3861,31 +3864,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="8">
+      <c r="A463" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="4">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="7"/>
-      <c r="B464" s="8"/>
+      <c r="A464" s="3"/>
+      <c r="B464" s="4"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="3"/>
-      <c r="C466" s="3"/>
+      <c r="A466" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="5"/>
+      <c r="C466" s="5"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="4" t="s">
+      <c r="A467" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="5"/>
-      <c r="C467" s="6"/>
+      <c r="B467" s="7"/>
+      <c r="C467" s="8"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3918,31 +3921,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="8">
+      <c r="A471" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="4">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="7"/>
-      <c r="B472" s="8"/>
+      <c r="A472" s="3"/>
+      <c r="B472" s="4"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="3"/>
-      <c r="C474" s="3"/>
+      <c r="A474" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="5"/>
+      <c r="C474" s="5"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="4" t="s">
+      <c r="A475" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="5"/>
-      <c r="C475" s="6"/>
+      <c r="B475" s="7"/>
+      <c r="C475" s="8"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3975,31 +3978,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="8">
+      <c r="A479" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="4">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="7"/>
-      <c r="B480" s="8"/>
+      <c r="A480" s="3"/>
+      <c r="B480" s="4"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="3"/>
-      <c r="C482" s="3"/>
+      <c r="A482" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="5"/>
+      <c r="C482" s="5"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="4" t="s">
+      <c r="A483" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="5"/>
-      <c r="C483" s="6"/>
+      <c r="B483" s="7"/>
+      <c r="C483" s="8"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4032,31 +4035,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="8">
+      <c r="A487" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="4">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="7"/>
-      <c r="B488" s="8"/>
+      <c r="A488" s="3"/>
+      <c r="B488" s="4"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="3"/>
-      <c r="C490" s="3"/>
+      <c r="A490" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="5"/>
+      <c r="C490" s="5"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="4" t="s">
+      <c r="A491" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="5"/>
-      <c r="C491" s="6"/>
+      <c r="B491" s="7"/>
+      <c r="C491" s="8"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4089,17 +4092,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="8">
+      <c r="A495" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="4">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="7"/>
-      <c r="B496" s="8"/>
+      <c r="A496" s="3"/>
+      <c r="B496" s="4"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4110,18 +4113,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="3"/>
-      <c r="C499" s="3"/>
+      <c r="A499" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="5"/>
+      <c r="C499" s="5"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="4" t="s">
+      <c r="A500" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="5"/>
-      <c r="C500" s="6"/>
+      <c r="B500" s="7"/>
+      <c r="C500" s="8"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4154,31 +4157,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="8">
+      <c r="A504" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="4">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="7"/>
-      <c r="B505" s="8"/>
+      <c r="A505" s="3"/>
+      <c r="B505" s="4"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="3"/>
-      <c r="C507" s="3"/>
+      <c r="A507" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="5"/>
+      <c r="C507" s="5"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="4" t="s">
+      <c r="A508" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="5"/>
-      <c r="C508" s="6"/>
+      <c r="B508" s="7"/>
+      <c r="C508" s="8"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4211,31 +4214,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="8">
+      <c r="A512" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="4">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="7"/>
-      <c r="B513" s="8"/>
+      <c r="A513" s="3"/>
+      <c r="B513" s="4"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="3"/>
-      <c r="C515" s="3"/>
+      <c r="A515" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="5"/>
+      <c r="C515" s="5"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="4" t="s">
+      <c r="A516" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="5"/>
-      <c r="C516" s="6"/>
+      <c r="B516" s="7"/>
+      <c r="C516" s="8"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4268,31 +4271,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="8">
+      <c r="A520" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="4">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="7"/>
-      <c r="B521" s="8"/>
+      <c r="A521" s="3"/>
+      <c r="B521" s="4"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="3"/>
-      <c r="C523" s="3"/>
+      <c r="A523" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="5"/>
+      <c r="C523" s="5"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="4" t="s">
+      <c r="A524" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="5"/>
-      <c r="C524" s="6"/>
+      <c r="B524" s="7"/>
+      <c r="C524" s="8"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4325,31 +4328,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="8">
+      <c r="A528" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="4">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="7"/>
-      <c r="B529" s="8"/>
+      <c r="A529" s="3"/>
+      <c r="B529" s="4"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="3"/>
-      <c r="C531" s="3"/>
+      <c r="A531" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="5"/>
+      <c r="C531" s="5"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="4" t="s">
+      <c r="A532" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="5"/>
-      <c r="C532" s="6"/>
+      <c r="B532" s="7"/>
+      <c r="C532" s="8"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4382,31 +4385,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="8">
+      <c r="A536" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="4">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="7"/>
-      <c r="B537" s="8"/>
+      <c r="A537" s="3"/>
+      <c r="B537" s="4"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="3"/>
-      <c r="C539" s="3"/>
+      <c r="A539" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="5"/>
+      <c r="C539" s="5"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="4" t="s">
+      <c r="A540" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="5"/>
-      <c r="C540" s="6"/>
+      <c r="B540" s="7"/>
+      <c r="C540" s="8"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4439,31 +4442,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="8">
+      <c r="A544" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="4">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="7"/>
-      <c r="B545" s="8"/>
+      <c r="A545" s="3"/>
+      <c r="B545" s="4"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="3"/>
-      <c r="C547" s="3"/>
+      <c r="A547" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="5"/>
+      <c r="C547" s="5"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="4" t="s">
+      <c r="A548" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="5"/>
-      <c r="C548" s="6"/>
+      <c r="B548" s="7"/>
+      <c r="C548" s="8"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4496,17 +4499,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="8">
+      <c r="A552" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="4">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="7"/>
-      <c r="B553" s="8"/>
+      <c r="A553" s="3"/>
+      <c r="B553" s="4"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4517,18 +4520,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="3"/>
-      <c r="C556" s="3"/>
+      <c r="A556" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="5"/>
+      <c r="C556" s="5"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="4" t="s">
+      <c r="A557" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="5"/>
-      <c r="C557" s="6"/>
+      <c r="B557" s="7"/>
+      <c r="C557" s="8"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4561,31 +4564,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="8">
+      <c r="A561" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="4">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="7"/>
-      <c r="B562" s="8"/>
+      <c r="A562" s="3"/>
+      <c r="B562" s="4"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="3"/>
-      <c r="C564" s="3"/>
+      <c r="A564" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="5"/>
+      <c r="C564" s="5"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="4" t="s">
+      <c r="A565" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="5"/>
-      <c r="C565" s="6"/>
+      <c r="B565" s="7"/>
+      <c r="C565" s="8"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4618,31 +4621,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="8">
+      <c r="A569" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="4">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="7"/>
-      <c r="B570" s="8"/>
+      <c r="A570" s="3"/>
+      <c r="B570" s="4"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="3"/>
-      <c r="C572" s="3"/>
+      <c r="A572" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="5"/>
+      <c r="C572" s="5"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="4" t="s">
+      <c r="A573" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="5"/>
-      <c r="C573" s="6"/>
+      <c r="B573" s="7"/>
+      <c r="C573" s="8"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4675,31 +4678,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="8">
+      <c r="A577" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="4">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="7"/>
-      <c r="B578" s="8"/>
+      <c r="A578" s="3"/>
+      <c r="B578" s="4"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="3"/>
-      <c r="C580" s="3"/>
+      <c r="A580" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="5"/>
+      <c r="C580" s="5"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="4" t="s">
+      <c r="A581" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="5"/>
-      <c r="C581" s="6"/>
+      <c r="B581" s="7"/>
+      <c r="C581" s="8"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4732,17 +4735,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="8">
+      <c r="A585" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="4">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="7"/>
-      <c r="B586" s="8"/>
+      <c r="A586" s="3"/>
+      <c r="B586" s="4"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4753,18 +4756,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="3"/>
-      <c r="C589" s="3"/>
+      <c r="A589" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="5"/>
+      <c r="C589" s="5"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="4" t="s">
+      <c r="A590" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="5"/>
-      <c r="C590" s="6"/>
+      <c r="B590" s="7"/>
+      <c r="C590" s="8"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4797,31 +4800,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="8">
+      <c r="A594" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="4">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="7"/>
-      <c r="B595" s="8"/>
+      <c r="A595" s="3"/>
+      <c r="B595" s="4"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="3"/>
-      <c r="C597" s="3"/>
+      <c r="A597" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="5"/>
+      <c r="C597" s="5"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="4" t="s">
+      <c r="A598" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="5"/>
-      <c r="C598" s="6"/>
+      <c r="B598" s="7"/>
+      <c r="C598" s="8"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4854,31 +4857,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="8">
+      <c r="A602" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="4">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="7"/>
-      <c r="B603" s="8"/>
+      <c r="A603" s="3"/>
+      <c r="B603" s="4"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="3"/>
-      <c r="C605" s="3"/>
+      <c r="A605" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="5"/>
+      <c r="C605" s="5"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="4" t="s">
+      <c r="A606" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="5"/>
-      <c r="C606" s="6"/>
+      <c r="B606" s="7"/>
+      <c r="C606" s="8"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4911,31 +4914,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="8">
+      <c r="A610" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="4">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="7"/>
-      <c r="B611" s="8"/>
+      <c r="A611" s="3"/>
+      <c r="B611" s="4"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="3"/>
-      <c r="C613" s="3"/>
+      <c r="A613" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="5"/>
+      <c r="C613" s="5"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="4" t="s">
+      <c r="A614" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="5"/>
-      <c r="C614" s="6"/>
+      <c r="B614" s="7"/>
+      <c r="C614" s="8"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4968,31 +4971,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="8">
+      <c r="A618" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="4">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="7"/>
-      <c r="B619" s="8"/>
+      <c r="A619" s="3"/>
+      <c r="B619" s="4"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="3"/>
-      <c r="C621" s="3"/>
+      <c r="A621" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="5"/>
+      <c r="C621" s="5"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="4" t="s">
+      <c r="A622" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="5"/>
-      <c r="C622" s="6"/>
+      <c r="B622" s="7"/>
+      <c r="C622" s="8"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5025,31 +5028,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="8">
+      <c r="A626" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="4">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="7"/>
-      <c r="B627" s="8"/>
+      <c r="A627" s="3"/>
+      <c r="B627" s="4"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="3"/>
-      <c r="C629" s="3"/>
+      <c r="A629" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="5"/>
+      <c r="C629" s="5"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="4" t="s">
+      <c r="A630" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="5"/>
-      <c r="C630" s="6"/>
+      <c r="B630" s="7"/>
+      <c r="C630" s="8"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5082,31 +5085,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="8">
+      <c r="A634" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="4">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="7"/>
-      <c r="B635" s="8"/>
+      <c r="A635" s="3"/>
+      <c r="B635" s="4"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="3"/>
-      <c r="C637" s="3"/>
+      <c r="A637" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="5"/>
+      <c r="C637" s="5"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="4" t="s">
+      <c r="A638" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="5"/>
-      <c r="C638" s="6"/>
+      <c r="B638" s="7"/>
+      <c r="C638" s="8"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5139,17 +5142,17 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="8">
+      <c r="A642" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="4">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="7"/>
-      <c r="B643" s="8"/>
+      <c r="A643" s="3"/>
+      <c r="B643" s="4"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
@@ -5160,18 +5163,18 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="3"/>
-      <c r="C646" s="3"/>
+      <c r="A646" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="5"/>
+      <c r="C646" s="5"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="4" t="s">
+      <c r="A647" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="5"/>
-      <c r="C647" s="6"/>
+      <c r="B647" s="7"/>
+      <c r="C647" s="8"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5204,31 +5207,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="8">
+      <c r="A651" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="4">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="7"/>
-      <c r="B652" s="8"/>
+      <c r="A652" s="3"/>
+      <c r="B652" s="4"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="3"/>
-      <c r="C654" s="3"/>
+      <c r="A654" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="5"/>
+      <c r="C654" s="5"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="4" t="s">
+      <c r="A655" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="5"/>
-      <c r="C655" s="6"/>
+      <c r="B655" s="7"/>
+      <c r="C655" s="8"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5261,31 +5264,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="8">
+      <c r="A659" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="4">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="7"/>
-      <c r="B660" s="8"/>
+      <c r="A660" s="3"/>
+      <c r="B660" s="4"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="3"/>
-      <c r="C662" s="3"/>
+      <c r="A662" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="5"/>
+      <c r="C662" s="5"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="4" t="s">
+      <c r="A663" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="5"/>
-      <c r="C663" s="6"/>
+      <c r="B663" s="7"/>
+      <c r="C663" s="8"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5318,31 +5321,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="8">
+      <c r="A667" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="4">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="7"/>
-      <c r="B668" s="8"/>
+      <c r="A668" s="3"/>
+      <c r="B668" s="4"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="3"/>
-      <c r="C670" s="3"/>
+      <c r="A670" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="5"/>
+      <c r="C670" s="5"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="4" t="s">
+      <c r="A671" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="5"/>
-      <c r="C671" s="6"/>
+      <c r="B671" s="7"/>
+      <c r="C671" s="8"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5375,31 +5378,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="8">
+      <c r="A675" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="4">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="7"/>
-      <c r="B676" s="8"/>
+      <c r="A676" s="3"/>
+      <c r="B676" s="4"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="3"/>
-      <c r="C678" s="3"/>
+      <c r="A678" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="5"/>
+      <c r="C678" s="5"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="4" t="s">
+      <c r="A679" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="5"/>
-      <c r="C679" s="6"/>
+      <c r="B679" s="7"/>
+      <c r="C679" s="8"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5432,31 +5435,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="8">
+      <c r="A683" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="4">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="7"/>
-      <c r="B684" s="8"/>
+      <c r="A684" s="3"/>
+      <c r="B684" s="4"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="3"/>
-      <c r="C686" s="3"/>
+      <c r="A686" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="5"/>
+      <c r="C686" s="5"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="4" t="s">
+      <c r="A687" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="5"/>
-      <c r="C687" s="6"/>
+      <c r="B687" s="7"/>
+      <c r="C687" s="8"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5489,31 +5492,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="8">
+      <c r="A691" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="4">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="7"/>
-      <c r="B692" s="8"/>
+      <c r="A692" s="3"/>
+      <c r="B692" s="4"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="3"/>
-      <c r="C694" s="3"/>
+      <c r="A694" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="5"/>
+      <c r="C694" s="5"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="4" t="s">
+      <c r="A695" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="5"/>
-      <c r="C695" s="6"/>
+      <c r="B695" s="7"/>
+      <c r="C695" s="8"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5546,31 +5549,31 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="8">
+      <c r="A699" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="4">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="7"/>
-      <c r="B700" s="8"/>
+      <c r="A700" s="3"/>
+      <c r="B700" s="4"/>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B702" s="3"/>
-      <c r="C702" s="3"/>
+      <c r="A702" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B702" s="5"/>
+      <c r="C702" s="5"/>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="4" t="s">
+      <c r="A703" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B703" s="5"/>
-      <c r="C703" s="6"/>
+      <c r="B703" s="7"/>
+      <c r="C703" s="8"/>
     </row>
     <row r="704" spans="1:3">
       <c r="A704" s="1" t="s">
@@ -5603,17 +5606,17 @@
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B707" s="8">
+      <c r="A707" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="4">
         <f>B705-B706</f>
         <v>448</v>
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="7"/>
-      <c r="B708" s="8"/>
+      <c r="A708" s="3"/>
+      <c r="B708" s="4"/>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" s="1" t="s">
@@ -5624,18 +5627,18 @@
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B711" s="3"/>
-      <c r="C711" s="3"/>
+      <c r="A711" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="5"/>
+      <c r="C711" s="5"/>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="4" t="s">
+      <c r="A712" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B712" s="5"/>
-      <c r="C712" s="6"/>
+      <c r="B712" s="7"/>
+      <c r="C712" s="8"/>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" s="1" t="s">
@@ -5668,31 +5671,31 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B716" s="8">
+      <c r="A716" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="4">
         <f>B714-B715</f>
         <v>27</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="7"/>
-      <c r="B717" s="8"/>
+      <c r="A717" s="3"/>
+      <c r="B717" s="4"/>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B719" s="3"/>
-      <c r="C719" s="3"/>
+      <c r="A719" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="5"/>
+      <c r="C719" s="5"/>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="4" t="s">
+      <c r="A720" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B720" s="5"/>
-      <c r="C720" s="6"/>
+      <c r="B720" s="7"/>
+      <c r="C720" s="8"/>
     </row>
     <row r="721" spans="1:3">
       <c r="A721" s="1" t="s">
@@ -5725,31 +5728,31 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B724" s="8">
+      <c r="A724" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="4">
         <f>B722-B723</f>
         <v>386</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="7"/>
-      <c r="B725" s="8"/>
+      <c r="A725" s="3"/>
+      <c r="B725" s="4"/>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B727" s="3"/>
-      <c r="C727" s="3"/>
+      <c r="A727" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="5"/>
+      <c r="C727" s="5"/>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="4" t="s">
+      <c r="A728" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B728" s="5"/>
-      <c r="C728" s="6"/>
+      <c r="B728" s="7"/>
+      <c r="C728" s="8"/>
     </row>
     <row r="729" spans="1:3">
       <c r="A729" s="1" t="s">
@@ -5782,31 +5785,31 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B732" s="8">
+      <c r="A732" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="4">
         <f>B730-B731</f>
         <v>1256</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="7"/>
-      <c r="B733" s="8"/>
+      <c r="A733" s="3"/>
+      <c r="B733" s="4"/>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B735" s="3"/>
-      <c r="C735" s="3"/>
+      <c r="A735" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="5"/>
+      <c r="C735" s="5"/>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="4" t="s">
+      <c r="A736" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B736" s="5"/>
-      <c r="C736" s="6"/>
+      <c r="B736" s="7"/>
+      <c r="C736" s="8"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="1" t="s">
@@ -5839,31 +5842,31 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B740" s="8">
+      <c r="A740" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="4">
         <f>B738-B739</f>
         <v>227</v>
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="7"/>
-      <c r="B741" s="8"/>
+      <c r="A741" s="3"/>
+      <c r="B741" s="4"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B743" s="3"/>
-      <c r="C743" s="3"/>
+      <c r="A743" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="5"/>
+      <c r="C743" s="5"/>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="4" t="s">
+      <c r="A744" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B744" s="5"/>
-      <c r="C744" s="6"/>
+      <c r="B744" s="7"/>
+      <c r="C744" s="8"/>
     </row>
     <row r="745" spans="1:3">
       <c r="A745" s="1" t="s">
@@ -5896,31 +5899,31 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B748" s="8">
+      <c r="A748" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="4">
         <f>B746-B747</f>
         <v>961</v>
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="7"/>
-      <c r="B749" s="8"/>
+      <c r="A749" s="3"/>
+      <c r="B749" s="4"/>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B751" s="3"/>
-      <c r="C751" s="3"/>
+      <c r="A751" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="5"/>
+      <c r="C751" s="5"/>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="4" t="s">
+      <c r="A752" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B752" s="5"/>
-      <c r="C752" s="6"/>
+      <c r="B752" s="7"/>
+      <c r="C752" s="8"/>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" s="1" t="s">
@@ -5953,31 +5956,31 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="8">
+      <c r="A756" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="4">
         <f>B754-B755</f>
         <v>6</v>
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="7"/>
-      <c r="B757" s="8"/>
+      <c r="A757" s="3"/>
+      <c r="B757" s="4"/>
     </row>
     <row r="759" spans="1:3">
-      <c r="A759" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B759" s="3"/>
-      <c r="C759" s="3"/>
+      <c r="A759" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B759" s="5"/>
+      <c r="C759" s="5"/>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="4" t="s">
+      <c r="A760" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B760" s="5"/>
-      <c r="C760" s="6"/>
+      <c r="B760" s="7"/>
+      <c r="C760" s="8"/>
     </row>
     <row r="761" spans="1:3">
       <c r="A761" s="1" t="s">
@@ -6010,31 +6013,31 @@
       </c>
     </row>
     <row r="764" spans="1:3">
-      <c r="A764" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B764" s="8">
+      <c r="A764" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764" s="4">
         <f>B762-B763</f>
         <v>616</v>
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="7"/>
-      <c r="B765" s="8"/>
+      <c r="A765" s="3"/>
+      <c r="B765" s="4"/>
     </row>
     <row r="767" spans="1:3">
-      <c r="A767" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B767" s="3"/>
-      <c r="C767" s="3"/>
+      <c r="A767" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B767" s="5"/>
+      <c r="C767" s="5"/>
     </row>
     <row r="768" spans="1:3">
-      <c r="A768" s="4" t="s">
+      <c r="A768" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B768" s="5"/>
-      <c r="C768" s="6"/>
+      <c r="B768" s="7"/>
+      <c r="C768" s="8"/>
     </row>
     <row r="769" spans="1:3">
       <c r="A769" s="1" t="s">
@@ -6067,17 +6070,17 @@
       </c>
     </row>
     <row r="772" spans="1:3">
-      <c r="A772" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B772" s="8">
+      <c r="A772" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B772" s="4">
         <f>B770-B771</f>
         <v>379</v>
       </c>
     </row>
     <row r="773" spans="1:3">
-      <c r="A773" s="7"/>
-      <c r="B773" s="8"/>
+      <c r="A773" s="3"/>
+      <c r="B773" s="4"/>
     </row>
     <row r="774" spans="1:3">
       <c r="A774" s="1" t="s">
@@ -6088,18 +6091,18 @@
       </c>
     </row>
     <row r="776" spans="1:3">
-      <c r="A776" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B776" s="3"/>
-      <c r="C776" s="3"/>
+      <c r="A776" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B776" s="5"/>
+      <c r="C776" s="5"/>
     </row>
     <row r="777" spans="1:3">
-      <c r="A777" s="4" t="s">
+      <c r="A777" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B777" s="5"/>
-      <c r="C777" s="6"/>
+      <c r="B777" s="7"/>
+      <c r="C777" s="8"/>
     </row>
     <row r="778" spans="1:3">
       <c r="A778" s="1" t="s">
@@ -6132,31 +6135,31 @@
       </c>
     </row>
     <row r="781" spans="1:3">
-      <c r="A781" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B781" s="8">
+      <c r="A781" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781" s="4">
         <f>B779-B780</f>
         <v>276</v>
       </c>
     </row>
     <row r="782" spans="1:3">
-      <c r="A782" s="7"/>
-      <c r="B782" s="8"/>
+      <c r="A782" s="3"/>
+      <c r="B782" s="4"/>
     </row>
     <row r="784" spans="1:3">
-      <c r="A784" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B784" s="3"/>
-      <c r="C784" s="3"/>
+      <c r="A784" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B784" s="5"/>
+      <c r="C784" s="5"/>
     </row>
     <row r="785" spans="1:3">
-      <c r="A785" s="4" t="s">
+      <c r="A785" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B785" s="5"/>
-      <c r="C785" s="6"/>
+      <c r="B785" s="7"/>
+      <c r="C785" s="8"/>
     </row>
     <row r="786" spans="1:3">
       <c r="A786" s="1" t="s">
@@ -6189,31 +6192,31 @@
       </c>
     </row>
     <row r="789" spans="1:3">
-      <c r="A789" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B789" s="8">
+      <c r="A789" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789" s="4">
         <f>B787-B788</f>
         <v>596</v>
       </c>
     </row>
     <row r="790" spans="1:3">
-      <c r="A790" s="7"/>
-      <c r="B790" s="8"/>
+      <c r="A790" s="3"/>
+      <c r="B790" s="4"/>
     </row>
     <row r="792" spans="1:3">
-      <c r="A792" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B792" s="3"/>
-      <c r="C792" s="3"/>
+      <c r="A792" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B792" s="5"/>
+      <c r="C792" s="5"/>
     </row>
     <row r="793" spans="1:3">
-      <c r="A793" s="4" t="s">
+      <c r="A793" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B793" s="5"/>
-      <c r="C793" s="6"/>
+      <c r="B793" s="7"/>
+      <c r="C793" s="8"/>
     </row>
     <row r="794" spans="1:3">
       <c r="A794" s="1" t="s">
@@ -6246,31 +6249,31 @@
       </c>
     </row>
     <row r="797" spans="1:3">
-      <c r="A797" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B797" s="8">
+      <c r="A797" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797" s="4">
         <f>B795-B796</f>
         <v>250</v>
       </c>
     </row>
     <row r="798" spans="1:3">
-      <c r="A798" s="7"/>
-      <c r="B798" s="8"/>
+      <c r="A798" s="3"/>
+      <c r="B798" s="4"/>
     </row>
     <row r="800" spans="1:3">
-      <c r="A800" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B800" s="3"/>
-      <c r="C800" s="3"/>
+      <c r="A800" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B800" s="5"/>
+      <c r="C800" s="5"/>
     </row>
     <row r="801" spans="1:3">
-      <c r="A801" s="4" t="s">
+      <c r="A801" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B801" s="5"/>
-      <c r="C801" s="6"/>
+      <c r="B801" s="7"/>
+      <c r="C801" s="8"/>
     </row>
     <row r="802" spans="1:3">
       <c r="A802" s="1" t="s">
@@ -6303,31 +6306,31 @@
       </c>
     </row>
     <row r="805" spans="1:3">
-      <c r="A805" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B805" s="8">
+      <c r="A805" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805" s="4">
         <f>B803-B804</f>
         <v>378</v>
       </c>
     </row>
     <row r="806" spans="1:3">
-      <c r="A806" s="7"/>
-      <c r="B806" s="8"/>
+      <c r="A806" s="3"/>
+      <c r="B806" s="4"/>
     </row>
     <row r="808" spans="1:3">
-      <c r="A808" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B808" s="3"/>
-      <c r="C808" s="3"/>
+      <c r="A808" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B808" s="5"/>
+      <c r="C808" s="5"/>
     </row>
     <row r="809" spans="1:3">
-      <c r="A809" s="4" t="s">
+      <c r="A809" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B809" s="5"/>
-      <c r="C809" s="6"/>
+      <c r="B809" s="7"/>
+      <c r="C809" s="8"/>
     </row>
     <row r="810" spans="1:3">
       <c r="A810" s="1" t="s">
@@ -6360,31 +6363,31 @@
       </c>
     </row>
     <row r="813" spans="1:3">
-      <c r="A813" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B813" s="8">
+      <c r="A813" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813" s="4">
         <f>B811-B812</f>
         <v>900</v>
       </c>
     </row>
     <row r="814" spans="1:3">
-      <c r="A814" s="7"/>
-      <c r="B814" s="8"/>
+      <c r="A814" s="3"/>
+      <c r="B814" s="4"/>
     </row>
     <row r="816" spans="1:3">
-      <c r="A816" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B816" s="3"/>
-      <c r="C816" s="3"/>
+      <c r="A816" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B816" s="5"/>
+      <c r="C816" s="5"/>
     </row>
     <row r="817" spans="1:3">
-      <c r="A817" s="4" t="s">
+      <c r="A817" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B817" s="5"/>
-      <c r="C817" s="6"/>
+      <c r="B817" s="7"/>
+      <c r="C817" s="8"/>
     </row>
     <row r="818" spans="1:3">
       <c r="A818" s="1" t="s">
@@ -6417,31 +6420,31 @@
       </c>
     </row>
     <row r="821" spans="1:3">
-      <c r="A821" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B821" s="8">
+      <c r="A821" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B821" s="4">
         <f>B819-B820</f>
         <v>74</v>
       </c>
     </row>
     <row r="822" spans="1:3">
-      <c r="A822" s="7"/>
-      <c r="B822" s="8"/>
+      <c r="A822" s="3"/>
+      <c r="B822" s="4"/>
     </row>
     <row r="824" spans="1:3">
-      <c r="A824" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B824" s="3"/>
-      <c r="C824" s="3"/>
+      <c r="A824" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B824" s="5"/>
+      <c r="C824" s="5"/>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825" s="4" t="s">
+      <c r="A825" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B825" s="5"/>
-      <c r="C825" s="6"/>
+      <c r="B825" s="7"/>
+      <c r="C825" s="8"/>
     </row>
     <row r="826" spans="1:3">
       <c r="A826" s="1" t="s">
@@ -6474,31 +6477,31 @@
       </c>
     </row>
     <row r="829" spans="1:3">
-      <c r="A829" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B829" s="8">
+      <c r="A829" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B829" s="4">
         <f>B827-B828</f>
         <v>0</v>
       </c>
     </row>
     <row r="830" spans="1:3">
-      <c r="A830" s="7"/>
-      <c r="B830" s="8"/>
+      <c r="A830" s="3"/>
+      <c r="B830" s="4"/>
     </row>
     <row r="832" spans="1:3">
-      <c r="A832" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B832" s="3"/>
-      <c r="C832" s="3"/>
+      <c r="A832" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B832" s="5"/>
+      <c r="C832" s="5"/>
     </row>
     <row r="833" spans="1:3">
-      <c r="A833" s="4" t="s">
+      <c r="A833" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B833" s="5"/>
-      <c r="C833" s="6"/>
+      <c r="B833" s="7"/>
+      <c r="C833" s="8"/>
     </row>
     <row r="834" spans="1:3">
       <c r="A834" s="1" t="s">
@@ -6531,17 +6534,17 @@
       </c>
     </row>
     <row r="837" spans="1:3">
-      <c r="A837" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B837" s="8">
+      <c r="A837" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B837" s="4">
         <f>B835-B836</f>
         <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:3">
-      <c r="A838" s="7"/>
-      <c r="B838" s="8"/>
+      <c r="A838" s="3"/>
+      <c r="B838" s="4"/>
     </row>
     <row r="839" spans="1:3">
       <c r="A839" s="1" t="s">
@@ -6552,18 +6555,18 @@
       </c>
     </row>
     <row r="841" spans="1:3">
-      <c r="A841" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B841" s="3"/>
-      <c r="C841" s="3"/>
+      <c r="A841" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B841" s="5"/>
+      <c r="C841" s="5"/>
     </row>
     <row r="842" spans="1:3">
-      <c r="A842" s="4" t="s">
+      <c r="A842" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B842" s="5"/>
-      <c r="C842" s="6"/>
+      <c r="B842" s="7"/>
+      <c r="C842" s="8"/>
     </row>
     <row r="843" spans="1:3">
       <c r="A843" s="1" t="s">
@@ -6596,31 +6599,31 @@
       </c>
     </row>
     <row r="846" spans="1:3">
-      <c r="A846" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B846" s="8">
+      <c r="A846" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846" s="4">
         <f>B844-B845</f>
         <v>717</v>
       </c>
     </row>
     <row r="847" spans="1:3">
-      <c r="A847" s="7"/>
-      <c r="B847" s="8"/>
+      <c r="A847" s="3"/>
+      <c r="B847" s="4"/>
     </row>
     <row r="849" spans="1:3">
-      <c r="A849" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B849" s="3"/>
-      <c r="C849" s="3"/>
+      <c r="A849" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B849" s="5"/>
+      <c r="C849" s="5"/>
     </row>
     <row r="850" spans="1:3">
-      <c r="A850" s="4" t="s">
+      <c r="A850" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B850" s="5"/>
-      <c r="C850" s="6"/>
+      <c r="B850" s="7"/>
+      <c r="C850" s="8"/>
     </row>
     <row r="851" spans="1:3">
       <c r="A851" s="1" t="s">
@@ -6653,31 +6656,31 @@
       </c>
     </row>
     <row r="854" spans="1:3">
-      <c r="A854" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B854" s="8">
+      <c r="A854" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854" s="4">
         <f>B852-B853</f>
         <v>0</v>
       </c>
     </row>
     <row r="855" spans="1:3">
-      <c r="A855" s="7"/>
-      <c r="B855" s="8"/>
+      <c r="A855" s="3"/>
+      <c r="B855" s="4"/>
     </row>
     <row r="857" spans="1:3">
-      <c r="A857" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B857" s="3"/>
-      <c r="C857" s="3"/>
+      <c r="A857" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B857" s="5"/>
+      <c r="C857" s="5"/>
     </row>
     <row r="858" spans="1:3">
-      <c r="A858" s="4" t="s">
+      <c r="A858" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B858" s="5"/>
-      <c r="C858" s="6"/>
+      <c r="B858" s="7"/>
+      <c r="C858" s="8"/>
     </row>
     <row r="859" spans="1:3">
       <c r="A859" s="1" t="s">
@@ -6710,31 +6713,31 @@
       </c>
     </row>
     <row r="862" spans="1:3">
-      <c r="A862" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B862" s="8">
+      <c r="A862" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862" s="4">
         <f>B860-B861</f>
         <v>224</v>
       </c>
     </row>
     <row r="863" spans="1:3">
-      <c r="A863" s="7"/>
-      <c r="B863" s="8"/>
+      <c r="A863" s="3"/>
+      <c r="B863" s="4"/>
     </row>
     <row r="865" spans="1:3">
-      <c r="A865" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B865" s="3"/>
-      <c r="C865" s="3"/>
+      <c r="A865" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B865" s="5"/>
+      <c r="C865" s="5"/>
     </row>
     <row r="866" spans="1:3">
-      <c r="A866" s="4" t="s">
+      <c r="A866" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B866" s="5"/>
-      <c r="C866" s="6"/>
+      <c r="B866" s="7"/>
+      <c r="C866" s="8"/>
     </row>
     <row r="867" spans="1:3">
       <c r="A867" s="1" t="s">
@@ -6767,31 +6770,31 @@
       </c>
     </row>
     <row r="870" spans="1:3">
-      <c r="A870" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B870" s="8">
+      <c r="A870" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870" s="4">
         <f>B868-B869</f>
         <v>124</v>
       </c>
     </row>
     <row r="871" spans="1:3">
-      <c r="A871" s="7"/>
-      <c r="B871" s="8"/>
+      <c r="A871" s="3"/>
+      <c r="B871" s="4"/>
     </row>
     <row r="873" spans="1:3">
-      <c r="A873" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B873" s="3"/>
-      <c r="C873" s="3"/>
+      <c r="A873" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B873" s="5"/>
+      <c r="C873" s="5"/>
     </row>
     <row r="874" spans="1:3">
-      <c r="A874" s="4" t="s">
+      <c r="A874" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B874" s="5"/>
-      <c r="C874" s="6"/>
+      <c r="B874" s="7"/>
+      <c r="C874" s="8"/>
     </row>
     <row r="875" spans="1:3">
       <c r="A875" s="1" t="s">
@@ -6824,31 +6827,31 @@
       </c>
     </row>
     <row r="878" spans="1:3">
-      <c r="A878" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B878" s="8">
+      <c r="A878" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B878" s="4">
         <f>B876-B877</f>
         <v>449</v>
       </c>
     </row>
     <row r="879" spans="1:3">
-      <c r="A879" s="7"/>
-      <c r="B879" s="8"/>
+      <c r="A879" s="3"/>
+      <c r="B879" s="4"/>
     </row>
     <row r="881" spans="1:3">
-      <c r="A881" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B881" s="3"/>
-      <c r="C881" s="3"/>
+      <c r="A881" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B881" s="5"/>
+      <c r="C881" s="5"/>
     </row>
     <row r="882" spans="1:3">
-      <c r="A882" s="4" t="s">
+      <c r="A882" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B882" s="5"/>
-      <c r="C882" s="6"/>
+      <c r="B882" s="7"/>
+      <c r="C882" s="8"/>
     </row>
     <row r="883" spans="1:3">
       <c r="A883" s="1" t="s">
@@ -6881,112 +6884,714 @@
       </c>
     </row>
     <row r="886" spans="1:3">
-      <c r="A886" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B886" s="8">
+      <c r="A886" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B886" s="4">
         <f>B884-B885</f>
         <v>821</v>
       </c>
     </row>
     <row r="887" spans="1:3">
-      <c r="A887" s="7"/>
-      <c r="B887" s="8"/>
+      <c r="A887" s="3"/>
+      <c r="B887" s="4"/>
+    </row>
+    <row r="889" spans="1:3">
+      <c r="A889" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B889" s="5"/>
+      <c r="C889" s="5"/>
+    </row>
+    <row r="890" spans="1:3">
+      <c r="A890" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B890" s="7"/>
+      <c r="C890" s="8"/>
+    </row>
+    <row r="891" spans="1:3">
+      <c r="A891" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B891" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C891" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3">
+      <c r="A892" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B892" s="2">
+        <v>69</v>
+      </c>
+      <c r="C892" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3">
+      <c r="A893" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B893" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3">
+      <c r="A894" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B894" s="4">
+        <f>B892-B893</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3">
+      <c r="A895" s="3"/>
+      <c r="B895" s="4"/>
+    </row>
+    <row r="896" spans="1:3">
+      <c r="A896" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B896" s="2">
+        <v>13341</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3">
+      <c r="A898" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B898" s="5"/>
+      <c r="C898" s="5"/>
+    </row>
+    <row r="899" spans="1:3">
+      <c r="A899" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B899" s="7"/>
+      <c r="C899" s="8"/>
+    </row>
+    <row r="900" spans="1:3">
+      <c r="A900" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B900" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C900" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="901" spans="1:3">
+      <c r="A901" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B901" s="2">
+        <v>32</v>
+      </c>
+      <c r="C901" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3">
+      <c r="A902" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B902" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="903" spans="1:3">
+      <c r="A903" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B903" s="4">
+        <f>B901-B902</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3">
+      <c r="A904" s="3"/>
+      <c r="B904" s="4"/>
+    </row>
+    <row r="906" spans="1:3">
+      <c r="A906" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B906" s="5"/>
+      <c r="C906" s="5"/>
+    </row>
+    <row r="907" spans="1:3">
+      <c r="A907" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B907" s="7"/>
+      <c r="C907" s="8"/>
+    </row>
+    <row r="908" spans="1:3">
+      <c r="A908" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B908" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C908" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="909" spans="1:3">
+      <c r="A909" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B909" s="2">
+        <v>127</v>
+      </c>
+      <c r="C909" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="910" spans="1:3">
+      <c r="A910" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B910" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3">
+      <c r="A911" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B911" s="4">
+        <f>B909-B910</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="912" spans="1:3">
+      <c r="A912" s="3"/>
+      <c r="B912" s="4"/>
+    </row>
+    <row r="914" spans="1:3">
+      <c r="A914" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B914" s="5"/>
+      <c r="C914" s="5"/>
+    </row>
+    <row r="915" spans="1:3">
+      <c r="A915" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B915" s="7"/>
+      <c r="C915" s="8"/>
+    </row>
+    <row r="916" spans="1:3">
+      <c r="A916" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B916" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C916" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3">
+      <c r="A917" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B917" s="2">
+        <v>190</v>
+      </c>
+      <c r="C917" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="918" spans="1:3">
+      <c r="A918" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B918" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="919" spans="1:3">
+      <c r="A919" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B919" s="4">
+        <f>B917-B918</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3">
+      <c r="A920" s="3"/>
+      <c r="B920" s="4"/>
+    </row>
+    <row r="922" spans="1:3">
+      <c r="A922" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B922" s="5"/>
+      <c r="C922" s="5"/>
+    </row>
+    <row r="923" spans="1:3">
+      <c r="A923" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B923" s="7"/>
+      <c r="C923" s="8"/>
+    </row>
+    <row r="924" spans="1:3">
+      <c r="A924" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B924" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C924" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="925" spans="1:3">
+      <c r="A925" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B925" s="2">
+        <v>91</v>
+      </c>
+      <c r="C925" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3">
+      <c r="A926" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B926" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="927" spans="1:3">
+      <c r="A927" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B927" s="4">
+        <f>B925-B926</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="928" spans="1:3">
+      <c r="A928" s="3"/>
+      <c r="B928" s="4"/>
+    </row>
+    <row r="930" spans="1:3">
+      <c r="A930" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B930" s="5"/>
+      <c r="C930" s="5"/>
+    </row>
+    <row r="931" spans="1:3">
+      <c r="A931" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B931" s="7"/>
+      <c r="C931" s="8"/>
+    </row>
+    <row r="932" spans="1:3">
+      <c r="A932" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B932" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C932" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="933" spans="1:3">
+      <c r="A933" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B933" s="2">
+        <v>103</v>
+      </c>
+      <c r="C933" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="934" spans="1:3">
+      <c r="A934" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B934" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3">
+      <c r="A935" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B935" s="4">
+        <f>B933-B934</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936" spans="1:3">
+      <c r="A936" s="3"/>
+      <c r="B936" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="436">
-    <mergeCell ref="A870:A871"/>
-    <mergeCell ref="B870:B871"/>
-    <mergeCell ref="A873:C873"/>
-    <mergeCell ref="A874:C874"/>
-    <mergeCell ref="A878:A879"/>
-    <mergeCell ref="B878:B879"/>
-    <mergeCell ref="A881:C881"/>
-    <mergeCell ref="A882:C882"/>
-    <mergeCell ref="A886:A887"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="A850:C850"/>
-    <mergeCell ref="A854:A855"/>
-    <mergeCell ref="B854:B855"/>
-    <mergeCell ref="A857:C857"/>
-    <mergeCell ref="A858:C858"/>
-    <mergeCell ref="A862:A863"/>
-    <mergeCell ref="B862:B863"/>
-    <mergeCell ref="A865:C865"/>
-    <mergeCell ref="A866:C866"/>
-    <mergeCell ref="A832:C832"/>
-    <mergeCell ref="A833:C833"/>
-    <mergeCell ref="A837:A838"/>
-    <mergeCell ref="B837:B838"/>
-    <mergeCell ref="A841:C841"/>
-    <mergeCell ref="A842:C842"/>
-    <mergeCell ref="A846:A847"/>
-    <mergeCell ref="B846:B847"/>
-    <mergeCell ref="A849:C849"/>
-    <mergeCell ref="A759:C759"/>
-    <mergeCell ref="A760:C760"/>
-    <mergeCell ref="A764:A765"/>
-    <mergeCell ref="B764:B765"/>
-    <mergeCell ref="A740:A741"/>
-    <mergeCell ref="B740:B741"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A744:C744"/>
-    <mergeCell ref="A748:A749"/>
-    <mergeCell ref="B748:B749"/>
-    <mergeCell ref="A751:C751"/>
-    <mergeCell ref="A752:C752"/>
-    <mergeCell ref="A756:A757"/>
-    <mergeCell ref="B756:B757"/>
-    <mergeCell ref="A720:C720"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="B724:B725"/>
-    <mergeCell ref="A727:C727"/>
-    <mergeCell ref="A728:C728"/>
-    <mergeCell ref="A732:A733"/>
-    <mergeCell ref="B732:B733"/>
-    <mergeCell ref="A735:C735"/>
-    <mergeCell ref="A736:C736"/>
-    <mergeCell ref="A702:C702"/>
-    <mergeCell ref="A703:C703"/>
-    <mergeCell ref="A707:A708"/>
-    <mergeCell ref="B707:B708"/>
-    <mergeCell ref="A711:C711"/>
-    <mergeCell ref="A712:C712"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="B716:B717"/>
-    <mergeCell ref="A719:C719"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
+  <mergeCells count="460">
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="B927:B928"/>
+    <mergeCell ref="A930:C930"/>
+    <mergeCell ref="A931:C931"/>
+    <mergeCell ref="A935:A936"/>
+    <mergeCell ref="B935:B936"/>
+    <mergeCell ref="A907:C907"/>
+    <mergeCell ref="A911:A912"/>
+    <mergeCell ref="B911:B912"/>
+    <mergeCell ref="A914:C914"/>
+    <mergeCell ref="A915:C915"/>
+    <mergeCell ref="A919:A920"/>
+    <mergeCell ref="B919:B920"/>
+    <mergeCell ref="A922:C922"/>
+    <mergeCell ref="A923:C923"/>
+    <mergeCell ref="A889:C889"/>
+    <mergeCell ref="A890:C890"/>
+    <mergeCell ref="A894:A895"/>
+    <mergeCell ref="B894:B895"/>
+    <mergeCell ref="A898:C898"/>
+    <mergeCell ref="A899:C899"/>
+    <mergeCell ref="A903:A904"/>
+    <mergeCell ref="B903:B904"/>
+    <mergeCell ref="A906:C906"/>
+    <mergeCell ref="A824:C824"/>
+    <mergeCell ref="A825:C825"/>
+    <mergeCell ref="A829:A830"/>
+    <mergeCell ref="B829:B830"/>
+    <mergeCell ref="A805:A806"/>
+    <mergeCell ref="B805:B806"/>
+    <mergeCell ref="A808:C808"/>
+    <mergeCell ref="A809:C809"/>
+    <mergeCell ref="A813:A814"/>
+    <mergeCell ref="B813:B814"/>
+    <mergeCell ref="A816:C816"/>
+    <mergeCell ref="A817:C817"/>
+    <mergeCell ref="A821:A822"/>
+    <mergeCell ref="B821:B822"/>
+    <mergeCell ref="A785:C785"/>
+    <mergeCell ref="A789:A790"/>
+    <mergeCell ref="B789:B790"/>
+    <mergeCell ref="A792:C792"/>
+    <mergeCell ref="A793:C793"/>
+    <mergeCell ref="A797:A798"/>
+    <mergeCell ref="B797:B798"/>
+    <mergeCell ref="A800:C800"/>
+    <mergeCell ref="A801:C801"/>
+    <mergeCell ref="A767:C767"/>
+    <mergeCell ref="A768:C768"/>
+    <mergeCell ref="A772:A773"/>
+    <mergeCell ref="B772:B773"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A777:C777"/>
+    <mergeCell ref="A781:A782"/>
+    <mergeCell ref="B781:B782"/>
+    <mergeCell ref="A784:C784"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A490:C490"/>
+    <mergeCell ref="A491:C491"/>
+    <mergeCell ref="A495:A496"/>
+    <mergeCell ref="B495:B496"/>
+    <mergeCell ref="A499:C499"/>
+    <mergeCell ref="A500:C500"/>
+    <mergeCell ref="A433:C433"/>
+    <mergeCell ref="A434:C434"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:C442"/>
+    <mergeCell ref="A443:C443"/>
+    <mergeCell ref="A447:A448"/>
+    <mergeCell ref="B447:B448"/>
+    <mergeCell ref="A450:C450"/>
+    <mergeCell ref="A451:C451"/>
+    <mergeCell ref="A455:A456"/>
+    <mergeCell ref="B455:B456"/>
+    <mergeCell ref="A458:C458"/>
+    <mergeCell ref="A459:C459"/>
+    <mergeCell ref="A463:A464"/>
+    <mergeCell ref="B463:B464"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
     <mergeCell ref="A483:C483"/>
     <mergeCell ref="A487:A488"/>
     <mergeCell ref="B487:B488"/>
@@ -7011,326 +7616,98 @@
     <mergeCell ref="A512:A513"/>
     <mergeCell ref="B512:B513"/>
     <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A490:C490"/>
-    <mergeCell ref="A491:C491"/>
-    <mergeCell ref="A495:A496"/>
-    <mergeCell ref="B495:B496"/>
-    <mergeCell ref="A499:C499"/>
-    <mergeCell ref="A500:C500"/>
-    <mergeCell ref="A433:C433"/>
-    <mergeCell ref="A434:C434"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A442:C442"/>
-    <mergeCell ref="A443:C443"/>
-    <mergeCell ref="A447:A448"/>
-    <mergeCell ref="B447:B448"/>
-    <mergeCell ref="A450:C450"/>
-    <mergeCell ref="A451:C451"/>
-    <mergeCell ref="A455:A456"/>
-    <mergeCell ref="B455:B456"/>
-    <mergeCell ref="A458:C458"/>
-    <mergeCell ref="A459:C459"/>
-    <mergeCell ref="A463:A464"/>
-    <mergeCell ref="B463:B464"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
-    <mergeCell ref="A767:C767"/>
-    <mergeCell ref="A768:C768"/>
-    <mergeCell ref="A772:A773"/>
-    <mergeCell ref="B772:B773"/>
-    <mergeCell ref="A776:C776"/>
-    <mergeCell ref="A777:C777"/>
-    <mergeCell ref="A781:A782"/>
-    <mergeCell ref="B781:B782"/>
-    <mergeCell ref="A784:C784"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="A789:A790"/>
-    <mergeCell ref="B789:B790"/>
-    <mergeCell ref="A792:C792"/>
-    <mergeCell ref="A793:C793"/>
-    <mergeCell ref="A797:A798"/>
-    <mergeCell ref="B797:B798"/>
-    <mergeCell ref="A800:C800"/>
-    <mergeCell ref="A801:C801"/>
-    <mergeCell ref="A824:C824"/>
-    <mergeCell ref="A825:C825"/>
-    <mergeCell ref="A829:A830"/>
-    <mergeCell ref="B829:B830"/>
-    <mergeCell ref="A805:A806"/>
-    <mergeCell ref="B805:B806"/>
-    <mergeCell ref="A808:C808"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="A813:A814"/>
-    <mergeCell ref="B813:B814"/>
-    <mergeCell ref="A816:C816"/>
-    <mergeCell ref="A817:C817"/>
-    <mergeCell ref="A821:A822"/>
-    <mergeCell ref="B821:B822"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A702:C702"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A707:A708"/>
+    <mergeCell ref="B707:B708"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A759:C759"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A764:A765"/>
+    <mergeCell ref="B764:B765"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A832:C832"/>
+    <mergeCell ref="A833:C833"/>
+    <mergeCell ref="A837:A838"/>
+    <mergeCell ref="B837:B838"/>
+    <mergeCell ref="A841:C841"/>
+    <mergeCell ref="A842:C842"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="B846:B847"/>
+    <mergeCell ref="A849:C849"/>
+    <mergeCell ref="A850:C850"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="B854:B855"/>
+    <mergeCell ref="A857:C857"/>
+    <mergeCell ref="A858:C858"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="B862:B863"/>
+    <mergeCell ref="A865:C865"/>
+    <mergeCell ref="A866:C866"/>
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="B870:B871"/>
+    <mergeCell ref="A873:C873"/>
+    <mergeCell ref="A874:C874"/>
+    <mergeCell ref="A878:A879"/>
+    <mergeCell ref="B878:B879"/>
+    <mergeCell ref="A881:C881"/>
+    <mergeCell ref="A882:C882"/>
+    <mergeCell ref="A886:A887"/>
+    <mergeCell ref="B886:B887"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7D225E-6A4C-4E45-8FD4-34A2C602371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7429CE9B-BCEE-4F3B-BD5E-B43F941887A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="40">
   <si>
     <t>Data</t>
   </si>
@@ -152,6 +152,9 @@
   <si>
     <t>26.10.2026</t>
   </si>
+  <si>
+    <t>27.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -255,12 +258,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -270,6 +267,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C936"/>
+  <dimension ref="A1:C1001"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -556,18 +559,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -600,17 +603,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -621,18 +624,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -665,31 +668,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="A15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
+      <c r="A18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -722,31 +725,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="4">
+      <c r="A23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="8">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
+      <c r="A26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -779,31 +782,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="4">
+      <c r="A31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="8">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
+      <c r="A34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -836,31 +839,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="4">
+      <c r="A39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="3"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
+      <c r="A42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -893,31 +896,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="4">
+      <c r="A47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="8">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="3"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="8"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
+      <c r="A50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -950,31 +953,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="4">
+      <c r="A55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="8">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="3"/>
-      <c r="B56" s="4"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
+      <c r="A58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="8"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -1007,17 +1010,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="4">
+      <c r="A63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="8">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="8"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1028,18 +1031,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
+      <c r="A67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1072,31 +1075,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="4">
+      <c r="A72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="8">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="3"/>
-      <c r="B73" s="4"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="8"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="8"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="6"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1129,31 +1132,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="4">
+      <c r="A80" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="8">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="3"/>
-      <c r="B81" s="4"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="8"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
+      <c r="A83" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="8"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="6"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1186,31 +1189,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="4">
+      <c r="A88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="8">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="3"/>
-      <c r="B89" s="4"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="8"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
+      <c r="A91" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="8"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="6"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1243,31 +1246,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="4">
+      <c r="A96" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="8">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="3"/>
-      <c r="B97" s="4"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="8"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
+      <c r="A99" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="8"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="6"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1300,31 +1303,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="4">
+      <c r="A104" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="8">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="4"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="8"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
+      <c r="A107" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="7"/>
-      <c r="C108" s="8"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="6"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1357,31 +1360,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="4">
+      <c r="A112" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="8">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="3"/>
-      <c r="B113" s="4"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="8"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
+      <c r="A115" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="7"/>
-      <c r="C116" s="8"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="6"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1414,31 +1417,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="4">
+      <c r="A120" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="8">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="3"/>
-      <c r="B121" s="4"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="8"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
+      <c r="A123" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="7"/>
-      <c r="C124" s="8"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="6"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1471,17 +1474,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="4">
+      <c r="A128" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="8">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="3"/>
-      <c r="B129" s="4"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="8"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1492,18 +1495,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
+      <c r="A132" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="7"/>
-      <c r="C133" s="8"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="6"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1536,31 +1539,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="4">
+      <c r="A137" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="8">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="3"/>
-      <c r="B138" s="4"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="8"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
+      <c r="A140" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="7"/>
-      <c r="C141" s="8"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="6"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1593,31 +1596,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="4">
+      <c r="A145" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="8">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="3"/>
-      <c r="B146" s="4"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="8"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
+      <c r="A148" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="8"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="6"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1650,31 +1653,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="4">
+      <c r="A153" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="8">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="3"/>
-      <c r="B154" s="4"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="8"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
+      <c r="A156" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="7"/>
-      <c r="C157" s="8"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="6"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1707,31 +1710,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="4">
+      <c r="A161" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="8">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="3"/>
-      <c r="B162" s="4"/>
+      <c r="A162" s="7"/>
+      <c r="B162" s="8"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5"/>
+      <c r="A164" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="7"/>
-      <c r="C165" s="8"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="6"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1764,31 +1767,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="4">
+      <c r="A169" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="8">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="3"/>
-      <c r="B170" s="4"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="8"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="5"/>
-      <c r="C172" s="5"/>
+      <c r="A172" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="6" t="s">
+      <c r="A173" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="7"/>
-      <c r="C173" s="8"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="6"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1821,31 +1824,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="4">
+      <c r="A177" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="8">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="3"/>
-      <c r="B178" s="4"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="8"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
+      <c r="A180" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="6" t="s">
+      <c r="A181" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="7"/>
-      <c r="C181" s="8"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="6"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1878,17 +1881,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="4">
+      <c r="A185" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="8">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="3"/>
-      <c r="B186" s="4"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="8"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1899,18 +1902,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="5"/>
-      <c r="C189" s="5"/>
+      <c r="A189" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="7"/>
-      <c r="C190" s="8"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="6"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1943,31 +1946,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="4">
+      <c r="A194" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="8">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="3"/>
-      <c r="B195" s="4"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="8"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="5"/>
-      <c r="C197" s="5"/>
+      <c r="A197" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="6" t="s">
+      <c r="A198" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="7"/>
-      <c r="C198" s="8"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="6"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -2000,31 +2003,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="4">
+      <c r="A202" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="8">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="3"/>
-      <c r="B203" s="4"/>
+      <c r="A203" s="7"/>
+      <c r="B203" s="8"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
+      <c r="A205" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="6" t="s">
+      <c r="A206" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="7"/>
-      <c r="C206" s="8"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="6"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2057,31 +2060,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="4">
+      <c r="A210" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="8">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="3"/>
-      <c r="B211" s="4"/>
+      <c r="A211" s="7"/>
+      <c r="B211" s="8"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
+      <c r="A213" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="7"/>
-      <c r="C214" s="8"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="6"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2114,31 +2117,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="4">
+      <c r="A218" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="8">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="3"/>
-      <c r="B219" s="4"/>
+      <c r="A219" s="7"/>
+      <c r="B219" s="8"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="5"/>
-      <c r="C221" s="5"/>
+      <c r="A221" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="6" t="s">
+      <c r="A222" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="7"/>
-      <c r="C222" s="8"/>
+      <c r="B222" s="5"/>
+      <c r="C222" s="6"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2171,31 +2174,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="4">
+      <c r="A226" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="8">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="3"/>
-      <c r="B227" s="4"/>
+      <c r="A227" s="7"/>
+      <c r="B227" s="8"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="5"/>
-      <c r="C229" s="5"/>
+      <c r="A229" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="6" t="s">
+      <c r="A230" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="7"/>
-      <c r="C230" s="8"/>
+      <c r="B230" s="5"/>
+      <c r="C230" s="6"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2228,31 +2231,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="4">
+      <c r="A234" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="8">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="3"/>
-      <c r="B235" s="4"/>
+      <c r="A235" s="7"/>
+      <c r="B235" s="8"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5"/>
+      <c r="A237" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="6" t="s">
+      <c r="A238" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="7"/>
-      <c r="C238" s="8"/>
+      <c r="B238" s="5"/>
+      <c r="C238" s="6"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2285,17 +2288,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="4">
+      <c r="A242" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="8">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="3"/>
-      <c r="B243" s="4"/>
+      <c r="A243" s="7"/>
+      <c r="B243" s="8"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2306,18 +2309,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
+      <c r="A246" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="6" t="s">
+      <c r="A247" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="7"/>
-      <c r="C247" s="8"/>
+      <c r="B247" s="5"/>
+      <c r="C247" s="6"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2350,31 +2353,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="4">
+      <c r="A251" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="8">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="3"/>
-      <c r="B252" s="4"/>
+      <c r="A252" s="7"/>
+      <c r="B252" s="8"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
+      <c r="A254" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="6" t="s">
+      <c r="A255" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="7"/>
-      <c r="C255" s="8"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="6"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2407,31 +2410,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="4">
+      <c r="A259" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="8">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="3"/>
-      <c r="B260" s="4"/>
+      <c r="A260" s="7"/>
+      <c r="B260" s="8"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5"/>
+      <c r="A262" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="6" t="s">
+      <c r="A263" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="7"/>
-      <c r="C263" s="8"/>
+      <c r="B263" s="5"/>
+      <c r="C263" s="6"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2464,17 +2467,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="4">
+      <c r="A267" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="8">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="3"/>
-      <c r="B268" s="4"/>
+      <c r="A268" s="7"/>
+      <c r="B268" s="8"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2485,18 +2488,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="5"/>
-      <c r="C271" s="5"/>
+      <c r="A271" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="6" t="s">
+      <c r="A272" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="7"/>
-      <c r="C272" s="8"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="6"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2529,31 +2532,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="4">
+      <c r="A276" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="8">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="3"/>
-      <c r="B277" s="4"/>
+      <c r="A277" s="7"/>
+      <c r="B277" s="8"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="5"/>
-      <c r="C279" s="5"/>
+      <c r="A279" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="7"/>
-      <c r="C280" s="8"/>
+      <c r="B280" s="5"/>
+      <c r="C280" s="6"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2586,31 +2589,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="4">
+      <c r="A284" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="8">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="3"/>
-      <c r="B285" s="4"/>
+      <c r="A285" s="7"/>
+      <c r="B285" s="8"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="5"/>
-      <c r="C287" s="5"/>
+      <c r="A287" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="3"/>
+      <c r="C287" s="3"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="6" t="s">
+      <c r="A288" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="7"/>
-      <c r="C288" s="8"/>
+      <c r="B288" s="5"/>
+      <c r="C288" s="6"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2643,31 +2646,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="4">
+      <c r="A292" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="8">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="3"/>
-      <c r="B293" s="4"/>
+      <c r="A293" s="7"/>
+      <c r="B293" s="8"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="5"/>
-      <c r="C295" s="5"/>
+      <c r="A295" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="6" t="s">
+      <c r="A296" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="7"/>
-      <c r="C296" s="8"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="6"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2700,31 +2703,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="4">
+      <c r="A300" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="8">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="3"/>
-      <c r="B301" s="4"/>
+      <c r="A301" s="7"/>
+      <c r="B301" s="8"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="5"/>
-      <c r="C303" s="5"/>
+      <c r="A303" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="6" t="s">
+      <c r="A304" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="7"/>
-      <c r="C304" s="8"/>
+      <c r="B304" s="5"/>
+      <c r="C304" s="6"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2757,31 +2760,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="4">
+      <c r="A308" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="8">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="3"/>
-      <c r="B309" s="4"/>
+      <c r="A309" s="7"/>
+      <c r="B309" s="8"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="5"/>
-      <c r="C311" s="5"/>
+      <c r="A311" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="3"/>
+      <c r="C311" s="3"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="6" t="s">
+      <c r="A312" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="7"/>
-      <c r="C312" s="8"/>
+      <c r="B312" s="5"/>
+      <c r="C312" s="6"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2814,31 +2817,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="4">
+      <c r="A316" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="8">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="3"/>
-      <c r="B317" s="4"/>
+      <c r="A317" s="7"/>
+      <c r="B317" s="8"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="5"/>
-      <c r="C319" s="5"/>
+      <c r="A319" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="3"/>
+      <c r="C319" s="3"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="6" t="s">
+      <c r="A320" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="7"/>
-      <c r="C320" s="8"/>
+      <c r="B320" s="5"/>
+      <c r="C320" s="6"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2871,17 +2874,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="4">
+      <c r="A324" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="8">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="3"/>
-      <c r="B325" s="4"/>
+      <c r="A325" s="7"/>
+      <c r="B325" s="8"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2892,18 +2895,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="5"/>
-      <c r="C328" s="5"/>
+      <c r="A328" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="6" t="s">
+      <c r="A329" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="7"/>
-      <c r="C329" s="8"/>
+      <c r="B329" s="5"/>
+      <c r="C329" s="6"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2936,31 +2939,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="4">
+      <c r="A333" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="8">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="3"/>
-      <c r="B334" s="4"/>
+      <c r="A334" s="7"/>
+      <c r="B334" s="8"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="5"/>
-      <c r="C336" s="5"/>
+      <c r="A336" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="3"/>
+      <c r="C336" s="3"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="6" t="s">
+      <c r="A337" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="7"/>
-      <c r="C337" s="8"/>
+      <c r="B337" s="5"/>
+      <c r="C337" s="6"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2993,31 +2996,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="4">
+      <c r="A341" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="8">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="3"/>
-      <c r="B342" s="4"/>
+      <c r="A342" s="7"/>
+      <c r="B342" s="8"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="5"/>
-      <c r="C344" s="5"/>
+      <c r="A344" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="3"/>
+      <c r="C344" s="3"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="6" t="s">
+      <c r="A345" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="7"/>
-      <c r="C345" s="8"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="6"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3050,31 +3053,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="4">
+      <c r="A349" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="8">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="3"/>
-      <c r="B350" s="4"/>
+      <c r="A350" s="7"/>
+      <c r="B350" s="8"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="5"/>
-      <c r="C352" s="5"/>
+      <c r="A352" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="3"/>
+      <c r="C352" s="3"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="6" t="s">
+      <c r="A353" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="7"/>
-      <c r="C353" s="8"/>
+      <c r="B353" s="5"/>
+      <c r="C353" s="6"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3107,31 +3110,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="4">
+      <c r="A357" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="8">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="3"/>
-      <c r="B358" s="4"/>
+      <c r="A358" s="7"/>
+      <c r="B358" s="8"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="5"/>
-      <c r="C360" s="5"/>
+      <c r="A360" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="3"/>
+      <c r="C360" s="3"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="6" t="s">
+      <c r="A361" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="7"/>
-      <c r="C361" s="8"/>
+      <c r="B361" s="5"/>
+      <c r="C361" s="6"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3164,31 +3167,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="4">
+      <c r="A365" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="8">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="3"/>
-      <c r="B366" s="4"/>
+      <c r="A366" s="7"/>
+      <c r="B366" s="8"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="5"/>
-      <c r="C368" s="5"/>
+      <c r="A368" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="3"/>
+      <c r="C368" s="3"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="6" t="s">
+      <c r="A369" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="7"/>
-      <c r="C369" s="8"/>
+      <c r="B369" s="5"/>
+      <c r="C369" s="6"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3221,31 +3224,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="4">
+      <c r="A373" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="8">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="3"/>
-      <c r="B374" s="4"/>
+      <c r="A374" s="7"/>
+      <c r="B374" s="8"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="5"/>
-      <c r="C376" s="5"/>
+      <c r="A376" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="3"/>
+      <c r="C376" s="3"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="6" t="s">
+      <c r="A377" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="7"/>
-      <c r="C377" s="8"/>
+      <c r="B377" s="5"/>
+      <c r="C377" s="6"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3278,17 +3281,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="4">
+      <c r="A381" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="8">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="3"/>
-      <c r="B382" s="4"/>
+      <c r="A382" s="7"/>
+      <c r="B382" s="8"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3299,18 +3302,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="5"/>
-      <c r="C385" s="5"/>
+      <c r="A385" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="3"/>
+      <c r="C385" s="3"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="6" t="s">
+      <c r="A386" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="7"/>
-      <c r="C386" s="8"/>
+      <c r="B386" s="5"/>
+      <c r="C386" s="6"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3343,31 +3346,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="4">
+      <c r="A390" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="8">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="3"/>
-      <c r="B391" s="4"/>
+      <c r="A391" s="7"/>
+      <c r="B391" s="8"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="5"/>
-      <c r="C393" s="5"/>
+      <c r="A393" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="3"/>
+      <c r="C393" s="3"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="6" t="s">
+      <c r="A394" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="7"/>
-      <c r="C394" s="8"/>
+      <c r="B394" s="5"/>
+      <c r="C394" s="6"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3400,31 +3403,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="4">
+      <c r="A398" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="8">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="3"/>
-      <c r="B399" s="4"/>
+      <c r="A399" s="7"/>
+      <c r="B399" s="8"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="5"/>
-      <c r="C401" s="5"/>
+      <c r="A401" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="3"/>
+      <c r="C401" s="3"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="6" t="s">
+      <c r="A402" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="7"/>
-      <c r="C402" s="8"/>
+      <c r="B402" s="5"/>
+      <c r="C402" s="6"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3457,31 +3460,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="4">
+      <c r="A406" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="8">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="3"/>
-      <c r="B407" s="4"/>
+      <c r="A407" s="7"/>
+      <c r="B407" s="8"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="5"/>
-      <c r="C409" s="5"/>
+      <c r="A409" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="3"/>
+      <c r="C409" s="3"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="6" t="s">
+      <c r="A410" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="7"/>
-      <c r="C410" s="8"/>
+      <c r="B410" s="5"/>
+      <c r="C410" s="6"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3514,31 +3517,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="4">
+      <c r="A414" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="8">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="3"/>
-      <c r="B415" s="4"/>
+      <c r="A415" s="7"/>
+      <c r="B415" s="8"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="5"/>
-      <c r="C417" s="5"/>
+      <c r="A417" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="3"/>
+      <c r="C417" s="3"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="6" t="s">
+      <c r="A418" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="7"/>
-      <c r="C418" s="8"/>
+      <c r="B418" s="5"/>
+      <c r="C418" s="6"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3571,31 +3574,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="4">
+      <c r="A422" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="8">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="3"/>
-      <c r="B423" s="4"/>
+      <c r="A423" s="7"/>
+      <c r="B423" s="8"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="5"/>
-      <c r="C425" s="5"/>
+      <c r="A425" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="6" t="s">
+      <c r="A426" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="7"/>
-      <c r="C426" s="8"/>
+      <c r="B426" s="5"/>
+      <c r="C426" s="6"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3628,31 +3631,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="4">
+      <c r="A430" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="8">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="3"/>
-      <c r="B431" s="4"/>
+      <c r="A431" s="7"/>
+      <c r="B431" s="8"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="5"/>
-      <c r="C433" s="5"/>
+      <c r="A433" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="6" t="s">
+      <c r="A434" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="7"/>
-      <c r="C434" s="8"/>
+      <c r="B434" s="5"/>
+      <c r="C434" s="6"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3685,17 +3688,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="4">
+      <c r="A438" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="8">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="3"/>
-      <c r="B439" s="4"/>
+      <c r="A439" s="7"/>
+      <c r="B439" s="8"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3706,18 +3709,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="5"/>
-      <c r="C442" s="5"/>
+      <c r="A442" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="6" t="s">
+      <c r="A443" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="7"/>
-      <c r="C443" s="8"/>
+      <c r="B443" s="5"/>
+      <c r="C443" s="6"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3750,31 +3753,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="4">
+      <c r="A447" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="8">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="3"/>
-      <c r="B448" s="4"/>
+      <c r="A448" s="7"/>
+      <c r="B448" s="8"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="5"/>
-      <c r="C450" s="5"/>
+      <c r="A450" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="3"/>
+      <c r="C450" s="3"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="6" t="s">
+      <c r="A451" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="7"/>
-      <c r="C451" s="8"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="6"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3807,31 +3810,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="4">
+      <c r="A455" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="8">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="3"/>
-      <c r="B456" s="4"/>
+      <c r="A456" s="7"/>
+      <c r="B456" s="8"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="5"/>
-      <c r="C458" s="5"/>
+      <c r="A458" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="6" t="s">
+      <c r="A459" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="7"/>
-      <c r="C459" s="8"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="6"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3864,31 +3867,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="4">
+      <c r="A463" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="8">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="3"/>
-      <c r="B464" s="4"/>
+      <c r="A464" s="7"/>
+      <c r="B464" s="8"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="5"/>
-      <c r="C466" s="5"/>
+      <c r="A466" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="3"/>
+      <c r="C466" s="3"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="6" t="s">
+      <c r="A467" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="7"/>
-      <c r="C467" s="8"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="6"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3921,31 +3924,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="4">
+      <c r="A471" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="8">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="3"/>
-      <c r="B472" s="4"/>
+      <c r="A472" s="7"/>
+      <c r="B472" s="8"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="5"/>
-      <c r="C474" s="5"/>
+      <c r="A474" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="3"/>
+      <c r="C474" s="3"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="6" t="s">
+      <c r="A475" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="7"/>
-      <c r="C475" s="8"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="6"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3978,31 +3981,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="4">
+      <c r="A479" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="8">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="3"/>
-      <c r="B480" s="4"/>
+      <c r="A480" s="7"/>
+      <c r="B480" s="8"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="5"/>
-      <c r="C482" s="5"/>
+      <c r="A482" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="3"/>
+      <c r="C482" s="3"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="6" t="s">
+      <c r="A483" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="7"/>
-      <c r="C483" s="8"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="6"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4035,31 +4038,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="4">
+      <c r="A487" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="8">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="3"/>
-      <c r="B488" s="4"/>
+      <c r="A488" s="7"/>
+      <c r="B488" s="8"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="5"/>
-      <c r="C490" s="5"/>
+      <c r="A490" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="3"/>
+      <c r="C490" s="3"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="6" t="s">
+      <c r="A491" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="7"/>
-      <c r="C491" s="8"/>
+      <c r="B491" s="5"/>
+      <c r="C491" s="6"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4092,17 +4095,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="4">
+      <c r="A495" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="8">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="3"/>
-      <c r="B496" s="4"/>
+      <c r="A496" s="7"/>
+      <c r="B496" s="8"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4113,18 +4116,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="5"/>
-      <c r="C499" s="5"/>
+      <c r="A499" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="3"/>
+      <c r="C499" s="3"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="6" t="s">
+      <c r="A500" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="7"/>
-      <c r="C500" s="8"/>
+      <c r="B500" s="5"/>
+      <c r="C500" s="6"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4157,31 +4160,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="4">
+      <c r="A504" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="8">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="3"/>
-      <c r="B505" s="4"/>
+      <c r="A505" s="7"/>
+      <c r="B505" s="8"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="5"/>
-      <c r="C507" s="5"/>
+      <c r="A507" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="3"/>
+      <c r="C507" s="3"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="6" t="s">
+      <c r="A508" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="7"/>
-      <c r="C508" s="8"/>
+      <c r="B508" s="5"/>
+      <c r="C508" s="6"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4214,31 +4217,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="4">
+      <c r="A512" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="8">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="3"/>
-      <c r="B513" s="4"/>
+      <c r="A513" s="7"/>
+      <c r="B513" s="8"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="5"/>
-      <c r="C515" s="5"/>
+      <c r="A515" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="3"/>
+      <c r="C515" s="3"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="6" t="s">
+      <c r="A516" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="7"/>
-      <c r="C516" s="8"/>
+      <c r="B516" s="5"/>
+      <c r="C516" s="6"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4271,31 +4274,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="4">
+      <c r="A520" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="8">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="3"/>
-      <c r="B521" s="4"/>
+      <c r="A521" s="7"/>
+      <c r="B521" s="8"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="5"/>
-      <c r="C523" s="5"/>
+      <c r="A523" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="3"/>
+      <c r="C523" s="3"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="6" t="s">
+      <c r="A524" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="7"/>
-      <c r="C524" s="8"/>
+      <c r="B524" s="5"/>
+      <c r="C524" s="6"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4328,31 +4331,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="4">
+      <c r="A528" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="8">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="3"/>
-      <c r="B529" s="4"/>
+      <c r="A529" s="7"/>
+      <c r="B529" s="8"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="5"/>
-      <c r="C531" s="5"/>
+      <c r="A531" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="3"/>
+      <c r="C531" s="3"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="6" t="s">
+      <c r="A532" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="7"/>
-      <c r="C532" s="8"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="6"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4385,31 +4388,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="4">
+      <c r="A536" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="8">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="3"/>
-      <c r="B537" s="4"/>
+      <c r="A537" s="7"/>
+      <c r="B537" s="8"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="5"/>
-      <c r="C539" s="5"/>
+      <c r="A539" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="3"/>
+      <c r="C539" s="3"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="6" t="s">
+      <c r="A540" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="7"/>
-      <c r="C540" s="8"/>
+      <c r="B540" s="5"/>
+      <c r="C540" s="6"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4442,31 +4445,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="4">
+      <c r="A544" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="8">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="3"/>
-      <c r="B545" s="4"/>
+      <c r="A545" s="7"/>
+      <c r="B545" s="8"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="5"/>
-      <c r="C547" s="5"/>
+      <c r="A547" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="3"/>
+      <c r="C547" s="3"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="6" t="s">
+      <c r="A548" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="7"/>
-      <c r="C548" s="8"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="6"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4499,17 +4502,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="4">
+      <c r="A552" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="8">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="3"/>
-      <c r="B553" s="4"/>
+      <c r="A553" s="7"/>
+      <c r="B553" s="8"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4520,18 +4523,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="5"/>
-      <c r="C556" s="5"/>
+      <c r="A556" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="3"/>
+      <c r="C556" s="3"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="6" t="s">
+      <c r="A557" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="7"/>
-      <c r="C557" s="8"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="6"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4564,31 +4567,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="4">
+      <c r="A561" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="8">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="3"/>
-      <c r="B562" s="4"/>
+      <c r="A562" s="7"/>
+      <c r="B562" s="8"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="5"/>
-      <c r="C564" s="5"/>
+      <c r="A564" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="3"/>
+      <c r="C564" s="3"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="6" t="s">
+      <c r="A565" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="7"/>
-      <c r="C565" s="8"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="6"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4621,31 +4624,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="4">
+      <c r="A569" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="8">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="3"/>
-      <c r="B570" s="4"/>
+      <c r="A570" s="7"/>
+      <c r="B570" s="8"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="5"/>
-      <c r="C572" s="5"/>
+      <c r="A572" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="3"/>
+      <c r="C572" s="3"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="6" t="s">
+      <c r="A573" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="7"/>
-      <c r="C573" s="8"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="6"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4678,31 +4681,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="4">
+      <c r="A577" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="8">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="3"/>
-      <c r="B578" s="4"/>
+      <c r="A578" s="7"/>
+      <c r="B578" s="8"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="5"/>
-      <c r="C580" s="5"/>
+      <c r="A580" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="3"/>
+      <c r="C580" s="3"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="6" t="s">
+      <c r="A581" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="7"/>
-      <c r="C581" s="8"/>
+      <c r="B581" s="5"/>
+      <c r="C581" s="6"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4735,17 +4738,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="4">
+      <c r="A585" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="8">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="3"/>
-      <c r="B586" s="4"/>
+      <c r="A586" s="7"/>
+      <c r="B586" s="8"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4756,18 +4759,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="5"/>
-      <c r="C589" s="5"/>
+      <c r="A589" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="3"/>
+      <c r="C589" s="3"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="6" t="s">
+      <c r="A590" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="7"/>
-      <c r="C590" s="8"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="6"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4800,31 +4803,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="4">
+      <c r="A594" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="8">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="3"/>
-      <c r="B595" s="4"/>
+      <c r="A595" s="7"/>
+      <c r="B595" s="8"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="5"/>
-      <c r="C597" s="5"/>
+      <c r="A597" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="3"/>
+      <c r="C597" s="3"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="6" t="s">
+      <c r="A598" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="7"/>
-      <c r="C598" s="8"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="6"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4857,31 +4860,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="4">
+      <c r="A602" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="8">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="3"/>
-      <c r="B603" s="4"/>
+      <c r="A603" s="7"/>
+      <c r="B603" s="8"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="5"/>
-      <c r="C605" s="5"/>
+      <c r="A605" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="3"/>
+      <c r="C605" s="3"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="6" t="s">
+      <c r="A606" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="7"/>
-      <c r="C606" s="8"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="6"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4914,31 +4917,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="4">
+      <c r="A610" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="8">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="3"/>
-      <c r="B611" s="4"/>
+      <c r="A611" s="7"/>
+      <c r="B611" s="8"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="5"/>
-      <c r="C613" s="5"/>
+      <c r="A613" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="3"/>
+      <c r="C613" s="3"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="6" t="s">
+      <c r="A614" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="7"/>
-      <c r="C614" s="8"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="6"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4971,31 +4974,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="4">
+      <c r="A618" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="8">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="3"/>
-      <c r="B619" s="4"/>
+      <c r="A619" s="7"/>
+      <c r="B619" s="8"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="5"/>
-      <c r="C621" s="5"/>
+      <c r="A621" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="3"/>
+      <c r="C621" s="3"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="6" t="s">
+      <c r="A622" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="7"/>
-      <c r="C622" s="8"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="6"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5028,31 +5031,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="4">
+      <c r="A626" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="8">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="3"/>
-      <c r="B627" s="4"/>
+      <c r="A627" s="7"/>
+      <c r="B627" s="8"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="5"/>
-      <c r="C629" s="5"/>
+      <c r="A629" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="3"/>
+      <c r="C629" s="3"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="6" t="s">
+      <c r="A630" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="7"/>
-      <c r="C630" s="8"/>
+      <c r="B630" s="5"/>
+      <c r="C630" s="6"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5085,31 +5088,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="4">
+      <c r="A634" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="8">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="3"/>
-      <c r="B635" s="4"/>
+      <c r="A635" s="7"/>
+      <c r="B635" s="8"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="5"/>
-      <c r="C637" s="5"/>
+      <c r="A637" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="3"/>
+      <c r="C637" s="3"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="6" t="s">
+      <c r="A638" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="7"/>
-      <c r="C638" s="8"/>
+      <c r="B638" s="5"/>
+      <c r="C638" s="6"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5142,17 +5145,17 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="4">
+      <c r="A642" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="8">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="3"/>
-      <c r="B643" s="4"/>
+      <c r="A643" s="7"/>
+      <c r="B643" s="8"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
@@ -5163,18 +5166,18 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="5"/>
-      <c r="C646" s="5"/>
+      <c r="A646" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="3"/>
+      <c r="C646" s="3"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="6" t="s">
+      <c r="A647" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="7"/>
-      <c r="C647" s="8"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="6"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5207,31 +5210,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="4">
+      <c r="A651" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="8">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="3"/>
-      <c r="B652" s="4"/>
+      <c r="A652" s="7"/>
+      <c r="B652" s="8"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="5"/>
-      <c r="C654" s="5"/>
+      <c r="A654" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="3"/>
+      <c r="C654" s="3"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="6" t="s">
+      <c r="A655" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="7"/>
-      <c r="C655" s="8"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="6"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5264,31 +5267,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="4">
+      <c r="A659" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="8">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="3"/>
-      <c r="B660" s="4"/>
+      <c r="A660" s="7"/>
+      <c r="B660" s="8"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="5"/>
-      <c r="C662" s="5"/>
+      <c r="A662" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="3"/>
+      <c r="C662" s="3"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="6" t="s">
+      <c r="A663" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="7"/>
-      <c r="C663" s="8"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="6"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5321,31 +5324,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="4">
+      <c r="A667" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="8">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="3"/>
-      <c r="B668" s="4"/>
+      <c r="A668" s="7"/>
+      <c r="B668" s="8"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="5"/>
-      <c r="C670" s="5"/>
+      <c r="A670" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="3"/>
+      <c r="C670" s="3"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="6" t="s">
+      <c r="A671" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="7"/>
-      <c r="C671" s="8"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="6"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5378,31 +5381,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="4">
+      <c r="A675" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="8">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="3"/>
-      <c r="B676" s="4"/>
+      <c r="A676" s="7"/>
+      <c r="B676" s="8"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="5"/>
-      <c r="C678" s="5"/>
+      <c r="A678" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="3"/>
+      <c r="C678" s="3"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="6" t="s">
+      <c r="A679" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="7"/>
-      <c r="C679" s="8"/>
+      <c r="B679" s="5"/>
+      <c r="C679" s="6"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5435,31 +5438,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="4">
+      <c r="A683" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="8">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="3"/>
-      <c r="B684" s="4"/>
+      <c r="A684" s="7"/>
+      <c r="B684" s="8"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="5"/>
-      <c r="C686" s="5"/>
+      <c r="A686" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="3"/>
+      <c r="C686" s="3"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="6" t="s">
+      <c r="A687" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="7"/>
-      <c r="C687" s="8"/>
+      <c r="B687" s="5"/>
+      <c r="C687" s="6"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5492,31 +5495,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="4">
+      <c r="A691" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="8">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="3"/>
-      <c r="B692" s="4"/>
+      <c r="A692" s="7"/>
+      <c r="B692" s="8"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="5"/>
-      <c r="C694" s="5"/>
+      <c r="A694" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="3"/>
+      <c r="C694" s="3"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="6" t="s">
+      <c r="A695" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="7"/>
-      <c r="C695" s="8"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="6"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5549,31 +5552,31 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="4">
+      <c r="A699" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="8">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="3"/>
-      <c r="B700" s="4"/>
+      <c r="A700" s="7"/>
+      <c r="B700" s="8"/>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B702" s="5"/>
-      <c r="C702" s="5"/>
+      <c r="A702" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B702" s="3"/>
+      <c r="C702" s="3"/>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="6" t="s">
+      <c r="A703" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B703" s="7"/>
-      <c r="C703" s="8"/>
+      <c r="B703" s="5"/>
+      <c r="C703" s="6"/>
     </row>
     <row r="704" spans="1:3">
       <c r="A704" s="1" t="s">
@@ -5606,17 +5609,17 @@
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B707" s="4">
+      <c r="A707" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="8">
         <f>B705-B706</f>
         <v>448</v>
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="3"/>
-      <c r="B708" s="4"/>
+      <c r="A708" s="7"/>
+      <c r="B708" s="8"/>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" s="1" t="s">
@@ -5627,18 +5630,18 @@
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B711" s="5"/>
-      <c r="C711" s="5"/>
+      <c r="A711" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="3"/>
+      <c r="C711" s="3"/>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="6" t="s">
+      <c r="A712" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B712" s="7"/>
-      <c r="C712" s="8"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="6"/>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" s="1" t="s">
@@ -5671,31 +5674,31 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B716" s="4">
+      <c r="A716" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="8">
         <f>B714-B715</f>
         <v>27</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="3"/>
-      <c r="B717" s="4"/>
+      <c r="A717" s="7"/>
+      <c r="B717" s="8"/>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B719" s="5"/>
-      <c r="C719" s="5"/>
+      <c r="A719" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="3"/>
+      <c r="C719" s="3"/>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="6" t="s">
+      <c r="A720" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B720" s="7"/>
-      <c r="C720" s="8"/>
+      <c r="B720" s="5"/>
+      <c r="C720" s="6"/>
     </row>
     <row r="721" spans="1:3">
       <c r="A721" s="1" t="s">
@@ -5728,31 +5731,31 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B724" s="4">
+      <c r="A724" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="8">
         <f>B722-B723</f>
         <v>386</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="3"/>
-      <c r="B725" s="4"/>
+      <c r="A725" s="7"/>
+      <c r="B725" s="8"/>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B727" s="5"/>
-      <c r="C727" s="5"/>
+      <c r="A727" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="3"/>
+      <c r="C727" s="3"/>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="6" t="s">
+      <c r="A728" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B728" s="7"/>
-      <c r="C728" s="8"/>
+      <c r="B728" s="5"/>
+      <c r="C728" s="6"/>
     </row>
     <row r="729" spans="1:3">
       <c r="A729" s="1" t="s">
@@ -5785,31 +5788,31 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B732" s="4">
+      <c r="A732" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="8">
         <f>B730-B731</f>
         <v>1256</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="3"/>
-      <c r="B733" s="4"/>
+      <c r="A733" s="7"/>
+      <c r="B733" s="8"/>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B735" s="5"/>
-      <c r="C735" s="5"/>
+      <c r="A735" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="3"/>
+      <c r="C735" s="3"/>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="6" t="s">
+      <c r="A736" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B736" s="7"/>
-      <c r="C736" s="8"/>
+      <c r="B736" s="5"/>
+      <c r="C736" s="6"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="1" t="s">
@@ -5842,31 +5845,31 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B740" s="4">
+      <c r="A740" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="8">
         <f>B738-B739</f>
         <v>227</v>
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="3"/>
-      <c r="B741" s="4"/>
+      <c r="A741" s="7"/>
+      <c r="B741" s="8"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B743" s="5"/>
-      <c r="C743" s="5"/>
+      <c r="A743" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="3"/>
+      <c r="C743" s="3"/>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="6" t="s">
+      <c r="A744" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B744" s="7"/>
-      <c r="C744" s="8"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="6"/>
     </row>
     <row r="745" spans="1:3">
       <c r="A745" s="1" t="s">
@@ -5899,31 +5902,31 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B748" s="4">
+      <c r="A748" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="8">
         <f>B746-B747</f>
         <v>961</v>
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="3"/>
-      <c r="B749" s="4"/>
+      <c r="A749" s="7"/>
+      <c r="B749" s="8"/>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B751" s="5"/>
-      <c r="C751" s="5"/>
+      <c r="A751" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="3"/>
+      <c r="C751" s="3"/>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="6" t="s">
+      <c r="A752" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B752" s="7"/>
-      <c r="C752" s="8"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="6"/>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" s="1" t="s">
@@ -5956,31 +5959,31 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="4">
+      <c r="A756" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="8">
         <f>B754-B755</f>
         <v>6</v>
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="3"/>
-      <c r="B757" s="4"/>
+      <c r="A757" s="7"/>
+      <c r="B757" s="8"/>
     </row>
     <row r="759" spans="1:3">
-      <c r="A759" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B759" s="5"/>
-      <c r="C759" s="5"/>
+      <c r="A759" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B759" s="3"/>
+      <c r="C759" s="3"/>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="6" t="s">
+      <c r="A760" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B760" s="7"/>
-      <c r="C760" s="8"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="6"/>
     </row>
     <row r="761" spans="1:3">
       <c r="A761" s="1" t="s">
@@ -6013,31 +6016,31 @@
       </c>
     </row>
     <row r="764" spans="1:3">
-      <c r="A764" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B764" s="4">
+      <c r="A764" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764" s="8">
         <f>B762-B763</f>
         <v>616</v>
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="3"/>
-      <c r="B765" s="4"/>
+      <c r="A765" s="7"/>
+      <c r="B765" s="8"/>
     </row>
     <row r="767" spans="1:3">
-      <c r="A767" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B767" s="5"/>
-      <c r="C767" s="5"/>
+      <c r="A767" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B767" s="3"/>
+      <c r="C767" s="3"/>
     </row>
     <row r="768" spans="1:3">
-      <c r="A768" s="6" t="s">
+      <c r="A768" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B768" s="7"/>
-      <c r="C768" s="8"/>
+      <c r="B768" s="5"/>
+      <c r="C768" s="6"/>
     </row>
     <row r="769" spans="1:3">
       <c r="A769" s="1" t="s">
@@ -6070,17 +6073,17 @@
       </c>
     </row>
     <row r="772" spans="1:3">
-      <c r="A772" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B772" s="4">
+      <c r="A772" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B772" s="8">
         <f>B770-B771</f>
         <v>379</v>
       </c>
     </row>
     <row r="773" spans="1:3">
-      <c r="A773" s="3"/>
-      <c r="B773" s="4"/>
+      <c r="A773" s="7"/>
+      <c r="B773" s="8"/>
     </row>
     <row r="774" spans="1:3">
       <c r="A774" s="1" t="s">
@@ -6091,18 +6094,18 @@
       </c>
     </row>
     <row r="776" spans="1:3">
-      <c r="A776" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B776" s="5"/>
-      <c r="C776" s="5"/>
+      <c r="A776" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B776" s="3"/>
+      <c r="C776" s="3"/>
     </row>
     <row r="777" spans="1:3">
-      <c r="A777" s="6" t="s">
+      <c r="A777" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B777" s="7"/>
-      <c r="C777" s="8"/>
+      <c r="B777" s="5"/>
+      <c r="C777" s="6"/>
     </row>
     <row r="778" spans="1:3">
       <c r="A778" s="1" t="s">
@@ -6135,31 +6138,31 @@
       </c>
     </row>
     <row r="781" spans="1:3">
-      <c r="A781" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B781" s="4">
+      <c r="A781" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781" s="8">
         <f>B779-B780</f>
         <v>276</v>
       </c>
     </row>
     <row r="782" spans="1:3">
-      <c r="A782" s="3"/>
-      <c r="B782" s="4"/>
+      <c r="A782" s="7"/>
+      <c r="B782" s="8"/>
     </row>
     <row r="784" spans="1:3">
-      <c r="A784" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B784" s="5"/>
-      <c r="C784" s="5"/>
+      <c r="A784" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B784" s="3"/>
+      <c r="C784" s="3"/>
     </row>
     <row r="785" spans="1:3">
-      <c r="A785" s="6" t="s">
+      <c r="A785" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B785" s="7"/>
-      <c r="C785" s="8"/>
+      <c r="B785" s="5"/>
+      <c r="C785" s="6"/>
     </row>
     <row r="786" spans="1:3">
       <c r="A786" s="1" t="s">
@@ -6192,31 +6195,31 @@
       </c>
     </row>
     <row r="789" spans="1:3">
-      <c r="A789" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B789" s="4">
+      <c r="A789" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789" s="8">
         <f>B787-B788</f>
         <v>596</v>
       </c>
     </row>
     <row r="790" spans="1:3">
-      <c r="A790" s="3"/>
-      <c r="B790" s="4"/>
+      <c r="A790" s="7"/>
+      <c r="B790" s="8"/>
     </row>
     <row r="792" spans="1:3">
-      <c r="A792" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B792" s="5"/>
-      <c r="C792" s="5"/>
+      <c r="A792" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B792" s="3"/>
+      <c r="C792" s="3"/>
     </row>
     <row r="793" spans="1:3">
-      <c r="A793" s="6" t="s">
+      <c r="A793" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B793" s="7"/>
-      <c r="C793" s="8"/>
+      <c r="B793" s="5"/>
+      <c r="C793" s="6"/>
     </row>
     <row r="794" spans="1:3">
       <c r="A794" s="1" t="s">
@@ -6249,31 +6252,31 @@
       </c>
     </row>
     <row r="797" spans="1:3">
-      <c r="A797" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B797" s="4">
+      <c r="A797" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797" s="8">
         <f>B795-B796</f>
         <v>250</v>
       </c>
     </row>
     <row r="798" spans="1:3">
-      <c r="A798" s="3"/>
-      <c r="B798" s="4"/>
+      <c r="A798" s="7"/>
+      <c r="B798" s="8"/>
     </row>
     <row r="800" spans="1:3">
-      <c r="A800" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B800" s="5"/>
-      <c r="C800" s="5"/>
+      <c r="A800" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B800" s="3"/>
+      <c r="C800" s="3"/>
     </row>
     <row r="801" spans="1:3">
-      <c r="A801" s="6" t="s">
+      <c r="A801" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B801" s="7"/>
-      <c r="C801" s="8"/>
+      <c r="B801" s="5"/>
+      <c r="C801" s="6"/>
     </row>
     <row r="802" spans="1:3">
       <c r="A802" s="1" t="s">
@@ -6306,31 +6309,31 @@
       </c>
     </row>
     <row r="805" spans="1:3">
-      <c r="A805" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B805" s="4">
+      <c r="A805" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805" s="8">
         <f>B803-B804</f>
         <v>378</v>
       </c>
     </row>
     <row r="806" spans="1:3">
-      <c r="A806" s="3"/>
-      <c r="B806" s="4"/>
+      <c r="A806" s="7"/>
+      <c r="B806" s="8"/>
     </row>
     <row r="808" spans="1:3">
-      <c r="A808" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B808" s="5"/>
-      <c r="C808" s="5"/>
+      <c r="A808" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B808" s="3"/>
+      <c r="C808" s="3"/>
     </row>
     <row r="809" spans="1:3">
-      <c r="A809" s="6" t="s">
+      <c r="A809" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B809" s="7"/>
-      <c r="C809" s="8"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="6"/>
     </row>
     <row r="810" spans="1:3">
       <c r="A810" s="1" t="s">
@@ -6363,31 +6366,31 @@
       </c>
     </row>
     <row r="813" spans="1:3">
-      <c r="A813" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B813" s="4">
+      <c r="A813" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813" s="8">
         <f>B811-B812</f>
         <v>900</v>
       </c>
     </row>
     <row r="814" spans="1:3">
-      <c r="A814" s="3"/>
-      <c r="B814" s="4"/>
+      <c r="A814" s="7"/>
+      <c r="B814" s="8"/>
     </row>
     <row r="816" spans="1:3">
-      <c r="A816" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B816" s="5"/>
-      <c r="C816" s="5"/>
+      <c r="A816" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B816" s="3"/>
+      <c r="C816" s="3"/>
     </row>
     <row r="817" spans="1:3">
-      <c r="A817" s="6" t="s">
+      <c r="A817" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B817" s="7"/>
-      <c r="C817" s="8"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="6"/>
     </row>
     <row r="818" spans="1:3">
       <c r="A818" s="1" t="s">
@@ -6420,31 +6423,31 @@
       </c>
     </row>
     <row r="821" spans="1:3">
-      <c r="A821" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B821" s="4">
+      <c r="A821" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B821" s="8">
         <f>B819-B820</f>
         <v>74</v>
       </c>
     </row>
     <row r="822" spans="1:3">
-      <c r="A822" s="3"/>
-      <c r="B822" s="4"/>
+      <c r="A822" s="7"/>
+      <c r="B822" s="8"/>
     </row>
     <row r="824" spans="1:3">
-      <c r="A824" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B824" s="5"/>
-      <c r="C824" s="5"/>
+      <c r="A824" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B824" s="3"/>
+      <c r="C824" s="3"/>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825" s="6" t="s">
+      <c r="A825" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B825" s="7"/>
-      <c r="C825" s="8"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="6"/>
     </row>
     <row r="826" spans="1:3">
       <c r="A826" s="1" t="s">
@@ -6477,31 +6480,31 @@
       </c>
     </row>
     <row r="829" spans="1:3">
-      <c r="A829" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B829" s="4">
+      <c r="A829" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B829" s="8">
         <f>B827-B828</f>
         <v>0</v>
       </c>
     </row>
     <row r="830" spans="1:3">
-      <c r="A830" s="3"/>
-      <c r="B830" s="4"/>
+      <c r="A830" s="7"/>
+      <c r="B830" s="8"/>
     </row>
     <row r="832" spans="1:3">
-      <c r="A832" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B832" s="5"/>
-      <c r="C832" s="5"/>
+      <c r="A832" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B832" s="3"/>
+      <c r="C832" s="3"/>
     </row>
     <row r="833" spans="1:3">
-      <c r="A833" s="6" t="s">
+      <c r="A833" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B833" s="7"/>
-      <c r="C833" s="8"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="6"/>
     </row>
     <row r="834" spans="1:3">
       <c r="A834" s="1" t="s">
@@ -6534,17 +6537,17 @@
       </c>
     </row>
     <row r="837" spans="1:3">
-      <c r="A837" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B837" s="4">
+      <c r="A837" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B837" s="8">
         <f>B835-B836</f>
         <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:3">
-      <c r="A838" s="3"/>
-      <c r="B838" s="4"/>
+      <c r="A838" s="7"/>
+      <c r="B838" s="8"/>
     </row>
     <row r="839" spans="1:3">
       <c r="A839" s="1" t="s">
@@ -6555,18 +6558,18 @@
       </c>
     </row>
     <row r="841" spans="1:3">
-      <c r="A841" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B841" s="5"/>
-      <c r="C841" s="5"/>
+      <c r="A841" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B841" s="3"/>
+      <c r="C841" s="3"/>
     </row>
     <row r="842" spans="1:3">
-      <c r="A842" s="6" t="s">
+      <c r="A842" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B842" s="7"/>
-      <c r="C842" s="8"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="6"/>
     </row>
     <row r="843" spans="1:3">
       <c r="A843" s="1" t="s">
@@ -6599,31 +6602,31 @@
       </c>
     </row>
     <row r="846" spans="1:3">
-      <c r="A846" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B846" s="4">
+      <c r="A846" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846" s="8">
         <f>B844-B845</f>
         <v>717</v>
       </c>
     </row>
     <row r="847" spans="1:3">
-      <c r="A847" s="3"/>
-      <c r="B847" s="4"/>
+      <c r="A847" s="7"/>
+      <c r="B847" s="8"/>
     </row>
     <row r="849" spans="1:3">
-      <c r="A849" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B849" s="5"/>
-      <c r="C849" s="5"/>
+      <c r="A849" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B849" s="3"/>
+      <c r="C849" s="3"/>
     </row>
     <row r="850" spans="1:3">
-      <c r="A850" s="6" t="s">
+      <c r="A850" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B850" s="7"/>
-      <c r="C850" s="8"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="6"/>
     </row>
     <row r="851" spans="1:3">
       <c r="A851" s="1" t="s">
@@ -6656,31 +6659,31 @@
       </c>
     </row>
     <row r="854" spans="1:3">
-      <c r="A854" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B854" s="4">
+      <c r="A854" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854" s="8">
         <f>B852-B853</f>
         <v>0</v>
       </c>
     </row>
     <row r="855" spans="1:3">
-      <c r="A855" s="3"/>
-      <c r="B855" s="4"/>
+      <c r="A855" s="7"/>
+      <c r="B855" s="8"/>
     </row>
     <row r="857" spans="1:3">
-      <c r="A857" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B857" s="5"/>
-      <c r="C857" s="5"/>
+      <c r="A857" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B857" s="3"/>
+      <c r="C857" s="3"/>
     </row>
     <row r="858" spans="1:3">
-      <c r="A858" s="6" t="s">
+      <c r="A858" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B858" s="7"/>
-      <c r="C858" s="8"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="6"/>
     </row>
     <row r="859" spans="1:3">
       <c r="A859" s="1" t="s">
@@ -6713,31 +6716,31 @@
       </c>
     </row>
     <row r="862" spans="1:3">
-      <c r="A862" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B862" s="4">
+      <c r="A862" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862" s="8">
         <f>B860-B861</f>
         <v>224</v>
       </c>
     </row>
     <row r="863" spans="1:3">
-      <c r="A863" s="3"/>
-      <c r="B863" s="4"/>
+      <c r="A863" s="7"/>
+      <c r="B863" s="8"/>
     </row>
     <row r="865" spans="1:3">
-      <c r="A865" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B865" s="5"/>
-      <c r="C865" s="5"/>
+      <c r="A865" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B865" s="3"/>
+      <c r="C865" s="3"/>
     </row>
     <row r="866" spans="1:3">
-      <c r="A866" s="6" t="s">
+      <c r="A866" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B866" s="7"/>
-      <c r="C866" s="8"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="6"/>
     </row>
     <row r="867" spans="1:3">
       <c r="A867" s="1" t="s">
@@ -6770,31 +6773,31 @@
       </c>
     </row>
     <row r="870" spans="1:3">
-      <c r="A870" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B870" s="4">
+      <c r="A870" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870" s="8">
         <f>B868-B869</f>
         <v>124</v>
       </c>
     </row>
     <row r="871" spans="1:3">
-      <c r="A871" s="3"/>
-      <c r="B871" s="4"/>
+      <c r="A871" s="7"/>
+      <c r="B871" s="8"/>
     </row>
     <row r="873" spans="1:3">
-      <c r="A873" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B873" s="5"/>
-      <c r="C873" s="5"/>
+      <c r="A873" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B873" s="3"/>
+      <c r="C873" s="3"/>
     </row>
     <row r="874" spans="1:3">
-      <c r="A874" s="6" t="s">
+      <c r="A874" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B874" s="7"/>
-      <c r="C874" s="8"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="6"/>
     </row>
     <row r="875" spans="1:3">
       <c r="A875" s="1" t="s">
@@ -6827,31 +6830,31 @@
       </c>
     </row>
     <row r="878" spans="1:3">
-      <c r="A878" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B878" s="4">
+      <c r="A878" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B878" s="8">
         <f>B876-B877</f>
         <v>449</v>
       </c>
     </row>
     <row r="879" spans="1:3">
-      <c r="A879" s="3"/>
-      <c r="B879" s="4"/>
+      <c r="A879" s="7"/>
+      <c r="B879" s="8"/>
     </row>
     <row r="881" spans="1:3">
-      <c r="A881" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B881" s="5"/>
-      <c r="C881" s="5"/>
+      <c r="A881" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B881" s="3"/>
+      <c r="C881" s="3"/>
     </row>
     <row r="882" spans="1:3">
-      <c r="A882" s="6" t="s">
+      <c r="A882" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B882" s="7"/>
-      <c r="C882" s="8"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="6"/>
     </row>
     <row r="883" spans="1:3">
       <c r="A883" s="1" t="s">
@@ -6884,31 +6887,31 @@
       </c>
     </row>
     <row r="886" spans="1:3">
-      <c r="A886" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B886" s="4">
+      <c r="A886" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B886" s="8">
         <f>B884-B885</f>
         <v>821</v>
       </c>
     </row>
     <row r="887" spans="1:3">
-      <c r="A887" s="3"/>
-      <c r="B887" s="4"/>
+      <c r="A887" s="7"/>
+      <c r="B887" s="8"/>
     </row>
     <row r="889" spans="1:3">
-      <c r="A889" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B889" s="5"/>
-      <c r="C889" s="5"/>
+      <c r="A889" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B889" s="3"/>
+      <c r="C889" s="3"/>
     </row>
     <row r="890" spans="1:3">
-      <c r="A890" s="6" t="s">
+      <c r="A890" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B890" s="7"/>
-      <c r="C890" s="8"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="6"/>
     </row>
     <row r="891" spans="1:3">
       <c r="A891" s="1" t="s">
@@ -6941,17 +6944,17 @@
       </c>
     </row>
     <row r="894" spans="1:3">
-      <c r="A894" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B894" s="4">
+      <c r="A894" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B894" s="8">
         <f>B892-B893</f>
         <v>31</v>
       </c>
     </row>
     <row r="895" spans="1:3">
-      <c r="A895" s="3"/>
-      <c r="B895" s="4"/>
+      <c r="A895" s="7"/>
+      <c r="B895" s="8"/>
     </row>
     <row r="896" spans="1:3">
       <c r="A896" s="1" t="s">
@@ -6962,18 +6965,18 @@
       </c>
     </row>
     <row r="898" spans="1:3">
-      <c r="A898" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B898" s="5"/>
-      <c r="C898" s="5"/>
+      <c r="A898" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B898" s="3"/>
+      <c r="C898" s="3"/>
     </row>
     <row r="899" spans="1:3">
-      <c r="A899" s="6" t="s">
+      <c r="A899" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B899" s="7"/>
-      <c r="C899" s="8"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="6"/>
     </row>
     <row r="900" spans="1:3">
       <c r="A900" s="1" t="s">
@@ -7006,31 +7009,31 @@
       </c>
     </row>
     <row r="903" spans="1:3">
-      <c r="A903" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B903" s="4">
+      <c r="A903" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B903" s="8">
         <f>B901-B902</f>
         <v>22</v>
       </c>
     </row>
     <row r="904" spans="1:3">
-      <c r="A904" s="3"/>
-      <c r="B904" s="4"/>
+      <c r="A904" s="7"/>
+      <c r="B904" s="8"/>
     </row>
     <row r="906" spans="1:3">
-      <c r="A906" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B906" s="5"/>
-      <c r="C906" s="5"/>
+      <c r="A906" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B906" s="3"/>
+      <c r="C906" s="3"/>
     </row>
     <row r="907" spans="1:3">
-      <c r="A907" s="6" t="s">
+      <c r="A907" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B907" s="7"/>
-      <c r="C907" s="8"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="6"/>
     </row>
     <row r="908" spans="1:3">
       <c r="A908" s="1" t="s">
@@ -7063,31 +7066,31 @@
       </c>
     </row>
     <row r="911" spans="1:3">
-      <c r="A911" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B911" s="4">
+      <c r="A911" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B911" s="8">
         <f>B909-B910</f>
         <v>75</v>
       </c>
     </row>
     <row r="912" spans="1:3">
-      <c r="A912" s="3"/>
-      <c r="B912" s="4"/>
+      <c r="A912" s="7"/>
+      <c r="B912" s="8"/>
     </row>
     <row r="914" spans="1:3">
-      <c r="A914" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B914" s="5"/>
-      <c r="C914" s="5"/>
+      <c r="A914" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B914" s="3"/>
+      <c r="C914" s="3"/>
     </row>
     <row r="915" spans="1:3">
-      <c r="A915" s="6" t="s">
+      <c r="A915" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B915" s="7"/>
-      <c r="C915" s="8"/>
+      <c r="B915" s="5"/>
+      <c r="C915" s="6"/>
     </row>
     <row r="916" spans="1:3">
       <c r="A916" s="1" t="s">
@@ -7120,31 +7123,31 @@
       </c>
     </row>
     <row r="919" spans="1:3">
-      <c r="A919" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B919" s="4">
+      <c r="A919" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B919" s="8">
         <f>B917-B918</f>
         <v>39</v>
       </c>
     </row>
     <row r="920" spans="1:3">
-      <c r="A920" s="3"/>
-      <c r="B920" s="4"/>
+      <c r="A920" s="7"/>
+      <c r="B920" s="8"/>
     </row>
     <row r="922" spans="1:3">
-      <c r="A922" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B922" s="5"/>
-      <c r="C922" s="5"/>
+      <c r="A922" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B922" s="3"/>
+      <c r="C922" s="3"/>
     </row>
     <row r="923" spans="1:3">
-      <c r="A923" s="6" t="s">
+      <c r="A923" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B923" s="7"/>
-      <c r="C923" s="8"/>
+      <c r="B923" s="5"/>
+      <c r="C923" s="6"/>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" s="1" t="s">
@@ -7177,31 +7180,31 @@
       </c>
     </row>
     <row r="927" spans="1:3">
-      <c r="A927" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B927" s="4">
+      <c r="A927" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B927" s="8">
         <f>B925-B926</f>
         <v>70</v>
       </c>
     </row>
     <row r="928" spans="1:3">
-      <c r="A928" s="3"/>
-      <c r="B928" s="4"/>
+      <c r="A928" s="7"/>
+      <c r="B928" s="8"/>
     </row>
     <row r="930" spans="1:3">
-      <c r="A930" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B930" s="5"/>
-      <c r="C930" s="5"/>
+      <c r="A930" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B930" s="3"/>
+      <c r="C930" s="3"/>
     </row>
     <row r="931" spans="1:3">
-      <c r="A931" s="6" t="s">
+      <c r="A931" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B931" s="7"/>
-      <c r="C931" s="8"/>
+      <c r="B931" s="5"/>
+      <c r="C931" s="6"/>
     </row>
     <row r="932" spans="1:3">
       <c r="A932" s="1" t="s">
@@ -7234,20 +7237,484 @@
       </c>
     </row>
     <row r="935" spans="1:3">
-      <c r="A935" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B935" s="4">
+      <c r="A935" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B935" s="8">
         <f>B933-B934</f>
         <v>0</v>
       </c>
     </row>
     <row r="936" spans="1:3">
-      <c r="A936" s="3"/>
-      <c r="B936" s="4"/>
+      <c r="A936" s="7"/>
+      <c r="B936" s="8"/>
+    </row>
+    <row r="938" spans="1:3">
+      <c r="A938" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B938" s="3"/>
+      <c r="C938" s="3"/>
+    </row>
+    <row r="939" spans="1:3">
+      <c r="A939" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B939" s="5"/>
+      <c r="C939" s="6"/>
+    </row>
+    <row r="940" spans="1:3">
+      <c r="A940" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B940" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C940" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="941" spans="1:3">
+      <c r="A941" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B941" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C941" s="2">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="942" spans="1:3">
+      <c r="A942" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B942" s="2">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3">
+      <c r="A943" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B943" s="8">
+        <f>B941-B942</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="944" spans="1:3">
+      <c r="A944" s="7"/>
+      <c r="B944" s="8"/>
+    </row>
+    <row r="945" spans="1:3">
+      <c r="A945" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B945" s="2">
+        <v>67520</v>
+      </c>
+    </row>
+    <row r="947" spans="1:3">
+      <c r="A947" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B947" s="3"/>
+      <c r="C947" s="3"/>
+    </row>
+    <row r="948" spans="1:3">
+      <c r="A948" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B948" s="5"/>
+      <c r="C948" s="6"/>
+    </row>
+    <row r="949" spans="1:3">
+      <c r="A949" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B949" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C949" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3">
+      <c r="A950" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B950" s="2">
+        <v>2448</v>
+      </c>
+      <c r="C950" s="2">
+        <v>7994</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3">
+      <c r="A951" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B951" s="2">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3">
+      <c r="A952" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B952" s="8">
+        <f>B950-B951</f>
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="953" spans="1:3">
+      <c r="A953" s="7"/>
+      <c r="B953" s="8"/>
+    </row>
+    <row r="955" spans="1:3">
+      <c r="A955" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B955" s="3"/>
+      <c r="C955" s="3"/>
+    </row>
+    <row r="956" spans="1:3">
+      <c r="A956" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B956" s="5"/>
+      <c r="C956" s="6"/>
+    </row>
+    <row r="957" spans="1:3">
+      <c r="A957" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C957" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3">
+      <c r="A958" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B958" s="2">
+        <v>63</v>
+      </c>
+      <c r="C958" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3">
+      <c r="A959" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B959" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3">
+      <c r="A960" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B960" s="8">
+        <f>B958-B959</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3">
+      <c r="A961" s="7"/>
+      <c r="B961" s="8"/>
+    </row>
+    <row r="963" spans="1:3">
+      <c r="A963" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B963" s="3"/>
+      <c r="C963" s="3"/>
+    </row>
+    <row r="964" spans="1:3">
+      <c r="A964" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B964" s="5"/>
+      <c r="C964" s="6"/>
+    </row>
+    <row r="965" spans="1:3">
+      <c r="A965" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C965" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3">
+      <c r="A966" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B966" s="2">
+        <v>261</v>
+      </c>
+      <c r="C966" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3">
+      <c r="A967" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B967" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3">
+      <c r="A968" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B968" s="8">
+        <f>B966-B967</f>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3">
+      <c r="A969" s="7"/>
+      <c r="B969" s="8"/>
+    </row>
+    <row r="971" spans="1:3">
+      <c r="A971" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B971" s="3"/>
+      <c r="C971" s="3"/>
+    </row>
+    <row r="972" spans="1:3">
+      <c r="A972" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B972" s="5"/>
+      <c r="C972" s="6"/>
+    </row>
+    <row r="973" spans="1:3">
+      <c r="A973" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B973" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C973" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3">
+      <c r="A974" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B974" s="2">
+        <v>664</v>
+      </c>
+      <c r="C974" s="2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3">
+      <c r="A975" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B975" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3">
+      <c r="A976" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B976" s="8">
+        <f>B974-B975</f>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3">
+      <c r="A977" s="7"/>
+      <c r="B977" s="8"/>
+    </row>
+    <row r="979" spans="1:3">
+      <c r="A979" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B979" s="3"/>
+      <c r="C979" s="3"/>
+    </row>
+    <row r="980" spans="1:3">
+      <c r="A980" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B980" s="5"/>
+      <c r="C980" s="6"/>
+    </row>
+    <row r="981" spans="1:3">
+      <c r="A981" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C981" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3">
+      <c r="A982" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B982" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C982" s="2">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3">
+      <c r="A983" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B983" s="2">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3">
+      <c r="A984" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B984" s="8">
+        <f>B982-B983</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3">
+      <c r="A985" s="7"/>
+      <c r="B985" s="8"/>
+    </row>
+    <row r="987" spans="1:3">
+      <c r="A987" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B987" s="3"/>
+      <c r="C987" s="3"/>
+    </row>
+    <row r="988" spans="1:3">
+      <c r="A988" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B988" s="5"/>
+      <c r="C988" s="6"/>
+    </row>
+    <row r="989" spans="1:3">
+      <c r="A989" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C989" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3">
+      <c r="A990" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B990" s="2">
+        <v>701</v>
+      </c>
+      <c r="C990" s="2">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3">
+      <c r="A991" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B991" s="2">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3">
+      <c r="A992" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B992" s="8">
+        <f>B990-B991</f>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3">
+      <c r="A993" s="7"/>
+      <c r="B993" s="8"/>
+    </row>
+    <row r="995" spans="1:3">
+      <c r="A995" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B995" s="3"/>
+      <c r="C995" s="3"/>
+    </row>
+    <row r="996" spans="1:3">
+      <c r="A996" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B996" s="5"/>
+      <c r="C996" s="6"/>
+    </row>
+    <row r="997" spans="1:3">
+      <c r="A997" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C997" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3">
+      <c r="A998" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B998" s="2">
+        <v>1700</v>
+      </c>
+      <c r="C998" s="2">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3">
+      <c r="A999" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B999" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3">
+      <c r="A1000" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1000" s="8">
+        <f>B998-B999</f>
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3">
+      <c r="A1001" s="7"/>
+      <c r="B1001" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="460">
+  <mergeCells count="492">
     <mergeCell ref="A927:A928"/>
     <mergeCell ref="B927:B928"/>
     <mergeCell ref="A930:C930"/>
@@ -7708,6 +8175,38 @@
     <mergeCell ref="A882:C882"/>
     <mergeCell ref="A886:A887"/>
     <mergeCell ref="B886:B887"/>
+    <mergeCell ref="A938:C938"/>
+    <mergeCell ref="A939:C939"/>
+    <mergeCell ref="A943:A944"/>
+    <mergeCell ref="B943:B944"/>
+    <mergeCell ref="A947:C947"/>
+    <mergeCell ref="A948:C948"/>
+    <mergeCell ref="A952:A953"/>
+    <mergeCell ref="B952:B953"/>
+    <mergeCell ref="A955:C955"/>
+    <mergeCell ref="A956:C956"/>
+    <mergeCell ref="A960:A961"/>
+    <mergeCell ref="B960:B961"/>
+    <mergeCell ref="A963:C963"/>
+    <mergeCell ref="A964:C964"/>
+    <mergeCell ref="A968:A969"/>
+    <mergeCell ref="B968:B969"/>
+    <mergeCell ref="A971:C971"/>
+    <mergeCell ref="A972:C972"/>
+    <mergeCell ref="A995:C995"/>
+    <mergeCell ref="A996:C996"/>
+    <mergeCell ref="A1000:A1001"/>
+    <mergeCell ref="B1000:B1001"/>
+    <mergeCell ref="A976:A977"/>
+    <mergeCell ref="B976:B977"/>
+    <mergeCell ref="A979:C979"/>
+    <mergeCell ref="A980:C980"/>
+    <mergeCell ref="A984:A985"/>
+    <mergeCell ref="B984:B985"/>
+    <mergeCell ref="A987:C987"/>
+    <mergeCell ref="A988:C988"/>
+    <mergeCell ref="A992:A993"/>
+    <mergeCell ref="B992:B993"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7429CE9B-BCEE-4F3B-BD5E-B43F941887A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050556EF-AC8D-4839-91D8-7BDDACCF362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="41">
   <si>
     <t>Data</t>
   </si>
@@ -155,6 +155,9 @@
   <si>
     <t>27.10.2026</t>
   </si>
+  <si>
+    <t>28.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -258,6 +261,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -267,12 +276,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -550,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1001"/>
+  <dimension ref="A1:C1066"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -559,18 +562,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -603,17 +606,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -624,18 +627,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -668,31 +671,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="A18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -725,31 +728,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -782,31 +785,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="A34" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -839,31 +842,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="4">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="A42" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -896,31 +899,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="4">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="4"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
+      <c r="A50" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -953,31 +956,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="4">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="A58" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -1010,17 +1013,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="4">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1031,18 +1034,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
+      <c r="A67" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1075,31 +1078,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="8">
+      <c r="A72" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="4">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
+      <c r="A75" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="6"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1132,31 +1135,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="8">
+      <c r="A80" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="4">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="4"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="A83" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="6"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="8"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1189,31 +1192,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="8">
+      <c r="A88" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="4">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="4"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
+      <c r="A91" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="6"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1246,31 +1249,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="8">
+      <c r="A96" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="4">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="7"/>
-      <c r="B97" s="8"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="4"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="A99" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="6"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="8"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1303,31 +1306,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="8">
+      <c r="A104" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="4">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="7"/>
-      <c r="B105" s="8"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="4"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="A107" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="6"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="8"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1360,31 +1363,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="8">
+      <c r="A112" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="4">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="7"/>
-      <c r="B113" s="8"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="4"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="A115" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="6"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="8"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1417,31 +1420,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="8">
+      <c r="A120" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="4">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="7"/>
-      <c r="B121" s="8"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="4"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="A123" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="6"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="8"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1474,17 +1477,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="8">
+      <c r="A128" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="4">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="7"/>
-      <c r="B129" s="8"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="4"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1495,18 +1498,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="A132" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="5"/>
-      <c r="C133" s="6"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="8"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1539,31 +1542,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="8">
+      <c r="A137" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="4">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="7"/>
-      <c r="B138" s="8"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="4"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
+      <c r="A140" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="5"/>
-      <c r="C141" s="6"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="8"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1596,31 +1599,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="8">
+      <c r="A145" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="4">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="7"/>
-      <c r="B146" s="8"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="4"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
+      <c r="A148" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="6"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="8"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1653,31 +1656,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="8">
+      <c r="A153" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="4">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="7"/>
-      <c r="B154" s="8"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="4"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
+      <c r="A156" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="5"/>
-      <c r="C157" s="6"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="8"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1710,31 +1713,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="8">
+      <c r="A161" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="4">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="7"/>
-      <c r="B162" s="8"/>
+      <c r="A162" s="3"/>
+      <c r="B162" s="4"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
+      <c r="A164" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="5"/>
-      <c r="C165" s="6"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1767,31 +1770,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="8">
+      <c r="A169" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="4">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="7"/>
-      <c r="B170" s="8"/>
+      <c r="A170" s="3"/>
+      <c r="B170" s="4"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
+      <c r="A172" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="6"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="8"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1824,31 +1827,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="8">
+      <c r="A177" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="4">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="7"/>
-      <c r="B178" s="8"/>
+      <c r="A178" s="3"/>
+      <c r="B178" s="4"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
+      <c r="A180" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="6"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="8"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1881,17 +1884,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="8">
+      <c r="A185" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="4">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="7"/>
-      <c r="B186" s="8"/>
+      <c r="A186" s="3"/>
+      <c r="B186" s="4"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1902,18 +1905,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
+      <c r="A189" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="5"/>
-      <c r="C190" s="6"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="8"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1946,31 +1949,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="8">
+      <c r="A194" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="4">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="7"/>
-      <c r="B195" s="8"/>
+      <c r="A195" s="3"/>
+      <c r="B195" s="4"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
+      <c r="A197" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="5"/>
+      <c r="C197" s="5"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="5"/>
-      <c r="C198" s="6"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="8"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -2003,31 +2006,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="8">
+      <c r="A202" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="4">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="7"/>
-      <c r="B203" s="8"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="4"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="3"/>
-      <c r="C205" s="3"/>
+      <c r="A205" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="5"/>
-      <c r="C206" s="6"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="8"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2060,31 +2063,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="8">
+      <c r="A210" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="4">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="7"/>
-      <c r="B211" s="8"/>
+      <c r="A211" s="3"/>
+      <c r="B211" s="4"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="3"/>
-      <c r="C213" s="3"/>
+      <c r="A213" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="5"/>
+      <c r="C213" s="5"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="6"/>
+      <c r="B214" s="7"/>
+      <c r="C214" s="8"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2117,31 +2120,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="8">
+      <c r="A218" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="4">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="7"/>
-      <c r="B219" s="8"/>
+      <c r="A219" s="3"/>
+      <c r="B219" s="4"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="3"/>
-      <c r="C221" s="3"/>
+      <c r="A221" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="5"/>
+      <c r="C221" s="5"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="5"/>
-      <c r="C222" s="6"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="8"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2174,31 +2177,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="8">
+      <c r="A226" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="4">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="7"/>
-      <c r="B227" s="8"/>
+      <c r="A227" s="3"/>
+      <c r="B227" s="4"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="3"/>
-      <c r="C229" s="3"/>
+      <c r="A229" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="5"/>
+      <c r="C229" s="5"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="5"/>
-      <c r="C230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="8"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2231,31 +2234,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="8">
+      <c r="A234" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="4">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="7"/>
-      <c r="B235" s="8"/>
+      <c r="A235" s="3"/>
+      <c r="B235" s="4"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="3"/>
-      <c r="C237" s="3"/>
+      <c r="A237" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="5"/>
+      <c r="C237" s="5"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="6"/>
+      <c r="B238" s="7"/>
+      <c r="C238" s="8"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2288,17 +2291,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="8">
+      <c r="A242" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="4">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="7"/>
-      <c r="B243" s="8"/>
+      <c r="A243" s="3"/>
+      <c r="B243" s="4"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2309,18 +2312,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="3"/>
-      <c r="C246" s="3"/>
+      <c r="A246" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="5"/>
+      <c r="C246" s="5"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="4" t="s">
+      <c r="A247" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="5"/>
-      <c r="C247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="8"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2353,31 +2356,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="8">
+      <c r="A251" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="4">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="7"/>
-      <c r="B252" s="8"/>
+      <c r="A252" s="3"/>
+      <c r="B252" s="4"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="3"/>
-      <c r="C254" s="3"/>
+      <c r="A254" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="5"/>
+      <c r="C254" s="5"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="5"/>
-      <c r="C255" s="6"/>
+      <c r="B255" s="7"/>
+      <c r="C255" s="8"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2410,31 +2413,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="8">
+      <c r="A259" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="4">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="7"/>
-      <c r="B260" s="8"/>
+      <c r="A260" s="3"/>
+      <c r="B260" s="4"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="3"/>
-      <c r="C262" s="3"/>
+      <c r="A262" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="5"/>
+      <c r="C262" s="5"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="4" t="s">
+      <c r="A263" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="5"/>
-      <c r="C263" s="6"/>
+      <c r="B263" s="7"/>
+      <c r="C263" s="8"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2467,17 +2470,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="8">
+      <c r="A267" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="4">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="7"/>
-      <c r="B268" s="8"/>
+      <c r="A268" s="3"/>
+      <c r="B268" s="4"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2488,18 +2491,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="3"/>
-      <c r="C271" s="3"/>
+      <c r="A271" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="5"/>
+      <c r="C271" s="5"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="5"/>
-      <c r="C272" s="6"/>
+      <c r="B272" s="7"/>
+      <c r="C272" s="8"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2532,31 +2535,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="8">
+      <c r="A276" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="4">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="7"/>
-      <c r="B277" s="8"/>
+      <c r="A277" s="3"/>
+      <c r="B277" s="4"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="3"/>
-      <c r="C279" s="3"/>
+      <c r="A279" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="5"/>
+      <c r="C279" s="5"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="5"/>
-      <c r="C280" s="6"/>
+      <c r="B280" s="7"/>
+      <c r="C280" s="8"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2589,31 +2592,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="8">
+      <c r="A284" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="4">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="7"/>
-      <c r="B285" s="8"/>
+      <c r="A285" s="3"/>
+      <c r="B285" s="4"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="3"/>
-      <c r="C287" s="3"/>
+      <c r="A287" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="5"/>
+      <c r="C287" s="5"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="4" t="s">
+      <c r="A288" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="5"/>
-      <c r="C288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="8"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2646,31 +2649,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="8">
+      <c r="A292" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="4">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="7"/>
-      <c r="B293" s="8"/>
+      <c r="A293" s="3"/>
+      <c r="B293" s="4"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="3"/>
-      <c r="C295" s="3"/>
+      <c r="A295" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="5"/>
+      <c r="C295" s="5"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="5"/>
-      <c r="C296" s="6"/>
+      <c r="B296" s="7"/>
+      <c r="C296" s="8"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2703,31 +2706,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="8">
+      <c r="A300" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="4">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="7"/>
-      <c r="B301" s="8"/>
+      <c r="A301" s="3"/>
+      <c r="B301" s="4"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="3"/>
-      <c r="C303" s="3"/>
+      <c r="A303" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="5"/>
+      <c r="C303" s="5"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="4" t="s">
+      <c r="A304" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="5"/>
-      <c r="C304" s="6"/>
+      <c r="B304" s="7"/>
+      <c r="C304" s="8"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2760,31 +2763,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="8">
+      <c r="A308" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="4">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="7"/>
-      <c r="B309" s="8"/>
+      <c r="A309" s="3"/>
+      <c r="B309" s="4"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="3"/>
-      <c r="C311" s="3"/>
+      <c r="A311" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="5"/>
+      <c r="C311" s="5"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="4" t="s">
+      <c r="A312" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="5"/>
-      <c r="C312" s="6"/>
+      <c r="B312" s="7"/>
+      <c r="C312" s="8"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2817,31 +2820,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="8">
+      <c r="A316" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="4">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="7"/>
-      <c r="B317" s="8"/>
+      <c r="A317" s="3"/>
+      <c r="B317" s="4"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="3"/>
-      <c r="C319" s="3"/>
+      <c r="A319" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="5"/>
+      <c r="C319" s="5"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="4" t="s">
+      <c r="A320" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="5"/>
-      <c r="C320" s="6"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="8"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2874,17 +2877,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="8">
+      <c r="A324" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="4">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="7"/>
-      <c r="B325" s="8"/>
+      <c r="A325" s="3"/>
+      <c r="B325" s="4"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2895,18 +2898,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="3"/>
-      <c r="C328" s="3"/>
+      <c r="A328" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="5"/>
+      <c r="C328" s="5"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="4" t="s">
+      <c r="A329" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="5"/>
-      <c r="C329" s="6"/>
+      <c r="B329" s="7"/>
+      <c r="C329" s="8"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2939,31 +2942,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="8">
+      <c r="A333" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="4">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="7"/>
-      <c r="B334" s="8"/>
+      <c r="A334" s="3"/>
+      <c r="B334" s="4"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="3"/>
-      <c r="C336" s="3"/>
+      <c r="A336" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="5"/>
+      <c r="C336" s="5"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="5"/>
-      <c r="C337" s="6"/>
+      <c r="B337" s="7"/>
+      <c r="C337" s="8"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2996,31 +2999,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="8">
+      <c r="A341" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="4">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="7"/>
-      <c r="B342" s="8"/>
+      <c r="A342" s="3"/>
+      <c r="B342" s="4"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="3"/>
-      <c r="C344" s="3"/>
+      <c r="A344" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="5"/>
+      <c r="C344" s="5"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="5"/>
-      <c r="C345" s="6"/>
+      <c r="B345" s="7"/>
+      <c r="C345" s="8"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3053,31 +3056,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="8">
+      <c r="A349" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="4">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="7"/>
-      <c r="B350" s="8"/>
+      <c r="A350" s="3"/>
+      <c r="B350" s="4"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="3"/>
-      <c r="C352" s="3"/>
+      <c r="A352" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="5"/>
+      <c r="C352" s="5"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="4" t="s">
+      <c r="A353" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="5"/>
-      <c r="C353" s="6"/>
+      <c r="B353" s="7"/>
+      <c r="C353" s="8"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3110,31 +3113,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="8">
+      <c r="A357" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="4">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="7"/>
-      <c r="B358" s="8"/>
+      <c r="A358" s="3"/>
+      <c r="B358" s="4"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="3"/>
-      <c r="C360" s="3"/>
+      <c r="A360" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="5"/>
+      <c r="C360" s="5"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="5"/>
-      <c r="C361" s="6"/>
+      <c r="B361" s="7"/>
+      <c r="C361" s="8"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3167,31 +3170,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="8">
+      <c r="A365" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="4">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="7"/>
-      <c r="B366" s="8"/>
+      <c r="A366" s="3"/>
+      <c r="B366" s="4"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="3"/>
-      <c r="C368" s="3"/>
+      <c r="A368" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="5"/>
+      <c r="C368" s="5"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="4" t="s">
+      <c r="A369" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="5"/>
-      <c r="C369" s="6"/>
+      <c r="B369" s="7"/>
+      <c r="C369" s="8"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3224,31 +3227,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="8">
+      <c r="A373" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="4">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="7"/>
-      <c r="B374" s="8"/>
+      <c r="A374" s="3"/>
+      <c r="B374" s="4"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="3"/>
-      <c r="C376" s="3"/>
+      <c r="A376" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="5"/>
+      <c r="C376" s="5"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="4" t="s">
+      <c r="A377" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="5"/>
-      <c r="C377" s="6"/>
+      <c r="B377" s="7"/>
+      <c r="C377" s="8"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3281,17 +3284,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="8">
+      <c r="A381" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="4">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="7"/>
-      <c r="B382" s="8"/>
+      <c r="A382" s="3"/>
+      <c r="B382" s="4"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3302,18 +3305,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="3"/>
-      <c r="C385" s="3"/>
+      <c r="A385" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="5"/>
+      <c r="C385" s="5"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="5"/>
-      <c r="C386" s="6"/>
+      <c r="B386" s="7"/>
+      <c r="C386" s="8"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3346,31 +3349,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="8">
+      <c r="A390" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="4">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="7"/>
-      <c r="B391" s="8"/>
+      <c r="A391" s="3"/>
+      <c r="B391" s="4"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="3"/>
-      <c r="C393" s="3"/>
+      <c r="A393" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="5"/>
+      <c r="C393" s="5"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="4" t="s">
+      <c r="A394" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="5"/>
-      <c r="C394" s="6"/>
+      <c r="B394" s="7"/>
+      <c r="C394" s="8"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3403,31 +3406,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="8">
+      <c r="A398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="4">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="7"/>
-      <c r="B399" s="8"/>
+      <c r="A399" s="3"/>
+      <c r="B399" s="4"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="3"/>
-      <c r="C401" s="3"/>
+      <c r="A401" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="5"/>
+      <c r="C401" s="5"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="4" t="s">
+      <c r="A402" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="5"/>
-      <c r="C402" s="6"/>
+      <c r="B402" s="7"/>
+      <c r="C402" s="8"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3460,31 +3463,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="8">
+      <c r="A406" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="4">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="7"/>
-      <c r="B407" s="8"/>
+      <c r="A407" s="3"/>
+      <c r="B407" s="4"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="3"/>
-      <c r="C409" s="3"/>
+      <c r="A409" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="5"/>
+      <c r="C409" s="5"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="4" t="s">
+      <c r="A410" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="5"/>
-      <c r="C410" s="6"/>
+      <c r="B410" s="7"/>
+      <c r="C410" s="8"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3517,31 +3520,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="8">
+      <c r="A414" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="4">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="7"/>
-      <c r="B415" s="8"/>
+      <c r="A415" s="3"/>
+      <c r="B415" s="4"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="3"/>
-      <c r="C417" s="3"/>
+      <c r="A417" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="5"/>
+      <c r="C417" s="5"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="4" t="s">
+      <c r="A418" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="5"/>
-      <c r="C418" s="6"/>
+      <c r="B418" s="7"/>
+      <c r="C418" s="8"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3574,31 +3577,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="8">
+      <c r="A422" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="4">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="7"/>
-      <c r="B423" s="8"/>
+      <c r="A423" s="3"/>
+      <c r="B423" s="4"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="3"/>
-      <c r="C425" s="3"/>
+      <c r="A425" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="5"/>
+      <c r="C425" s="5"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="4" t="s">
+      <c r="A426" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="5"/>
-      <c r="C426" s="6"/>
+      <c r="B426" s="7"/>
+      <c r="C426" s="8"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3631,31 +3634,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="8">
+      <c r="A430" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="4">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="7"/>
-      <c r="B431" s="8"/>
+      <c r="A431" s="3"/>
+      <c r="B431" s="4"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
+      <c r="A433" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="5"/>
+      <c r="C433" s="5"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="4" t="s">
+      <c r="A434" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="5"/>
-      <c r="C434" s="6"/>
+      <c r="B434" s="7"/>
+      <c r="C434" s="8"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3688,17 +3691,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="8">
+      <c r="A438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="4">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="7"/>
-      <c r="B439" s="8"/>
+      <c r="A439" s="3"/>
+      <c r="B439" s="4"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3709,18 +3712,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
+      <c r="A442" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="5"/>
+      <c r="C442" s="5"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="4" t="s">
+      <c r="A443" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="5"/>
-      <c r="C443" s="6"/>
+      <c r="B443" s="7"/>
+      <c r="C443" s="8"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3753,31 +3756,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="8">
+      <c r="A447" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="4">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="7"/>
-      <c r="B448" s="8"/>
+      <c r="A448" s="3"/>
+      <c r="B448" s="4"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="3"/>
-      <c r="C450" s="3"/>
+      <c r="A450" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="5"/>
+      <c r="C450" s="5"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="5"/>
-      <c r="C451" s="6"/>
+      <c r="B451" s="7"/>
+      <c r="C451" s="8"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3810,31 +3813,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="8">
+      <c r="A455" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="4">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="7"/>
-      <c r="B456" s="8"/>
+      <c r="A456" s="3"/>
+      <c r="B456" s="4"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
+      <c r="A458" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="5"/>
+      <c r="C458" s="5"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="4" t="s">
+      <c r="A459" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="5"/>
-      <c r="C459" s="6"/>
+      <c r="B459" s="7"/>
+      <c r="C459" s="8"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3867,31 +3870,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="8">
+      <c r="A463" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="4">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="7"/>
-      <c r="B464" s="8"/>
+      <c r="A464" s="3"/>
+      <c r="B464" s="4"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="3"/>
-      <c r="C466" s="3"/>
+      <c r="A466" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="5"/>
+      <c r="C466" s="5"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="4" t="s">
+      <c r="A467" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="5"/>
-      <c r="C467" s="6"/>
+      <c r="B467" s="7"/>
+      <c r="C467" s="8"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3924,31 +3927,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="8">
+      <c r="A471" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="4">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="7"/>
-      <c r="B472" s="8"/>
+      <c r="A472" s="3"/>
+      <c r="B472" s="4"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="3"/>
-      <c r="C474" s="3"/>
+      <c r="A474" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="5"/>
+      <c r="C474" s="5"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="4" t="s">
+      <c r="A475" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="5"/>
-      <c r="C475" s="6"/>
+      <c r="B475" s="7"/>
+      <c r="C475" s="8"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3981,31 +3984,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="8">
+      <c r="A479" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="4">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="7"/>
-      <c r="B480" s="8"/>
+      <c r="A480" s="3"/>
+      <c r="B480" s="4"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="3"/>
-      <c r="C482" s="3"/>
+      <c r="A482" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="5"/>
+      <c r="C482" s="5"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="4" t="s">
+      <c r="A483" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="5"/>
-      <c r="C483" s="6"/>
+      <c r="B483" s="7"/>
+      <c r="C483" s="8"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4038,31 +4041,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="8">
+      <c r="A487" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="4">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="7"/>
-      <c r="B488" s="8"/>
+      <c r="A488" s="3"/>
+      <c r="B488" s="4"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="3"/>
-      <c r="C490" s="3"/>
+      <c r="A490" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="5"/>
+      <c r="C490" s="5"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="4" t="s">
+      <c r="A491" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="5"/>
-      <c r="C491" s="6"/>
+      <c r="B491" s="7"/>
+      <c r="C491" s="8"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4095,17 +4098,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="8">
+      <c r="A495" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="4">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="7"/>
-      <c r="B496" s="8"/>
+      <c r="A496" s="3"/>
+      <c r="B496" s="4"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4116,18 +4119,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="3"/>
-      <c r="C499" s="3"/>
+      <c r="A499" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="5"/>
+      <c r="C499" s="5"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="4" t="s">
+      <c r="A500" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="5"/>
-      <c r="C500" s="6"/>
+      <c r="B500" s="7"/>
+      <c r="C500" s="8"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4160,31 +4163,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="8">
+      <c r="A504" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="4">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="7"/>
-      <c r="B505" s="8"/>
+      <c r="A505" s="3"/>
+      <c r="B505" s="4"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="3"/>
-      <c r="C507" s="3"/>
+      <c r="A507" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="5"/>
+      <c r="C507" s="5"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="4" t="s">
+      <c r="A508" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="5"/>
-      <c r="C508" s="6"/>
+      <c r="B508" s="7"/>
+      <c r="C508" s="8"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4217,31 +4220,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="8">
+      <c r="A512" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="4">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="7"/>
-      <c r="B513" s="8"/>
+      <c r="A513" s="3"/>
+      <c r="B513" s="4"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="3"/>
-      <c r="C515" s="3"/>
+      <c r="A515" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="5"/>
+      <c r="C515" s="5"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="4" t="s">
+      <c r="A516" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="5"/>
-      <c r="C516" s="6"/>
+      <c r="B516" s="7"/>
+      <c r="C516" s="8"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4274,31 +4277,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="8">
+      <c r="A520" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="4">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="7"/>
-      <c r="B521" s="8"/>
+      <c r="A521" s="3"/>
+      <c r="B521" s="4"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="3"/>
-      <c r="C523" s="3"/>
+      <c r="A523" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="5"/>
+      <c r="C523" s="5"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="4" t="s">
+      <c r="A524" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="5"/>
-      <c r="C524" s="6"/>
+      <c r="B524" s="7"/>
+      <c r="C524" s="8"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4331,31 +4334,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="8">
+      <c r="A528" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="4">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="7"/>
-      <c r="B529" s="8"/>
+      <c r="A529" s="3"/>
+      <c r="B529" s="4"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="3"/>
-      <c r="C531" s="3"/>
+      <c r="A531" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="5"/>
+      <c r="C531" s="5"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="4" t="s">
+      <c r="A532" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="5"/>
-      <c r="C532" s="6"/>
+      <c r="B532" s="7"/>
+      <c r="C532" s="8"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4388,31 +4391,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="8">
+      <c r="A536" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="4">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="7"/>
-      <c r="B537" s="8"/>
+      <c r="A537" s="3"/>
+      <c r="B537" s="4"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="3"/>
-      <c r="C539" s="3"/>
+      <c r="A539" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="5"/>
+      <c r="C539" s="5"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="4" t="s">
+      <c r="A540" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="5"/>
-      <c r="C540" s="6"/>
+      <c r="B540" s="7"/>
+      <c r="C540" s="8"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4445,31 +4448,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="8">
+      <c r="A544" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="4">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="7"/>
-      <c r="B545" s="8"/>
+      <c r="A545" s="3"/>
+      <c r="B545" s="4"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="3"/>
-      <c r="C547" s="3"/>
+      <c r="A547" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="5"/>
+      <c r="C547" s="5"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="4" t="s">
+      <c r="A548" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="5"/>
-      <c r="C548" s="6"/>
+      <c r="B548" s="7"/>
+      <c r="C548" s="8"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4502,17 +4505,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="8">
+      <c r="A552" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="4">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="7"/>
-      <c r="B553" s="8"/>
+      <c r="A553" s="3"/>
+      <c r="B553" s="4"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4523,18 +4526,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="3"/>
-      <c r="C556" s="3"/>
+      <c r="A556" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="5"/>
+      <c r="C556" s="5"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="4" t="s">
+      <c r="A557" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="5"/>
-      <c r="C557" s="6"/>
+      <c r="B557" s="7"/>
+      <c r="C557" s="8"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4567,31 +4570,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="8">
+      <c r="A561" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="4">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="7"/>
-      <c r="B562" s="8"/>
+      <c r="A562" s="3"/>
+      <c r="B562" s="4"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="3"/>
-      <c r="C564" s="3"/>
+      <c r="A564" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="5"/>
+      <c r="C564" s="5"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="4" t="s">
+      <c r="A565" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="5"/>
-      <c r="C565" s="6"/>
+      <c r="B565" s="7"/>
+      <c r="C565" s="8"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4624,31 +4627,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="8">
+      <c r="A569" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="4">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="7"/>
-      <c r="B570" s="8"/>
+      <c r="A570" s="3"/>
+      <c r="B570" s="4"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="3"/>
-      <c r="C572" s="3"/>
+      <c r="A572" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="5"/>
+      <c r="C572" s="5"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="4" t="s">
+      <c r="A573" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="5"/>
-      <c r="C573" s="6"/>
+      <c r="B573" s="7"/>
+      <c r="C573" s="8"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4681,31 +4684,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="8">
+      <c r="A577" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="4">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="7"/>
-      <c r="B578" s="8"/>
+      <c r="A578" s="3"/>
+      <c r="B578" s="4"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="3"/>
-      <c r="C580" s="3"/>
+      <c r="A580" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="5"/>
+      <c r="C580" s="5"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="4" t="s">
+      <c r="A581" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="5"/>
-      <c r="C581" s="6"/>
+      <c r="B581" s="7"/>
+      <c r="C581" s="8"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4738,17 +4741,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="8">
+      <c r="A585" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="4">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="7"/>
-      <c r="B586" s="8"/>
+      <c r="A586" s="3"/>
+      <c r="B586" s="4"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4759,18 +4762,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="3"/>
-      <c r="C589" s="3"/>
+      <c r="A589" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="5"/>
+      <c r="C589" s="5"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="4" t="s">
+      <c r="A590" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="5"/>
-      <c r="C590" s="6"/>
+      <c r="B590" s="7"/>
+      <c r="C590" s="8"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4803,31 +4806,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="8">
+      <c r="A594" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="4">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="7"/>
-      <c r="B595" s="8"/>
+      <c r="A595" s="3"/>
+      <c r="B595" s="4"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="3"/>
-      <c r="C597" s="3"/>
+      <c r="A597" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="5"/>
+      <c r="C597" s="5"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="4" t="s">
+      <c r="A598" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="5"/>
-      <c r="C598" s="6"/>
+      <c r="B598" s="7"/>
+      <c r="C598" s="8"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4860,31 +4863,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="8">
+      <c r="A602" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="4">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="7"/>
-      <c r="B603" s="8"/>
+      <c r="A603" s="3"/>
+      <c r="B603" s="4"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="3"/>
-      <c r="C605" s="3"/>
+      <c r="A605" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="5"/>
+      <c r="C605" s="5"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="4" t="s">
+      <c r="A606" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="5"/>
-      <c r="C606" s="6"/>
+      <c r="B606" s="7"/>
+      <c r="C606" s="8"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4917,31 +4920,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="8">
+      <c r="A610" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="4">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="7"/>
-      <c r="B611" s="8"/>
+      <c r="A611" s="3"/>
+      <c r="B611" s="4"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="3"/>
-      <c r="C613" s="3"/>
+      <c r="A613" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="5"/>
+      <c r="C613" s="5"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="4" t="s">
+      <c r="A614" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="5"/>
-      <c r="C614" s="6"/>
+      <c r="B614" s="7"/>
+      <c r="C614" s="8"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4974,31 +4977,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="8">
+      <c r="A618" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="4">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="7"/>
-      <c r="B619" s="8"/>
+      <c r="A619" s="3"/>
+      <c r="B619" s="4"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="3"/>
-      <c r="C621" s="3"/>
+      <c r="A621" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="5"/>
+      <c r="C621" s="5"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="4" t="s">
+      <c r="A622" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="5"/>
-      <c r="C622" s="6"/>
+      <c r="B622" s="7"/>
+      <c r="C622" s="8"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5031,31 +5034,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="8">
+      <c r="A626" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="4">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="7"/>
-      <c r="B627" s="8"/>
+      <c r="A627" s="3"/>
+      <c r="B627" s="4"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="3"/>
-      <c r="C629" s="3"/>
+      <c r="A629" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="5"/>
+      <c r="C629" s="5"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="4" t="s">
+      <c r="A630" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="5"/>
-      <c r="C630" s="6"/>
+      <c r="B630" s="7"/>
+      <c r="C630" s="8"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5088,31 +5091,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="8">
+      <c r="A634" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="4">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="7"/>
-      <c r="B635" s="8"/>
+      <c r="A635" s="3"/>
+      <c r="B635" s="4"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="3"/>
-      <c r="C637" s="3"/>
+      <c r="A637" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="5"/>
+      <c r="C637" s="5"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="4" t="s">
+      <c r="A638" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="5"/>
-      <c r="C638" s="6"/>
+      <c r="B638" s="7"/>
+      <c r="C638" s="8"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5145,17 +5148,17 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="8">
+      <c r="A642" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="4">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="7"/>
-      <c r="B643" s="8"/>
+      <c r="A643" s="3"/>
+      <c r="B643" s="4"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
@@ -5166,18 +5169,18 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="3"/>
-      <c r="C646" s="3"/>
+      <c r="A646" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="5"/>
+      <c r="C646" s="5"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="4" t="s">
+      <c r="A647" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="5"/>
-      <c r="C647" s="6"/>
+      <c r="B647" s="7"/>
+      <c r="C647" s="8"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5210,31 +5213,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="8">
+      <c r="A651" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="4">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="7"/>
-      <c r="B652" s="8"/>
+      <c r="A652" s="3"/>
+      <c r="B652" s="4"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="3"/>
-      <c r="C654" s="3"/>
+      <c r="A654" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="5"/>
+      <c r="C654" s="5"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="4" t="s">
+      <c r="A655" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="5"/>
-      <c r="C655" s="6"/>
+      <c r="B655" s="7"/>
+      <c r="C655" s="8"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5267,31 +5270,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="8">
+      <c r="A659" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="4">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="7"/>
-      <c r="B660" s="8"/>
+      <c r="A660" s="3"/>
+      <c r="B660" s="4"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="3"/>
-      <c r="C662" s="3"/>
+      <c r="A662" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="5"/>
+      <c r="C662" s="5"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="4" t="s">
+      <c r="A663" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="5"/>
-      <c r="C663" s="6"/>
+      <c r="B663" s="7"/>
+      <c r="C663" s="8"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5324,31 +5327,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="8">
+      <c r="A667" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="4">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="7"/>
-      <c r="B668" s="8"/>
+      <c r="A668" s="3"/>
+      <c r="B668" s="4"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="3"/>
-      <c r="C670" s="3"/>
+      <c r="A670" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="5"/>
+      <c r="C670" s="5"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="4" t="s">
+      <c r="A671" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="5"/>
-      <c r="C671" s="6"/>
+      <c r="B671" s="7"/>
+      <c r="C671" s="8"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5381,31 +5384,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="8">
+      <c r="A675" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="4">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="7"/>
-      <c r="B676" s="8"/>
+      <c r="A676" s="3"/>
+      <c r="B676" s="4"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="3"/>
-      <c r="C678" s="3"/>
+      <c r="A678" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="5"/>
+      <c r="C678" s="5"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="4" t="s">
+      <c r="A679" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="5"/>
-      <c r="C679" s="6"/>
+      <c r="B679" s="7"/>
+      <c r="C679" s="8"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5438,31 +5441,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="8">
+      <c r="A683" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="4">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="7"/>
-      <c r="B684" s="8"/>
+      <c r="A684" s="3"/>
+      <c r="B684" s="4"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="3"/>
-      <c r="C686" s="3"/>
+      <c r="A686" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="5"/>
+      <c r="C686" s="5"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="4" t="s">
+      <c r="A687" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="5"/>
-      <c r="C687" s="6"/>
+      <c r="B687" s="7"/>
+      <c r="C687" s="8"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5495,31 +5498,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="8">
+      <c r="A691" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="4">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="7"/>
-      <c r="B692" s="8"/>
+      <c r="A692" s="3"/>
+      <c r="B692" s="4"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="3"/>
-      <c r="C694" s="3"/>
+      <c r="A694" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="5"/>
+      <c r="C694" s="5"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="4" t="s">
+      <c r="A695" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="5"/>
-      <c r="C695" s="6"/>
+      <c r="B695" s="7"/>
+      <c r="C695" s="8"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5552,31 +5555,31 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="8">
+      <c r="A699" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="4">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="7"/>
-      <c r="B700" s="8"/>
+      <c r="A700" s="3"/>
+      <c r="B700" s="4"/>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B702" s="3"/>
-      <c r="C702" s="3"/>
+      <c r="A702" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B702" s="5"/>
+      <c r="C702" s="5"/>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="4" t="s">
+      <c r="A703" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B703" s="5"/>
-      <c r="C703" s="6"/>
+      <c r="B703" s="7"/>
+      <c r="C703" s="8"/>
     </row>
     <row r="704" spans="1:3">
       <c r="A704" s="1" t="s">
@@ -5609,17 +5612,17 @@
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B707" s="8">
+      <c r="A707" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="4">
         <f>B705-B706</f>
         <v>448</v>
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="7"/>
-      <c r="B708" s="8"/>
+      <c r="A708" s="3"/>
+      <c r="B708" s="4"/>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" s="1" t="s">
@@ -5630,18 +5633,18 @@
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B711" s="3"/>
-      <c r="C711" s="3"/>
+      <c r="A711" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="5"/>
+      <c r="C711" s="5"/>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="4" t="s">
+      <c r="A712" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B712" s="5"/>
-      <c r="C712" s="6"/>
+      <c r="B712" s="7"/>
+      <c r="C712" s="8"/>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" s="1" t="s">
@@ -5674,31 +5677,31 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B716" s="8">
+      <c r="A716" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="4">
         <f>B714-B715</f>
         <v>27</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="7"/>
-      <c r="B717" s="8"/>
+      <c r="A717" s="3"/>
+      <c r="B717" s="4"/>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B719" s="3"/>
-      <c r="C719" s="3"/>
+      <c r="A719" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="5"/>
+      <c r="C719" s="5"/>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="4" t="s">
+      <c r="A720" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B720" s="5"/>
-      <c r="C720" s="6"/>
+      <c r="B720" s="7"/>
+      <c r="C720" s="8"/>
     </row>
     <row r="721" spans="1:3">
       <c r="A721" s="1" t="s">
@@ -5731,31 +5734,31 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B724" s="8">
+      <c r="A724" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="4">
         <f>B722-B723</f>
         <v>386</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="7"/>
-      <c r="B725" s="8"/>
+      <c r="A725" s="3"/>
+      <c r="B725" s="4"/>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B727" s="3"/>
-      <c r="C727" s="3"/>
+      <c r="A727" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="5"/>
+      <c r="C727" s="5"/>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="4" t="s">
+      <c r="A728" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B728" s="5"/>
-      <c r="C728" s="6"/>
+      <c r="B728" s="7"/>
+      <c r="C728" s="8"/>
     </row>
     <row r="729" spans="1:3">
       <c r="A729" s="1" t="s">
@@ -5788,31 +5791,31 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B732" s="8">
+      <c r="A732" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="4">
         <f>B730-B731</f>
         <v>1256</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="7"/>
-      <c r="B733" s="8"/>
+      <c r="A733" s="3"/>
+      <c r="B733" s="4"/>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B735" s="3"/>
-      <c r="C735" s="3"/>
+      <c r="A735" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="5"/>
+      <c r="C735" s="5"/>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="4" t="s">
+      <c r="A736" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B736" s="5"/>
-      <c r="C736" s="6"/>
+      <c r="B736" s="7"/>
+      <c r="C736" s="8"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="1" t="s">
@@ -5845,31 +5848,31 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B740" s="8">
+      <c r="A740" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="4">
         <f>B738-B739</f>
         <v>227</v>
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="7"/>
-      <c r="B741" s="8"/>
+      <c r="A741" s="3"/>
+      <c r="B741" s="4"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B743" s="3"/>
-      <c r="C743" s="3"/>
+      <c r="A743" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="5"/>
+      <c r="C743" s="5"/>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="4" t="s">
+      <c r="A744" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B744" s="5"/>
-      <c r="C744" s="6"/>
+      <c r="B744" s="7"/>
+      <c r="C744" s="8"/>
     </row>
     <row r="745" spans="1:3">
       <c r="A745" s="1" t="s">
@@ -5902,31 +5905,31 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B748" s="8">
+      <c r="A748" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="4">
         <f>B746-B747</f>
         <v>961</v>
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="7"/>
-      <c r="B749" s="8"/>
+      <c r="A749" s="3"/>
+      <c r="B749" s="4"/>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B751" s="3"/>
-      <c r="C751" s="3"/>
+      <c r="A751" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="5"/>
+      <c r="C751" s="5"/>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="4" t="s">
+      <c r="A752" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B752" s="5"/>
-      <c r="C752" s="6"/>
+      <c r="B752" s="7"/>
+      <c r="C752" s="8"/>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" s="1" t="s">
@@ -5959,31 +5962,31 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="8">
+      <c r="A756" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="4">
         <f>B754-B755</f>
         <v>6</v>
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="7"/>
-      <c r="B757" s="8"/>
+      <c r="A757" s="3"/>
+      <c r="B757" s="4"/>
     </row>
     <row r="759" spans="1:3">
-      <c r="A759" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B759" s="3"/>
-      <c r="C759" s="3"/>
+      <c r="A759" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B759" s="5"/>
+      <c r="C759" s="5"/>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="4" t="s">
+      <c r="A760" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B760" s="5"/>
-      <c r="C760" s="6"/>
+      <c r="B760" s="7"/>
+      <c r="C760" s="8"/>
     </row>
     <row r="761" spans="1:3">
       <c r="A761" s="1" t="s">
@@ -6016,31 +6019,31 @@
       </c>
     </row>
     <row r="764" spans="1:3">
-      <c r="A764" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B764" s="8">
+      <c r="A764" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764" s="4">
         <f>B762-B763</f>
         <v>616</v>
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="7"/>
-      <c r="B765" s="8"/>
+      <c r="A765" s="3"/>
+      <c r="B765" s="4"/>
     </row>
     <row r="767" spans="1:3">
-      <c r="A767" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B767" s="3"/>
-      <c r="C767" s="3"/>
+      <c r="A767" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B767" s="5"/>
+      <c r="C767" s="5"/>
     </row>
     <row r="768" spans="1:3">
-      <c r="A768" s="4" t="s">
+      <c r="A768" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B768" s="5"/>
-      <c r="C768" s="6"/>
+      <c r="B768" s="7"/>
+      <c r="C768" s="8"/>
     </row>
     <row r="769" spans="1:3">
       <c r="A769" s="1" t="s">
@@ -6073,17 +6076,17 @@
       </c>
     </row>
     <row r="772" spans="1:3">
-      <c r="A772" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B772" s="8">
+      <c r="A772" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B772" s="4">
         <f>B770-B771</f>
         <v>379</v>
       </c>
     </row>
     <row r="773" spans="1:3">
-      <c r="A773" s="7"/>
-      <c r="B773" s="8"/>
+      <c r="A773" s="3"/>
+      <c r="B773" s="4"/>
     </row>
     <row r="774" spans="1:3">
       <c r="A774" s="1" t="s">
@@ -6094,18 +6097,18 @@
       </c>
     </row>
     <row r="776" spans="1:3">
-      <c r="A776" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B776" s="3"/>
-      <c r="C776" s="3"/>
+      <c r="A776" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B776" s="5"/>
+      <c r="C776" s="5"/>
     </row>
     <row r="777" spans="1:3">
-      <c r="A777" s="4" t="s">
+      <c r="A777" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B777" s="5"/>
-      <c r="C777" s="6"/>
+      <c r="B777" s="7"/>
+      <c r="C777" s="8"/>
     </row>
     <row r="778" spans="1:3">
       <c r="A778" s="1" t="s">
@@ -6138,31 +6141,31 @@
       </c>
     </row>
     <row r="781" spans="1:3">
-      <c r="A781" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B781" s="8">
+      <c r="A781" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781" s="4">
         <f>B779-B780</f>
         <v>276</v>
       </c>
     </row>
     <row r="782" spans="1:3">
-      <c r="A782" s="7"/>
-      <c r="B782" s="8"/>
+      <c r="A782" s="3"/>
+      <c r="B782" s="4"/>
     </row>
     <row r="784" spans="1:3">
-      <c r="A784" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B784" s="3"/>
-      <c r="C784" s="3"/>
+      <c r="A784" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B784" s="5"/>
+      <c r="C784" s="5"/>
     </row>
     <row r="785" spans="1:3">
-      <c r="A785" s="4" t="s">
+      <c r="A785" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B785" s="5"/>
-      <c r="C785" s="6"/>
+      <c r="B785" s="7"/>
+      <c r="C785" s="8"/>
     </row>
     <row r="786" spans="1:3">
       <c r="A786" s="1" t="s">
@@ -6195,31 +6198,31 @@
       </c>
     </row>
     <row r="789" spans="1:3">
-      <c r="A789" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B789" s="8">
+      <c r="A789" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789" s="4">
         <f>B787-B788</f>
         <v>596</v>
       </c>
     </row>
     <row r="790" spans="1:3">
-      <c r="A790" s="7"/>
-      <c r="B790" s="8"/>
+      <c r="A790" s="3"/>
+      <c r="B790" s="4"/>
     </row>
     <row r="792" spans="1:3">
-      <c r="A792" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B792" s="3"/>
-      <c r="C792" s="3"/>
+      <c r="A792" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B792" s="5"/>
+      <c r="C792" s="5"/>
     </row>
     <row r="793" spans="1:3">
-      <c r="A793" s="4" t="s">
+      <c r="A793" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B793" s="5"/>
-      <c r="C793" s="6"/>
+      <c r="B793" s="7"/>
+      <c r="C793" s="8"/>
     </row>
     <row r="794" spans="1:3">
       <c r="A794" s="1" t="s">
@@ -6252,31 +6255,31 @@
       </c>
     </row>
     <row r="797" spans="1:3">
-      <c r="A797" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B797" s="8">
+      <c r="A797" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797" s="4">
         <f>B795-B796</f>
         <v>250</v>
       </c>
     </row>
     <row r="798" spans="1:3">
-      <c r="A798" s="7"/>
-      <c r="B798" s="8"/>
+      <c r="A798" s="3"/>
+      <c r="B798" s="4"/>
     </row>
     <row r="800" spans="1:3">
-      <c r="A800" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B800" s="3"/>
-      <c r="C800" s="3"/>
+      <c r="A800" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B800" s="5"/>
+      <c r="C800" s="5"/>
     </row>
     <row r="801" spans="1:3">
-      <c r="A801" s="4" t="s">
+      <c r="A801" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B801" s="5"/>
-      <c r="C801" s="6"/>
+      <c r="B801" s="7"/>
+      <c r="C801" s="8"/>
     </row>
     <row r="802" spans="1:3">
       <c r="A802" s="1" t="s">
@@ -6309,31 +6312,31 @@
       </c>
     </row>
     <row r="805" spans="1:3">
-      <c r="A805" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B805" s="8">
+      <c r="A805" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805" s="4">
         <f>B803-B804</f>
         <v>378</v>
       </c>
     </row>
     <row r="806" spans="1:3">
-      <c r="A806" s="7"/>
-      <c r="B806" s="8"/>
+      <c r="A806" s="3"/>
+      <c r="B806" s="4"/>
     </row>
     <row r="808" spans="1:3">
-      <c r="A808" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B808" s="3"/>
-      <c r="C808" s="3"/>
+      <c r="A808" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B808" s="5"/>
+      <c r="C808" s="5"/>
     </row>
     <row r="809" spans="1:3">
-      <c r="A809" s="4" t="s">
+      <c r="A809" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B809" s="5"/>
-      <c r="C809" s="6"/>
+      <c r="B809" s="7"/>
+      <c r="C809" s="8"/>
     </row>
     <row r="810" spans="1:3">
       <c r="A810" s="1" t="s">
@@ -6366,31 +6369,31 @@
       </c>
     </row>
     <row r="813" spans="1:3">
-      <c r="A813" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B813" s="8">
+      <c r="A813" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813" s="4">
         <f>B811-B812</f>
         <v>900</v>
       </c>
     </row>
     <row r="814" spans="1:3">
-      <c r="A814" s="7"/>
-      <c r="B814" s="8"/>
+      <c r="A814" s="3"/>
+      <c r="B814" s="4"/>
     </row>
     <row r="816" spans="1:3">
-      <c r="A816" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B816" s="3"/>
-      <c r="C816" s="3"/>
+      <c r="A816" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B816" s="5"/>
+      <c r="C816" s="5"/>
     </row>
     <row r="817" spans="1:3">
-      <c r="A817" s="4" t="s">
+      <c r="A817" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B817" s="5"/>
-      <c r="C817" s="6"/>
+      <c r="B817" s="7"/>
+      <c r="C817" s="8"/>
     </row>
     <row r="818" spans="1:3">
       <c r="A818" s="1" t="s">
@@ -6423,31 +6426,31 @@
       </c>
     </row>
     <row r="821" spans="1:3">
-      <c r="A821" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B821" s="8">
+      <c r="A821" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B821" s="4">
         <f>B819-B820</f>
         <v>74</v>
       </c>
     </row>
     <row r="822" spans="1:3">
-      <c r="A822" s="7"/>
-      <c r="B822" s="8"/>
+      <c r="A822" s="3"/>
+      <c r="B822" s="4"/>
     </row>
     <row r="824" spans="1:3">
-      <c r="A824" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B824" s="3"/>
-      <c r="C824" s="3"/>
+      <c r="A824" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B824" s="5"/>
+      <c r="C824" s="5"/>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825" s="4" t="s">
+      <c r="A825" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B825" s="5"/>
-      <c r="C825" s="6"/>
+      <c r="B825" s="7"/>
+      <c r="C825" s="8"/>
     </row>
     <row r="826" spans="1:3">
       <c r="A826" s="1" t="s">
@@ -6480,31 +6483,31 @@
       </c>
     </row>
     <row r="829" spans="1:3">
-      <c r="A829" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B829" s="8">
+      <c r="A829" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B829" s="4">
         <f>B827-B828</f>
         <v>0</v>
       </c>
     </row>
     <row r="830" spans="1:3">
-      <c r="A830" s="7"/>
-      <c r="B830" s="8"/>
+      <c r="A830" s="3"/>
+      <c r="B830" s="4"/>
     </row>
     <row r="832" spans="1:3">
-      <c r="A832" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B832" s="3"/>
-      <c r="C832" s="3"/>
+      <c r="A832" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B832" s="5"/>
+      <c r="C832" s="5"/>
     </row>
     <row r="833" spans="1:3">
-      <c r="A833" s="4" t="s">
+      <c r="A833" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B833" s="5"/>
-      <c r="C833" s="6"/>
+      <c r="B833" s="7"/>
+      <c r="C833" s="8"/>
     </row>
     <row r="834" spans="1:3">
       <c r="A834" s="1" t="s">
@@ -6537,17 +6540,17 @@
       </c>
     </row>
     <row r="837" spans="1:3">
-      <c r="A837" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B837" s="8">
+      <c r="A837" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B837" s="4">
         <f>B835-B836</f>
         <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:3">
-      <c r="A838" s="7"/>
-      <c r="B838" s="8"/>
+      <c r="A838" s="3"/>
+      <c r="B838" s="4"/>
     </row>
     <row r="839" spans="1:3">
       <c r="A839" s="1" t="s">
@@ -6558,18 +6561,18 @@
       </c>
     </row>
     <row r="841" spans="1:3">
-      <c r="A841" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B841" s="3"/>
-      <c r="C841" s="3"/>
+      <c r="A841" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B841" s="5"/>
+      <c r="C841" s="5"/>
     </row>
     <row r="842" spans="1:3">
-      <c r="A842" s="4" t="s">
+      <c r="A842" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B842" s="5"/>
-      <c r="C842" s="6"/>
+      <c r="B842" s="7"/>
+      <c r="C842" s="8"/>
     </row>
     <row r="843" spans="1:3">
       <c r="A843" s="1" t="s">
@@ -6602,31 +6605,31 @@
       </c>
     </row>
     <row r="846" spans="1:3">
-      <c r="A846" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B846" s="8">
+      <c r="A846" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846" s="4">
         <f>B844-B845</f>
         <v>717</v>
       </c>
     </row>
     <row r="847" spans="1:3">
-      <c r="A847" s="7"/>
-      <c r="B847" s="8"/>
+      <c r="A847" s="3"/>
+      <c r="B847" s="4"/>
     </row>
     <row r="849" spans="1:3">
-      <c r="A849" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B849" s="3"/>
-      <c r="C849" s="3"/>
+      <c r="A849" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B849" s="5"/>
+      <c r="C849" s="5"/>
     </row>
     <row r="850" spans="1:3">
-      <c r="A850" s="4" t="s">
+      <c r="A850" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B850" s="5"/>
-      <c r="C850" s="6"/>
+      <c r="B850" s="7"/>
+      <c r="C850" s="8"/>
     </row>
     <row r="851" spans="1:3">
       <c r="A851" s="1" t="s">
@@ -6659,31 +6662,31 @@
       </c>
     </row>
     <row r="854" spans="1:3">
-      <c r="A854" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B854" s="8">
+      <c r="A854" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854" s="4">
         <f>B852-B853</f>
         <v>0</v>
       </c>
     </row>
     <row r="855" spans="1:3">
-      <c r="A855" s="7"/>
-      <c r="B855" s="8"/>
+      <c r="A855" s="3"/>
+      <c r="B855" s="4"/>
     </row>
     <row r="857" spans="1:3">
-      <c r="A857" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B857" s="3"/>
-      <c r="C857" s="3"/>
+      <c r="A857" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B857" s="5"/>
+      <c r="C857" s="5"/>
     </row>
     <row r="858" spans="1:3">
-      <c r="A858" s="4" t="s">
+      <c r="A858" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B858" s="5"/>
-      <c r="C858" s="6"/>
+      <c r="B858" s="7"/>
+      <c r="C858" s="8"/>
     </row>
     <row r="859" spans="1:3">
       <c r="A859" s="1" t="s">
@@ -6716,31 +6719,31 @@
       </c>
     </row>
     <row r="862" spans="1:3">
-      <c r="A862" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B862" s="8">
+      <c r="A862" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862" s="4">
         <f>B860-B861</f>
         <v>224</v>
       </c>
     </row>
     <row r="863" spans="1:3">
-      <c r="A863" s="7"/>
-      <c r="B863" s="8"/>
+      <c r="A863" s="3"/>
+      <c r="B863" s="4"/>
     </row>
     <row r="865" spans="1:3">
-      <c r="A865" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B865" s="3"/>
-      <c r="C865" s="3"/>
+      <c r="A865" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B865" s="5"/>
+      <c r="C865" s="5"/>
     </row>
     <row r="866" spans="1:3">
-      <c r="A866" s="4" t="s">
+      <c r="A866" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B866" s="5"/>
-      <c r="C866" s="6"/>
+      <c r="B866" s="7"/>
+      <c r="C866" s="8"/>
     </row>
     <row r="867" spans="1:3">
       <c r="A867" s="1" t="s">
@@ -6773,31 +6776,31 @@
       </c>
     </row>
     <row r="870" spans="1:3">
-      <c r="A870" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B870" s="8">
+      <c r="A870" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870" s="4">
         <f>B868-B869</f>
         <v>124</v>
       </c>
     </row>
     <row r="871" spans="1:3">
-      <c r="A871" s="7"/>
-      <c r="B871" s="8"/>
+      <c r="A871" s="3"/>
+      <c r="B871" s="4"/>
     </row>
     <row r="873" spans="1:3">
-      <c r="A873" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B873" s="3"/>
-      <c r="C873" s="3"/>
+      <c r="A873" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B873" s="5"/>
+      <c r="C873" s="5"/>
     </row>
     <row r="874" spans="1:3">
-      <c r="A874" s="4" t="s">
+      <c r="A874" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B874" s="5"/>
-      <c r="C874" s="6"/>
+      <c r="B874" s="7"/>
+      <c r="C874" s="8"/>
     </row>
     <row r="875" spans="1:3">
       <c r="A875" s="1" t="s">
@@ -6830,31 +6833,31 @@
       </c>
     </row>
     <row r="878" spans="1:3">
-      <c r="A878" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B878" s="8">
+      <c r="A878" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B878" s="4">
         <f>B876-B877</f>
         <v>449</v>
       </c>
     </row>
     <row r="879" spans="1:3">
-      <c r="A879" s="7"/>
-      <c r="B879" s="8"/>
+      <c r="A879" s="3"/>
+      <c r="B879" s="4"/>
     </row>
     <row r="881" spans="1:3">
-      <c r="A881" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B881" s="3"/>
-      <c r="C881" s="3"/>
+      <c r="A881" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B881" s="5"/>
+      <c r="C881" s="5"/>
     </row>
     <row r="882" spans="1:3">
-      <c r="A882" s="4" t="s">
+      <c r="A882" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B882" s="5"/>
-      <c r="C882" s="6"/>
+      <c r="B882" s="7"/>
+      <c r="C882" s="8"/>
     </row>
     <row r="883" spans="1:3">
       <c r="A883" s="1" t="s">
@@ -6887,31 +6890,31 @@
       </c>
     </row>
     <row r="886" spans="1:3">
-      <c r="A886" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B886" s="8">
+      <c r="A886" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B886" s="4">
         <f>B884-B885</f>
         <v>821</v>
       </c>
     </row>
     <row r="887" spans="1:3">
-      <c r="A887" s="7"/>
-      <c r="B887" s="8"/>
+      <c r="A887" s="3"/>
+      <c r="B887" s="4"/>
     </row>
     <row r="889" spans="1:3">
-      <c r="A889" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B889" s="3"/>
-      <c r="C889" s="3"/>
+      <c r="A889" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B889" s="5"/>
+      <c r="C889" s="5"/>
     </row>
     <row r="890" spans="1:3">
-      <c r="A890" s="4" t="s">
+      <c r="A890" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B890" s="5"/>
-      <c r="C890" s="6"/>
+      <c r="B890" s="7"/>
+      <c r="C890" s="8"/>
     </row>
     <row r="891" spans="1:3">
       <c r="A891" s="1" t="s">
@@ -6944,17 +6947,17 @@
       </c>
     </row>
     <row r="894" spans="1:3">
-      <c r="A894" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B894" s="8">
+      <c r="A894" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B894" s="4">
         <f>B892-B893</f>
         <v>31</v>
       </c>
     </row>
     <row r="895" spans="1:3">
-      <c r="A895" s="7"/>
-      <c r="B895" s="8"/>
+      <c r="A895" s="3"/>
+      <c r="B895" s="4"/>
     </row>
     <row r="896" spans="1:3">
       <c r="A896" s="1" t="s">
@@ -6965,18 +6968,18 @@
       </c>
     </row>
     <row r="898" spans="1:3">
-      <c r="A898" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B898" s="3"/>
-      <c r="C898" s="3"/>
+      <c r="A898" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B898" s="5"/>
+      <c r="C898" s="5"/>
     </row>
     <row r="899" spans="1:3">
-      <c r="A899" s="4" t="s">
+      <c r="A899" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B899" s="5"/>
-      <c r="C899" s="6"/>
+      <c r="B899" s="7"/>
+      <c r="C899" s="8"/>
     </row>
     <row r="900" spans="1:3">
       <c r="A900" s="1" t="s">
@@ -7009,31 +7012,31 @@
       </c>
     </row>
     <row r="903" spans="1:3">
-      <c r="A903" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B903" s="8">
+      <c r="A903" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B903" s="4">
         <f>B901-B902</f>
         <v>22</v>
       </c>
     </row>
     <row r="904" spans="1:3">
-      <c r="A904" s="7"/>
-      <c r="B904" s="8"/>
+      <c r="A904" s="3"/>
+      <c r="B904" s="4"/>
     </row>
     <row r="906" spans="1:3">
-      <c r="A906" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B906" s="3"/>
-      <c r="C906" s="3"/>
+      <c r="A906" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B906" s="5"/>
+      <c r="C906" s="5"/>
     </row>
     <row r="907" spans="1:3">
-      <c r="A907" s="4" t="s">
+      <c r="A907" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B907" s="5"/>
-      <c r="C907" s="6"/>
+      <c r="B907" s="7"/>
+      <c r="C907" s="8"/>
     </row>
     <row r="908" spans="1:3">
       <c r="A908" s="1" t="s">
@@ -7066,31 +7069,31 @@
       </c>
     </row>
     <row r="911" spans="1:3">
-      <c r="A911" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B911" s="8">
+      <c r="A911" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B911" s="4">
         <f>B909-B910</f>
         <v>75</v>
       </c>
     </row>
     <row r="912" spans="1:3">
-      <c r="A912" s="7"/>
-      <c r="B912" s="8"/>
+      <c r="A912" s="3"/>
+      <c r="B912" s="4"/>
     </row>
     <row r="914" spans="1:3">
-      <c r="A914" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B914" s="3"/>
-      <c r="C914" s="3"/>
+      <c r="A914" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B914" s="5"/>
+      <c r="C914" s="5"/>
     </row>
     <row r="915" spans="1:3">
-      <c r="A915" s="4" t="s">
+      <c r="A915" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B915" s="5"/>
-      <c r="C915" s="6"/>
+      <c r="B915" s="7"/>
+      <c r="C915" s="8"/>
     </row>
     <row r="916" spans="1:3">
       <c r="A916" s="1" t="s">
@@ -7123,31 +7126,31 @@
       </c>
     </row>
     <row r="919" spans="1:3">
-      <c r="A919" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B919" s="8">
+      <c r="A919" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B919" s="4">
         <f>B917-B918</f>
         <v>39</v>
       </c>
     </row>
     <row r="920" spans="1:3">
-      <c r="A920" s="7"/>
-      <c r="B920" s="8"/>
+      <c r="A920" s="3"/>
+      <c r="B920" s="4"/>
     </row>
     <row r="922" spans="1:3">
-      <c r="A922" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B922" s="3"/>
-      <c r="C922" s="3"/>
+      <c r="A922" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B922" s="5"/>
+      <c r="C922" s="5"/>
     </row>
     <row r="923" spans="1:3">
-      <c r="A923" s="4" t="s">
+      <c r="A923" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B923" s="5"/>
-      <c r="C923" s="6"/>
+      <c r="B923" s="7"/>
+      <c r="C923" s="8"/>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" s="1" t="s">
@@ -7180,31 +7183,31 @@
       </c>
     </row>
     <row r="927" spans="1:3">
-      <c r="A927" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B927" s="8">
+      <c r="A927" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B927" s="4">
         <f>B925-B926</f>
         <v>70</v>
       </c>
     </row>
     <row r="928" spans="1:3">
-      <c r="A928" s="7"/>
-      <c r="B928" s="8"/>
+      <c r="A928" s="3"/>
+      <c r="B928" s="4"/>
     </row>
     <row r="930" spans="1:3">
-      <c r="A930" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B930" s="3"/>
-      <c r="C930" s="3"/>
+      <c r="A930" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B930" s="5"/>
+      <c r="C930" s="5"/>
     </row>
     <row r="931" spans="1:3">
-      <c r="A931" s="4" t="s">
+      <c r="A931" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B931" s="5"/>
-      <c r="C931" s="6"/>
+      <c r="B931" s="7"/>
+      <c r="C931" s="8"/>
     </row>
     <row r="932" spans="1:3">
       <c r="A932" s="1" t="s">
@@ -7237,31 +7240,31 @@
       </c>
     </row>
     <row r="935" spans="1:3">
-      <c r="A935" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B935" s="8">
+      <c r="A935" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B935" s="4">
         <f>B933-B934</f>
         <v>0</v>
       </c>
     </row>
     <row r="936" spans="1:3">
-      <c r="A936" s="7"/>
-      <c r="B936" s="8"/>
+      <c r="A936" s="3"/>
+      <c r="B936" s="4"/>
     </row>
     <row r="938" spans="1:3">
-      <c r="A938" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B938" s="3"/>
-      <c r="C938" s="3"/>
+      <c r="A938" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B938" s="5"/>
+      <c r="C938" s="5"/>
     </row>
     <row r="939" spans="1:3">
-      <c r="A939" s="4" t="s">
+      <c r="A939" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B939" s="5"/>
-      <c r="C939" s="6"/>
+      <c r="B939" s="7"/>
+      <c r="C939" s="8"/>
     </row>
     <row r="940" spans="1:3">
       <c r="A940" s="1" t="s">
@@ -7294,17 +7297,17 @@
       </c>
     </row>
     <row r="943" spans="1:3">
-      <c r="A943" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B943" s="8">
+      <c r="A943" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B943" s="4">
         <f>B941-B942</f>
         <v>59</v>
       </c>
     </row>
     <row r="944" spans="1:3">
-      <c r="A944" s="7"/>
-      <c r="B944" s="8"/>
+      <c r="A944" s="3"/>
+      <c r="B944" s="4"/>
     </row>
     <row r="945" spans="1:3">
       <c r="A945" s="1" t="s">
@@ -7315,18 +7318,18 @@
       </c>
     </row>
     <row r="947" spans="1:3">
-      <c r="A947" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B947" s="3"/>
-      <c r="C947" s="3"/>
+      <c r="A947" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B947" s="5"/>
+      <c r="C947" s="5"/>
     </row>
     <row r="948" spans="1:3">
-      <c r="A948" s="4" t="s">
+      <c r="A948" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B948" s="5"/>
-      <c r="C948" s="6"/>
+      <c r="B948" s="7"/>
+      <c r="C948" s="8"/>
     </row>
     <row r="949" spans="1:3">
       <c r="A949" s="1" t="s">
@@ -7359,31 +7362,31 @@
       </c>
     </row>
     <row r="952" spans="1:3">
-      <c r="A952" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B952" s="8">
+      <c r="A952" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B952" s="4">
         <f>B950-B951</f>
         <v>1667</v>
       </c>
     </row>
     <row r="953" spans="1:3">
-      <c r="A953" s="7"/>
-      <c r="B953" s="8"/>
+      <c r="A953" s="3"/>
+      <c r="B953" s="4"/>
     </row>
     <row r="955" spans="1:3">
-      <c r="A955" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B955" s="3"/>
-      <c r="C955" s="3"/>
+      <c r="A955" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B955" s="5"/>
+      <c r="C955" s="5"/>
     </row>
     <row r="956" spans="1:3">
-      <c r="A956" s="4" t="s">
+      <c r="A956" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B956" s="5"/>
-      <c r="C956" s="6"/>
+      <c r="B956" s="7"/>
+      <c r="C956" s="8"/>
     </row>
     <row r="957" spans="1:3">
       <c r="A957" s="1" t="s">
@@ -7416,31 +7419,31 @@
       </c>
     </row>
     <row r="960" spans="1:3">
-      <c r="A960" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B960" s="8">
+      <c r="A960" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B960" s="4">
         <f>B958-B959</f>
         <v>61</v>
       </c>
     </row>
     <row r="961" spans="1:3">
-      <c r="A961" s="7"/>
-      <c r="B961" s="8"/>
+      <c r="A961" s="3"/>
+      <c r="B961" s="4"/>
     </row>
     <row r="963" spans="1:3">
-      <c r="A963" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B963" s="3"/>
-      <c r="C963" s="3"/>
+      <c r="A963" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B963" s="5"/>
+      <c r="C963" s="5"/>
     </row>
     <row r="964" spans="1:3">
-      <c r="A964" s="4" t="s">
+      <c r="A964" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B964" s="5"/>
-      <c r="C964" s="6"/>
+      <c r="B964" s="7"/>
+      <c r="C964" s="8"/>
     </row>
     <row r="965" spans="1:3">
       <c r="A965" s="1" t="s">
@@ -7473,31 +7476,31 @@
       </c>
     </row>
     <row r="968" spans="1:3">
-      <c r="A968" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B968" s="8">
+      <c r="A968" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B968" s="4">
         <f>B966-B967</f>
         <v>199</v>
       </c>
     </row>
     <row r="969" spans="1:3">
-      <c r="A969" s="7"/>
-      <c r="B969" s="8"/>
+      <c r="A969" s="3"/>
+      <c r="B969" s="4"/>
     </row>
     <row r="971" spans="1:3">
-      <c r="A971" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B971" s="3"/>
-      <c r="C971" s="3"/>
+      <c r="A971" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B971" s="5"/>
+      <c r="C971" s="5"/>
     </row>
     <row r="972" spans="1:3">
-      <c r="A972" s="4" t="s">
+      <c r="A972" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B972" s="5"/>
-      <c r="C972" s="6"/>
+      <c r="B972" s="7"/>
+      <c r="C972" s="8"/>
     </row>
     <row r="973" spans="1:3">
       <c r="A973" s="1" t="s">
@@ -7530,31 +7533,31 @@
       </c>
     </row>
     <row r="976" spans="1:3">
-      <c r="A976" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B976" s="8">
+      <c r="A976" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B976" s="4">
         <f>B974-B975</f>
         <v>534</v>
       </c>
     </row>
     <row r="977" spans="1:3">
-      <c r="A977" s="7"/>
-      <c r="B977" s="8"/>
+      <c r="A977" s="3"/>
+      <c r="B977" s="4"/>
     </row>
     <row r="979" spans="1:3">
-      <c r="A979" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B979" s="3"/>
-      <c r="C979" s="3"/>
+      <c r="A979" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B979" s="5"/>
+      <c r="C979" s="5"/>
     </row>
     <row r="980" spans="1:3">
-      <c r="A980" s="4" t="s">
+      <c r="A980" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B980" s="5"/>
-      <c r="C980" s="6"/>
+      <c r="B980" s="7"/>
+      <c r="C980" s="8"/>
     </row>
     <row r="981" spans="1:3">
       <c r="A981" s="1" t="s">
@@ -7587,31 +7590,31 @@
       </c>
     </row>
     <row r="984" spans="1:3">
-      <c r="A984" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B984" s="8">
+      <c r="A984" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B984" s="4">
         <f>B982-B983</f>
         <v>59</v>
       </c>
     </row>
     <row r="985" spans="1:3">
-      <c r="A985" s="7"/>
-      <c r="B985" s="8"/>
+      <c r="A985" s="3"/>
+      <c r="B985" s="4"/>
     </row>
     <row r="987" spans="1:3">
-      <c r="A987" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B987" s="3"/>
-      <c r="C987" s="3"/>
+      <c r="A987" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B987" s="5"/>
+      <c r="C987" s="5"/>
     </row>
     <row r="988" spans="1:3">
-      <c r="A988" s="4" t="s">
+      <c r="A988" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B988" s="5"/>
-      <c r="C988" s="6"/>
+      <c r="B988" s="7"/>
+      <c r="C988" s="8"/>
     </row>
     <row r="989" spans="1:3">
       <c r="A989" s="1" t="s">
@@ -7644,31 +7647,31 @@
       </c>
     </row>
     <row r="992" spans="1:3">
-      <c r="A992" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B992" s="8">
+      <c r="A992" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B992" s="4">
         <f>B990-B991</f>
         <v>164</v>
       </c>
     </row>
     <row r="993" spans="1:3">
-      <c r="A993" s="7"/>
-      <c r="B993" s="8"/>
+      <c r="A993" s="3"/>
+      <c r="B993" s="4"/>
     </row>
     <row r="995" spans="1:3">
-      <c r="A995" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B995" s="3"/>
-      <c r="C995" s="3"/>
+      <c r="A995" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B995" s="5"/>
+      <c r="C995" s="5"/>
     </row>
     <row r="996" spans="1:3">
-      <c r="A996" s="4" t="s">
+      <c r="A996" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B996" s="5"/>
-      <c r="C996" s="6"/>
+      <c r="B996" s="7"/>
+      <c r="C996" s="8"/>
     </row>
     <row r="997" spans="1:3">
       <c r="A997" s="1" t="s">
@@ -7701,121 +7704,883 @@
       </c>
     </row>
     <row r="1000" spans="1:3">
-      <c r="A1000" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1000" s="8">
+      <c r="A1000" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1000" s="4">
         <f>B998-B999</f>
         <v>1579</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
-      <c r="A1001" s="7"/>
-      <c r="B1001" s="8"/>
+      <c r="A1001" s="3"/>
+      <c r="B1001" s="4"/>
+    </row>
+    <row r="1003" spans="1:3">
+      <c r="A1003" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1003" s="5"/>
+      <c r="C1003" s="5"/>
+    </row>
+    <row r="1004" spans="1:3">
+      <c r="A1004" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1004" s="7"/>
+      <c r="C1004" s="8"/>
+    </row>
+    <row r="1005" spans="1:3">
+      <c r="A1005" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1005" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3">
+      <c r="A1006" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1006" s="2">
+        <v>4534</v>
+      </c>
+      <c r="C1006" s="2">
+        <v>9389</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3">
+      <c r="A1007" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1007" s="2">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3">
+      <c r="A1008" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1008" s="4">
+        <f>B1006-B1007</f>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3">
+      <c r="A1009" s="3"/>
+      <c r="B1009" s="4"/>
+    </row>
+    <row r="1010" spans="1:3">
+      <c r="A1010" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1010" s="2">
+        <v>72258</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3">
+      <c r="A1012" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1012" s="5"/>
+      <c r="C1012" s="5"/>
+    </row>
+    <row r="1013" spans="1:3">
+      <c r="A1013" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1013" s="7"/>
+      <c r="C1013" s="8"/>
+    </row>
+    <row r="1014" spans="1:3">
+      <c r="A1014" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1014" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3">
+      <c r="A1015" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1015" s="2">
+        <v>744</v>
+      </c>
+      <c r="C1015" s="2">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3">
+      <c r="A1016" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1016" s="2">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3">
+      <c r="A1017" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1017" s="4">
+        <f>B1015-B1016</f>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3">
+      <c r="A1018" s="3"/>
+      <c r="B1018" s="4"/>
+    </row>
+    <row r="1020" spans="1:3">
+      <c r="A1020" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1020" s="5"/>
+      <c r="C1020" s="5"/>
+    </row>
+    <row r="1021" spans="1:3">
+      <c r="A1021" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1021" s="7"/>
+      <c r="C1021" s="8"/>
+    </row>
+    <row r="1022" spans="1:3">
+      <c r="A1022" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1022" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1022" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:3">
+      <c r="A1023" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1023" s="2">
+        <v>193</v>
+      </c>
+      <c r="C1023" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3">
+      <c r="A1024" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1024" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:3">
+      <c r="A1025" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1025" s="4">
+        <f>B1023-B1024</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:3">
+      <c r="A1026" s="3"/>
+      <c r="B1026" s="4"/>
+    </row>
+    <row r="1028" spans="1:3">
+      <c r="A1028" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1028" s="5"/>
+      <c r="C1028" s="5"/>
+    </row>
+    <row r="1029" spans="1:3">
+      <c r="A1029" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1029" s="7"/>
+      <c r="C1029" s="8"/>
+    </row>
+    <row r="1030" spans="1:3">
+      <c r="A1030" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1030" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1030" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:3">
+      <c r="A1031" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1031" s="2">
+        <v>16</v>
+      </c>
+      <c r="C1031" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:3">
+      <c r="A1032" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1032" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3">
+      <c r="A1033" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1033" s="4">
+        <f>B1031-B1032</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:3">
+      <c r="A1034" s="3"/>
+      <c r="B1034" s="4"/>
+    </row>
+    <row r="1036" spans="1:3">
+      <c r="A1036" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1036" s="5"/>
+      <c r="C1036" s="5"/>
+    </row>
+    <row r="1037" spans="1:3">
+      <c r="A1037" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1037" s="7"/>
+      <c r="C1037" s="8"/>
+    </row>
+    <row r="1038" spans="1:3">
+      <c r="A1038" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1038" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1038" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3">
+      <c r="A1039" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1039" s="2">
+        <v>201</v>
+      </c>
+      <c r="C1039" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:3">
+      <c r="A1040" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1040" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:3">
+      <c r="A1041" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1041" s="4">
+        <f>B1039-B1040</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3">
+      <c r="A1042" s="3"/>
+      <c r="B1042" s="4"/>
+    </row>
+    <row r="1044" spans="1:3">
+      <c r="A1044" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1044" s="5"/>
+      <c r="C1044" s="5"/>
+    </row>
+    <row r="1045" spans="1:3">
+      <c r="A1045" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1045" s="7"/>
+      <c r="C1045" s="8"/>
+    </row>
+    <row r="1046" spans="1:3">
+      <c r="A1046" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1046" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1046" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:3">
+      <c r="A1047" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1047" s="2">
+        <v>3363</v>
+      </c>
+      <c r="C1047" s="2">
+        <v>4235</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3">
+      <c r="A1048" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1048" s="2">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:3">
+      <c r="A1049" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1049" s="4">
+        <f>B1047-B1048</f>
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:3">
+      <c r="A1050" s="3"/>
+      <c r="B1050" s="4"/>
+    </row>
+    <row r="1052" spans="1:3">
+      <c r="A1052" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1052" s="5"/>
+      <c r="C1052" s="5"/>
+    </row>
+    <row r="1053" spans="1:3">
+      <c r="A1053" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1053" s="7"/>
+      <c r="C1053" s="8"/>
+    </row>
+    <row r="1054" spans="1:3">
+      <c r="A1054" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1054" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1054" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:3">
+      <c r="A1055" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1055" s="2">
+        <v>776</v>
+      </c>
+      <c r="C1055" s="2">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:3">
+      <c r="A1056" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1056" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3">
+      <c r="A1057" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1057" s="4">
+        <f>B1055-B1056</f>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:3">
+      <c r="A1058" s="3"/>
+      <c r="B1058" s="4"/>
+    </row>
+    <row r="1060" spans="1:3">
+      <c r="A1060" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1060" s="5"/>
+      <c r="C1060" s="5"/>
+    </row>
+    <row r="1061" spans="1:3">
+      <c r="A1061" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1061" s="7"/>
+      <c r="C1061" s="8"/>
+    </row>
+    <row r="1062" spans="1:3">
+      <c r="A1062" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1062" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1062" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3">
+      <c r="A1063" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1063" s="2">
+        <v>251</v>
+      </c>
+      <c r="C1063" s="2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3">
+      <c r="A1064" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1064" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:3">
+      <c r="A1065" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1065" s="4">
+        <f>B1063-B1064</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3">
+      <c r="A1066" s="3"/>
+      <c r="B1066" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="492">
-    <mergeCell ref="A927:A928"/>
-    <mergeCell ref="B927:B928"/>
-    <mergeCell ref="A930:C930"/>
-    <mergeCell ref="A931:C931"/>
-    <mergeCell ref="A935:A936"/>
-    <mergeCell ref="B935:B936"/>
-    <mergeCell ref="A907:C907"/>
-    <mergeCell ref="A911:A912"/>
-    <mergeCell ref="B911:B912"/>
-    <mergeCell ref="A914:C914"/>
-    <mergeCell ref="A915:C915"/>
-    <mergeCell ref="A919:A920"/>
-    <mergeCell ref="B919:B920"/>
-    <mergeCell ref="A922:C922"/>
-    <mergeCell ref="A923:C923"/>
-    <mergeCell ref="A889:C889"/>
-    <mergeCell ref="A890:C890"/>
-    <mergeCell ref="A894:A895"/>
-    <mergeCell ref="B894:B895"/>
-    <mergeCell ref="A898:C898"/>
-    <mergeCell ref="A899:C899"/>
-    <mergeCell ref="A903:A904"/>
-    <mergeCell ref="B903:B904"/>
-    <mergeCell ref="A906:C906"/>
-    <mergeCell ref="A824:C824"/>
-    <mergeCell ref="A825:C825"/>
-    <mergeCell ref="A829:A830"/>
-    <mergeCell ref="B829:B830"/>
-    <mergeCell ref="A805:A806"/>
-    <mergeCell ref="B805:B806"/>
-    <mergeCell ref="A808:C808"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="A813:A814"/>
-    <mergeCell ref="B813:B814"/>
-    <mergeCell ref="A816:C816"/>
-    <mergeCell ref="A817:C817"/>
-    <mergeCell ref="A821:A822"/>
-    <mergeCell ref="B821:B822"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="A789:A790"/>
-    <mergeCell ref="B789:B790"/>
-    <mergeCell ref="A792:C792"/>
-    <mergeCell ref="A793:C793"/>
-    <mergeCell ref="A797:A798"/>
-    <mergeCell ref="B797:B798"/>
-    <mergeCell ref="A800:C800"/>
-    <mergeCell ref="A801:C801"/>
-    <mergeCell ref="A767:C767"/>
-    <mergeCell ref="A768:C768"/>
-    <mergeCell ref="A772:A773"/>
-    <mergeCell ref="B772:B773"/>
-    <mergeCell ref="A776:C776"/>
-    <mergeCell ref="A777:C777"/>
-    <mergeCell ref="A781:A782"/>
-    <mergeCell ref="B781:B782"/>
-    <mergeCell ref="A784:C784"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
+  <mergeCells count="524">
+    <mergeCell ref="A1060:C1060"/>
+    <mergeCell ref="A1061:C1061"/>
+    <mergeCell ref="A1065:A1066"/>
+    <mergeCell ref="B1065:B1066"/>
+    <mergeCell ref="A1041:A1042"/>
+    <mergeCell ref="B1041:B1042"/>
+    <mergeCell ref="A1044:C1044"/>
+    <mergeCell ref="A1045:C1045"/>
+    <mergeCell ref="A1049:A1050"/>
+    <mergeCell ref="B1049:B1050"/>
+    <mergeCell ref="A1052:C1052"/>
+    <mergeCell ref="A1053:C1053"/>
+    <mergeCell ref="A1057:A1058"/>
+    <mergeCell ref="B1057:B1058"/>
+    <mergeCell ref="A1021:C1021"/>
+    <mergeCell ref="A1025:A1026"/>
+    <mergeCell ref="B1025:B1026"/>
+    <mergeCell ref="A1028:C1028"/>
+    <mergeCell ref="A1029:C1029"/>
+    <mergeCell ref="A1033:A1034"/>
+    <mergeCell ref="B1033:B1034"/>
+    <mergeCell ref="A1036:C1036"/>
+    <mergeCell ref="A1037:C1037"/>
+    <mergeCell ref="A1003:C1003"/>
+    <mergeCell ref="A1004:C1004"/>
+    <mergeCell ref="A1008:A1009"/>
+    <mergeCell ref="B1008:B1009"/>
+    <mergeCell ref="A1012:C1012"/>
+    <mergeCell ref="A1013:C1013"/>
+    <mergeCell ref="A1017:A1018"/>
+    <mergeCell ref="B1017:B1018"/>
+    <mergeCell ref="A1020:C1020"/>
+    <mergeCell ref="A995:C995"/>
+    <mergeCell ref="A996:C996"/>
+    <mergeCell ref="A1000:A1001"/>
+    <mergeCell ref="B1000:B1001"/>
+    <mergeCell ref="A976:A977"/>
+    <mergeCell ref="B976:B977"/>
+    <mergeCell ref="A979:C979"/>
+    <mergeCell ref="A980:C980"/>
+    <mergeCell ref="A984:A985"/>
+    <mergeCell ref="B984:B985"/>
+    <mergeCell ref="A987:C987"/>
+    <mergeCell ref="A988:C988"/>
+    <mergeCell ref="A992:A993"/>
+    <mergeCell ref="B992:B993"/>
+    <mergeCell ref="A956:C956"/>
+    <mergeCell ref="A960:A961"/>
+    <mergeCell ref="B960:B961"/>
+    <mergeCell ref="A963:C963"/>
+    <mergeCell ref="A964:C964"/>
+    <mergeCell ref="A968:A969"/>
+    <mergeCell ref="B968:B969"/>
+    <mergeCell ref="A971:C971"/>
+    <mergeCell ref="A972:C972"/>
+    <mergeCell ref="A938:C938"/>
+    <mergeCell ref="A939:C939"/>
+    <mergeCell ref="A943:A944"/>
+    <mergeCell ref="B943:B944"/>
+    <mergeCell ref="A947:C947"/>
+    <mergeCell ref="A948:C948"/>
+    <mergeCell ref="A952:A953"/>
+    <mergeCell ref="B952:B953"/>
+    <mergeCell ref="A955:C955"/>
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="B870:B871"/>
+    <mergeCell ref="A873:C873"/>
+    <mergeCell ref="A874:C874"/>
+    <mergeCell ref="A878:A879"/>
+    <mergeCell ref="B878:B879"/>
+    <mergeCell ref="A881:C881"/>
+    <mergeCell ref="A882:C882"/>
+    <mergeCell ref="A886:A887"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="A850:C850"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="B854:B855"/>
+    <mergeCell ref="A857:C857"/>
+    <mergeCell ref="A858:C858"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="B862:B863"/>
+    <mergeCell ref="A865:C865"/>
+    <mergeCell ref="A866:C866"/>
+    <mergeCell ref="A832:C832"/>
+    <mergeCell ref="A833:C833"/>
+    <mergeCell ref="A837:A838"/>
+    <mergeCell ref="B837:B838"/>
+    <mergeCell ref="A841:C841"/>
+    <mergeCell ref="A842:C842"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="B846:B847"/>
+    <mergeCell ref="A849:C849"/>
+    <mergeCell ref="A759:C759"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A764:A765"/>
+    <mergeCell ref="B764:B765"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A702:C702"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A707:A708"/>
+    <mergeCell ref="B707:B708"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A487:A488"/>
+    <mergeCell ref="B487:B488"/>
+    <mergeCell ref="A565:C565"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="B569:B570"/>
+    <mergeCell ref="A572:C572"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A547:C547"/>
+    <mergeCell ref="A548:C548"/>
+    <mergeCell ref="A552:A553"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A557:C557"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="B561:B562"/>
+    <mergeCell ref="A564:C564"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A507:C507"/>
+    <mergeCell ref="A508:C508"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
+    <mergeCell ref="A515:C515"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
     <mergeCell ref="A430:A431"/>
     <mergeCell ref="B430:B431"/>
     <mergeCell ref="A490:C490"/>
@@ -7840,373 +8605,107 @@
     <mergeCell ref="A459:C459"/>
     <mergeCell ref="A463:A464"/>
     <mergeCell ref="B463:B464"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A487:A488"/>
-    <mergeCell ref="B487:B488"/>
-    <mergeCell ref="A565:C565"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="B569:B570"/>
-    <mergeCell ref="A572:C572"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A547:C547"/>
-    <mergeCell ref="A548:C548"/>
-    <mergeCell ref="A552:A553"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A557:C557"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="B561:B562"/>
-    <mergeCell ref="A564:C564"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A507:C507"/>
-    <mergeCell ref="A508:C508"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
-    <mergeCell ref="A702:C702"/>
-    <mergeCell ref="A703:C703"/>
-    <mergeCell ref="A707:A708"/>
-    <mergeCell ref="B707:B708"/>
-    <mergeCell ref="A711:C711"/>
-    <mergeCell ref="A712:C712"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="B716:B717"/>
-    <mergeCell ref="A719:C719"/>
-    <mergeCell ref="A720:C720"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="B724:B725"/>
-    <mergeCell ref="A727:C727"/>
-    <mergeCell ref="A728:C728"/>
-    <mergeCell ref="A732:A733"/>
-    <mergeCell ref="B732:B733"/>
-    <mergeCell ref="A735:C735"/>
-    <mergeCell ref="A736:C736"/>
-    <mergeCell ref="A759:C759"/>
-    <mergeCell ref="A760:C760"/>
-    <mergeCell ref="A764:A765"/>
-    <mergeCell ref="B764:B765"/>
-    <mergeCell ref="A740:A741"/>
-    <mergeCell ref="B740:B741"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A744:C744"/>
-    <mergeCell ref="A748:A749"/>
-    <mergeCell ref="B748:B749"/>
-    <mergeCell ref="A751:C751"/>
-    <mergeCell ref="A752:C752"/>
-    <mergeCell ref="A756:A757"/>
-    <mergeCell ref="B756:B757"/>
-    <mergeCell ref="A832:C832"/>
-    <mergeCell ref="A833:C833"/>
-    <mergeCell ref="A837:A838"/>
-    <mergeCell ref="B837:B838"/>
-    <mergeCell ref="A841:C841"/>
-    <mergeCell ref="A842:C842"/>
-    <mergeCell ref="A846:A847"/>
-    <mergeCell ref="B846:B847"/>
-    <mergeCell ref="A849:C849"/>
-    <mergeCell ref="A850:C850"/>
-    <mergeCell ref="A854:A855"/>
-    <mergeCell ref="B854:B855"/>
-    <mergeCell ref="A857:C857"/>
-    <mergeCell ref="A858:C858"/>
-    <mergeCell ref="A862:A863"/>
-    <mergeCell ref="B862:B863"/>
-    <mergeCell ref="A865:C865"/>
-    <mergeCell ref="A866:C866"/>
-    <mergeCell ref="A870:A871"/>
-    <mergeCell ref="B870:B871"/>
-    <mergeCell ref="A873:C873"/>
-    <mergeCell ref="A874:C874"/>
-    <mergeCell ref="A878:A879"/>
-    <mergeCell ref="B878:B879"/>
-    <mergeCell ref="A881:C881"/>
-    <mergeCell ref="A882:C882"/>
-    <mergeCell ref="A886:A887"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="A938:C938"/>
-    <mergeCell ref="A939:C939"/>
-    <mergeCell ref="A943:A944"/>
-    <mergeCell ref="B943:B944"/>
-    <mergeCell ref="A947:C947"/>
-    <mergeCell ref="A948:C948"/>
-    <mergeCell ref="A952:A953"/>
-    <mergeCell ref="B952:B953"/>
-    <mergeCell ref="A955:C955"/>
-    <mergeCell ref="A956:C956"/>
-    <mergeCell ref="A960:A961"/>
-    <mergeCell ref="B960:B961"/>
-    <mergeCell ref="A963:C963"/>
-    <mergeCell ref="A964:C964"/>
-    <mergeCell ref="A968:A969"/>
-    <mergeCell ref="B968:B969"/>
-    <mergeCell ref="A971:C971"/>
-    <mergeCell ref="A972:C972"/>
-    <mergeCell ref="A995:C995"/>
-    <mergeCell ref="A996:C996"/>
-    <mergeCell ref="A1000:A1001"/>
-    <mergeCell ref="B1000:B1001"/>
-    <mergeCell ref="A976:A977"/>
-    <mergeCell ref="B976:B977"/>
-    <mergeCell ref="A979:C979"/>
-    <mergeCell ref="A980:C980"/>
-    <mergeCell ref="A984:A985"/>
-    <mergeCell ref="B984:B985"/>
-    <mergeCell ref="A987:C987"/>
-    <mergeCell ref="A988:C988"/>
-    <mergeCell ref="A992:A993"/>
-    <mergeCell ref="B992:B993"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A767:C767"/>
+    <mergeCell ref="A768:C768"/>
+    <mergeCell ref="A772:A773"/>
+    <mergeCell ref="B772:B773"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A777:C777"/>
+    <mergeCell ref="A781:A782"/>
+    <mergeCell ref="B781:B782"/>
+    <mergeCell ref="A784:C784"/>
+    <mergeCell ref="A785:C785"/>
+    <mergeCell ref="A789:A790"/>
+    <mergeCell ref="B789:B790"/>
+    <mergeCell ref="A792:C792"/>
+    <mergeCell ref="A793:C793"/>
+    <mergeCell ref="A797:A798"/>
+    <mergeCell ref="B797:B798"/>
+    <mergeCell ref="A800:C800"/>
+    <mergeCell ref="A801:C801"/>
+    <mergeCell ref="A824:C824"/>
+    <mergeCell ref="A825:C825"/>
+    <mergeCell ref="A829:A830"/>
+    <mergeCell ref="B829:B830"/>
+    <mergeCell ref="A805:A806"/>
+    <mergeCell ref="B805:B806"/>
+    <mergeCell ref="A808:C808"/>
+    <mergeCell ref="A809:C809"/>
+    <mergeCell ref="A813:A814"/>
+    <mergeCell ref="B813:B814"/>
+    <mergeCell ref="A816:C816"/>
+    <mergeCell ref="A817:C817"/>
+    <mergeCell ref="A821:A822"/>
+    <mergeCell ref="B821:B822"/>
+    <mergeCell ref="A889:C889"/>
+    <mergeCell ref="A890:C890"/>
+    <mergeCell ref="A894:A895"/>
+    <mergeCell ref="B894:B895"/>
+    <mergeCell ref="A898:C898"/>
+    <mergeCell ref="A899:C899"/>
+    <mergeCell ref="A903:A904"/>
+    <mergeCell ref="B903:B904"/>
+    <mergeCell ref="A906:C906"/>
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="B927:B928"/>
+    <mergeCell ref="A930:C930"/>
+    <mergeCell ref="A931:C931"/>
+    <mergeCell ref="A935:A936"/>
+    <mergeCell ref="B935:B936"/>
+    <mergeCell ref="A907:C907"/>
+    <mergeCell ref="A911:A912"/>
+    <mergeCell ref="B911:B912"/>
+    <mergeCell ref="A914:C914"/>
+    <mergeCell ref="A915:C915"/>
+    <mergeCell ref="A919:A920"/>
+    <mergeCell ref="B919:B920"/>
+    <mergeCell ref="A922:C922"/>
+    <mergeCell ref="A923:C923"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050556EF-AC8D-4839-91D8-7BDDACCF362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F566621-9C5E-48D2-9383-BAF5EA059548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="42">
   <si>
     <t>Data</t>
   </si>
@@ -158,6 +158,9 @@
   <si>
     <t>28.10.2026</t>
   </si>
+  <si>
+    <t>29.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -261,12 +264,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -276,6 +273,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -553,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1066"/>
+  <dimension ref="A1:C1115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -562,18 +565,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -606,17 +609,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -627,18 +630,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -671,31 +674,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="A15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
+      <c r="A18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -728,31 +731,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="4">
+      <c r="A23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="8">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
+      <c r="A26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -785,31 +788,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="4">
+      <c r="A31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="8">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
+      <c r="A34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="8"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -842,31 +845,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="4">
+      <c r="A39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="8">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="3"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
+      <c r="A42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -899,31 +902,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="4">
+      <c r="A47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="8">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="3"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="8"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
+      <c r="A50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -956,31 +959,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="4">
+      <c r="A55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="8">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="3"/>
-      <c r="B56" s="4"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
+      <c r="A58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="8"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -1013,17 +1016,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="4">
+      <c r="A63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="8">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="3"/>
-      <c r="B64" s="4"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="8"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1034,18 +1037,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
+      <c r="A67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1078,31 +1081,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="4">
+      <c r="A72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="8">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="3"/>
-      <c r="B73" s="4"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="8"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="8"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="6"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1135,31 +1138,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="4">
+      <c r="A80" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="8">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="3"/>
-      <c r="B81" s="4"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="8"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
+      <c r="A83" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="8"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="6"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1192,31 +1195,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="4">
+      <c r="A88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="8">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="3"/>
-      <c r="B89" s="4"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="8"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
+      <c r="A91" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="7"/>
-      <c r="C92" s="8"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="6"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1249,31 +1252,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="4">
+      <c r="A96" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="8">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="3"/>
-      <c r="B97" s="4"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="8"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
+      <c r="A99" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="8"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="6"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1306,31 +1309,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="4">
+      <c r="A104" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="8">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="4"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="8"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
+      <c r="A107" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="7"/>
-      <c r="C108" s="8"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="6"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1363,31 +1366,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="4">
+      <c r="A112" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="8">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="3"/>
-      <c r="B113" s="4"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="8"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
+      <c r="A115" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="7"/>
-      <c r="C116" s="8"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="6"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1420,31 +1423,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="4">
+      <c r="A120" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="8">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="3"/>
-      <c r="B121" s="4"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="8"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
+      <c r="A123" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="7"/>
-      <c r="C124" s="8"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="6"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1477,17 +1480,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="4">
+      <c r="A128" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="8">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="3"/>
-      <c r="B129" s="4"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="8"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1498,18 +1501,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
+      <c r="A132" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="7"/>
-      <c r="C133" s="8"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="6"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1542,31 +1545,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="4">
+      <c r="A137" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="8">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="3"/>
-      <c r="B138" s="4"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="8"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
+      <c r="A140" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="7"/>
-      <c r="C141" s="8"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="6"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1599,31 +1602,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="4">
+      <c r="A145" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="8">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="3"/>
-      <c r="B146" s="4"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="8"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
+      <c r="A148" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="8"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="6"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1656,31 +1659,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="4">
+      <c r="A153" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="8">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="3"/>
-      <c r="B154" s="4"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="8"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
+      <c r="A156" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="7"/>
-      <c r="C157" s="8"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="6"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1713,31 +1716,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="4">
+      <c r="A161" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="8">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="3"/>
-      <c r="B162" s="4"/>
+      <c r="A162" s="7"/>
+      <c r="B162" s="8"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5"/>
+      <c r="A164" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="7"/>
-      <c r="C165" s="8"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="6"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1770,31 +1773,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="4">
+      <c r="A169" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="8">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="3"/>
-      <c r="B170" s="4"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="8"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="5"/>
-      <c r="C172" s="5"/>
+      <c r="A172" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="6" t="s">
+      <c r="A173" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="7"/>
-      <c r="C173" s="8"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="6"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1827,31 +1830,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="4">
+      <c r="A177" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="8">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="3"/>
-      <c r="B178" s="4"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="8"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
+      <c r="A180" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="6" t="s">
+      <c r="A181" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="7"/>
-      <c r="C181" s="8"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="6"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1884,17 +1887,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="4">
+      <c r="A185" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="8">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="3"/>
-      <c r="B186" s="4"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="8"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1905,18 +1908,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="5"/>
-      <c r="C189" s="5"/>
+      <c r="A189" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="7"/>
-      <c r="C190" s="8"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="6"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1949,31 +1952,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="4">
+      <c r="A194" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="8">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="3"/>
-      <c r="B195" s="4"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="8"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="5"/>
-      <c r="C197" s="5"/>
+      <c r="A197" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="6" t="s">
+      <c r="A198" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="7"/>
-      <c r="C198" s="8"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="6"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -2006,31 +2009,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="4">
+      <c r="A202" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="8">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="3"/>
-      <c r="B203" s="4"/>
+      <c r="A203" s="7"/>
+      <c r="B203" s="8"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
+      <c r="A205" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="6" t="s">
+      <c r="A206" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="7"/>
-      <c r="C206" s="8"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="6"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2063,31 +2066,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="4">
+      <c r="A210" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="8">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="3"/>
-      <c r="B211" s="4"/>
+      <c r="A211" s="7"/>
+      <c r="B211" s="8"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
+      <c r="A213" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="7"/>
-      <c r="C214" s="8"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="6"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2120,31 +2123,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="4">
+      <c r="A218" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="8">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="3"/>
-      <c r="B219" s="4"/>
+      <c r="A219" s="7"/>
+      <c r="B219" s="8"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="5"/>
-      <c r="C221" s="5"/>
+      <c r="A221" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="6" t="s">
+      <c r="A222" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="7"/>
-      <c r="C222" s="8"/>
+      <c r="B222" s="5"/>
+      <c r="C222" s="6"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2177,31 +2180,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="4">
+      <c r="A226" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="8">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="3"/>
-      <c r="B227" s="4"/>
+      <c r="A227" s="7"/>
+      <c r="B227" s="8"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="5"/>
-      <c r="C229" s="5"/>
+      <c r="A229" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="6" t="s">
+      <c r="A230" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="7"/>
-      <c r="C230" s="8"/>
+      <c r="B230" s="5"/>
+      <c r="C230" s="6"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2234,31 +2237,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="4">
+      <c r="A234" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="8">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="3"/>
-      <c r="B235" s="4"/>
+      <c r="A235" s="7"/>
+      <c r="B235" s="8"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5"/>
+      <c r="A237" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="6" t="s">
+      <c r="A238" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="7"/>
-      <c r="C238" s="8"/>
+      <c r="B238" s="5"/>
+      <c r="C238" s="6"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2291,17 +2294,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="4">
+      <c r="A242" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="8">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="3"/>
-      <c r="B243" s="4"/>
+      <c r="A243" s="7"/>
+      <c r="B243" s="8"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2312,18 +2315,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
+      <c r="A246" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="6" t="s">
+      <c r="A247" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="7"/>
-      <c r="C247" s="8"/>
+      <c r="B247" s="5"/>
+      <c r="C247" s="6"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2356,31 +2359,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="4">
+      <c r="A251" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="8">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="3"/>
-      <c r="B252" s="4"/>
+      <c r="A252" s="7"/>
+      <c r="B252" s="8"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
+      <c r="A254" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="3"/>
+      <c r="C254" s="3"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="6" t="s">
+      <c r="A255" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="7"/>
-      <c r="C255" s="8"/>
+      <c r="B255" s="5"/>
+      <c r="C255" s="6"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2413,31 +2416,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="4">
+      <c r="A259" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="8">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="3"/>
-      <c r="B260" s="4"/>
+      <c r="A260" s="7"/>
+      <c r="B260" s="8"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5"/>
+      <c r="A262" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="6" t="s">
+      <c r="A263" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="7"/>
-      <c r="C263" s="8"/>
+      <c r="B263" s="5"/>
+      <c r="C263" s="6"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2470,17 +2473,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="4">
+      <c r="A267" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="8">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="3"/>
-      <c r="B268" s="4"/>
+      <c r="A268" s="7"/>
+      <c r="B268" s="8"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2491,18 +2494,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="5"/>
-      <c r="C271" s="5"/>
+      <c r="A271" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="3"/>
+      <c r="C271" s="3"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="6" t="s">
+      <c r="A272" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="7"/>
-      <c r="C272" s="8"/>
+      <c r="B272" s="5"/>
+      <c r="C272" s="6"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2535,31 +2538,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="4">
+      <c r="A276" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="8">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="3"/>
-      <c r="B277" s="4"/>
+      <c r="A277" s="7"/>
+      <c r="B277" s="8"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="5"/>
-      <c r="C279" s="5"/>
+      <c r="A279" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="3"/>
+      <c r="C279" s="3"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="7"/>
-      <c r="C280" s="8"/>
+      <c r="B280" s="5"/>
+      <c r="C280" s="6"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2592,31 +2595,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="4">
+      <c r="A284" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="8">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="3"/>
-      <c r="B285" s="4"/>
+      <c r="A285" s="7"/>
+      <c r="B285" s="8"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="5"/>
-      <c r="C287" s="5"/>
+      <c r="A287" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="3"/>
+      <c r="C287" s="3"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="6" t="s">
+      <c r="A288" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="7"/>
-      <c r="C288" s="8"/>
+      <c r="B288" s="5"/>
+      <c r="C288" s="6"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2649,31 +2652,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="4">
+      <c r="A292" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="8">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="3"/>
-      <c r="B293" s="4"/>
+      <c r="A293" s="7"/>
+      <c r="B293" s="8"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="5"/>
-      <c r="C295" s="5"/>
+      <c r="A295" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="3"/>
+      <c r="C295" s="3"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="6" t="s">
+      <c r="A296" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="7"/>
-      <c r="C296" s="8"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="6"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2706,31 +2709,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="4">
+      <c r="A300" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="8">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="3"/>
-      <c r="B301" s="4"/>
+      <c r="A301" s="7"/>
+      <c r="B301" s="8"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="5"/>
-      <c r="C303" s="5"/>
+      <c r="A303" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="6" t="s">
+      <c r="A304" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="7"/>
-      <c r="C304" s="8"/>
+      <c r="B304" s="5"/>
+      <c r="C304" s="6"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2763,31 +2766,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="4">
+      <c r="A308" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="8">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="3"/>
-      <c r="B309" s="4"/>
+      <c r="A309" s="7"/>
+      <c r="B309" s="8"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="5"/>
-      <c r="C311" s="5"/>
+      <c r="A311" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="3"/>
+      <c r="C311" s="3"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="6" t="s">
+      <c r="A312" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="7"/>
-      <c r="C312" s="8"/>
+      <c r="B312" s="5"/>
+      <c r="C312" s="6"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2820,31 +2823,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="4">
+      <c r="A316" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="8">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="3"/>
-      <c r="B317" s="4"/>
+      <c r="A317" s="7"/>
+      <c r="B317" s="8"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="5"/>
-      <c r="C319" s="5"/>
+      <c r="A319" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="3"/>
+      <c r="C319" s="3"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="6" t="s">
+      <c r="A320" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="7"/>
-      <c r="C320" s="8"/>
+      <c r="B320" s="5"/>
+      <c r="C320" s="6"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2877,17 +2880,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="4">
+      <c r="A324" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="8">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="3"/>
-      <c r="B325" s="4"/>
+      <c r="A325" s="7"/>
+      <c r="B325" s="8"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2898,18 +2901,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="5"/>
-      <c r="C328" s="5"/>
+      <c r="A328" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="6" t="s">
+      <c r="A329" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="7"/>
-      <c r="C329" s="8"/>
+      <c r="B329" s="5"/>
+      <c r="C329" s="6"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2942,31 +2945,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="4">
+      <c r="A333" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="8">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="3"/>
-      <c r="B334" s="4"/>
+      <c r="A334" s="7"/>
+      <c r="B334" s="8"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="5"/>
-      <c r="C336" s="5"/>
+      <c r="A336" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="3"/>
+      <c r="C336" s="3"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="6" t="s">
+      <c r="A337" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="7"/>
-      <c r="C337" s="8"/>
+      <c r="B337" s="5"/>
+      <c r="C337" s="6"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -2999,31 +3002,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="4">
+      <c r="A341" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="8">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="3"/>
-      <c r="B342" s="4"/>
+      <c r="A342" s="7"/>
+      <c r="B342" s="8"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="5"/>
-      <c r="C344" s="5"/>
+      <c r="A344" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="3"/>
+      <c r="C344" s="3"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="6" t="s">
+      <c r="A345" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="7"/>
-      <c r="C345" s="8"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="6"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3056,31 +3059,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="4">
+      <c r="A349" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="8">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="3"/>
-      <c r="B350" s="4"/>
+      <c r="A350" s="7"/>
+      <c r="B350" s="8"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="5"/>
-      <c r="C352" s="5"/>
+      <c r="A352" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="3"/>
+      <c r="C352" s="3"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="6" t="s">
+      <c r="A353" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="7"/>
-      <c r="C353" s="8"/>
+      <c r="B353" s="5"/>
+      <c r="C353" s="6"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3113,31 +3116,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="4">
+      <c r="A357" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="8">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="3"/>
-      <c r="B358" s="4"/>
+      <c r="A358" s="7"/>
+      <c r="B358" s="8"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="5"/>
-      <c r="C360" s="5"/>
+      <c r="A360" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="3"/>
+      <c r="C360" s="3"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="6" t="s">
+      <c r="A361" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="7"/>
-      <c r="C361" s="8"/>
+      <c r="B361" s="5"/>
+      <c r="C361" s="6"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3170,31 +3173,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="4">
+      <c r="A365" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="8">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="3"/>
-      <c r="B366" s="4"/>
+      <c r="A366" s="7"/>
+      <c r="B366" s="8"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="5"/>
-      <c r="C368" s="5"/>
+      <c r="A368" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="3"/>
+      <c r="C368" s="3"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="6" t="s">
+      <c r="A369" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="7"/>
-      <c r="C369" s="8"/>
+      <c r="B369" s="5"/>
+      <c r="C369" s="6"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3227,31 +3230,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="4">
+      <c r="A373" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="8">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="3"/>
-      <c r="B374" s="4"/>
+      <c r="A374" s="7"/>
+      <c r="B374" s="8"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="5"/>
-      <c r="C376" s="5"/>
+      <c r="A376" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="3"/>
+      <c r="C376" s="3"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="6" t="s">
+      <c r="A377" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="7"/>
-      <c r="C377" s="8"/>
+      <c r="B377" s="5"/>
+      <c r="C377" s="6"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3284,17 +3287,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="4">
+      <c r="A381" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="8">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="3"/>
-      <c r="B382" s="4"/>
+      <c r="A382" s="7"/>
+      <c r="B382" s="8"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3305,18 +3308,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="5"/>
-      <c r="C385" s="5"/>
+      <c r="A385" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="3"/>
+      <c r="C385" s="3"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="6" t="s">
+      <c r="A386" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="7"/>
-      <c r="C386" s="8"/>
+      <c r="B386" s="5"/>
+      <c r="C386" s="6"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3349,31 +3352,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="4">
+      <c r="A390" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="8">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="3"/>
-      <c r="B391" s="4"/>
+      <c r="A391" s="7"/>
+      <c r="B391" s="8"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="5"/>
-      <c r="C393" s="5"/>
+      <c r="A393" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="3"/>
+      <c r="C393" s="3"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="6" t="s">
+      <c r="A394" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="7"/>
-      <c r="C394" s="8"/>
+      <c r="B394" s="5"/>
+      <c r="C394" s="6"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3406,31 +3409,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="4">
+      <c r="A398" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="8">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="3"/>
-      <c r="B399" s="4"/>
+      <c r="A399" s="7"/>
+      <c r="B399" s="8"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="5"/>
-      <c r="C401" s="5"/>
+      <c r="A401" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="3"/>
+      <c r="C401" s="3"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="6" t="s">
+      <c r="A402" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="7"/>
-      <c r="C402" s="8"/>
+      <c r="B402" s="5"/>
+      <c r="C402" s="6"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3463,31 +3466,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="4">
+      <c r="A406" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="8">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="3"/>
-      <c r="B407" s="4"/>
+      <c r="A407" s="7"/>
+      <c r="B407" s="8"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="5"/>
-      <c r="C409" s="5"/>
+      <c r="A409" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="3"/>
+      <c r="C409" s="3"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="6" t="s">
+      <c r="A410" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="7"/>
-      <c r="C410" s="8"/>
+      <c r="B410" s="5"/>
+      <c r="C410" s="6"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3520,31 +3523,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="4">
+      <c r="A414" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="8">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="3"/>
-      <c r="B415" s="4"/>
+      <c r="A415" s="7"/>
+      <c r="B415" s="8"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="5"/>
-      <c r="C417" s="5"/>
+      <c r="A417" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="3"/>
+      <c r="C417" s="3"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="6" t="s">
+      <c r="A418" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="7"/>
-      <c r="C418" s="8"/>
+      <c r="B418" s="5"/>
+      <c r="C418" s="6"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3577,31 +3580,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="4">
+      <c r="A422" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="8">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="3"/>
-      <c r="B423" s="4"/>
+      <c r="A423" s="7"/>
+      <c r="B423" s="8"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="5"/>
-      <c r="C425" s="5"/>
+      <c r="A425" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="6" t="s">
+      <c r="A426" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="7"/>
-      <c r="C426" s="8"/>
+      <c r="B426" s="5"/>
+      <c r="C426" s="6"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3634,31 +3637,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="4">
+      <c r="A430" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="8">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="3"/>
-      <c r="B431" s="4"/>
+      <c r="A431" s="7"/>
+      <c r="B431" s="8"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="5"/>
-      <c r="C433" s="5"/>
+      <c r="A433" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="3"/>
+      <c r="C433" s="3"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="6" t="s">
+      <c r="A434" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="7"/>
-      <c r="C434" s="8"/>
+      <c r="B434" s="5"/>
+      <c r="C434" s="6"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3691,17 +3694,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="4">
+      <c r="A438" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="8">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="3"/>
-      <c r="B439" s="4"/>
+      <c r="A439" s="7"/>
+      <c r="B439" s="8"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3712,18 +3715,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="5"/>
-      <c r="C442" s="5"/>
+      <c r="A442" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="3"/>
+      <c r="C442" s="3"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="6" t="s">
+      <c r="A443" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="7"/>
-      <c r="C443" s="8"/>
+      <c r="B443" s="5"/>
+      <c r="C443" s="6"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3756,31 +3759,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="4">
+      <c r="A447" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="8">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="3"/>
-      <c r="B448" s="4"/>
+      <c r="A448" s="7"/>
+      <c r="B448" s="8"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="5"/>
-      <c r="C450" s="5"/>
+      <c r="A450" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="3"/>
+      <c r="C450" s="3"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="6" t="s">
+      <c r="A451" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="7"/>
-      <c r="C451" s="8"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="6"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3813,31 +3816,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="4">
+      <c r="A455" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="8">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="3"/>
-      <c r="B456" s="4"/>
+      <c r="A456" s="7"/>
+      <c r="B456" s="8"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="5"/>
-      <c r="C458" s="5"/>
+      <c r="A458" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="3"/>
+      <c r="C458" s="3"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="6" t="s">
+      <c r="A459" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="7"/>
-      <c r="C459" s="8"/>
+      <c r="B459" s="5"/>
+      <c r="C459" s="6"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3870,31 +3873,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="4">
+      <c r="A463" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="8">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="3"/>
-      <c r="B464" s="4"/>
+      <c r="A464" s="7"/>
+      <c r="B464" s="8"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="5"/>
-      <c r="C466" s="5"/>
+      <c r="A466" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="3"/>
+      <c r="C466" s="3"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="6" t="s">
+      <c r="A467" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="7"/>
-      <c r="C467" s="8"/>
+      <c r="B467" s="5"/>
+      <c r="C467" s="6"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3927,31 +3930,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="4">
+      <c r="A471" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="8">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="3"/>
-      <c r="B472" s="4"/>
+      <c r="A472" s="7"/>
+      <c r="B472" s="8"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="5"/>
-      <c r="C474" s="5"/>
+      <c r="A474" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="3"/>
+      <c r="C474" s="3"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="6" t="s">
+      <c r="A475" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="7"/>
-      <c r="C475" s="8"/>
+      <c r="B475" s="5"/>
+      <c r="C475" s="6"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3984,31 +3987,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="4">
+      <c r="A479" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="8">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="3"/>
-      <c r="B480" s="4"/>
+      <c r="A480" s="7"/>
+      <c r="B480" s="8"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="5"/>
-      <c r="C482" s="5"/>
+      <c r="A482" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="3"/>
+      <c r="C482" s="3"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="6" t="s">
+      <c r="A483" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="7"/>
-      <c r="C483" s="8"/>
+      <c r="B483" s="5"/>
+      <c r="C483" s="6"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4041,31 +4044,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="4">
+      <c r="A487" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="8">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="3"/>
-      <c r="B488" s="4"/>
+      <c r="A488" s="7"/>
+      <c r="B488" s="8"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="5"/>
-      <c r="C490" s="5"/>
+      <c r="A490" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="3"/>
+      <c r="C490" s="3"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="6" t="s">
+      <c r="A491" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="7"/>
-      <c r="C491" s="8"/>
+      <c r="B491" s="5"/>
+      <c r="C491" s="6"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4098,17 +4101,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="4">
+      <c r="A495" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="8">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="3"/>
-      <c r="B496" s="4"/>
+      <c r="A496" s="7"/>
+      <c r="B496" s="8"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4119,18 +4122,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="5"/>
-      <c r="C499" s="5"/>
+      <c r="A499" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="3"/>
+      <c r="C499" s="3"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="6" t="s">
+      <c r="A500" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="7"/>
-      <c r="C500" s="8"/>
+      <c r="B500" s="5"/>
+      <c r="C500" s="6"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4163,31 +4166,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="4">
+      <c r="A504" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="8">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="3"/>
-      <c r="B505" s="4"/>
+      <c r="A505" s="7"/>
+      <c r="B505" s="8"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="5"/>
-      <c r="C507" s="5"/>
+      <c r="A507" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="3"/>
+      <c r="C507" s="3"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="6" t="s">
+      <c r="A508" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="7"/>
-      <c r="C508" s="8"/>
+      <c r="B508" s="5"/>
+      <c r="C508" s="6"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4220,31 +4223,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="4">
+      <c r="A512" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="8">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="3"/>
-      <c r="B513" s="4"/>
+      <c r="A513" s="7"/>
+      <c r="B513" s="8"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="5"/>
-      <c r="C515" s="5"/>
+      <c r="A515" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="3"/>
+      <c r="C515" s="3"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="6" t="s">
+      <c r="A516" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="7"/>
-      <c r="C516" s="8"/>
+      <c r="B516" s="5"/>
+      <c r="C516" s="6"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4277,31 +4280,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="4">
+      <c r="A520" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="8">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="3"/>
-      <c r="B521" s="4"/>
+      <c r="A521" s="7"/>
+      <c r="B521" s="8"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="5"/>
-      <c r="C523" s="5"/>
+      <c r="A523" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="3"/>
+      <c r="C523" s="3"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="6" t="s">
+      <c r="A524" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="7"/>
-      <c r="C524" s="8"/>
+      <c r="B524" s="5"/>
+      <c r="C524" s="6"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4334,31 +4337,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="4">
+      <c r="A528" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="8">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="3"/>
-      <c r="B529" s="4"/>
+      <c r="A529" s="7"/>
+      <c r="B529" s="8"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="5"/>
-      <c r="C531" s="5"/>
+      <c r="A531" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="3"/>
+      <c r="C531" s="3"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="6" t="s">
+      <c r="A532" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="7"/>
-      <c r="C532" s="8"/>
+      <c r="B532" s="5"/>
+      <c r="C532" s="6"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4391,31 +4394,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="4">
+      <c r="A536" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="8">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="3"/>
-      <c r="B537" s="4"/>
+      <c r="A537" s="7"/>
+      <c r="B537" s="8"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="5"/>
-      <c r="C539" s="5"/>
+      <c r="A539" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="3"/>
+      <c r="C539" s="3"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="6" t="s">
+      <c r="A540" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="7"/>
-      <c r="C540" s="8"/>
+      <c r="B540" s="5"/>
+      <c r="C540" s="6"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4448,31 +4451,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="4">
+      <c r="A544" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="8">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="3"/>
-      <c r="B545" s="4"/>
+      <c r="A545" s="7"/>
+      <c r="B545" s="8"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="5"/>
-      <c r="C547" s="5"/>
+      <c r="A547" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="3"/>
+      <c r="C547" s="3"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="6" t="s">
+      <c r="A548" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="7"/>
-      <c r="C548" s="8"/>
+      <c r="B548" s="5"/>
+      <c r="C548" s="6"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4505,17 +4508,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="4">
+      <c r="A552" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="8">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="3"/>
-      <c r="B553" s="4"/>
+      <c r="A553" s="7"/>
+      <c r="B553" s="8"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4526,18 +4529,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="5"/>
-      <c r="C556" s="5"/>
+      <c r="A556" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="3"/>
+      <c r="C556" s="3"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="6" t="s">
+      <c r="A557" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="7"/>
-      <c r="C557" s="8"/>
+      <c r="B557" s="5"/>
+      <c r="C557" s="6"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4570,31 +4573,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="4">
+      <c r="A561" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="8">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="3"/>
-      <c r="B562" s="4"/>
+      <c r="A562" s="7"/>
+      <c r="B562" s="8"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="5"/>
-      <c r="C564" s="5"/>
+      <c r="A564" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="3"/>
+      <c r="C564" s="3"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="6" t="s">
+      <c r="A565" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="7"/>
-      <c r="C565" s="8"/>
+      <c r="B565" s="5"/>
+      <c r="C565" s="6"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4627,31 +4630,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="4">
+      <c r="A569" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="8">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="3"/>
-      <c r="B570" s="4"/>
+      <c r="A570" s="7"/>
+      <c r="B570" s="8"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="5"/>
-      <c r="C572" s="5"/>
+      <c r="A572" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="3"/>
+      <c r="C572" s="3"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="6" t="s">
+      <c r="A573" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="7"/>
-      <c r="C573" s="8"/>
+      <c r="B573" s="5"/>
+      <c r="C573" s="6"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4684,31 +4687,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="4">
+      <c r="A577" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="8">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="3"/>
-      <c r="B578" s="4"/>
+      <c r="A578" s="7"/>
+      <c r="B578" s="8"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="5"/>
-      <c r="C580" s="5"/>
+      <c r="A580" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="3"/>
+      <c r="C580" s="3"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="6" t="s">
+      <c r="A581" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="7"/>
-      <c r="C581" s="8"/>
+      <c r="B581" s="5"/>
+      <c r="C581" s="6"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4741,17 +4744,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="4">
+      <c r="A585" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="8">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="3"/>
-      <c r="B586" s="4"/>
+      <c r="A586" s="7"/>
+      <c r="B586" s="8"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4762,18 +4765,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="5"/>
-      <c r="C589" s="5"/>
+      <c r="A589" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="3"/>
+      <c r="C589" s="3"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="6" t="s">
+      <c r="A590" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="7"/>
-      <c r="C590" s="8"/>
+      <c r="B590" s="5"/>
+      <c r="C590" s="6"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4806,31 +4809,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="4">
+      <c r="A594" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="8">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="3"/>
-      <c r="B595" s="4"/>
+      <c r="A595" s="7"/>
+      <c r="B595" s="8"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="5"/>
-      <c r="C597" s="5"/>
+      <c r="A597" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="3"/>
+      <c r="C597" s="3"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="6" t="s">
+      <c r="A598" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="7"/>
-      <c r="C598" s="8"/>
+      <c r="B598" s="5"/>
+      <c r="C598" s="6"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4863,31 +4866,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="4">
+      <c r="A602" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="8">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="3"/>
-      <c r="B603" s="4"/>
+      <c r="A603" s="7"/>
+      <c r="B603" s="8"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="5"/>
-      <c r="C605" s="5"/>
+      <c r="A605" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="3"/>
+      <c r="C605" s="3"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="6" t="s">
+      <c r="A606" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="7"/>
-      <c r="C606" s="8"/>
+      <c r="B606" s="5"/>
+      <c r="C606" s="6"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4920,31 +4923,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="4">
+      <c r="A610" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="8">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="3"/>
-      <c r="B611" s="4"/>
+      <c r="A611" s="7"/>
+      <c r="B611" s="8"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="5"/>
-      <c r="C613" s="5"/>
+      <c r="A613" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="3"/>
+      <c r="C613" s="3"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="6" t="s">
+      <c r="A614" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="7"/>
-      <c r="C614" s="8"/>
+      <c r="B614" s="5"/>
+      <c r="C614" s="6"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4977,31 +4980,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="4">
+      <c r="A618" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="8">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="3"/>
-      <c r="B619" s="4"/>
+      <c r="A619" s="7"/>
+      <c r="B619" s="8"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="5"/>
-      <c r="C621" s="5"/>
+      <c r="A621" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="3"/>
+      <c r="C621" s="3"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="6" t="s">
+      <c r="A622" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="7"/>
-      <c r="C622" s="8"/>
+      <c r="B622" s="5"/>
+      <c r="C622" s="6"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5034,31 +5037,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="4">
+      <c r="A626" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="8">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="3"/>
-      <c r="B627" s="4"/>
+      <c r="A627" s="7"/>
+      <c r="B627" s="8"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="5"/>
-      <c r="C629" s="5"/>
+      <c r="A629" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="3"/>
+      <c r="C629" s="3"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="6" t="s">
+      <c r="A630" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="7"/>
-      <c r="C630" s="8"/>
+      <c r="B630" s="5"/>
+      <c r="C630" s="6"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5091,31 +5094,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="4">
+      <c r="A634" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="8">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="3"/>
-      <c r="B635" s="4"/>
+      <c r="A635" s="7"/>
+      <c r="B635" s="8"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="5"/>
-      <c r="C637" s="5"/>
+      <c r="A637" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="3"/>
+      <c r="C637" s="3"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="6" t="s">
+      <c r="A638" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="7"/>
-      <c r="C638" s="8"/>
+      <c r="B638" s="5"/>
+      <c r="C638" s="6"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5148,17 +5151,17 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="4">
+      <c r="A642" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="8">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="3"/>
-      <c r="B643" s="4"/>
+      <c r="A643" s="7"/>
+      <c r="B643" s="8"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
@@ -5169,18 +5172,18 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="5"/>
-      <c r="C646" s="5"/>
+      <c r="A646" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="3"/>
+      <c r="C646" s="3"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="6" t="s">
+      <c r="A647" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="7"/>
-      <c r="C647" s="8"/>
+      <c r="B647" s="5"/>
+      <c r="C647" s="6"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5213,31 +5216,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="4">
+      <c r="A651" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="8">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="3"/>
-      <c r="B652" s="4"/>
+      <c r="A652" s="7"/>
+      <c r="B652" s="8"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="5"/>
-      <c r="C654" s="5"/>
+      <c r="A654" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="3"/>
+      <c r="C654" s="3"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="6" t="s">
+      <c r="A655" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="7"/>
-      <c r="C655" s="8"/>
+      <c r="B655" s="5"/>
+      <c r="C655" s="6"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5270,31 +5273,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="4">
+      <c r="A659" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="8">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="3"/>
-      <c r="B660" s="4"/>
+      <c r="A660" s="7"/>
+      <c r="B660" s="8"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="5"/>
-      <c r="C662" s="5"/>
+      <c r="A662" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="3"/>
+      <c r="C662" s="3"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="6" t="s">
+      <c r="A663" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="7"/>
-      <c r="C663" s="8"/>
+      <c r="B663" s="5"/>
+      <c r="C663" s="6"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5327,31 +5330,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="4">
+      <c r="A667" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="8">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="3"/>
-      <c r="B668" s="4"/>
+      <c r="A668" s="7"/>
+      <c r="B668" s="8"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="5"/>
-      <c r="C670" s="5"/>
+      <c r="A670" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="3"/>
+      <c r="C670" s="3"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="6" t="s">
+      <c r="A671" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="7"/>
-      <c r="C671" s="8"/>
+      <c r="B671" s="5"/>
+      <c r="C671" s="6"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5384,31 +5387,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="4">
+      <c r="A675" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="8">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="3"/>
-      <c r="B676" s="4"/>
+      <c r="A676" s="7"/>
+      <c r="B676" s="8"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="5"/>
-      <c r="C678" s="5"/>
+      <c r="A678" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="3"/>
+      <c r="C678" s="3"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="6" t="s">
+      <c r="A679" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="7"/>
-      <c r="C679" s="8"/>
+      <c r="B679" s="5"/>
+      <c r="C679" s="6"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5441,31 +5444,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="4">
+      <c r="A683" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="8">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="3"/>
-      <c r="B684" s="4"/>
+      <c r="A684" s="7"/>
+      <c r="B684" s="8"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="5"/>
-      <c r="C686" s="5"/>
+      <c r="A686" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="3"/>
+      <c r="C686" s="3"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="6" t="s">
+      <c r="A687" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="7"/>
-      <c r="C687" s="8"/>
+      <c r="B687" s="5"/>
+      <c r="C687" s="6"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5498,31 +5501,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="4">
+      <c r="A691" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="8">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="3"/>
-      <c r="B692" s="4"/>
+      <c r="A692" s="7"/>
+      <c r="B692" s="8"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="5"/>
-      <c r="C694" s="5"/>
+      <c r="A694" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="3"/>
+      <c r="C694" s="3"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="6" t="s">
+      <c r="A695" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="7"/>
-      <c r="C695" s="8"/>
+      <c r="B695" s="5"/>
+      <c r="C695" s="6"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5555,31 +5558,31 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="4">
+      <c r="A699" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="8">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="3"/>
-      <c r="B700" s="4"/>
+      <c r="A700" s="7"/>
+      <c r="B700" s="8"/>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B702" s="5"/>
-      <c r="C702" s="5"/>
+      <c r="A702" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B702" s="3"/>
+      <c r="C702" s="3"/>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="6" t="s">
+      <c r="A703" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B703" s="7"/>
-      <c r="C703" s="8"/>
+      <c r="B703" s="5"/>
+      <c r="C703" s="6"/>
     </row>
     <row r="704" spans="1:3">
       <c r="A704" s="1" t="s">
@@ -5612,17 +5615,17 @@
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B707" s="4">
+      <c r="A707" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="8">
         <f>B705-B706</f>
         <v>448</v>
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="3"/>
-      <c r="B708" s="4"/>
+      <c r="A708" s="7"/>
+      <c r="B708" s="8"/>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" s="1" t="s">
@@ -5633,18 +5636,18 @@
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B711" s="5"/>
-      <c r="C711" s="5"/>
+      <c r="A711" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="3"/>
+      <c r="C711" s="3"/>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="6" t="s">
+      <c r="A712" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B712" s="7"/>
-      <c r="C712" s="8"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="6"/>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" s="1" t="s">
@@ -5677,31 +5680,31 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B716" s="4">
+      <c r="A716" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="8">
         <f>B714-B715</f>
         <v>27</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="3"/>
-      <c r="B717" s="4"/>
+      <c r="A717" s="7"/>
+      <c r="B717" s="8"/>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B719" s="5"/>
-      <c r="C719" s="5"/>
+      <c r="A719" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="3"/>
+      <c r="C719" s="3"/>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="6" t="s">
+      <c r="A720" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B720" s="7"/>
-      <c r="C720" s="8"/>
+      <c r="B720" s="5"/>
+      <c r="C720" s="6"/>
     </row>
     <row r="721" spans="1:3">
       <c r="A721" s="1" t="s">
@@ -5734,31 +5737,31 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B724" s="4">
+      <c r="A724" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="8">
         <f>B722-B723</f>
         <v>386</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="3"/>
-      <c r="B725" s="4"/>
+      <c r="A725" s="7"/>
+      <c r="B725" s="8"/>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B727" s="5"/>
-      <c r="C727" s="5"/>
+      <c r="A727" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="3"/>
+      <c r="C727" s="3"/>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="6" t="s">
+      <c r="A728" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B728" s="7"/>
-      <c r="C728" s="8"/>
+      <c r="B728" s="5"/>
+      <c r="C728" s="6"/>
     </row>
     <row r="729" spans="1:3">
       <c r="A729" s="1" t="s">
@@ -5791,31 +5794,31 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B732" s="4">
+      <c r="A732" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="8">
         <f>B730-B731</f>
         <v>1256</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="3"/>
-      <c r="B733" s="4"/>
+      <c r="A733" s="7"/>
+      <c r="B733" s="8"/>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B735" s="5"/>
-      <c r="C735" s="5"/>
+      <c r="A735" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="3"/>
+      <c r="C735" s="3"/>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="6" t="s">
+      <c r="A736" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B736" s="7"/>
-      <c r="C736" s="8"/>
+      <c r="B736" s="5"/>
+      <c r="C736" s="6"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="1" t="s">
@@ -5848,31 +5851,31 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B740" s="4">
+      <c r="A740" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="8">
         <f>B738-B739</f>
         <v>227</v>
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="3"/>
-      <c r="B741" s="4"/>
+      <c r="A741" s="7"/>
+      <c r="B741" s="8"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B743" s="5"/>
-      <c r="C743" s="5"/>
+      <c r="A743" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="3"/>
+      <c r="C743" s="3"/>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="6" t="s">
+      <c r="A744" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B744" s="7"/>
-      <c r="C744" s="8"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="6"/>
     </row>
     <row r="745" spans="1:3">
       <c r="A745" s="1" t="s">
@@ -5905,31 +5908,31 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B748" s="4">
+      <c r="A748" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="8">
         <f>B746-B747</f>
         <v>961</v>
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="3"/>
-      <c r="B749" s="4"/>
+      <c r="A749" s="7"/>
+      <c r="B749" s="8"/>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B751" s="5"/>
-      <c r="C751" s="5"/>
+      <c r="A751" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="3"/>
+      <c r="C751" s="3"/>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="6" t="s">
+      <c r="A752" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B752" s="7"/>
-      <c r="C752" s="8"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="6"/>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" s="1" t="s">
@@ -5962,31 +5965,31 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="4">
+      <c r="A756" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="8">
         <f>B754-B755</f>
         <v>6</v>
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="3"/>
-      <c r="B757" s="4"/>
+      <c r="A757" s="7"/>
+      <c r="B757" s="8"/>
     </row>
     <row r="759" spans="1:3">
-      <c r="A759" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B759" s="5"/>
-      <c r="C759" s="5"/>
+      <c r="A759" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B759" s="3"/>
+      <c r="C759" s="3"/>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="6" t="s">
+      <c r="A760" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B760" s="7"/>
-      <c r="C760" s="8"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="6"/>
     </row>
     <row r="761" spans="1:3">
       <c r="A761" s="1" t="s">
@@ -6019,31 +6022,31 @@
       </c>
     </row>
     <row r="764" spans="1:3">
-      <c r="A764" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B764" s="4">
+      <c r="A764" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764" s="8">
         <f>B762-B763</f>
         <v>616</v>
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="3"/>
-      <c r="B765" s="4"/>
+      <c r="A765" s="7"/>
+      <c r="B765" s="8"/>
     </row>
     <row r="767" spans="1:3">
-      <c r="A767" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B767" s="5"/>
-      <c r="C767" s="5"/>
+      <c r="A767" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B767" s="3"/>
+      <c r="C767" s="3"/>
     </row>
     <row r="768" spans="1:3">
-      <c r="A768" s="6" t="s">
+      <c r="A768" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B768" s="7"/>
-      <c r="C768" s="8"/>
+      <c r="B768" s="5"/>
+      <c r="C768" s="6"/>
     </row>
     <row r="769" spans="1:3">
       <c r="A769" s="1" t="s">
@@ -6076,17 +6079,17 @@
       </c>
     </row>
     <row r="772" spans="1:3">
-      <c r="A772" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B772" s="4">
+      <c r="A772" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B772" s="8">
         <f>B770-B771</f>
         <v>379</v>
       </c>
     </row>
     <row r="773" spans="1:3">
-      <c r="A773" s="3"/>
-      <c r="B773" s="4"/>
+      <c r="A773" s="7"/>
+      <c r="B773" s="8"/>
     </row>
     <row r="774" spans="1:3">
       <c r="A774" s="1" t="s">
@@ -6097,18 +6100,18 @@
       </c>
     </row>
     <row r="776" spans="1:3">
-      <c r="A776" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B776" s="5"/>
-      <c r="C776" s="5"/>
+      <c r="A776" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B776" s="3"/>
+      <c r="C776" s="3"/>
     </row>
     <row r="777" spans="1:3">
-      <c r="A777" s="6" t="s">
+      <c r="A777" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B777" s="7"/>
-      <c r="C777" s="8"/>
+      <c r="B777" s="5"/>
+      <c r="C777" s="6"/>
     </row>
     <row r="778" spans="1:3">
       <c r="A778" s="1" t="s">
@@ -6141,31 +6144,31 @@
       </c>
     </row>
     <row r="781" spans="1:3">
-      <c r="A781" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B781" s="4">
+      <c r="A781" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781" s="8">
         <f>B779-B780</f>
         <v>276</v>
       </c>
     </row>
     <row r="782" spans="1:3">
-      <c r="A782" s="3"/>
-      <c r="B782" s="4"/>
+      <c r="A782" s="7"/>
+      <c r="B782" s="8"/>
     </row>
     <row r="784" spans="1:3">
-      <c r="A784" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B784" s="5"/>
-      <c r="C784" s="5"/>
+      <c r="A784" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B784" s="3"/>
+      <c r="C784" s="3"/>
     </row>
     <row r="785" spans="1:3">
-      <c r="A785" s="6" t="s">
+      <c r="A785" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B785" s="7"/>
-      <c r="C785" s="8"/>
+      <c r="B785" s="5"/>
+      <c r="C785" s="6"/>
     </row>
     <row r="786" spans="1:3">
       <c r="A786" s="1" t="s">
@@ -6198,31 +6201,31 @@
       </c>
     </row>
     <row r="789" spans="1:3">
-      <c r="A789" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B789" s="4">
+      <c r="A789" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789" s="8">
         <f>B787-B788</f>
         <v>596</v>
       </c>
     </row>
     <row r="790" spans="1:3">
-      <c r="A790" s="3"/>
-      <c r="B790" s="4"/>
+      <c r="A790" s="7"/>
+      <c r="B790" s="8"/>
     </row>
     <row r="792" spans="1:3">
-      <c r="A792" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B792" s="5"/>
-      <c r="C792" s="5"/>
+      <c r="A792" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B792" s="3"/>
+      <c r="C792" s="3"/>
     </row>
     <row r="793" spans="1:3">
-      <c r="A793" s="6" t="s">
+      <c r="A793" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B793" s="7"/>
-      <c r="C793" s="8"/>
+      <c r="B793" s="5"/>
+      <c r="C793" s="6"/>
     </row>
     <row r="794" spans="1:3">
       <c r="A794" s="1" t="s">
@@ -6255,31 +6258,31 @@
       </c>
     </row>
     <row r="797" spans="1:3">
-      <c r="A797" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B797" s="4">
+      <c r="A797" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797" s="8">
         <f>B795-B796</f>
         <v>250</v>
       </c>
     </row>
     <row r="798" spans="1:3">
-      <c r="A798" s="3"/>
-      <c r="B798" s="4"/>
+      <c r="A798" s="7"/>
+      <c r="B798" s="8"/>
     </row>
     <row r="800" spans="1:3">
-      <c r="A800" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B800" s="5"/>
-      <c r="C800" s="5"/>
+      <c r="A800" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B800" s="3"/>
+      <c r="C800" s="3"/>
     </row>
     <row r="801" spans="1:3">
-      <c r="A801" s="6" t="s">
+      <c r="A801" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B801" s="7"/>
-      <c r="C801" s="8"/>
+      <c r="B801" s="5"/>
+      <c r="C801" s="6"/>
     </row>
     <row r="802" spans="1:3">
       <c r="A802" s="1" t="s">
@@ -6312,31 +6315,31 @@
       </c>
     </row>
     <row r="805" spans="1:3">
-      <c r="A805" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B805" s="4">
+      <c r="A805" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805" s="8">
         <f>B803-B804</f>
         <v>378</v>
       </c>
     </row>
     <row r="806" spans="1:3">
-      <c r="A806" s="3"/>
-      <c r="B806" s="4"/>
+      <c r="A806" s="7"/>
+      <c r="B806" s="8"/>
     </row>
     <row r="808" spans="1:3">
-      <c r="A808" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B808" s="5"/>
-      <c r="C808" s="5"/>
+      <c r="A808" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B808" s="3"/>
+      <c r="C808" s="3"/>
     </row>
     <row r="809" spans="1:3">
-      <c r="A809" s="6" t="s">
+      <c r="A809" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B809" s="7"/>
-      <c r="C809" s="8"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="6"/>
     </row>
     <row r="810" spans="1:3">
       <c r="A810" s="1" t="s">
@@ -6369,31 +6372,31 @@
       </c>
     </row>
     <row r="813" spans="1:3">
-      <c r="A813" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B813" s="4">
+      <c r="A813" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813" s="8">
         <f>B811-B812</f>
         <v>900</v>
       </c>
     </row>
     <row r="814" spans="1:3">
-      <c r="A814" s="3"/>
-      <c r="B814" s="4"/>
+      <c r="A814" s="7"/>
+      <c r="B814" s="8"/>
     </row>
     <row r="816" spans="1:3">
-      <c r="A816" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B816" s="5"/>
-      <c r="C816" s="5"/>
+      <c r="A816" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B816" s="3"/>
+      <c r="C816" s="3"/>
     </row>
     <row r="817" spans="1:3">
-      <c r="A817" s="6" t="s">
+      <c r="A817" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B817" s="7"/>
-      <c r="C817" s="8"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="6"/>
     </row>
     <row r="818" spans="1:3">
       <c r="A818" s="1" t="s">
@@ -6426,31 +6429,31 @@
       </c>
     </row>
     <row r="821" spans="1:3">
-      <c r="A821" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B821" s="4">
+      <c r="A821" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B821" s="8">
         <f>B819-B820</f>
         <v>74</v>
       </c>
     </row>
     <row r="822" spans="1:3">
-      <c r="A822" s="3"/>
-      <c r="B822" s="4"/>
+      <c r="A822" s="7"/>
+      <c r="B822" s="8"/>
     </row>
     <row r="824" spans="1:3">
-      <c r="A824" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B824" s="5"/>
-      <c r="C824" s="5"/>
+      <c r="A824" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B824" s="3"/>
+      <c r="C824" s="3"/>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825" s="6" t="s">
+      <c r="A825" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B825" s="7"/>
-      <c r="C825" s="8"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="6"/>
     </row>
     <row r="826" spans="1:3">
       <c r="A826" s="1" t="s">
@@ -6483,31 +6486,31 @@
       </c>
     </row>
     <row r="829" spans="1:3">
-      <c r="A829" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B829" s="4">
+      <c r="A829" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B829" s="8">
         <f>B827-B828</f>
         <v>0</v>
       </c>
     </row>
     <row r="830" spans="1:3">
-      <c r="A830" s="3"/>
-      <c r="B830" s="4"/>
+      <c r="A830" s="7"/>
+      <c r="B830" s="8"/>
     </row>
     <row r="832" spans="1:3">
-      <c r="A832" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B832" s="5"/>
-      <c r="C832" s="5"/>
+      <c r="A832" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B832" s="3"/>
+      <c r="C832" s="3"/>
     </row>
     <row r="833" spans="1:3">
-      <c r="A833" s="6" t="s">
+      <c r="A833" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B833" s="7"/>
-      <c r="C833" s="8"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="6"/>
     </row>
     <row r="834" spans="1:3">
       <c r="A834" s="1" t="s">
@@ -6540,17 +6543,17 @@
       </c>
     </row>
     <row r="837" spans="1:3">
-      <c r="A837" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B837" s="4">
+      <c r="A837" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B837" s="8">
         <f>B835-B836</f>
         <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:3">
-      <c r="A838" s="3"/>
-      <c r="B838" s="4"/>
+      <c r="A838" s="7"/>
+      <c r="B838" s="8"/>
     </row>
     <row r="839" spans="1:3">
       <c r="A839" s="1" t="s">
@@ -6561,18 +6564,18 @@
       </c>
     </row>
     <row r="841" spans="1:3">
-      <c r="A841" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B841" s="5"/>
-      <c r="C841" s="5"/>
+      <c r="A841" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B841" s="3"/>
+      <c r="C841" s="3"/>
     </row>
     <row r="842" spans="1:3">
-      <c r="A842" s="6" t="s">
+      <c r="A842" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B842" s="7"/>
-      <c r="C842" s="8"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="6"/>
     </row>
     <row r="843" spans="1:3">
       <c r="A843" s="1" t="s">
@@ -6605,31 +6608,31 @@
       </c>
     </row>
     <row r="846" spans="1:3">
-      <c r="A846" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B846" s="4">
+      <c r="A846" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846" s="8">
         <f>B844-B845</f>
         <v>717</v>
       </c>
     </row>
     <row r="847" spans="1:3">
-      <c r="A847" s="3"/>
-      <c r="B847" s="4"/>
+      <c r="A847" s="7"/>
+      <c r="B847" s="8"/>
     </row>
     <row r="849" spans="1:3">
-      <c r="A849" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B849" s="5"/>
-      <c r="C849" s="5"/>
+      <c r="A849" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B849" s="3"/>
+      <c r="C849" s="3"/>
     </row>
     <row r="850" spans="1:3">
-      <c r="A850" s="6" t="s">
+      <c r="A850" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B850" s="7"/>
-      <c r="C850" s="8"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="6"/>
     </row>
     <row r="851" spans="1:3">
       <c r="A851" s="1" t="s">
@@ -6662,31 +6665,31 @@
       </c>
     </row>
     <row r="854" spans="1:3">
-      <c r="A854" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B854" s="4">
+      <c r="A854" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854" s="8">
         <f>B852-B853</f>
         <v>0</v>
       </c>
     </row>
     <row r="855" spans="1:3">
-      <c r="A855" s="3"/>
-      <c r="B855" s="4"/>
+      <c r="A855" s="7"/>
+      <c r="B855" s="8"/>
     </row>
     <row r="857" spans="1:3">
-      <c r="A857" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B857" s="5"/>
-      <c r="C857" s="5"/>
+      <c r="A857" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B857" s="3"/>
+      <c r="C857" s="3"/>
     </row>
     <row r="858" spans="1:3">
-      <c r="A858" s="6" t="s">
+      <c r="A858" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B858" s="7"/>
-      <c r="C858" s="8"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="6"/>
     </row>
     <row r="859" spans="1:3">
       <c r="A859" s="1" t="s">
@@ -6719,31 +6722,31 @@
       </c>
     </row>
     <row r="862" spans="1:3">
-      <c r="A862" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B862" s="4">
+      <c r="A862" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862" s="8">
         <f>B860-B861</f>
         <v>224</v>
       </c>
     </row>
     <row r="863" spans="1:3">
-      <c r="A863" s="3"/>
-      <c r="B863" s="4"/>
+      <c r="A863" s="7"/>
+      <c r="B863" s="8"/>
     </row>
     <row r="865" spans="1:3">
-      <c r="A865" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B865" s="5"/>
-      <c r="C865" s="5"/>
+      <c r="A865" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B865" s="3"/>
+      <c r="C865" s="3"/>
     </row>
     <row r="866" spans="1:3">
-      <c r="A866" s="6" t="s">
+      <c r="A866" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B866" s="7"/>
-      <c r="C866" s="8"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="6"/>
     </row>
     <row r="867" spans="1:3">
       <c r="A867" s="1" t="s">
@@ -6776,31 +6779,31 @@
       </c>
     </row>
     <row r="870" spans="1:3">
-      <c r="A870" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B870" s="4">
+      <c r="A870" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870" s="8">
         <f>B868-B869</f>
         <v>124</v>
       </c>
     </row>
     <row r="871" spans="1:3">
-      <c r="A871" s="3"/>
-      <c r="B871" s="4"/>
+      <c r="A871" s="7"/>
+      <c r="B871" s="8"/>
     </row>
     <row r="873" spans="1:3">
-      <c r="A873" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B873" s="5"/>
-      <c r="C873" s="5"/>
+      <c r="A873" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B873" s="3"/>
+      <c r="C873" s="3"/>
     </row>
     <row r="874" spans="1:3">
-      <c r="A874" s="6" t="s">
+      <c r="A874" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B874" s="7"/>
-      <c r="C874" s="8"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="6"/>
     </row>
     <row r="875" spans="1:3">
       <c r="A875" s="1" t="s">
@@ -6833,31 +6836,31 @@
       </c>
     </row>
     <row r="878" spans="1:3">
-      <c r="A878" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B878" s="4">
+      <c r="A878" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B878" s="8">
         <f>B876-B877</f>
         <v>449</v>
       </c>
     </row>
     <row r="879" spans="1:3">
-      <c r="A879" s="3"/>
-      <c r="B879" s="4"/>
+      <c r="A879" s="7"/>
+      <c r="B879" s="8"/>
     </row>
     <row r="881" spans="1:3">
-      <c r="A881" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B881" s="5"/>
-      <c r="C881" s="5"/>
+      <c r="A881" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B881" s="3"/>
+      <c r="C881" s="3"/>
     </row>
     <row r="882" spans="1:3">
-      <c r="A882" s="6" t="s">
+      <c r="A882" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B882" s="7"/>
-      <c r="C882" s="8"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="6"/>
     </row>
     <row r="883" spans="1:3">
       <c r="A883" s="1" t="s">
@@ -6890,31 +6893,31 @@
       </c>
     </row>
     <row r="886" spans="1:3">
-      <c r="A886" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B886" s="4">
+      <c r="A886" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B886" s="8">
         <f>B884-B885</f>
         <v>821</v>
       </c>
     </row>
     <row r="887" spans="1:3">
-      <c r="A887" s="3"/>
-      <c r="B887" s="4"/>
+      <c r="A887" s="7"/>
+      <c r="B887" s="8"/>
     </row>
     <row r="889" spans="1:3">
-      <c r="A889" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B889" s="5"/>
-      <c r="C889" s="5"/>
+      <c r="A889" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B889" s="3"/>
+      <c r="C889" s="3"/>
     </row>
     <row r="890" spans="1:3">
-      <c r="A890" s="6" t="s">
+      <c r="A890" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B890" s="7"/>
-      <c r="C890" s="8"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="6"/>
     </row>
     <row r="891" spans="1:3">
       <c r="A891" s="1" t="s">
@@ -6947,17 +6950,17 @@
       </c>
     </row>
     <row r="894" spans="1:3">
-      <c r="A894" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B894" s="4">
+      <c r="A894" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B894" s="8">
         <f>B892-B893</f>
         <v>31</v>
       </c>
     </row>
     <row r="895" spans="1:3">
-      <c r="A895" s="3"/>
-      <c r="B895" s="4"/>
+      <c r="A895" s="7"/>
+      <c r="B895" s="8"/>
     </row>
     <row r="896" spans="1:3">
       <c r="A896" s="1" t="s">
@@ -6968,18 +6971,18 @@
       </c>
     </row>
     <row r="898" spans="1:3">
-      <c r="A898" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B898" s="5"/>
-      <c r="C898" s="5"/>
+      <c r="A898" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B898" s="3"/>
+      <c r="C898" s="3"/>
     </row>
     <row r="899" spans="1:3">
-      <c r="A899" s="6" t="s">
+      <c r="A899" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B899" s="7"/>
-      <c r="C899" s="8"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="6"/>
     </row>
     <row r="900" spans="1:3">
       <c r="A900" s="1" t="s">
@@ -7012,31 +7015,31 @@
       </c>
     </row>
     <row r="903" spans="1:3">
-      <c r="A903" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B903" s="4">
+      <c r="A903" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B903" s="8">
         <f>B901-B902</f>
         <v>22</v>
       </c>
     </row>
     <row r="904" spans="1:3">
-      <c r="A904" s="3"/>
-      <c r="B904" s="4"/>
+      <c r="A904" s="7"/>
+      <c r="B904" s="8"/>
     </row>
     <row r="906" spans="1:3">
-      <c r="A906" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B906" s="5"/>
-      <c r="C906" s="5"/>
+      <c r="A906" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B906" s="3"/>
+      <c r="C906" s="3"/>
     </row>
     <row r="907" spans="1:3">
-      <c r="A907" s="6" t="s">
+      <c r="A907" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B907" s="7"/>
-      <c r="C907" s="8"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="6"/>
     </row>
     <row r="908" spans="1:3">
       <c r="A908" s="1" t="s">
@@ -7069,31 +7072,31 @@
       </c>
     </row>
     <row r="911" spans="1:3">
-      <c r="A911" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B911" s="4">
+      <c r="A911" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B911" s="8">
         <f>B909-B910</f>
         <v>75</v>
       </c>
     </row>
     <row r="912" spans="1:3">
-      <c r="A912" s="3"/>
-      <c r="B912" s="4"/>
+      <c r="A912" s="7"/>
+      <c r="B912" s="8"/>
     </row>
     <row r="914" spans="1:3">
-      <c r="A914" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B914" s="5"/>
-      <c r="C914" s="5"/>
+      <c r="A914" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B914" s="3"/>
+      <c r="C914" s="3"/>
     </row>
     <row r="915" spans="1:3">
-      <c r="A915" s="6" t="s">
+      <c r="A915" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B915" s="7"/>
-      <c r="C915" s="8"/>
+      <c r="B915" s="5"/>
+      <c r="C915" s="6"/>
     </row>
     <row r="916" spans="1:3">
       <c r="A916" s="1" t="s">
@@ -7126,31 +7129,31 @@
       </c>
     </row>
     <row r="919" spans="1:3">
-      <c r="A919" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B919" s="4">
+      <c r="A919" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B919" s="8">
         <f>B917-B918</f>
         <v>39</v>
       </c>
     </row>
     <row r="920" spans="1:3">
-      <c r="A920" s="3"/>
-      <c r="B920" s="4"/>
+      <c r="A920" s="7"/>
+      <c r="B920" s="8"/>
     </row>
     <row r="922" spans="1:3">
-      <c r="A922" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B922" s="5"/>
-      <c r="C922" s="5"/>
+      <c r="A922" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B922" s="3"/>
+      <c r="C922" s="3"/>
     </row>
     <row r="923" spans="1:3">
-      <c r="A923" s="6" t="s">
+      <c r="A923" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B923" s="7"/>
-      <c r="C923" s="8"/>
+      <c r="B923" s="5"/>
+      <c r="C923" s="6"/>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" s="1" t="s">
@@ -7183,31 +7186,31 @@
       </c>
     </row>
     <row r="927" spans="1:3">
-      <c r="A927" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B927" s="4">
+      <c r="A927" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B927" s="8">
         <f>B925-B926</f>
         <v>70</v>
       </c>
     </row>
     <row r="928" spans="1:3">
-      <c r="A928" s="3"/>
-      <c r="B928" s="4"/>
+      <c r="A928" s="7"/>
+      <c r="B928" s="8"/>
     </row>
     <row r="930" spans="1:3">
-      <c r="A930" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B930" s="5"/>
-      <c r="C930" s="5"/>
+      <c r="A930" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B930" s="3"/>
+      <c r="C930" s="3"/>
     </row>
     <row r="931" spans="1:3">
-      <c r="A931" s="6" t="s">
+      <c r="A931" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B931" s="7"/>
-      <c r="C931" s="8"/>
+      <c r="B931" s="5"/>
+      <c r="C931" s="6"/>
     </row>
     <row r="932" spans="1:3">
       <c r="A932" s="1" t="s">
@@ -7240,31 +7243,31 @@
       </c>
     </row>
     <row r="935" spans="1:3">
-      <c r="A935" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B935" s="4">
+      <c r="A935" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B935" s="8">
         <f>B933-B934</f>
         <v>0</v>
       </c>
     </row>
     <row r="936" spans="1:3">
-      <c r="A936" s="3"/>
-      <c r="B936" s="4"/>
+      <c r="A936" s="7"/>
+      <c r="B936" s="8"/>
     </row>
     <row r="938" spans="1:3">
-      <c r="A938" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B938" s="5"/>
-      <c r="C938" s="5"/>
+      <c r="A938" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B938" s="3"/>
+      <c r="C938" s="3"/>
     </row>
     <row r="939" spans="1:3">
-      <c r="A939" s="6" t="s">
+      <c r="A939" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B939" s="7"/>
-      <c r="C939" s="8"/>
+      <c r="B939" s="5"/>
+      <c r="C939" s="6"/>
     </row>
     <row r="940" spans="1:3">
       <c r="A940" s="1" t="s">
@@ -7297,17 +7300,17 @@
       </c>
     </row>
     <row r="943" spans="1:3">
-      <c r="A943" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B943" s="4">
+      <c r="A943" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B943" s="8">
         <f>B941-B942</f>
         <v>59</v>
       </c>
     </row>
     <row r="944" spans="1:3">
-      <c r="A944" s="3"/>
-      <c r="B944" s="4"/>
+      <c r="A944" s="7"/>
+      <c r="B944" s="8"/>
     </row>
     <row r="945" spans="1:3">
       <c r="A945" s="1" t="s">
@@ -7318,18 +7321,18 @@
       </c>
     </row>
     <row r="947" spans="1:3">
-      <c r="A947" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B947" s="5"/>
-      <c r="C947" s="5"/>
+      <c r="A947" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B947" s="3"/>
+      <c r="C947" s="3"/>
     </row>
     <row r="948" spans="1:3">
-      <c r="A948" s="6" t="s">
+      <c r="A948" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B948" s="7"/>
-      <c r="C948" s="8"/>
+      <c r="B948" s="5"/>
+      <c r="C948" s="6"/>
     </row>
     <row r="949" spans="1:3">
       <c r="A949" s="1" t="s">
@@ -7362,31 +7365,31 @@
       </c>
     </row>
     <row r="952" spans="1:3">
-      <c r="A952" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B952" s="4">
+      <c r="A952" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B952" s="8">
         <f>B950-B951</f>
         <v>1667</v>
       </c>
     </row>
     <row r="953" spans="1:3">
-      <c r="A953" s="3"/>
-      <c r="B953" s="4"/>
+      <c r="A953" s="7"/>
+      <c r="B953" s="8"/>
     </row>
     <row r="955" spans="1:3">
-      <c r="A955" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B955" s="5"/>
-      <c r="C955" s="5"/>
+      <c r="A955" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B955" s="3"/>
+      <c r="C955" s="3"/>
     </row>
     <row r="956" spans="1:3">
-      <c r="A956" s="6" t="s">
+      <c r="A956" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B956" s="7"/>
-      <c r="C956" s="8"/>
+      <c r="B956" s="5"/>
+      <c r="C956" s="6"/>
     </row>
     <row r="957" spans="1:3">
       <c r="A957" s="1" t="s">
@@ -7419,31 +7422,31 @@
       </c>
     </row>
     <row r="960" spans="1:3">
-      <c r="A960" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B960" s="4">
+      <c r="A960" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B960" s="8">
         <f>B958-B959</f>
         <v>61</v>
       </c>
     </row>
     <row r="961" spans="1:3">
-      <c r="A961" s="3"/>
-      <c r="B961" s="4"/>
+      <c r="A961" s="7"/>
+      <c r="B961" s="8"/>
     </row>
     <row r="963" spans="1:3">
-      <c r="A963" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B963" s="5"/>
-      <c r="C963" s="5"/>
+      <c r="A963" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B963" s="3"/>
+      <c r="C963" s="3"/>
     </row>
     <row r="964" spans="1:3">
-      <c r="A964" s="6" t="s">
+      <c r="A964" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B964" s="7"/>
-      <c r="C964" s="8"/>
+      <c r="B964" s="5"/>
+      <c r="C964" s="6"/>
     </row>
     <row r="965" spans="1:3">
       <c r="A965" s="1" t="s">
@@ -7476,31 +7479,31 @@
       </c>
     </row>
     <row r="968" spans="1:3">
-      <c r="A968" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B968" s="4">
+      <c r="A968" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B968" s="8">
         <f>B966-B967</f>
         <v>199</v>
       </c>
     </row>
     <row r="969" spans="1:3">
-      <c r="A969" s="3"/>
-      <c r="B969" s="4"/>
+      <c r="A969" s="7"/>
+      <c r="B969" s="8"/>
     </row>
     <row r="971" spans="1:3">
-      <c r="A971" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B971" s="5"/>
-      <c r="C971" s="5"/>
+      <c r="A971" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B971" s="3"/>
+      <c r="C971" s="3"/>
     </row>
     <row r="972" spans="1:3">
-      <c r="A972" s="6" t="s">
+      <c r="A972" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B972" s="7"/>
-      <c r="C972" s="8"/>
+      <c r="B972" s="5"/>
+      <c r="C972" s="6"/>
     </row>
     <row r="973" spans="1:3">
       <c r="A973" s="1" t="s">
@@ -7533,31 +7536,31 @@
       </c>
     </row>
     <row r="976" spans="1:3">
-      <c r="A976" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B976" s="4">
+      <c r="A976" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B976" s="8">
         <f>B974-B975</f>
         <v>534</v>
       </c>
     </row>
     <row r="977" spans="1:3">
-      <c r="A977" s="3"/>
-      <c r="B977" s="4"/>
+      <c r="A977" s="7"/>
+      <c r="B977" s="8"/>
     </row>
     <row r="979" spans="1:3">
-      <c r="A979" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B979" s="5"/>
-      <c r="C979" s="5"/>
+      <c r="A979" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B979" s="3"/>
+      <c r="C979" s="3"/>
     </row>
     <row r="980" spans="1:3">
-      <c r="A980" s="6" t="s">
+      <c r="A980" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B980" s="7"/>
-      <c r="C980" s="8"/>
+      <c r="B980" s="5"/>
+      <c r="C980" s="6"/>
     </row>
     <row r="981" spans="1:3">
       <c r="A981" s="1" t="s">
@@ -7590,31 +7593,31 @@
       </c>
     </row>
     <row r="984" spans="1:3">
-      <c r="A984" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B984" s="4">
+      <c r="A984" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B984" s="8">
         <f>B982-B983</f>
         <v>59</v>
       </c>
     </row>
     <row r="985" spans="1:3">
-      <c r="A985" s="3"/>
-      <c r="B985" s="4"/>
+      <c r="A985" s="7"/>
+      <c r="B985" s="8"/>
     </row>
     <row r="987" spans="1:3">
-      <c r="A987" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B987" s="5"/>
-      <c r="C987" s="5"/>
+      <c r="A987" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B987" s="3"/>
+      <c r="C987" s="3"/>
     </row>
     <row r="988" spans="1:3">
-      <c r="A988" s="6" t="s">
+      <c r="A988" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B988" s="7"/>
-      <c r="C988" s="8"/>
+      <c r="B988" s="5"/>
+      <c r="C988" s="6"/>
     </row>
     <row r="989" spans="1:3">
       <c r="A989" s="1" t="s">
@@ -7647,31 +7650,31 @@
       </c>
     </row>
     <row r="992" spans="1:3">
-      <c r="A992" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B992" s="4">
+      <c r="A992" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B992" s="8">
         <f>B990-B991</f>
         <v>164</v>
       </c>
     </row>
     <row r="993" spans="1:3">
-      <c r="A993" s="3"/>
-      <c r="B993" s="4"/>
+      <c r="A993" s="7"/>
+      <c r="B993" s="8"/>
     </row>
     <row r="995" spans="1:3">
-      <c r="A995" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B995" s="5"/>
-      <c r="C995" s="5"/>
+      <c r="A995" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B995" s="3"/>
+      <c r="C995" s="3"/>
     </row>
     <row r="996" spans="1:3">
-      <c r="A996" s="6" t="s">
+      <c r="A996" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B996" s="7"/>
-      <c r="C996" s="8"/>
+      <c r="B996" s="5"/>
+      <c r="C996" s="6"/>
     </row>
     <row r="997" spans="1:3">
       <c r="A997" s="1" t="s">
@@ -7704,31 +7707,31 @@
       </c>
     </row>
     <row r="1000" spans="1:3">
-      <c r="A1000" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1000" s="4">
+      <c r="A1000" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1000" s="8">
         <f>B998-B999</f>
         <v>1579</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
-      <c r="A1001" s="3"/>
-      <c r="B1001" s="4"/>
+      <c r="A1001" s="7"/>
+      <c r="B1001" s="8"/>
     </row>
     <row r="1003" spans="1:3">
-      <c r="A1003" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1003" s="5"/>
-      <c r="C1003" s="5"/>
+      <c r="A1003" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1003" s="3"/>
+      <c r="C1003" s="3"/>
     </row>
     <row r="1004" spans="1:3">
-      <c r="A1004" s="6" t="s">
+      <c r="A1004" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1004" s="7"/>
-      <c r="C1004" s="8"/>
+      <c r="B1004" s="5"/>
+      <c r="C1004" s="6"/>
     </row>
     <row r="1005" spans="1:3">
       <c r="A1005" s="1" t="s">
@@ -7761,17 +7764,17 @@
       </c>
     </row>
     <row r="1008" spans="1:3">
-      <c r="A1008" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1008" s="4">
+      <c r="A1008" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1008" s="8">
         <f>B1006-B1007</f>
         <v>618</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
-      <c r="A1009" s="3"/>
-      <c r="B1009" s="4"/>
+      <c r="A1009" s="7"/>
+      <c r="B1009" s="8"/>
     </row>
     <row r="1010" spans="1:3">
       <c r="A1010" s="1" t="s">
@@ -7782,18 +7785,18 @@
       </c>
     </row>
     <row r="1012" spans="1:3">
-      <c r="A1012" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1012" s="5"/>
-      <c r="C1012" s="5"/>
+      <c r="A1012" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1012" s="3"/>
+      <c r="C1012" s="3"/>
     </row>
     <row r="1013" spans="1:3">
-      <c r="A1013" s="6" t="s">
+      <c r="A1013" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1013" s="7"/>
-      <c r="C1013" s="8"/>
+      <c r="B1013" s="5"/>
+      <c r="C1013" s="6"/>
     </row>
     <row r="1014" spans="1:3">
       <c r="A1014" s="1" t="s">
@@ -7826,31 +7829,31 @@
       </c>
     </row>
     <row r="1017" spans="1:3">
-      <c r="A1017" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1017" s="4">
+      <c r="A1017" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1017" s="8">
         <f>B1015-B1016</f>
         <v>166</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
-      <c r="A1018" s="3"/>
-      <c r="B1018" s="4"/>
+      <c r="A1018" s="7"/>
+      <c r="B1018" s="8"/>
     </row>
     <row r="1020" spans="1:3">
-      <c r="A1020" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1020" s="5"/>
-      <c r="C1020" s="5"/>
+      <c r="A1020" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1020" s="3"/>
+      <c r="C1020" s="3"/>
     </row>
     <row r="1021" spans="1:3">
-      <c r="A1021" s="6" t="s">
+      <c r="A1021" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1021" s="7"/>
-      <c r="C1021" s="8"/>
+      <c r="B1021" s="5"/>
+      <c r="C1021" s="6"/>
     </row>
     <row r="1022" spans="1:3">
       <c r="A1022" s="1" t="s">
@@ -7883,31 +7886,31 @@
       </c>
     </row>
     <row r="1025" spans="1:3">
-      <c r="A1025" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1025" s="4">
+      <c r="A1025" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1025" s="8">
         <f>B1023-B1024</f>
         <v>77</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
-      <c r="A1026" s="3"/>
-      <c r="B1026" s="4"/>
+      <c r="A1026" s="7"/>
+      <c r="B1026" s="8"/>
     </row>
     <row r="1028" spans="1:3">
-      <c r="A1028" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1028" s="5"/>
-      <c r="C1028" s="5"/>
+      <c r="A1028" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1028" s="3"/>
+      <c r="C1028" s="3"/>
     </row>
     <row r="1029" spans="1:3">
-      <c r="A1029" s="6" t="s">
+      <c r="A1029" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1029" s="7"/>
-      <c r="C1029" s="8"/>
+      <c r="B1029" s="5"/>
+      <c r="C1029" s="6"/>
     </row>
     <row r="1030" spans="1:3">
       <c r="A1030" s="1" t="s">
@@ -7940,31 +7943,31 @@
       </c>
     </row>
     <row r="1033" spans="1:3">
-      <c r="A1033" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1033" s="4">
+      <c r="A1033" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1033" s="8">
         <f>B1031-B1032</f>
         <v>11</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
-      <c r="A1034" s="3"/>
-      <c r="B1034" s="4"/>
+      <c r="A1034" s="7"/>
+      <c r="B1034" s="8"/>
     </row>
     <row r="1036" spans="1:3">
-      <c r="A1036" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1036" s="5"/>
-      <c r="C1036" s="5"/>
+      <c r="A1036" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1036" s="3"/>
+      <c r="C1036" s="3"/>
     </row>
     <row r="1037" spans="1:3">
-      <c r="A1037" s="6" t="s">
+      <c r="A1037" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1037" s="7"/>
-      <c r="C1037" s="8"/>
+      <c r="B1037" s="5"/>
+      <c r="C1037" s="6"/>
     </row>
     <row r="1038" spans="1:3">
       <c r="A1038" s="1" t="s">
@@ -7997,31 +8000,31 @@
       </c>
     </row>
     <row r="1041" spans="1:3">
-      <c r="A1041" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1041" s="4">
+      <c r="A1041" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1041" s="8">
         <f>B1039-B1040</f>
         <v>148</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
-      <c r="A1042" s="3"/>
-      <c r="B1042" s="4"/>
+      <c r="A1042" s="7"/>
+      <c r="B1042" s="8"/>
     </row>
     <row r="1044" spans="1:3">
-      <c r="A1044" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1044" s="5"/>
-      <c r="C1044" s="5"/>
+      <c r="A1044" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1044" s="3"/>
+      <c r="C1044" s="3"/>
     </row>
     <row r="1045" spans="1:3">
-      <c r="A1045" s="6" t="s">
+      <c r="A1045" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1045" s="7"/>
-      <c r="C1045" s="8"/>
+      <c r="B1045" s="5"/>
+      <c r="C1045" s="6"/>
     </row>
     <row r="1046" spans="1:3">
       <c r="A1046" s="1" t="s">
@@ -8054,31 +8057,31 @@
       </c>
     </row>
     <row r="1049" spans="1:3">
-      <c r="A1049" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1049" s="4">
+      <c r="A1049" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1049" s="8">
         <f>B1047-B1048</f>
         <v>1669</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
-      <c r="A1050" s="3"/>
-      <c r="B1050" s="4"/>
+      <c r="A1050" s="7"/>
+      <c r="B1050" s="8"/>
     </row>
     <row r="1052" spans="1:3">
-      <c r="A1052" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1052" s="5"/>
-      <c r="C1052" s="5"/>
+      <c r="A1052" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1052" s="3"/>
+      <c r="C1052" s="3"/>
     </row>
     <row r="1053" spans="1:3">
-      <c r="A1053" s="6" t="s">
+      <c r="A1053" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1053" s="7"/>
-      <c r="C1053" s="8"/>
+      <c r="B1053" s="5"/>
+      <c r="C1053" s="6"/>
     </row>
     <row r="1054" spans="1:3">
       <c r="A1054" s="1" t="s">
@@ -8111,31 +8114,31 @@
       </c>
     </row>
     <row r="1057" spans="1:3">
-      <c r="A1057" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1057" s="4">
+      <c r="A1057" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1057" s="8">
         <f>B1055-B1056</f>
         <v>675</v>
       </c>
     </row>
     <row r="1058" spans="1:3">
-      <c r="A1058" s="3"/>
-      <c r="B1058" s="4"/>
+      <c r="A1058" s="7"/>
+      <c r="B1058" s="8"/>
     </row>
     <row r="1060" spans="1:3">
-      <c r="A1060" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1060" s="5"/>
-      <c r="C1060" s="5"/>
+      <c r="A1060" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1060" s="3"/>
+      <c r="C1060" s="3"/>
     </row>
     <row r="1061" spans="1:3">
-      <c r="A1061" s="6" t="s">
+      <c r="A1061" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1061" s="7"/>
-      <c r="C1061" s="8"/>
+      <c r="B1061" s="5"/>
+      <c r="C1061" s="6"/>
     </row>
     <row r="1062" spans="1:3">
       <c r="A1062" s="1" t="s">
@@ -8168,176 +8171,738 @@
       </c>
     </row>
     <row r="1065" spans="1:3">
-      <c r="A1065" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1065" s="4">
+      <c r="A1065" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1065" s="8">
         <f>B1063-B1064</f>
         <v>100</v>
       </c>
     </row>
     <row r="1066" spans="1:3">
-      <c r="A1066" s="3"/>
-      <c r="B1066" s="4"/>
+      <c r="A1066" s="7"/>
+      <c r="B1066" s="8"/>
+    </row>
+    <row r="1068" spans="1:3">
+      <c r="A1068" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1068" s="3"/>
+      <c r="C1068" s="3"/>
+    </row>
+    <row r="1069" spans="1:3">
+      <c r="A1069" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1069" s="5"/>
+      <c r="C1069" s="6"/>
+    </row>
+    <row r="1070" spans="1:3">
+      <c r="A1070" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1070" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1070" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3">
+      <c r="A1071" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1071" s="2">
+        <v>332</v>
+      </c>
+      <c r="C1071" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3">
+      <c r="A1072" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1072" s="2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3">
+      <c r="A1073" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1073" s="8">
+        <f>B1071-B1072</f>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:3">
+      <c r="A1074" s="7"/>
+      <c r="B1074" s="8"/>
+    </row>
+    <row r="1075" spans="1:3">
+      <c r="A1075" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1075" s="2">
+        <v>51293</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:3">
+      <c r="A1077" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1077" s="3"/>
+      <c r="C1077" s="3"/>
+    </row>
+    <row r="1078" spans="1:3">
+      <c r="A1078" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1078" s="5"/>
+      <c r="C1078" s="6"/>
+    </row>
+    <row r="1079" spans="1:3">
+      <c r="A1079" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1079" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1079" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:3">
+      <c r="A1080" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1080" s="2">
+        <v>115</v>
+      </c>
+      <c r="C1080" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3">
+      <c r="A1081" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1081" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:3">
+      <c r="A1082" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1082" s="8">
+        <f>B1080-B1081</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:3">
+      <c r="A1083" s="7"/>
+      <c r="B1083" s="8"/>
+    </row>
+    <row r="1085" spans="1:3">
+      <c r="A1085" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1085" s="3"/>
+      <c r="C1085" s="3"/>
+    </row>
+    <row r="1086" spans="1:3">
+      <c r="A1086" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1086" s="5"/>
+      <c r="C1086" s="6"/>
+    </row>
+    <row r="1087" spans="1:3">
+      <c r="A1087" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1087" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1087" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:3">
+      <c r="A1088" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1088" s="2">
+        <v>570</v>
+      </c>
+      <c r="C1088" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:3">
+      <c r="A1089" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1089" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3">
+      <c r="A1090" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1090" s="8">
+        <f>B1088-B1089</f>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:3">
+      <c r="A1091" s="7"/>
+      <c r="B1091" s="8"/>
+    </row>
+    <row r="1093" spans="1:3">
+      <c r="A1093" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1093" s="3"/>
+      <c r="C1093" s="3"/>
+    </row>
+    <row r="1094" spans="1:3">
+      <c r="A1094" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1094" s="5"/>
+      <c r="C1094" s="6"/>
+    </row>
+    <row r="1095" spans="1:3">
+      <c r="A1095" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1095" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1095" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3">
+      <c r="A1096" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1096" s="2">
+        <v>51</v>
+      </c>
+      <c r="C1096" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:3">
+      <c r="A1097" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1097" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:3">
+      <c r="A1098" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1098" s="8">
+        <f>B1096-B1097</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3">
+      <c r="A1099" s="7"/>
+      <c r="B1099" s="8"/>
+    </row>
+    <row r="1101" spans="1:3">
+      <c r="A1101" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1101" s="3"/>
+      <c r="C1101" s="3"/>
+    </row>
+    <row r="1102" spans="1:3">
+      <c r="A1102" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1102" s="5"/>
+      <c r="C1102" s="6"/>
+    </row>
+    <row r="1103" spans="1:3">
+      <c r="A1103" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1103" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:3">
+      <c r="A1104" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1104" s="2">
+        <v>570</v>
+      </c>
+      <c r="C1104" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3">
+      <c r="A1105" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1105" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:3">
+      <c r="A1106" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1106" s="8">
+        <f>B1104-B1105</f>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3">
+      <c r="A1107" s="7"/>
+      <c r="B1107" s="8"/>
+    </row>
+    <row r="1109" spans="1:3">
+      <c r="A1109" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1109" s="3"/>
+      <c r="C1109" s="3"/>
+    </row>
+    <row r="1110" spans="1:3">
+      <c r="A1110" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1110" s="5"/>
+      <c r="C1110" s="6"/>
+    </row>
+    <row r="1111" spans="1:3">
+      <c r="A1111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1111" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1111" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:3">
+      <c r="A1112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1112" s="2">
+        <v>63</v>
+      </c>
+      <c r="C1112" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3">
+      <c r="A1113" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1113" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:3">
+      <c r="A1114" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1114" s="8">
+        <f>B1112-B1113</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3">
+      <c r="A1115" s="7"/>
+      <c r="B1115" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="524">
-    <mergeCell ref="A1060:C1060"/>
-    <mergeCell ref="A1061:C1061"/>
-    <mergeCell ref="A1065:A1066"/>
-    <mergeCell ref="B1065:B1066"/>
-    <mergeCell ref="A1041:A1042"/>
-    <mergeCell ref="B1041:B1042"/>
-    <mergeCell ref="A1044:C1044"/>
-    <mergeCell ref="A1045:C1045"/>
-    <mergeCell ref="A1049:A1050"/>
-    <mergeCell ref="B1049:B1050"/>
-    <mergeCell ref="A1052:C1052"/>
-    <mergeCell ref="A1053:C1053"/>
-    <mergeCell ref="A1057:A1058"/>
-    <mergeCell ref="B1057:B1058"/>
-    <mergeCell ref="A1021:C1021"/>
-    <mergeCell ref="A1025:A1026"/>
-    <mergeCell ref="B1025:B1026"/>
-    <mergeCell ref="A1028:C1028"/>
-    <mergeCell ref="A1029:C1029"/>
-    <mergeCell ref="A1033:A1034"/>
-    <mergeCell ref="B1033:B1034"/>
-    <mergeCell ref="A1036:C1036"/>
-    <mergeCell ref="A1037:C1037"/>
-    <mergeCell ref="A1003:C1003"/>
-    <mergeCell ref="A1004:C1004"/>
-    <mergeCell ref="A1008:A1009"/>
-    <mergeCell ref="B1008:B1009"/>
-    <mergeCell ref="A1012:C1012"/>
-    <mergeCell ref="A1013:C1013"/>
-    <mergeCell ref="A1017:A1018"/>
-    <mergeCell ref="B1017:B1018"/>
-    <mergeCell ref="A1020:C1020"/>
-    <mergeCell ref="A995:C995"/>
-    <mergeCell ref="A996:C996"/>
-    <mergeCell ref="A1000:A1001"/>
-    <mergeCell ref="B1000:B1001"/>
-    <mergeCell ref="A976:A977"/>
-    <mergeCell ref="B976:B977"/>
-    <mergeCell ref="A979:C979"/>
-    <mergeCell ref="A980:C980"/>
-    <mergeCell ref="A984:A985"/>
-    <mergeCell ref="B984:B985"/>
-    <mergeCell ref="A987:C987"/>
-    <mergeCell ref="A988:C988"/>
-    <mergeCell ref="A992:A993"/>
-    <mergeCell ref="B992:B993"/>
-    <mergeCell ref="A956:C956"/>
-    <mergeCell ref="A960:A961"/>
-    <mergeCell ref="B960:B961"/>
-    <mergeCell ref="A963:C963"/>
-    <mergeCell ref="A964:C964"/>
-    <mergeCell ref="A968:A969"/>
-    <mergeCell ref="B968:B969"/>
-    <mergeCell ref="A971:C971"/>
-    <mergeCell ref="A972:C972"/>
-    <mergeCell ref="A938:C938"/>
-    <mergeCell ref="A939:C939"/>
-    <mergeCell ref="A943:A944"/>
-    <mergeCell ref="B943:B944"/>
-    <mergeCell ref="A947:C947"/>
-    <mergeCell ref="A948:C948"/>
-    <mergeCell ref="A952:A953"/>
-    <mergeCell ref="B952:B953"/>
-    <mergeCell ref="A955:C955"/>
-    <mergeCell ref="A870:A871"/>
-    <mergeCell ref="B870:B871"/>
-    <mergeCell ref="A873:C873"/>
-    <mergeCell ref="A874:C874"/>
-    <mergeCell ref="A878:A879"/>
-    <mergeCell ref="B878:B879"/>
-    <mergeCell ref="A881:C881"/>
-    <mergeCell ref="A882:C882"/>
-    <mergeCell ref="A886:A887"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="A850:C850"/>
-    <mergeCell ref="A854:A855"/>
-    <mergeCell ref="B854:B855"/>
-    <mergeCell ref="A857:C857"/>
-    <mergeCell ref="A858:C858"/>
-    <mergeCell ref="A862:A863"/>
-    <mergeCell ref="B862:B863"/>
-    <mergeCell ref="A865:C865"/>
-    <mergeCell ref="A866:C866"/>
-    <mergeCell ref="A832:C832"/>
-    <mergeCell ref="A833:C833"/>
-    <mergeCell ref="A837:A838"/>
-    <mergeCell ref="B837:B838"/>
-    <mergeCell ref="A841:C841"/>
-    <mergeCell ref="A842:C842"/>
-    <mergeCell ref="A846:A847"/>
-    <mergeCell ref="B846:B847"/>
-    <mergeCell ref="A849:C849"/>
-    <mergeCell ref="A759:C759"/>
-    <mergeCell ref="A760:C760"/>
-    <mergeCell ref="A764:A765"/>
-    <mergeCell ref="B764:B765"/>
-    <mergeCell ref="A740:A741"/>
-    <mergeCell ref="B740:B741"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A744:C744"/>
-    <mergeCell ref="A748:A749"/>
-    <mergeCell ref="B748:B749"/>
-    <mergeCell ref="A751:C751"/>
-    <mergeCell ref="A752:C752"/>
-    <mergeCell ref="A756:A757"/>
-    <mergeCell ref="B756:B757"/>
-    <mergeCell ref="A720:C720"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="B724:B725"/>
-    <mergeCell ref="A727:C727"/>
-    <mergeCell ref="A728:C728"/>
-    <mergeCell ref="A732:A733"/>
-    <mergeCell ref="B732:B733"/>
-    <mergeCell ref="A735:C735"/>
-    <mergeCell ref="A736:C736"/>
-    <mergeCell ref="A702:C702"/>
-    <mergeCell ref="A703:C703"/>
-    <mergeCell ref="A707:A708"/>
-    <mergeCell ref="B707:B708"/>
-    <mergeCell ref="A711:C711"/>
-    <mergeCell ref="A712:C712"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="B716:B717"/>
-    <mergeCell ref="A719:C719"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
+  <mergeCells count="548">
+    <mergeCell ref="A1106:A1107"/>
+    <mergeCell ref="B1106:B1107"/>
+    <mergeCell ref="A1109:C1109"/>
+    <mergeCell ref="A1110:C1110"/>
+    <mergeCell ref="A1114:A1115"/>
+    <mergeCell ref="B1114:B1115"/>
+    <mergeCell ref="A1086:C1086"/>
+    <mergeCell ref="A1090:A1091"/>
+    <mergeCell ref="B1090:B1091"/>
+    <mergeCell ref="A1093:C1093"/>
+    <mergeCell ref="A1094:C1094"/>
+    <mergeCell ref="A1098:A1099"/>
+    <mergeCell ref="B1098:B1099"/>
+    <mergeCell ref="A1101:C1101"/>
+    <mergeCell ref="A1102:C1102"/>
+    <mergeCell ref="A1068:C1068"/>
+    <mergeCell ref="A1069:C1069"/>
+    <mergeCell ref="A1073:A1074"/>
+    <mergeCell ref="B1073:B1074"/>
+    <mergeCell ref="A1077:C1077"/>
+    <mergeCell ref="A1078:C1078"/>
+    <mergeCell ref="A1082:A1083"/>
+    <mergeCell ref="B1082:B1083"/>
+    <mergeCell ref="A1085:C1085"/>
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="B927:B928"/>
+    <mergeCell ref="A930:C930"/>
+    <mergeCell ref="A931:C931"/>
+    <mergeCell ref="A935:A936"/>
+    <mergeCell ref="B935:B936"/>
+    <mergeCell ref="A907:C907"/>
+    <mergeCell ref="A911:A912"/>
+    <mergeCell ref="B911:B912"/>
+    <mergeCell ref="A914:C914"/>
+    <mergeCell ref="A915:C915"/>
+    <mergeCell ref="A919:A920"/>
+    <mergeCell ref="B919:B920"/>
+    <mergeCell ref="A922:C922"/>
+    <mergeCell ref="A923:C923"/>
+    <mergeCell ref="A889:C889"/>
+    <mergeCell ref="A890:C890"/>
+    <mergeCell ref="A894:A895"/>
+    <mergeCell ref="B894:B895"/>
+    <mergeCell ref="A898:C898"/>
+    <mergeCell ref="A899:C899"/>
+    <mergeCell ref="A903:A904"/>
+    <mergeCell ref="B903:B904"/>
+    <mergeCell ref="A906:C906"/>
+    <mergeCell ref="A824:C824"/>
+    <mergeCell ref="A825:C825"/>
+    <mergeCell ref="A829:A830"/>
+    <mergeCell ref="B829:B830"/>
+    <mergeCell ref="A805:A806"/>
+    <mergeCell ref="B805:B806"/>
+    <mergeCell ref="A808:C808"/>
+    <mergeCell ref="A809:C809"/>
+    <mergeCell ref="A813:A814"/>
+    <mergeCell ref="B813:B814"/>
+    <mergeCell ref="A816:C816"/>
+    <mergeCell ref="A817:C817"/>
+    <mergeCell ref="A821:A822"/>
+    <mergeCell ref="B821:B822"/>
+    <mergeCell ref="A785:C785"/>
+    <mergeCell ref="A789:A790"/>
+    <mergeCell ref="B789:B790"/>
+    <mergeCell ref="A792:C792"/>
+    <mergeCell ref="A793:C793"/>
+    <mergeCell ref="A797:A798"/>
+    <mergeCell ref="B797:B798"/>
+    <mergeCell ref="A800:C800"/>
+    <mergeCell ref="A801:C801"/>
+    <mergeCell ref="A767:C767"/>
+    <mergeCell ref="A768:C768"/>
+    <mergeCell ref="A772:A773"/>
+    <mergeCell ref="B772:B773"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A777:C777"/>
+    <mergeCell ref="A781:A782"/>
+    <mergeCell ref="B781:B782"/>
+    <mergeCell ref="A784:C784"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A430:A431"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="A490:C490"/>
+    <mergeCell ref="A491:C491"/>
+    <mergeCell ref="A495:A496"/>
+    <mergeCell ref="B495:B496"/>
+    <mergeCell ref="A499:C499"/>
+    <mergeCell ref="A500:C500"/>
+    <mergeCell ref="A433:C433"/>
+    <mergeCell ref="A434:C434"/>
+    <mergeCell ref="A438:A439"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="A442:C442"/>
+    <mergeCell ref="A443:C443"/>
+    <mergeCell ref="A447:A448"/>
+    <mergeCell ref="B447:B448"/>
+    <mergeCell ref="A450:C450"/>
+    <mergeCell ref="A451:C451"/>
+    <mergeCell ref="A455:A456"/>
+    <mergeCell ref="B455:B456"/>
+    <mergeCell ref="A458:C458"/>
+    <mergeCell ref="A459:C459"/>
+    <mergeCell ref="A463:A464"/>
+    <mergeCell ref="B463:B464"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
     <mergeCell ref="A483:C483"/>
     <mergeCell ref="A487:A488"/>
     <mergeCell ref="B487:B488"/>
@@ -8362,350 +8927,162 @@
     <mergeCell ref="A512:A513"/>
     <mergeCell ref="B512:B513"/>
     <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A430:A431"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="A490:C490"/>
-    <mergeCell ref="A491:C491"/>
-    <mergeCell ref="A495:A496"/>
-    <mergeCell ref="B495:B496"/>
-    <mergeCell ref="A499:C499"/>
-    <mergeCell ref="A500:C500"/>
-    <mergeCell ref="A433:C433"/>
-    <mergeCell ref="A434:C434"/>
-    <mergeCell ref="A438:A439"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="A442:C442"/>
-    <mergeCell ref="A443:C443"/>
-    <mergeCell ref="A447:A448"/>
-    <mergeCell ref="B447:B448"/>
-    <mergeCell ref="A450:C450"/>
-    <mergeCell ref="A451:C451"/>
-    <mergeCell ref="A455:A456"/>
-    <mergeCell ref="B455:B456"/>
-    <mergeCell ref="A458:C458"/>
-    <mergeCell ref="A459:C459"/>
-    <mergeCell ref="A463:A464"/>
-    <mergeCell ref="B463:B464"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
-    <mergeCell ref="A767:C767"/>
-    <mergeCell ref="A768:C768"/>
-    <mergeCell ref="A772:A773"/>
-    <mergeCell ref="B772:B773"/>
-    <mergeCell ref="A776:C776"/>
-    <mergeCell ref="A777:C777"/>
-    <mergeCell ref="A781:A782"/>
-    <mergeCell ref="B781:B782"/>
-    <mergeCell ref="A784:C784"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="A789:A790"/>
-    <mergeCell ref="B789:B790"/>
-    <mergeCell ref="A792:C792"/>
-    <mergeCell ref="A793:C793"/>
-    <mergeCell ref="A797:A798"/>
-    <mergeCell ref="B797:B798"/>
-    <mergeCell ref="A800:C800"/>
-    <mergeCell ref="A801:C801"/>
-    <mergeCell ref="A824:C824"/>
-    <mergeCell ref="A825:C825"/>
-    <mergeCell ref="A829:A830"/>
-    <mergeCell ref="B829:B830"/>
-    <mergeCell ref="A805:A806"/>
-    <mergeCell ref="B805:B806"/>
-    <mergeCell ref="A808:C808"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="A813:A814"/>
-    <mergeCell ref="B813:B814"/>
-    <mergeCell ref="A816:C816"/>
-    <mergeCell ref="A817:C817"/>
-    <mergeCell ref="A821:A822"/>
-    <mergeCell ref="B821:B822"/>
-    <mergeCell ref="A889:C889"/>
-    <mergeCell ref="A890:C890"/>
-    <mergeCell ref="A894:A895"/>
-    <mergeCell ref="B894:B895"/>
-    <mergeCell ref="A898:C898"/>
-    <mergeCell ref="A899:C899"/>
-    <mergeCell ref="A903:A904"/>
-    <mergeCell ref="B903:B904"/>
-    <mergeCell ref="A906:C906"/>
-    <mergeCell ref="A927:A928"/>
-    <mergeCell ref="B927:B928"/>
-    <mergeCell ref="A930:C930"/>
-    <mergeCell ref="A931:C931"/>
-    <mergeCell ref="A935:A936"/>
-    <mergeCell ref="B935:B936"/>
-    <mergeCell ref="A907:C907"/>
-    <mergeCell ref="A911:A912"/>
-    <mergeCell ref="B911:B912"/>
-    <mergeCell ref="A914:C914"/>
-    <mergeCell ref="A915:C915"/>
-    <mergeCell ref="A919:A920"/>
-    <mergeCell ref="B919:B920"/>
-    <mergeCell ref="A922:C922"/>
-    <mergeCell ref="A923:C923"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A702:C702"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A707:A708"/>
+    <mergeCell ref="B707:B708"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A759:C759"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A764:A765"/>
+    <mergeCell ref="B764:B765"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A832:C832"/>
+    <mergeCell ref="A833:C833"/>
+    <mergeCell ref="A837:A838"/>
+    <mergeCell ref="B837:B838"/>
+    <mergeCell ref="A841:C841"/>
+    <mergeCell ref="A842:C842"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="B846:B847"/>
+    <mergeCell ref="A849:C849"/>
+    <mergeCell ref="A850:C850"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="B854:B855"/>
+    <mergeCell ref="A857:C857"/>
+    <mergeCell ref="A858:C858"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="B862:B863"/>
+    <mergeCell ref="A865:C865"/>
+    <mergeCell ref="A866:C866"/>
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="B870:B871"/>
+    <mergeCell ref="A873:C873"/>
+    <mergeCell ref="A874:C874"/>
+    <mergeCell ref="A878:A879"/>
+    <mergeCell ref="B878:B879"/>
+    <mergeCell ref="A881:C881"/>
+    <mergeCell ref="A882:C882"/>
+    <mergeCell ref="A886:A887"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="A938:C938"/>
+    <mergeCell ref="A939:C939"/>
+    <mergeCell ref="A943:A944"/>
+    <mergeCell ref="B943:B944"/>
+    <mergeCell ref="A947:C947"/>
+    <mergeCell ref="A948:C948"/>
+    <mergeCell ref="A952:A953"/>
+    <mergeCell ref="B952:B953"/>
+    <mergeCell ref="A955:C955"/>
+    <mergeCell ref="A956:C956"/>
+    <mergeCell ref="A960:A961"/>
+    <mergeCell ref="B960:B961"/>
+    <mergeCell ref="A963:C963"/>
+    <mergeCell ref="A964:C964"/>
+    <mergeCell ref="A968:A969"/>
+    <mergeCell ref="B968:B969"/>
+    <mergeCell ref="A971:C971"/>
+    <mergeCell ref="A972:C972"/>
+    <mergeCell ref="A995:C995"/>
+    <mergeCell ref="A996:C996"/>
+    <mergeCell ref="A1000:A1001"/>
+    <mergeCell ref="B1000:B1001"/>
+    <mergeCell ref="A976:A977"/>
+    <mergeCell ref="B976:B977"/>
+    <mergeCell ref="A979:C979"/>
+    <mergeCell ref="A980:C980"/>
+    <mergeCell ref="A984:A985"/>
+    <mergeCell ref="B984:B985"/>
+    <mergeCell ref="A987:C987"/>
+    <mergeCell ref="A988:C988"/>
+    <mergeCell ref="A992:A993"/>
+    <mergeCell ref="B992:B993"/>
+    <mergeCell ref="A1003:C1003"/>
+    <mergeCell ref="A1004:C1004"/>
+    <mergeCell ref="A1008:A1009"/>
+    <mergeCell ref="B1008:B1009"/>
+    <mergeCell ref="A1012:C1012"/>
+    <mergeCell ref="A1013:C1013"/>
+    <mergeCell ref="A1017:A1018"/>
+    <mergeCell ref="B1017:B1018"/>
+    <mergeCell ref="A1020:C1020"/>
+    <mergeCell ref="A1021:C1021"/>
+    <mergeCell ref="A1025:A1026"/>
+    <mergeCell ref="B1025:B1026"/>
+    <mergeCell ref="A1028:C1028"/>
+    <mergeCell ref="A1029:C1029"/>
+    <mergeCell ref="A1033:A1034"/>
+    <mergeCell ref="B1033:B1034"/>
+    <mergeCell ref="A1036:C1036"/>
+    <mergeCell ref="A1037:C1037"/>
+    <mergeCell ref="A1060:C1060"/>
+    <mergeCell ref="A1061:C1061"/>
+    <mergeCell ref="A1065:A1066"/>
+    <mergeCell ref="B1065:B1066"/>
+    <mergeCell ref="A1041:A1042"/>
+    <mergeCell ref="B1041:B1042"/>
+    <mergeCell ref="A1044:C1044"/>
+    <mergeCell ref="A1045:C1045"/>
+    <mergeCell ref="A1049:A1050"/>
+    <mergeCell ref="B1049:B1050"/>
+    <mergeCell ref="A1052:C1052"/>
+    <mergeCell ref="A1053:C1053"/>
+    <mergeCell ref="A1057:A1058"/>
+    <mergeCell ref="B1057:B1058"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Recebimento.xlsx
+++ b/Recebimento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F566621-9C5E-48D2-9383-BAF5EA059548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559D3DEC-918D-4136-BC25-4F20630C7D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="43">
   <si>
     <t>Data</t>
   </si>
@@ -161,6 +161,9 @@
   <si>
     <t>29.10.2026</t>
   </si>
+  <si>
+    <t>30.10.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -264,6 +267,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -273,12 +282,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -556,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1115"/>
+  <dimension ref="A1:C1180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -565,18 +568,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
@@ -609,17 +612,17 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
         <f>B4-B5</f>
         <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -630,18 +633,18 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -674,31 +677,31 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
         <f>B13-B14</f>
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="A18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
@@ -731,31 +734,31 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4">
         <f>B21-B22</f>
         <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="8"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
@@ -788,31 +791,31 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4">
         <f>B29-B30</f>
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="A34" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
@@ -845,31 +848,31 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="4">
         <f>B37-B38</f>
         <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="4"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="A42" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="8"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
@@ -902,31 +905,31 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="4">
         <f>B45-B46</f>
         <v>470</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="4"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
+      <c r="A50" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="6"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
@@ -959,31 +962,31 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="4">
         <f>B53-B54</f>
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="A58" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
@@ -1016,17 +1019,17 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="4">
         <f>B61-B62</f>
         <v>1309</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="4"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
@@ -1037,18 +1040,18 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
+      <c r="A67" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="6"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
@@ -1081,31 +1084,31 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="8">
+      <c r="A72" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="4">
         <f>B70-B71</f>
         <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
+      <c r="A75" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="6"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
@@ -1138,31 +1141,31 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="8">
+      <c r="A80" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="4">
         <f>B78-B79</f>
         <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="4"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="A83" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="6"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="8"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
@@ -1195,31 +1198,31 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="8">
+      <c r="A88" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="4">
         <f>B86-B87</f>
         <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="4"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
+      <c r="A91" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="6"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="8"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
@@ -1252,31 +1255,31 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="8">
+      <c r="A96" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B96" s="4">
         <f>B94-B95</f>
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="7"/>
-      <c r="B97" s="8"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="4"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="A99" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="6"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="8"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="1" t="s">
@@ -1309,31 +1312,31 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B104" s="8">
+      <c r="A104" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="4">
         <f>B102-B103</f>
         <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="7"/>
-      <c r="B105" s="8"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="4"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="A107" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="6"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="8"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="1" t="s">
@@ -1366,31 +1369,31 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B112" s="8">
+      <c r="A112" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="4">
         <f>B110-B111</f>
         <v>701</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="7"/>
-      <c r="B113" s="8"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="4"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
+      <c r="A115" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="6"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="8"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="1" t="s">
@@ -1423,31 +1426,31 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="8">
+      <c r="A120" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="4">
         <f>B118-B119</f>
         <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="7"/>
-      <c r="B121" s="8"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="4"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="A123" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="6"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="8"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="1" t="s">
@@ -1480,17 +1483,17 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B128" s="8">
+      <c r="A128" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="4">
         <f>B126-B127</f>
         <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="7"/>
-      <c r="B129" s="8"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="4"/>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="1" t="s">
@@ -1501,18 +1504,18 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="A132" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B133" s="5"/>
-      <c r="C133" s="6"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="8"/>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="1" t="s">
@@ -1545,31 +1548,31 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B137" s="8">
+      <c r="A137" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="4">
         <f>B135-B136</f>
         <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="7"/>
-      <c r="B138" s="8"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="4"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
+      <c r="A140" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B141" s="5"/>
-      <c r="C141" s="6"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="8"/>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="1" t="s">
@@ -1602,31 +1605,31 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B145" s="8">
+      <c r="A145" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" s="4">
         <f>B143-B144</f>
         <v>1445</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="7"/>
-      <c r="B146" s="8"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="4"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B148" s="3"/>
-      <c r="C148" s="3"/>
+      <c r="A148" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="6"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="8"/>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="1" t="s">
@@ -1659,31 +1662,31 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B153" s="8">
+      <c r="A153" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="4">
         <f>B151-B152</f>
         <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="7"/>
-      <c r="B154" s="8"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="4"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B156" s="3"/>
-      <c r="C156" s="3"/>
+      <c r="A156" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B157" s="5"/>
-      <c r="C157" s="6"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="8"/>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
@@ -1716,31 +1719,31 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="8">
+      <c r="A161" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="4">
         <f>B159-B160</f>
         <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="7"/>
-      <c r="B162" s="8"/>
+      <c r="A162" s="3"/>
+      <c r="B162" s="4"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
+      <c r="A164" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B165" s="5"/>
-      <c r="C165" s="6"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
@@ -1773,31 +1776,31 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="8">
+      <c r="A169" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" s="4">
         <f>B167-B168</f>
         <v>402</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="7"/>
-      <c r="B170" s="8"/>
+      <c r="A170" s="3"/>
+      <c r="B170" s="4"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
+      <c r="A172" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="6"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="8"/>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
@@ -1830,31 +1833,31 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="8">
+      <c r="A177" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="4">
         <f>B175-B176</f>
         <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="7"/>
-      <c r="B178" s="8"/>
+      <c r="A178" s="3"/>
+      <c r="B178" s="4"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
+      <c r="A180" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="5"/>
-      <c r="C181" s="6"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="8"/>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
@@ -1887,17 +1890,17 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B185" s="8">
+      <c r="A185" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="4">
         <f>B183-B184</f>
         <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="7"/>
-      <c r="B186" s="8"/>
+      <c r="A186" s="3"/>
+      <c r="B186" s="4"/>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
@@ -1908,18 +1911,18 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
+      <c r="A189" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B190" s="5"/>
-      <c r="C190" s="6"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="8"/>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
@@ -1952,31 +1955,31 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B194" s="8">
+      <c r="A194" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B194" s="4">
         <f>B192-B193</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="7"/>
-      <c r="B195" s="8"/>
+      <c r="A195" s="3"/>
+      <c r="B195" s="4"/>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
+      <c r="A197" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" s="5"/>
+      <c r="C197" s="5"/>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B198" s="5"/>
-      <c r="C198" s="6"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="8"/>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
@@ -2009,31 +2012,31 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B202" s="8">
+      <c r="A202" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B202" s="4">
         <f>B200-B201</f>
         <v>416</v>
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="7"/>
-      <c r="B203" s="8"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="4"/>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B205" s="3"/>
-      <c r="C205" s="3"/>
+      <c r="A205" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B206" s="5"/>
-      <c r="C206" s="6"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="8"/>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
@@ -2066,31 +2069,31 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B210" s="8">
+      <c r="A210" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B210" s="4">
         <f>B208-B209</f>
         <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="7"/>
-      <c r="B211" s="8"/>
+      <c r="A211" s="3"/>
+      <c r="B211" s="4"/>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="3"/>
-      <c r="C213" s="3"/>
+      <c r="A213" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="5"/>
+      <c r="C213" s="5"/>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="4" t="s">
+      <c r="A214" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="6"/>
+      <c r="B214" s="7"/>
+      <c r="C214" s="8"/>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
@@ -2123,31 +2126,31 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B218" s="8">
+      <c r="A218" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B218" s="4">
         <f>B216-B217</f>
         <v>329</v>
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="7"/>
-      <c r="B219" s="8"/>
+      <c r="A219" s="3"/>
+      <c r="B219" s="4"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B221" s="3"/>
-      <c r="C221" s="3"/>
+      <c r="A221" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" s="5"/>
+      <c r="C221" s="5"/>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B222" s="5"/>
-      <c r="C222" s="6"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="8"/>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
@@ -2180,31 +2183,31 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B226" s="8">
+      <c r="A226" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B226" s="4">
         <f>B224-B225</f>
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="7"/>
-      <c r="B227" s="8"/>
+      <c r="A227" s="3"/>
+      <c r="B227" s="4"/>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B229" s="3"/>
-      <c r="C229" s="3"/>
+      <c r="A229" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B229" s="5"/>
+      <c r="C229" s="5"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="4" t="s">
+      <c r="A230" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B230" s="5"/>
-      <c r="C230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="8"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
@@ -2237,31 +2240,31 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B234" s="8">
+      <c r="A234" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B234" s="4">
         <f>B232-B233</f>
         <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="7"/>
-      <c r="B235" s="8"/>
+      <c r="A235" s="3"/>
+      <c r="B235" s="4"/>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="3"/>
-      <c r="C237" s="3"/>
+      <c r="A237" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B237" s="5"/>
+      <c r="C237" s="5"/>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="4" t="s">
+      <c r="A238" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="6"/>
+      <c r="B238" s="7"/>
+      <c r="C238" s="8"/>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
@@ -2294,17 +2297,17 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B242" s="8">
+      <c r="A242" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="4">
         <f>B240-B241</f>
         <v>617</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="7"/>
-      <c r="B243" s="8"/>
+      <c r="A243" s="3"/>
+      <c r="B243" s="4"/>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
@@ -2315,18 +2318,18 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B246" s="3"/>
-      <c r="C246" s="3"/>
+      <c r="A246" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B246" s="5"/>
+      <c r="C246" s="5"/>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="4" t="s">
+      <c r="A247" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B247" s="5"/>
-      <c r="C247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="8"/>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
@@ -2359,31 +2362,31 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B251" s="8">
+      <c r="A251" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B251" s="4">
         <f>B249-B250</f>
         <v>196</v>
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="7"/>
-      <c r="B252" s="8"/>
+      <c r="A252" s="3"/>
+      <c r="B252" s="4"/>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B254" s="3"/>
-      <c r="C254" s="3"/>
+      <c r="A254" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B254" s="5"/>
+      <c r="C254" s="5"/>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B255" s="5"/>
-      <c r="C255" s="6"/>
+      <c r="B255" s="7"/>
+      <c r="C255" s="8"/>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
@@ -2416,31 +2419,31 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B259" s="8">
+      <c r="A259" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B259" s="4">
         <f>B257-B258</f>
         <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="7"/>
-      <c r="B260" s="8"/>
+      <c r="A260" s="3"/>
+      <c r="B260" s="4"/>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B262" s="3"/>
-      <c r="C262" s="3"/>
+      <c r="A262" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B262" s="5"/>
+      <c r="C262" s="5"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="4" t="s">
+      <c r="A263" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B263" s="5"/>
-      <c r="C263" s="6"/>
+      <c r="B263" s="7"/>
+      <c r="C263" s="8"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="1" t="s">
@@ -2473,17 +2476,17 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B267" s="8">
+      <c r="A267" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B267" s="4">
         <f>B265-B266</f>
         <v>757</v>
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="7"/>
-      <c r="B268" s="8"/>
+      <c r="A268" s="3"/>
+      <c r="B268" s="4"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
@@ -2494,18 +2497,18 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B271" s="3"/>
-      <c r="C271" s="3"/>
+      <c r="A271" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B271" s="5"/>
+      <c r="C271" s="5"/>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B272" s="5"/>
-      <c r="C272" s="6"/>
+      <c r="B272" s="7"/>
+      <c r="C272" s="8"/>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
@@ -2538,31 +2541,31 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B276" s="8">
+      <c r="A276" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B276" s="4">
         <f>B274-B275</f>
         <v>244</v>
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="7"/>
-      <c r="B277" s="8"/>
+      <c r="A277" s="3"/>
+      <c r="B277" s="4"/>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B279" s="3"/>
-      <c r="C279" s="3"/>
+      <c r="A279" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B279" s="5"/>
+      <c r="C279" s="5"/>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="4" t="s">
+      <c r="A280" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B280" s="5"/>
-      <c r="C280" s="6"/>
+      <c r="B280" s="7"/>
+      <c r="C280" s="8"/>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
@@ -2595,31 +2598,31 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B284" s="8">
+      <c r="A284" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" s="4">
         <f>B282-B283</f>
         <v>167</v>
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="7"/>
-      <c r="B285" s="8"/>
+      <c r="A285" s="3"/>
+      <c r="B285" s="4"/>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B287" s="3"/>
-      <c r="C287" s="3"/>
+      <c r="A287" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B287" s="5"/>
+      <c r="C287" s="5"/>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="4" t="s">
+      <c r="A288" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="5"/>
-      <c r="C288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="8"/>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
@@ -2652,31 +2655,31 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B292" s="8">
+      <c r="A292" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" s="4">
         <f>B290-B291</f>
         <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="7"/>
-      <c r="B293" s="8"/>
+      <c r="A293" s="3"/>
+      <c r="B293" s="4"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B295" s="3"/>
-      <c r="C295" s="3"/>
+      <c r="A295" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B295" s="5"/>
+      <c r="C295" s="5"/>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B296" s="5"/>
-      <c r="C296" s="6"/>
+      <c r="B296" s="7"/>
+      <c r="C296" s="8"/>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
@@ -2709,31 +2712,31 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B300" s="8">
+      <c r="A300" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="4">
         <f>B298-B299</f>
         <v>20</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="7"/>
-      <c r="B301" s="8"/>
+      <c r="A301" s="3"/>
+      <c r="B301" s="4"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B303" s="3"/>
-      <c r="C303" s="3"/>
+      <c r="A303" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B303" s="5"/>
+      <c r="C303" s="5"/>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="4" t="s">
+      <c r="A304" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B304" s="5"/>
-      <c r="C304" s="6"/>
+      <c r="B304" s="7"/>
+      <c r="C304" s="8"/>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
@@ -2766,31 +2769,31 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B308" s="8">
+      <c r="A308" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" s="4">
         <f>B306-B307</f>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="7"/>
-      <c r="B309" s="8"/>
+      <c r="A309" s="3"/>
+      <c r="B309" s="4"/>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B311" s="3"/>
-      <c r="C311" s="3"/>
+      <c r="A311" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B311" s="5"/>
+      <c r="C311" s="5"/>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="4" t="s">
+      <c r="A312" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B312" s="5"/>
-      <c r="C312" s="6"/>
+      <c r="B312" s="7"/>
+      <c r="C312" s="8"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
@@ -2823,31 +2826,31 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B316" s="8">
+      <c r="A316" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" s="4">
         <f>B314-B315</f>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="7"/>
-      <c r="B317" s="8"/>
+      <c r="A317" s="3"/>
+      <c r="B317" s="4"/>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B319" s="3"/>
-      <c r="C319" s="3"/>
+      <c r="A319" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B319" s="5"/>
+      <c r="C319" s="5"/>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="4" t="s">
+      <c r="A320" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B320" s="5"/>
-      <c r="C320" s="6"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="8"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
@@ -2880,17 +2883,17 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B324" s="8">
+      <c r="A324" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" s="4">
         <f>B322-B323</f>
         <v>282</v>
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="7"/>
-      <c r="B325" s="8"/>
+      <c r="A325" s="3"/>
+      <c r="B325" s="4"/>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
@@ -2901,18 +2904,18 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B328" s="3"/>
-      <c r="C328" s="3"/>
+      <c r="A328" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B328" s="5"/>
+      <c r="C328" s="5"/>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="4" t="s">
+      <c r="A329" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B329" s="5"/>
-      <c r="C329" s="6"/>
+      <c r="B329" s="7"/>
+      <c r="C329" s="8"/>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
@@ -2945,31 +2948,31 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B333" s="8">
+      <c r="A333" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B333" s="4">
         <f>B331-B332</f>
         <v>2453</v>
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="7"/>
-      <c r="B334" s="8"/>
+      <c r="A334" s="3"/>
+      <c r="B334" s="4"/>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B336" s="3"/>
-      <c r="C336" s="3"/>
+      <c r="A336" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B336" s="5"/>
+      <c r="C336" s="5"/>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="4" t="s">
+      <c r="A337" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B337" s="5"/>
-      <c r="C337" s="6"/>
+      <c r="B337" s="7"/>
+      <c r="C337" s="8"/>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
@@ -3002,31 +3005,31 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B341" s="8">
+      <c r="A341" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B341" s="4">
         <f>B339-B340</f>
         <v>1173</v>
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="7"/>
-      <c r="B342" s="8"/>
+      <c r="A342" s="3"/>
+      <c r="B342" s="4"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B344" s="3"/>
-      <c r="C344" s="3"/>
+      <c r="A344" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B344" s="5"/>
+      <c r="C344" s="5"/>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B345" s="5"/>
-      <c r="C345" s="6"/>
+      <c r="B345" s="7"/>
+      <c r="C345" s="8"/>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
@@ -3059,31 +3062,31 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B349" s="8">
+      <c r="A349" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B349" s="4">
         <f>B347-B348</f>
         <v>1136</v>
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="7"/>
-      <c r="B350" s="8"/>
+      <c r="A350" s="3"/>
+      <c r="B350" s="4"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B352" s="3"/>
-      <c r="C352" s="3"/>
+      <c r="A352" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B352" s="5"/>
+      <c r="C352" s="5"/>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="4" t="s">
+      <c r="A353" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B353" s="5"/>
-      <c r="C353" s="6"/>
+      <c r="B353" s="7"/>
+      <c r="C353" s="8"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
@@ -3116,31 +3119,31 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B357" s="8">
+      <c r="A357" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B357" s="4">
         <f>B355-B356</f>
         <v>136</v>
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="7"/>
-      <c r="B358" s="8"/>
+      <c r="A358" s="3"/>
+      <c r="B358" s="4"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B360" s="3"/>
-      <c r="C360" s="3"/>
+      <c r="A360" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B360" s="5"/>
+      <c r="C360" s="5"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="4" t="s">
+      <c r="A361" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B361" s="5"/>
-      <c r="C361" s="6"/>
+      <c r="B361" s="7"/>
+      <c r="C361" s="8"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
@@ -3173,31 +3176,31 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B365" s="8">
+      <c r="A365" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B365" s="4">
         <f>B363-B364</f>
         <v>549</v>
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="7"/>
-      <c r="B366" s="8"/>
+      <c r="A366" s="3"/>
+      <c r="B366" s="4"/>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B368" s="3"/>
-      <c r="C368" s="3"/>
+      <c r="A368" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B368" s="5"/>
+      <c r="C368" s="5"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="4" t="s">
+      <c r="A369" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B369" s="5"/>
-      <c r="C369" s="6"/>
+      <c r="B369" s="7"/>
+      <c r="C369" s="8"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
@@ -3230,31 +3233,31 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B373" s="8">
+      <c r="A373" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B373" s="4">
         <f>B371-B372</f>
         <v>84</v>
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="7"/>
-      <c r="B374" s="8"/>
+      <c r="A374" s="3"/>
+      <c r="B374" s="4"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B376" s="3"/>
-      <c r="C376" s="3"/>
+      <c r="A376" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B376" s="5"/>
+      <c r="C376" s="5"/>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="4" t="s">
+      <c r="A377" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B377" s="5"/>
-      <c r="C377" s="6"/>
+      <c r="B377" s="7"/>
+      <c r="C377" s="8"/>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
@@ -3287,17 +3290,17 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B381" s="8">
+      <c r="A381" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B381" s="4">
         <f>B379-B380</f>
         <v>325</v>
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="7"/>
-      <c r="B382" s="8"/>
+      <c r="A382" s="3"/>
+      <c r="B382" s="4"/>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
@@ -3308,18 +3311,18 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B385" s="3"/>
-      <c r="C385" s="3"/>
+      <c r="A385" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B385" s="5"/>
+      <c r="C385" s="5"/>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="4" t="s">
+      <c r="A386" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B386" s="5"/>
-      <c r="C386" s="6"/>
+      <c r="B386" s="7"/>
+      <c r="C386" s="8"/>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
@@ -3352,31 +3355,31 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B390" s="8">
+      <c r="A390" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B390" s="4">
         <f>B388-B389</f>
         <v>31</v>
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="7"/>
-      <c r="B391" s="8"/>
+      <c r="A391" s="3"/>
+      <c r="B391" s="4"/>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B393" s="3"/>
-      <c r="C393" s="3"/>
+      <c r="A393" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B393" s="5"/>
+      <c r="C393" s="5"/>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="4" t="s">
+      <c r="A394" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B394" s="5"/>
-      <c r="C394" s="6"/>
+      <c r="B394" s="7"/>
+      <c r="C394" s="8"/>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
@@ -3409,31 +3412,31 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B398" s="8">
+      <c r="A398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B398" s="4">
         <f>B396-B397</f>
         <v>637</v>
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="7"/>
-      <c r="B399" s="8"/>
+      <c r="A399" s="3"/>
+      <c r="B399" s="4"/>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B401" s="3"/>
-      <c r="C401" s="3"/>
+      <c r="A401" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B401" s="5"/>
+      <c r="C401" s="5"/>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="4" t="s">
+      <c r="A402" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B402" s="5"/>
-      <c r="C402" s="6"/>
+      <c r="B402" s="7"/>
+      <c r="C402" s="8"/>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" s="1" t="s">
@@ -3466,31 +3469,31 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B406" s="8">
+      <c r="A406" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B406" s="4">
         <f>B404-B405</f>
         <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="7"/>
-      <c r="B407" s="8"/>
+      <c r="A407" s="3"/>
+      <c r="B407" s="4"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B409" s="3"/>
-      <c r="C409" s="3"/>
+      <c r="A409" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B409" s="5"/>
+      <c r="C409" s="5"/>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="4" t="s">
+      <c r="A410" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B410" s="5"/>
-      <c r="C410" s="6"/>
+      <c r="B410" s="7"/>
+      <c r="C410" s="8"/>
     </row>
     <row r="411" spans="1:3">
       <c r="A411" s="1" t="s">
@@ -3523,31 +3526,31 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B414" s="8">
+      <c r="A414" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B414" s="4">
         <f>B412-B413</f>
         <v>1579</v>
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="7"/>
-      <c r="B415" s="8"/>
+      <c r="A415" s="3"/>
+      <c r="B415" s="4"/>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B417" s="3"/>
-      <c r="C417" s="3"/>
+      <c r="A417" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B417" s="5"/>
+      <c r="C417" s="5"/>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="4" t="s">
+      <c r="A418" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B418" s="5"/>
-      <c r="C418" s="6"/>
+      <c r="B418" s="7"/>
+      <c r="C418" s="8"/>
     </row>
     <row r="419" spans="1:3">
       <c r="A419" s="1" t="s">
@@ -3580,31 +3583,31 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B422" s="8">
+      <c r="A422" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B422" s="4">
         <f>B420-B421</f>
         <v>201</v>
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="7"/>
-      <c r="B423" s="8"/>
+      <c r="A423" s="3"/>
+      <c r="B423" s="4"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B425" s="3"/>
-      <c r="C425" s="3"/>
+      <c r="A425" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B425" s="5"/>
+      <c r="C425" s="5"/>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="4" t="s">
+      <c r="A426" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B426" s="5"/>
-      <c r="C426" s="6"/>
+      <c r="B426" s="7"/>
+      <c r="C426" s="8"/>
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
@@ -3637,31 +3640,31 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B430" s="8">
+      <c r="A430" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B430" s="4">
         <f>B428-B429</f>
         <v>788</v>
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="7"/>
-      <c r="B431" s="8"/>
+      <c r="A431" s="3"/>
+      <c r="B431" s="4"/>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B433" s="3"/>
-      <c r="C433" s="3"/>
+      <c r="A433" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B433" s="5"/>
+      <c r="C433" s="5"/>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="4" t="s">
+      <c r="A434" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B434" s="5"/>
-      <c r="C434" s="6"/>
+      <c r="B434" s="7"/>
+      <c r="C434" s="8"/>
     </row>
     <row r="435" spans="1:3">
       <c r="A435" s="1" t="s">
@@ -3694,17 +3697,17 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B438" s="8">
+      <c r="A438" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B438" s="4">
         <f>B436-B437</f>
         <v>2041</v>
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="7"/>
-      <c r="B439" s="8"/>
+      <c r="A439" s="3"/>
+      <c r="B439" s="4"/>
     </row>
     <row r="440" spans="1:3">
       <c r="A440" s="1" t="s">
@@ -3715,18 +3718,18 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B442" s="3"/>
-      <c r="C442" s="3"/>
+      <c r="A442" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B442" s="5"/>
+      <c r="C442" s="5"/>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="4" t="s">
+      <c r="A443" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B443" s="5"/>
-      <c r="C443" s="6"/>
+      <c r="B443" s="7"/>
+      <c r="C443" s="8"/>
     </row>
     <row r="444" spans="1:3">
       <c r="A444" s="1" t="s">
@@ -3759,31 +3762,31 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B447" s="8">
+      <c r="A447" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B447" s="4">
         <f>B445-B446</f>
         <v>37</v>
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="7"/>
-      <c r="B448" s="8"/>
+      <c r="A448" s="3"/>
+      <c r="B448" s="4"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B450" s="3"/>
-      <c r="C450" s="3"/>
+      <c r="A450" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B450" s="5"/>
+      <c r="C450" s="5"/>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="4" t="s">
+      <c r="A451" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B451" s="5"/>
-      <c r="C451" s="6"/>
+      <c r="B451" s="7"/>
+      <c r="C451" s="8"/>
     </row>
     <row r="452" spans="1:3">
       <c r="A452" s="1" t="s">
@@ -3816,31 +3819,31 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B455" s="8">
+      <c r="A455" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B455" s="4">
         <f>B453-B454</f>
         <v>746</v>
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="7"/>
-      <c r="B456" s="8"/>
+      <c r="A456" s="3"/>
+      <c r="B456" s="4"/>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B458" s="3"/>
-      <c r="C458" s="3"/>
+      <c r="A458" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B458" s="5"/>
+      <c r="C458" s="5"/>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="4" t="s">
+      <c r="A459" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B459" s="5"/>
-      <c r="C459" s="6"/>
+      <c r="B459" s="7"/>
+      <c r="C459" s="8"/>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" s="1" t="s">
@@ -3873,31 +3876,31 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B463" s="8">
+      <c r="A463" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B463" s="4">
         <f>B461-B462</f>
         <v>65</v>
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="7"/>
-      <c r="B464" s="8"/>
+      <c r="A464" s="3"/>
+      <c r="B464" s="4"/>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B466" s="3"/>
-      <c r="C466" s="3"/>
+      <c r="A466" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B466" s="5"/>
+      <c r="C466" s="5"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="4" t="s">
+      <c r="A467" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B467" s="5"/>
-      <c r="C467" s="6"/>
+      <c r="B467" s="7"/>
+      <c r="C467" s="8"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="1" t="s">
@@ -3930,31 +3933,31 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B471" s="8">
+      <c r="A471" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B471" s="4">
         <f>B469-B470</f>
         <v>888</v>
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="7"/>
-      <c r="B472" s="8"/>
+      <c r="A472" s="3"/>
+      <c r="B472" s="4"/>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B474" s="3"/>
-      <c r="C474" s="3"/>
+      <c r="A474" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B474" s="5"/>
+      <c r="C474" s="5"/>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="4" t="s">
+      <c r="A475" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B475" s="5"/>
-      <c r="C475" s="6"/>
+      <c r="B475" s="7"/>
+      <c r="C475" s="8"/>
     </row>
     <row r="476" spans="1:3">
       <c r="A476" s="1" t="s">
@@ -3987,31 +3990,31 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B479" s="8">
+      <c r="A479" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B479" s="4">
         <f>B477-B478</f>
         <v>363</v>
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="7"/>
-      <c r="B480" s="8"/>
+      <c r="A480" s="3"/>
+      <c r="B480" s="4"/>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B482" s="3"/>
-      <c r="C482" s="3"/>
+      <c r="A482" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B482" s="5"/>
+      <c r="C482" s="5"/>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="4" t="s">
+      <c r="A483" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B483" s="5"/>
-      <c r="C483" s="6"/>
+      <c r="B483" s="7"/>
+      <c r="C483" s="8"/>
     </row>
     <row r="484" spans="1:3">
       <c r="A484" s="1" t="s">
@@ -4044,31 +4047,31 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B487" s="8">
+      <c r="A487" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B487" s="4">
         <f>B485-B486</f>
         <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="7"/>
-      <c r="B488" s="8"/>
+      <c r="A488" s="3"/>
+      <c r="B488" s="4"/>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B490" s="3"/>
-      <c r="C490" s="3"/>
+      <c r="A490" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B490" s="5"/>
+      <c r="C490" s="5"/>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="4" t="s">
+      <c r="A491" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B491" s="5"/>
-      <c r="C491" s="6"/>
+      <c r="B491" s="7"/>
+      <c r="C491" s="8"/>
     </row>
     <row r="492" spans="1:3">
       <c r="A492" s="1" t="s">
@@ -4101,17 +4104,17 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B495" s="8">
+      <c r="A495" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B495" s="4">
         <f>B493-B494</f>
         <v>260</v>
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="7"/>
-      <c r="B496" s="8"/>
+      <c r="A496" s="3"/>
+      <c r="B496" s="4"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="1" t="s">
@@ -4122,18 +4125,18 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B499" s="3"/>
-      <c r="C499" s="3"/>
+      <c r="A499" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B499" s="5"/>
+      <c r="C499" s="5"/>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="4" t="s">
+      <c r="A500" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="5"/>
-      <c r="C500" s="6"/>
+      <c r="B500" s="7"/>
+      <c r="C500" s="8"/>
     </row>
     <row r="501" spans="1:3">
       <c r="A501" s="1" t="s">
@@ -4166,31 +4169,31 @@
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B504" s="8">
+      <c r="A504" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B504" s="4">
         <f>B502-B503</f>
         <v>471</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="7"/>
-      <c r="B505" s="8"/>
+      <c r="A505" s="3"/>
+      <c r="B505" s="4"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="3"/>
-      <c r="C507" s="3"/>
+      <c r="A507" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B507" s="5"/>
+      <c r="C507" s="5"/>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="4" t="s">
+      <c r="A508" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B508" s="5"/>
-      <c r="C508" s="6"/>
+      <c r="B508" s="7"/>
+      <c r="C508" s="8"/>
     </row>
     <row r="509" spans="1:3">
       <c r="A509" s="1" t="s">
@@ -4223,31 +4226,31 @@
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B512" s="8">
+      <c r="A512" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B512" s="4">
         <f>B510-B511</f>
         <v>391</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="7"/>
-      <c r="B513" s="8"/>
+      <c r="A513" s="3"/>
+      <c r="B513" s="4"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B515" s="3"/>
-      <c r="C515" s="3"/>
+      <c r="A515" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B515" s="5"/>
+      <c r="C515" s="5"/>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="4" t="s">
+      <c r="A516" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B516" s="5"/>
-      <c r="C516" s="6"/>
+      <c r="B516" s="7"/>
+      <c r="C516" s="8"/>
     </row>
     <row r="517" spans="1:3">
       <c r="A517" s="1" t="s">
@@ -4280,31 +4283,31 @@
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B520" s="8">
+      <c r="A520" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B520" s="4">
         <f>B518-B519</f>
         <v>1654</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="7"/>
-      <c r="B521" s="8"/>
+      <c r="A521" s="3"/>
+      <c r="B521" s="4"/>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B523" s="3"/>
-      <c r="C523" s="3"/>
+      <c r="A523" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B523" s="5"/>
+      <c r="C523" s="5"/>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="4" t="s">
+      <c r="A524" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B524" s="5"/>
-      <c r="C524" s="6"/>
+      <c r="B524" s="7"/>
+      <c r="C524" s="8"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525" s="1" t="s">
@@ -4337,31 +4340,31 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B528" s="8">
+      <c r="A528" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B528" s="4">
         <f>B526-B527</f>
         <v>1076</v>
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="7"/>
-      <c r="B529" s="8"/>
+      <c r="A529" s="3"/>
+      <c r="B529" s="4"/>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B531" s="3"/>
-      <c r="C531" s="3"/>
+      <c r="A531" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B531" s="5"/>
+      <c r="C531" s="5"/>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="4" t="s">
+      <c r="A532" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B532" s="5"/>
-      <c r="C532" s="6"/>
+      <c r="B532" s="7"/>
+      <c r="C532" s="8"/>
     </row>
     <row r="533" spans="1:3">
       <c r="A533" s="1" t="s">
@@ -4394,31 +4397,31 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B536" s="8">
+      <c r="A536" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="4">
         <f>B534-B535</f>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="7"/>
-      <c r="B537" s="8"/>
+      <c r="A537" s="3"/>
+      <c r="B537" s="4"/>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B539" s="3"/>
-      <c r="C539" s="3"/>
+      <c r="A539" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B539" s="5"/>
+      <c r="C539" s="5"/>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="4" t="s">
+      <c r="A540" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B540" s="5"/>
-      <c r="C540" s="6"/>
+      <c r="B540" s="7"/>
+      <c r="C540" s="8"/>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" s="1" t="s">
@@ -4451,31 +4454,31 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B544" s="8">
+      <c r="A544" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B544" s="4">
         <f>B542-B543</f>
         <v>207</v>
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="7"/>
-      <c r="B545" s="8"/>
+      <c r="A545" s="3"/>
+      <c r="B545" s="4"/>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B547" s="3"/>
-      <c r="C547" s="3"/>
+      <c r="A547" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B547" s="5"/>
+      <c r="C547" s="5"/>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="4" t="s">
+      <c r="A548" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B548" s="5"/>
-      <c r="C548" s="6"/>
+      <c r="B548" s="7"/>
+      <c r="C548" s="8"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="1" t="s">
@@ -4508,17 +4511,17 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B552" s="8">
+      <c r="A552" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B552" s="4">
         <f>B550-B551</f>
         <v>12</v>
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="7"/>
-      <c r="B553" s="8"/>
+      <c r="A553" s="3"/>
+      <c r="B553" s="4"/>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" s="1" t="s">
@@ -4529,18 +4532,18 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B556" s="3"/>
-      <c r="C556" s="3"/>
+      <c r="A556" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B556" s="5"/>
+      <c r="C556" s="5"/>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="4" t="s">
+      <c r="A557" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B557" s="5"/>
-      <c r="C557" s="6"/>
+      <c r="B557" s="7"/>
+      <c r="C557" s="8"/>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" s="1" t="s">
@@ -4573,31 +4576,31 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B561" s="8">
+      <c r="A561" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B561" s="4">
         <f>B559-B560</f>
         <v>923</v>
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="7"/>
-      <c r="B562" s="8"/>
+      <c r="A562" s="3"/>
+      <c r="B562" s="4"/>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B564" s="3"/>
-      <c r="C564" s="3"/>
+      <c r="A564" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B564" s="5"/>
+      <c r="C564" s="5"/>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="4" t="s">
+      <c r="A565" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B565" s="5"/>
-      <c r="C565" s="6"/>
+      <c r="B565" s="7"/>
+      <c r="C565" s="8"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566" s="1" t="s">
@@ -4630,31 +4633,31 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B569" s="8">
+      <c r="A569" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="4">
         <f>B567-B568</f>
         <v>149</v>
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="7"/>
-      <c r="B570" s="8"/>
+      <c r="A570" s="3"/>
+      <c r="B570" s="4"/>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B572" s="3"/>
-      <c r="C572" s="3"/>
+      <c r="A572" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B572" s="5"/>
+      <c r="C572" s="5"/>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="4" t="s">
+      <c r="A573" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B573" s="5"/>
-      <c r="C573" s="6"/>
+      <c r="B573" s="7"/>
+      <c r="C573" s="8"/>
     </row>
     <row r="574" spans="1:3">
       <c r="A574" s="1" t="s">
@@ -4687,31 +4690,31 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B577" s="8">
+      <c r="A577" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="4">
         <f>B575-B576</f>
         <v>26</v>
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="7"/>
-      <c r="B578" s="8"/>
+      <c r="A578" s="3"/>
+      <c r="B578" s="4"/>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B580" s="3"/>
-      <c r="C580" s="3"/>
+      <c r="A580" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B580" s="5"/>
+      <c r="C580" s="5"/>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="4" t="s">
+      <c r="A581" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B581" s="5"/>
-      <c r="C581" s="6"/>
+      <c r="B581" s="7"/>
+      <c r="C581" s="8"/>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" s="1" t="s">
@@ -4744,17 +4747,17 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B585" s="8">
+      <c r="A585" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="4">
         <f>B583-B584</f>
         <v>1024</v>
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="7"/>
-      <c r="B586" s="8"/>
+      <c r="A586" s="3"/>
+      <c r="B586" s="4"/>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" s="1" t="s">
@@ -4765,18 +4768,18 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B589" s="3"/>
-      <c r="C589" s="3"/>
+      <c r="A589" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B589" s="5"/>
+      <c r="C589" s="5"/>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="4" t="s">
+      <c r="A590" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B590" s="5"/>
-      <c r="C590" s="6"/>
+      <c r="B590" s="7"/>
+      <c r="C590" s="8"/>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" s="1" t="s">
@@ -4809,31 +4812,31 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B594" s="8">
+      <c r="A594" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B594" s="4">
         <f>B592-B593</f>
         <v>288</v>
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="7"/>
-      <c r="B595" s="8"/>
+      <c r="A595" s="3"/>
+      <c r="B595" s="4"/>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B597" s="3"/>
-      <c r="C597" s="3"/>
+      <c r="A597" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B597" s="5"/>
+      <c r="C597" s="5"/>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="4" t="s">
+      <c r="A598" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B598" s="5"/>
-      <c r="C598" s="6"/>
+      <c r="B598" s="7"/>
+      <c r="C598" s="8"/>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" s="1" t="s">
@@ -4866,31 +4869,31 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B602" s="8">
+      <c r="A602" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B602" s="4">
         <f>B600-B601</f>
         <v>163</v>
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="7"/>
-      <c r="B603" s="8"/>
+      <c r="A603" s="3"/>
+      <c r="B603" s="4"/>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B605" s="3"/>
-      <c r="C605" s="3"/>
+      <c r="A605" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B605" s="5"/>
+      <c r="C605" s="5"/>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="4" t="s">
+      <c r="A606" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B606" s="5"/>
-      <c r="C606" s="6"/>
+      <c r="B606" s="7"/>
+      <c r="C606" s="8"/>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" s="1" t="s">
@@ -4923,31 +4926,31 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B610" s="8">
+      <c r="A610" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B610" s="4">
         <f>B608-B609</f>
         <v>1067</v>
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="7"/>
-      <c r="B611" s="8"/>
+      <c r="A611" s="3"/>
+      <c r="B611" s="4"/>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B613" s="3"/>
-      <c r="C613" s="3"/>
+      <c r="A613" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B613" s="5"/>
+      <c r="C613" s="5"/>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="4" t="s">
+      <c r="A614" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B614" s="5"/>
-      <c r="C614" s="6"/>
+      <c r="B614" s="7"/>
+      <c r="C614" s="8"/>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" s="1" t="s">
@@ -4980,31 +4983,31 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B618" s="8">
+      <c r="A618" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B618" s="4">
         <f>B616-B617</f>
         <v>48</v>
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="7"/>
-      <c r="B619" s="8"/>
+      <c r="A619" s="3"/>
+      <c r="B619" s="4"/>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B621" s="3"/>
-      <c r="C621" s="3"/>
+      <c r="A621" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B621" s="5"/>
+      <c r="C621" s="5"/>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="4" t="s">
+      <c r="A622" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B622" s="5"/>
-      <c r="C622" s="6"/>
+      <c r="B622" s="7"/>
+      <c r="C622" s="8"/>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" s="1" t="s">
@@ -5037,31 +5040,31 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B626" s="8">
+      <c r="A626" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="4">
         <f>B624-B625</f>
         <v>25</v>
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="7"/>
-      <c r="B627" s="8"/>
+      <c r="A627" s="3"/>
+      <c r="B627" s="4"/>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B629" s="3"/>
-      <c r="C629" s="3"/>
+      <c r="A629" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B629" s="5"/>
+      <c r="C629" s="5"/>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="4" t="s">
+      <c r="A630" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B630" s="5"/>
-      <c r="C630" s="6"/>
+      <c r="B630" s="7"/>
+      <c r="C630" s="8"/>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" s="1" t="s">
@@ -5094,31 +5097,31 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B634" s="8">
+      <c r="A634" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B634" s="4">
         <f>B632-B633</f>
         <v>104</v>
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="7"/>
-      <c r="B635" s="8"/>
+      <c r="A635" s="3"/>
+      <c r="B635" s="4"/>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B637" s="3"/>
-      <c r="C637" s="3"/>
+      <c r="A637" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B637" s="5"/>
+      <c r="C637" s="5"/>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="4" t="s">
+      <c r="A638" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B638" s="5"/>
-      <c r="C638" s="6"/>
+      <c r="B638" s="7"/>
+      <c r="C638" s="8"/>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" s="1" t="s">
@@ -5151,17 +5154,17 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B642" s="8">
+      <c r="A642" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="4">
         <f>B640-B641</f>
         <v>288</v>
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="7"/>
-      <c r="B643" s="8"/>
+      <c r="A643" s="3"/>
+      <c r="B643" s="4"/>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" s="1" t="s">
@@ -5172,18 +5175,18 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B646" s="3"/>
-      <c r="C646" s="3"/>
+      <c r="A646" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B646" s="5"/>
+      <c r="C646" s="5"/>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="4" t="s">
+      <c r="A647" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B647" s="5"/>
-      <c r="C647" s="6"/>
+      <c r="B647" s="7"/>
+      <c r="C647" s="8"/>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" s="1" t="s">
@@ -5216,31 +5219,31 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B651" s="8">
+      <c r="A651" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B651" s="4">
         <f>B649-B650</f>
         <v>324</v>
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="7"/>
-      <c r="B652" s="8"/>
+      <c r="A652" s="3"/>
+      <c r="B652" s="4"/>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B654" s="3"/>
-      <c r="C654" s="3"/>
+      <c r="A654" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B654" s="5"/>
+      <c r="C654" s="5"/>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="4" t="s">
+      <c r="A655" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="5"/>
-      <c r="C655" s="6"/>
+      <c r="B655" s="7"/>
+      <c r="C655" s="8"/>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" s="1" t="s">
@@ -5273,31 +5276,31 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B659" s="8">
+      <c r="A659" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B659" s="4">
         <f>B657-B658</f>
         <v>317</v>
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="7"/>
-      <c r="B660" s="8"/>
+      <c r="A660" s="3"/>
+      <c r="B660" s="4"/>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B662" s="3"/>
-      <c r="C662" s="3"/>
+      <c r="A662" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="5"/>
+      <c r="C662" s="5"/>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="4" t="s">
+      <c r="A663" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B663" s="5"/>
-      <c r="C663" s="6"/>
+      <c r="B663" s="7"/>
+      <c r="C663" s="8"/>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" s="1" t="s">
@@ -5330,31 +5333,31 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B667" s="8">
+      <c r="A667" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="4">
         <f>B665-B666</f>
         <v>126</v>
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="7"/>
-      <c r="B668" s="8"/>
+      <c r="A668" s="3"/>
+      <c r="B668" s="4"/>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B670" s="3"/>
-      <c r="C670" s="3"/>
+      <c r="A670" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B670" s="5"/>
+      <c r="C670" s="5"/>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="4" t="s">
+      <c r="A671" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B671" s="5"/>
-      <c r="C671" s="6"/>
+      <c r="B671" s="7"/>
+      <c r="C671" s="8"/>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" s="1" t="s">
@@ -5387,31 +5390,31 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B675" s="8">
+      <c r="A675" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="4">
         <f>B673-B674</f>
         <v>934</v>
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="7"/>
-      <c r="B676" s="8"/>
+      <c r="A676" s="3"/>
+      <c r="B676" s="4"/>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B678" s="3"/>
-      <c r="C678" s="3"/>
+      <c r="A678" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B678" s="5"/>
+      <c r="C678" s="5"/>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="4" t="s">
+      <c r="A679" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B679" s="5"/>
-      <c r="C679" s="6"/>
+      <c r="B679" s="7"/>
+      <c r="C679" s="8"/>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" s="1" t="s">
@@ -5444,31 +5447,31 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B683" s="8">
+      <c r="A683" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="4">
         <f>B681-B682</f>
         <v>17</v>
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="7"/>
-      <c r="B684" s="8"/>
+      <c r="A684" s="3"/>
+      <c r="B684" s="4"/>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B686" s="3"/>
-      <c r="C686" s="3"/>
+      <c r="A686" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B686" s="5"/>
+      <c r="C686" s="5"/>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="4" t="s">
+      <c r="A687" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B687" s="5"/>
-      <c r="C687" s="6"/>
+      <c r="B687" s="7"/>
+      <c r="C687" s="8"/>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" s="1" t="s">
@@ -5501,31 +5504,31 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B691" s="8">
+      <c r="A691" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B691" s="4">
         <f>B689-B690</f>
         <v>108</v>
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="7"/>
-      <c r="B692" s="8"/>
+      <c r="A692" s="3"/>
+      <c r="B692" s="4"/>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B694" s="3"/>
-      <c r="C694" s="3"/>
+      <c r="A694" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B694" s="5"/>
+      <c r="C694" s="5"/>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="4" t="s">
+      <c r="A695" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B695" s="5"/>
-      <c r="C695" s="6"/>
+      <c r="B695" s="7"/>
+      <c r="C695" s="8"/>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" s="1" t="s">
@@ -5558,31 +5561,31 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B699" s="8">
+      <c r="A699" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B699" s="4">
         <f>B697-B698</f>
         <v>326</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="7"/>
-      <c r="B700" s="8"/>
+      <c r="A700" s="3"/>
+      <c r="B700" s="4"/>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B702" s="3"/>
-      <c r="C702" s="3"/>
+      <c r="A702" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B702" s="5"/>
+      <c r="C702" s="5"/>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="4" t="s">
+      <c r="A703" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B703" s="5"/>
-      <c r="C703" s="6"/>
+      <c r="B703" s="7"/>
+      <c r="C703" s="8"/>
     </row>
     <row r="704" spans="1:3">
       <c r="A704" s="1" t="s">
@@ -5615,17 +5618,17 @@
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B707" s="8">
+      <c r="A707" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="4">
         <f>B705-B706</f>
         <v>448</v>
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="7"/>
-      <c r="B708" s="8"/>
+      <c r="A708" s="3"/>
+      <c r="B708" s="4"/>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" s="1" t="s">
@@ -5636,18 +5639,18 @@
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B711" s="3"/>
-      <c r="C711" s="3"/>
+      <c r="A711" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B711" s="5"/>
+      <c r="C711" s="5"/>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="4" t="s">
+      <c r="A712" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B712" s="5"/>
-      <c r="C712" s="6"/>
+      <c r="B712" s="7"/>
+      <c r="C712" s="8"/>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" s="1" t="s">
@@ -5680,31 +5683,31 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B716" s="8">
+      <c r="A716" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="4">
         <f>B714-B715</f>
         <v>27</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="7"/>
-      <c r="B717" s="8"/>
+      <c r="A717" s="3"/>
+      <c r="B717" s="4"/>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B719" s="3"/>
-      <c r="C719" s="3"/>
+      <c r="A719" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B719" s="5"/>
+      <c r="C719" s="5"/>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="4" t="s">
+      <c r="A720" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B720" s="5"/>
-      <c r="C720" s="6"/>
+      <c r="B720" s="7"/>
+      <c r="C720" s="8"/>
     </row>
     <row r="721" spans="1:3">
       <c r="A721" s="1" t="s">
@@ -5737,31 +5740,31 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B724" s="8">
+      <c r="A724" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B724" s="4">
         <f>B722-B723</f>
         <v>386</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="7"/>
-      <c r="B725" s="8"/>
+      <c r="A725" s="3"/>
+      <c r="B725" s="4"/>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B727" s="3"/>
-      <c r="C727" s="3"/>
+      <c r="A727" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B727" s="5"/>
+      <c r="C727" s="5"/>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="4" t="s">
+      <c r="A728" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B728" s="5"/>
-      <c r="C728" s="6"/>
+      <c r="B728" s="7"/>
+      <c r="C728" s="8"/>
     </row>
     <row r="729" spans="1:3">
       <c r="A729" s="1" t="s">
@@ -5794,31 +5797,31 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B732" s="8">
+      <c r="A732" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B732" s="4">
         <f>B730-B731</f>
         <v>1256</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="7"/>
-      <c r="B733" s="8"/>
+      <c r="A733" s="3"/>
+      <c r="B733" s="4"/>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B735" s="3"/>
-      <c r="C735" s="3"/>
+      <c r="A735" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B735" s="5"/>
+      <c r="C735" s="5"/>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="4" t="s">
+      <c r="A736" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B736" s="5"/>
-      <c r="C736" s="6"/>
+      <c r="B736" s="7"/>
+      <c r="C736" s="8"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="1" t="s">
@@ -5851,31 +5854,31 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B740" s="8">
+      <c r="A740" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B740" s="4">
         <f>B738-B739</f>
         <v>227</v>
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="7"/>
-      <c r="B741" s="8"/>
+      <c r="A741" s="3"/>
+      <c r="B741" s="4"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B743" s="3"/>
-      <c r="C743" s="3"/>
+      <c r="A743" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B743" s="5"/>
+      <c r="C743" s="5"/>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="4" t="s">
+      <c r="A744" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B744" s="5"/>
-      <c r="C744" s="6"/>
+      <c r="B744" s="7"/>
+      <c r="C744" s="8"/>
     </row>
     <row r="745" spans="1:3">
       <c r="A745" s="1" t="s">
@@ -5908,31 +5911,31 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B748" s="8">
+      <c r="A748" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B748" s="4">
         <f>B746-B747</f>
         <v>961</v>
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="7"/>
-      <c r="B749" s="8"/>
+      <c r="A749" s="3"/>
+      <c r="B749" s="4"/>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B751" s="3"/>
-      <c r="C751" s="3"/>
+      <c r="A751" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B751" s="5"/>
+      <c r="C751" s="5"/>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="4" t="s">
+      <c r="A752" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B752" s="5"/>
-      <c r="C752" s="6"/>
+      <c r="B752" s="7"/>
+      <c r="C752" s="8"/>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" s="1" t="s">
@@ -5965,31 +5968,31 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B756" s="8">
+      <c r="A756" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="4">
         <f>B754-B755</f>
         <v>6</v>
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="7"/>
-      <c r="B757" s="8"/>
+      <c r="A757" s="3"/>
+      <c r="B757" s="4"/>
     </row>
     <row r="759" spans="1:3">
-      <c r="A759" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B759" s="3"/>
-      <c r="C759" s="3"/>
+      <c r="A759" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B759" s="5"/>
+      <c r="C759" s="5"/>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="4" t="s">
+      <c r="A760" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B760" s="5"/>
-      <c r="C760" s="6"/>
+      <c r="B760" s="7"/>
+      <c r="C760" s="8"/>
     </row>
     <row r="761" spans="1:3">
       <c r="A761" s="1" t="s">
@@ -6022,31 +6025,31 @@
       </c>
     </row>
     <row r="764" spans="1:3">
-      <c r="A764" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B764" s="8">
+      <c r="A764" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B764" s="4">
         <f>B762-B763</f>
         <v>616</v>
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="7"/>
-      <c r="B765" s="8"/>
+      <c r="A765" s="3"/>
+      <c r="B765" s="4"/>
     </row>
     <row r="767" spans="1:3">
-      <c r="A767" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B767" s="3"/>
-      <c r="C767" s="3"/>
+      <c r="A767" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B767" s="5"/>
+      <c r="C767" s="5"/>
     </row>
     <row r="768" spans="1:3">
-      <c r="A768" s="4" t="s">
+      <c r="A768" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B768" s="5"/>
-      <c r="C768" s="6"/>
+      <c r="B768" s="7"/>
+      <c r="C768" s="8"/>
     </row>
     <row r="769" spans="1:3">
       <c r="A769" s="1" t="s">
@@ -6079,17 +6082,17 @@
       </c>
     </row>
     <row r="772" spans="1:3">
-      <c r="A772" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B772" s="8">
+      <c r="A772" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B772" s="4">
         <f>B770-B771</f>
         <v>379</v>
       </c>
     </row>
     <row r="773" spans="1:3">
-      <c r="A773" s="7"/>
-      <c r="B773" s="8"/>
+      <c r="A773" s="3"/>
+      <c r="B773" s="4"/>
     </row>
     <row r="774" spans="1:3">
       <c r="A774" s="1" t="s">
@@ -6100,18 +6103,18 @@
       </c>
     </row>
     <row r="776" spans="1:3">
-      <c r="A776" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B776" s="3"/>
-      <c r="C776" s="3"/>
+      <c r="A776" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B776" s="5"/>
+      <c r="C776" s="5"/>
     </row>
     <row r="777" spans="1:3">
-      <c r="A777" s="4" t="s">
+      <c r="A777" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B777" s="5"/>
-      <c r="C777" s="6"/>
+      <c r="B777" s="7"/>
+      <c r="C777" s="8"/>
     </row>
     <row r="778" spans="1:3">
       <c r="A778" s="1" t="s">
@@ -6144,31 +6147,31 @@
       </c>
     </row>
     <row r="781" spans="1:3">
-      <c r="A781" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B781" s="8">
+      <c r="A781" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B781" s="4">
         <f>B779-B780</f>
         <v>276</v>
       </c>
     </row>
     <row r="782" spans="1:3">
-      <c r="A782" s="7"/>
-      <c r="B782" s="8"/>
+      <c r="A782" s="3"/>
+      <c r="B782" s="4"/>
     </row>
     <row r="784" spans="1:3">
-      <c r="A784" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B784" s="3"/>
-      <c r="C784" s="3"/>
+      <c r="A784" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B784" s="5"/>
+      <c r="C784" s="5"/>
     </row>
     <row r="785" spans="1:3">
-      <c r="A785" s="4" t="s">
+      <c r="A785" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B785" s="5"/>
-      <c r="C785" s="6"/>
+      <c r="B785" s="7"/>
+      <c r="C785" s="8"/>
     </row>
     <row r="786" spans="1:3">
       <c r="A786" s="1" t="s">
@@ -6201,31 +6204,31 @@
       </c>
     </row>
     <row r="789" spans="1:3">
-      <c r="A789" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B789" s="8">
+      <c r="A789" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B789" s="4">
         <f>B787-B788</f>
         <v>596</v>
       </c>
     </row>
     <row r="790" spans="1:3">
-      <c r="A790" s="7"/>
-      <c r="B790" s="8"/>
+      <c r="A790" s="3"/>
+      <c r="B790" s="4"/>
     </row>
     <row r="792" spans="1:3">
-      <c r="A792" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B792" s="3"/>
-      <c r="C792" s="3"/>
+      <c r="A792" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B792" s="5"/>
+      <c r="C792" s="5"/>
     </row>
     <row r="793" spans="1:3">
-      <c r="A793" s="4" t="s">
+      <c r="A793" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B793" s="5"/>
-      <c r="C793" s="6"/>
+      <c r="B793" s="7"/>
+      <c r="C793" s="8"/>
     </row>
     <row r="794" spans="1:3">
       <c r="A794" s="1" t="s">
@@ -6258,31 +6261,31 @@
       </c>
     </row>
     <row r="797" spans="1:3">
-      <c r="A797" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B797" s="8">
+      <c r="A797" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B797" s="4">
         <f>B795-B796</f>
         <v>250</v>
       </c>
     </row>
     <row r="798" spans="1:3">
-      <c r="A798" s="7"/>
-      <c r="B798" s="8"/>
+      <c r="A798" s="3"/>
+      <c r="B798" s="4"/>
     </row>
     <row r="800" spans="1:3">
-      <c r="A800" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B800" s="3"/>
-      <c r="C800" s="3"/>
+      <c r="A800" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B800" s="5"/>
+      <c r="C800" s="5"/>
     </row>
     <row r="801" spans="1:3">
-      <c r="A801" s="4" t="s">
+      <c r="A801" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B801" s="5"/>
-      <c r="C801" s="6"/>
+      <c r="B801" s="7"/>
+      <c r="C801" s="8"/>
     </row>
     <row r="802" spans="1:3">
       <c r="A802" s="1" t="s">
@@ -6315,31 +6318,31 @@
       </c>
     </row>
     <row r="805" spans="1:3">
-      <c r="A805" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B805" s="8">
+      <c r="A805" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B805" s="4">
         <f>B803-B804</f>
         <v>378</v>
       </c>
     </row>
     <row r="806" spans="1:3">
-      <c r="A806" s="7"/>
-      <c r="B806" s="8"/>
+      <c r="A806" s="3"/>
+      <c r="B806" s="4"/>
     </row>
     <row r="808" spans="1:3">
-      <c r="A808" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B808" s="3"/>
-      <c r="C808" s="3"/>
+      <c r="A808" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B808" s="5"/>
+      <c r="C808" s="5"/>
     </row>
     <row r="809" spans="1:3">
-      <c r="A809" s="4" t="s">
+      <c r="A809" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B809" s="5"/>
-      <c r="C809" s="6"/>
+      <c r="B809" s="7"/>
+      <c r="C809" s="8"/>
     </row>
     <row r="810" spans="1:3">
       <c r="A810" s="1" t="s">
@@ -6372,31 +6375,31 @@
       </c>
     </row>
     <row r="813" spans="1:3">
-      <c r="A813" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B813" s="8">
+      <c r="A813" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B813" s="4">
         <f>B811-B812</f>
         <v>900</v>
       </c>
     </row>
     <row r="814" spans="1:3">
-      <c r="A814" s="7"/>
-      <c r="B814" s="8"/>
+      <c r="A814" s="3"/>
+      <c r="B814" s="4"/>
     </row>
     <row r="816" spans="1:3">
-      <c r="A816" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B816" s="3"/>
-      <c r="C816" s="3"/>
+      <c r="A816" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B816" s="5"/>
+      <c r="C816" s="5"/>
     </row>
     <row r="817" spans="1:3">
-      <c r="A817" s="4" t="s">
+      <c r="A817" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B817" s="5"/>
-      <c r="C817" s="6"/>
+      <c r="B817" s="7"/>
+      <c r="C817" s="8"/>
     </row>
     <row r="818" spans="1:3">
       <c r="A818" s="1" t="s">
@@ -6429,31 +6432,31 @@
       </c>
     </row>
     <row r="821" spans="1:3">
-      <c r="A821" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B821" s="8">
+      <c r="A821" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B821" s="4">
         <f>B819-B820</f>
         <v>74</v>
       </c>
     </row>
     <row r="822" spans="1:3">
-      <c r="A822" s="7"/>
-      <c r="B822" s="8"/>
+      <c r="A822" s="3"/>
+      <c r="B822" s="4"/>
     </row>
     <row r="824" spans="1:3">
-      <c r="A824" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B824" s="3"/>
-      <c r="C824" s="3"/>
+      <c r="A824" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B824" s="5"/>
+      <c r="C824" s="5"/>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825" s="4" t="s">
+      <c r="A825" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B825" s="5"/>
-      <c r="C825" s="6"/>
+      <c r="B825" s="7"/>
+      <c r="C825" s="8"/>
     </row>
     <row r="826" spans="1:3">
       <c r="A826" s="1" t="s">
@@ -6486,31 +6489,31 @@
       </c>
     </row>
     <row r="829" spans="1:3">
-      <c r="A829" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B829" s="8">
+      <c r="A829" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B829" s="4">
         <f>B827-B828</f>
         <v>0</v>
       </c>
     </row>
     <row r="830" spans="1:3">
-      <c r="A830" s="7"/>
-      <c r="B830" s="8"/>
+      <c r="A830" s="3"/>
+      <c r="B830" s="4"/>
     </row>
     <row r="832" spans="1:3">
-      <c r="A832" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B832" s="3"/>
-      <c r="C832" s="3"/>
+      <c r="A832" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B832" s="5"/>
+      <c r="C832" s="5"/>
     </row>
     <row r="833" spans="1:3">
-      <c r="A833" s="4" t="s">
+      <c r="A833" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B833" s="5"/>
-      <c r="C833" s="6"/>
+      <c r="B833" s="7"/>
+      <c r="C833" s="8"/>
     </row>
     <row r="834" spans="1:3">
       <c r="A834" s="1" t="s">
@@ -6543,17 +6546,17 @@
       </c>
     </row>
     <row r="837" spans="1:3">
-      <c r="A837" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B837" s="8">
+      <c r="A837" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B837" s="4">
         <f>B835-B836</f>
         <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:3">
-      <c r="A838" s="7"/>
-      <c r="B838" s="8"/>
+      <c r="A838" s="3"/>
+      <c r="B838" s="4"/>
     </row>
     <row r="839" spans="1:3">
       <c r="A839" s="1" t="s">
@@ -6564,18 +6567,18 @@
       </c>
     </row>
     <row r="841" spans="1:3">
-      <c r="A841" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B841" s="3"/>
-      <c r="C841" s="3"/>
+      <c r="A841" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B841" s="5"/>
+      <c r="C841" s="5"/>
     </row>
     <row r="842" spans="1:3">
-      <c r="A842" s="4" t="s">
+      <c r="A842" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B842" s="5"/>
-      <c r="C842" s="6"/>
+      <c r="B842" s="7"/>
+      <c r="C842" s="8"/>
     </row>
     <row r="843" spans="1:3">
       <c r="A843" s="1" t="s">
@@ -6608,31 +6611,31 @@
       </c>
     </row>
     <row r="846" spans="1:3">
-      <c r="A846" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B846" s="8">
+      <c r="A846" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B846" s="4">
         <f>B844-B845</f>
         <v>717</v>
       </c>
     </row>
     <row r="847" spans="1:3">
-      <c r="A847" s="7"/>
-      <c r="B847" s="8"/>
+      <c r="A847" s="3"/>
+      <c r="B847" s="4"/>
     </row>
     <row r="849" spans="1:3">
-      <c r="A849" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B849" s="3"/>
-      <c r="C849" s="3"/>
+      <c r="A849" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B849" s="5"/>
+      <c r="C849" s="5"/>
     </row>
     <row r="850" spans="1:3">
-      <c r="A850" s="4" t="s">
+      <c r="A850" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B850" s="5"/>
-      <c r="C850" s="6"/>
+      <c r="B850" s="7"/>
+      <c r="C850" s="8"/>
     </row>
     <row r="851" spans="1:3">
       <c r="A851" s="1" t="s">
@@ -6665,31 +6668,31 @@
       </c>
     </row>
     <row r="854" spans="1:3">
-      <c r="A854" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B854" s="8">
+      <c r="A854" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B854" s="4">
         <f>B852-B853</f>
         <v>0</v>
       </c>
     </row>
     <row r="855" spans="1:3">
-      <c r="A855" s="7"/>
-      <c r="B855" s="8"/>
+      <c r="A855" s="3"/>
+      <c r="B855" s="4"/>
     </row>
     <row r="857" spans="1:3">
-      <c r="A857" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B857" s="3"/>
-      <c r="C857" s="3"/>
+      <c r="A857" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B857" s="5"/>
+      <c r="C857" s="5"/>
     </row>
     <row r="858" spans="1:3">
-      <c r="A858" s="4" t="s">
+      <c r="A858" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B858" s="5"/>
-      <c r="C858" s="6"/>
+      <c r="B858" s="7"/>
+      <c r="C858" s="8"/>
     </row>
     <row r="859" spans="1:3">
       <c r="A859" s="1" t="s">
@@ -6722,31 +6725,31 @@
       </c>
     </row>
     <row r="862" spans="1:3">
-      <c r="A862" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B862" s="8">
+      <c r="A862" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B862" s="4">
         <f>B860-B861</f>
         <v>224</v>
       </c>
     </row>
     <row r="863" spans="1:3">
-      <c r="A863" s="7"/>
-      <c r="B863" s="8"/>
+      <c r="A863" s="3"/>
+      <c r="B863" s="4"/>
     </row>
     <row r="865" spans="1:3">
-      <c r="A865" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B865" s="3"/>
-      <c r="C865" s="3"/>
+      <c r="A865" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B865" s="5"/>
+      <c r="C865" s="5"/>
     </row>
     <row r="866" spans="1:3">
-      <c r="A866" s="4" t="s">
+      <c r="A866" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B866" s="5"/>
-      <c r="C866" s="6"/>
+      <c r="B866" s="7"/>
+      <c r="C866" s="8"/>
     </row>
     <row r="867" spans="1:3">
       <c r="A867" s="1" t="s">
@@ -6779,31 +6782,31 @@
       </c>
     </row>
     <row r="870" spans="1:3">
-      <c r="A870" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B870" s="8">
+      <c r="A870" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B870" s="4">
         <f>B868-B869</f>
         <v>124</v>
       </c>
     </row>
     <row r="871" spans="1:3">
-      <c r="A871" s="7"/>
-      <c r="B871" s="8"/>
+      <c r="A871" s="3"/>
+      <c r="B871" s="4"/>
     </row>
     <row r="873" spans="1:3">
-      <c r="A873" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B873" s="3"/>
-      <c r="C873" s="3"/>
+      <c r="A873" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B873" s="5"/>
+      <c r="C873" s="5"/>
     </row>
     <row r="874" spans="1:3">
-      <c r="A874" s="4" t="s">
+      <c r="A874" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B874" s="5"/>
-      <c r="C874" s="6"/>
+      <c r="B874" s="7"/>
+      <c r="C874" s="8"/>
     </row>
     <row r="875" spans="1:3">
       <c r="A875" s="1" t="s">
@@ -6836,31 +6839,31 @@
       </c>
     </row>
     <row r="878" spans="1:3">
-      <c r="A878" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B878" s="8">
+      <c r="A878" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B878" s="4">
         <f>B876-B877</f>
         <v>449</v>
       </c>
     </row>
     <row r="879" spans="1:3">
-      <c r="A879" s="7"/>
-      <c r="B879" s="8"/>
+      <c r="A879" s="3"/>
+      <c r="B879" s="4"/>
     </row>
     <row r="881" spans="1:3">
-      <c r="A881" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B881" s="3"/>
-      <c r="C881" s="3"/>
+      <c r="A881" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B881" s="5"/>
+      <c r="C881" s="5"/>
     </row>
     <row r="882" spans="1:3">
-      <c r="A882" s="4" t="s">
+      <c r="A882" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B882" s="5"/>
-      <c r="C882" s="6"/>
+      <c r="B882" s="7"/>
+      <c r="C882" s="8"/>
     </row>
     <row r="883" spans="1:3">
       <c r="A883" s="1" t="s">
@@ -6893,31 +6896,31 @@
       </c>
     </row>
     <row r="886" spans="1:3">
-      <c r="A886" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B886" s="8">
+      <c r="A886" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B886" s="4">
         <f>B884-B885</f>
         <v>821</v>
       </c>
     </row>
     <row r="887" spans="1:3">
-      <c r="A887" s="7"/>
-      <c r="B887" s="8"/>
+      <c r="A887" s="3"/>
+      <c r="B887" s="4"/>
     </row>
     <row r="889" spans="1:3">
-      <c r="A889" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B889" s="3"/>
-      <c r="C889" s="3"/>
+      <c r="A889" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B889" s="5"/>
+      <c r="C889" s="5"/>
     </row>
     <row r="890" spans="1:3">
-      <c r="A890" s="4" t="s">
+      <c r="A890" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B890" s="5"/>
-      <c r="C890" s="6"/>
+      <c r="B890" s="7"/>
+      <c r="C890" s="8"/>
     </row>
     <row r="891" spans="1:3">
       <c r="A891" s="1" t="s">
@@ -6950,17 +6953,17 @@
       </c>
     </row>
     <row r="894" spans="1:3">
-      <c r="A894" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B894" s="8">
+      <c r="A894" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B894" s="4">
         <f>B892-B893</f>
         <v>31</v>
       </c>
     </row>
     <row r="895" spans="1:3">
-      <c r="A895" s="7"/>
-      <c r="B895" s="8"/>
+      <c r="A895" s="3"/>
+      <c r="B895" s="4"/>
     </row>
     <row r="896" spans="1:3">
       <c r="A896" s="1" t="s">
@@ -6971,18 +6974,18 @@
       </c>
     </row>
     <row r="898" spans="1:3">
-      <c r="A898" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B898" s="3"/>
-      <c r="C898" s="3"/>
+      <c r="A898" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B898" s="5"/>
+      <c r="C898" s="5"/>
     </row>
     <row r="899" spans="1:3">
-      <c r="A899" s="4" t="s">
+      <c r="A899" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B899" s="5"/>
-      <c r="C899" s="6"/>
+      <c r="B899" s="7"/>
+      <c r="C899" s="8"/>
     </row>
     <row r="900" spans="1:3">
       <c r="A900" s="1" t="s">
@@ -7015,31 +7018,31 @@
       </c>
     </row>
     <row r="903" spans="1:3">
-      <c r="A903" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B903" s="8">
+      <c r="A903" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B903" s="4">
         <f>B901-B902</f>
         <v>22</v>
       </c>
     </row>
     <row r="904" spans="1:3">
-      <c r="A904" s="7"/>
-      <c r="B904" s="8"/>
+      <c r="A904" s="3"/>
+      <c r="B904" s="4"/>
     </row>
     <row r="906" spans="1:3">
-      <c r="A906" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B906" s="3"/>
-      <c r="C906" s="3"/>
+      <c r="A906" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B906" s="5"/>
+      <c r="C906" s="5"/>
     </row>
     <row r="907" spans="1:3">
-      <c r="A907" s="4" t="s">
+      <c r="A907" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B907" s="5"/>
-      <c r="C907" s="6"/>
+      <c r="B907" s="7"/>
+      <c r="C907" s="8"/>
     </row>
     <row r="908" spans="1:3">
       <c r="A908" s="1" t="s">
@@ -7072,31 +7075,31 @@
       </c>
     </row>
     <row r="911" spans="1:3">
-      <c r="A911" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B911" s="8">
+      <c r="A911" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B911" s="4">
         <f>B909-B910</f>
         <v>75</v>
       </c>
     </row>
     <row r="912" spans="1:3">
-      <c r="A912" s="7"/>
-      <c r="B912" s="8"/>
+      <c r="A912" s="3"/>
+      <c r="B912" s="4"/>
     </row>
     <row r="914" spans="1:3">
-      <c r="A914" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B914" s="3"/>
-      <c r="C914" s="3"/>
+      <c r="A914" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B914" s="5"/>
+      <c r="C914" s="5"/>
     </row>
     <row r="915" spans="1:3">
-      <c r="A915" s="4" t="s">
+      <c r="A915" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B915" s="5"/>
-      <c r="C915" s="6"/>
+      <c r="B915" s="7"/>
+      <c r="C915" s="8"/>
     </row>
     <row r="916" spans="1:3">
       <c r="A916" s="1" t="s">
@@ -7129,31 +7132,31 @@
       </c>
     </row>
     <row r="919" spans="1:3">
-      <c r="A919" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B919" s="8">
+      <c r="A919" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B919" s="4">
         <f>B917-B918</f>
         <v>39</v>
       </c>
     </row>
     <row r="920" spans="1:3">
-      <c r="A920" s="7"/>
-      <c r="B920" s="8"/>
+      <c r="A920" s="3"/>
+      <c r="B920" s="4"/>
     </row>
     <row r="922" spans="1:3">
-      <c r="A922" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B922" s="3"/>
-      <c r="C922" s="3"/>
+      <c r="A922" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B922" s="5"/>
+      <c r="C922" s="5"/>
     </row>
     <row r="923" spans="1:3">
-      <c r="A923" s="4" t="s">
+      <c r="A923" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B923" s="5"/>
-      <c r="C923" s="6"/>
+      <c r="B923" s="7"/>
+      <c r="C923" s="8"/>
     </row>
     <row r="924" spans="1:3">
       <c r="A924" s="1" t="s">
@@ -7186,31 +7189,31 @@
       </c>
     </row>
     <row r="927" spans="1:3">
-      <c r="A927" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B927" s="8">
+      <c r="A927" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B927" s="4">
         <f>B925-B926</f>
         <v>70</v>
       </c>
     </row>
     <row r="928" spans="1:3">
-      <c r="A928" s="7"/>
-      <c r="B928" s="8"/>
+      <c r="A928" s="3"/>
+      <c r="B928" s="4"/>
     </row>
     <row r="930" spans="1:3">
-      <c r="A930" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B930" s="3"/>
-      <c r="C930" s="3"/>
+      <c r="A930" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B930" s="5"/>
+      <c r="C930" s="5"/>
     </row>
     <row r="931" spans="1:3">
-      <c r="A931" s="4" t="s">
+      <c r="A931" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B931" s="5"/>
-      <c r="C931" s="6"/>
+      <c r="B931" s="7"/>
+      <c r="C931" s="8"/>
     </row>
     <row r="932" spans="1:3">
       <c r="A932" s="1" t="s">
@@ -7243,31 +7246,31 @@
       </c>
     </row>
     <row r="935" spans="1:3">
-      <c r="A935" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B935" s="8">
+      <c r="A935" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B935" s="4">
         <f>B933-B934</f>
         <v>0</v>
       </c>
     </row>
     <row r="936" spans="1:3">
-      <c r="A936" s="7"/>
-      <c r="B936" s="8"/>
+      <c r="A936" s="3"/>
+      <c r="B936" s="4"/>
     </row>
     <row r="938" spans="1:3">
-      <c r="A938" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B938" s="3"/>
-      <c r="C938" s="3"/>
+      <c r="A938" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B938" s="5"/>
+      <c r="C938" s="5"/>
     </row>
     <row r="939" spans="1:3">
-      <c r="A939" s="4" t="s">
+      <c r="A939" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B939" s="5"/>
-      <c r="C939" s="6"/>
+      <c r="B939" s="7"/>
+      <c r="C939" s="8"/>
     </row>
     <row r="940" spans="1:3">
       <c r="A940" s="1" t="s">
@@ -7300,17 +7303,17 @@
       </c>
     </row>
     <row r="943" spans="1:3">
-      <c r="A943" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B943" s="8">
+      <c r="A943" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B943" s="4">
         <f>B941-B942</f>
         <v>59</v>
       </c>
     </row>
     <row r="944" spans="1:3">
-      <c r="A944" s="7"/>
-      <c r="B944" s="8"/>
+      <c r="A944" s="3"/>
+      <c r="B944" s="4"/>
     </row>
     <row r="945" spans="1:3">
       <c r="A945" s="1" t="s">
@@ -7321,18 +7324,18 @@
       </c>
     </row>
     <row r="947" spans="1:3">
-      <c r="A947" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B947" s="3"/>
-      <c r="C947" s="3"/>
+      <c r="A947" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B947" s="5"/>
+      <c r="C947" s="5"/>
     </row>
     <row r="948" spans="1:3">
-      <c r="A948" s="4" t="s">
+      <c r="A948" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B948" s="5"/>
-      <c r="C948" s="6"/>
+      <c r="B948" s="7"/>
+      <c r="C948" s="8"/>
     </row>
     <row r="949" spans="1:3">
       <c r="A949" s="1" t="s">
@@ -7365,31 +7368,31 @@
       </c>
     </row>
     <row r="952" spans="1:3">
-      <c r="A952" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B952" s="8">
+      <c r="A952" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B952" s="4">
         <f>B950-B951</f>
         <v>1667</v>
       </c>
     </row>
     <row r="953" spans="1:3">
-      <c r="A953" s="7"/>
-      <c r="B953" s="8"/>
+      <c r="A953" s="3"/>
+      <c r="B953" s="4"/>
     </row>
     <row r="955" spans="1:3">
-      <c r="A955" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B955" s="3"/>
-      <c r="C955" s="3"/>
+      <c r="A955" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B955" s="5"/>
+      <c r="C955" s="5"/>
     </row>
     <row r="956" spans="1:3">
-      <c r="A956" s="4" t="s">
+      <c r="A956" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B956" s="5"/>
-      <c r="C956" s="6"/>
+      <c r="B956" s="7"/>
+      <c r="C956" s="8"/>
     </row>
     <row r="957" spans="1:3">
       <c r="A957" s="1" t="s">
@@ -7422,31 +7425,31 @@
       </c>
     </row>
     <row r="960" spans="1:3">
-      <c r="A960" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B960" s="8">
+      <c r="A960" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B960" s="4">
         <f>B958-B959</f>
         <v>61</v>
       </c>
     </row>
     <row r="961" spans="1:3">
-      <c r="A961" s="7"/>
-      <c r="B961" s="8"/>
+      <c r="A961" s="3"/>
+      <c r="B961" s="4"/>
     </row>
     <row r="963" spans="1:3">
-      <c r="A963" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B963" s="3"/>
-      <c r="C963" s="3"/>
+      <c r="A963" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B963" s="5"/>
+      <c r="C963" s="5"/>
     </row>
     <row r="964" spans="1:3">
-      <c r="A964" s="4" t="s">
+      <c r="A964" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B964" s="5"/>
-      <c r="C964" s="6"/>
+      <c r="B964" s="7"/>
+      <c r="C964" s="8"/>
     </row>
     <row r="965" spans="1:3">
       <c r="A965" s="1" t="s">
@@ -7479,31 +7482,31 @@
       </c>
     </row>
     <row r="968" spans="1:3">
-      <c r="A968" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B968" s="8">
+      <c r="A968" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B968" s="4">
         <f>B966-B967</f>
         <v>199</v>
       </c>
     </row>
     <row r="969" spans="1:3">
-      <c r="A969" s="7"/>
-      <c r="B969" s="8"/>
+      <c r="A969" s="3"/>
+      <c r="B969" s="4"/>
     </row>
     <row r="971" spans="1:3">
-      <c r="A971" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B971" s="3"/>
-      <c r="C971" s="3"/>
+      <c r="A971" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B971" s="5"/>
+      <c r="C971" s="5"/>
     </row>
     <row r="972" spans="1:3">
-      <c r="A972" s="4" t="s">
+      <c r="A972" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B972" s="5"/>
-      <c r="C972" s="6"/>
+      <c r="B972" s="7"/>
+      <c r="C972" s="8"/>
     </row>
     <row r="973" spans="1:3">
       <c r="A973" s="1" t="s">
@@ -7536,31 +7539,31 @@
       </c>
     </row>
     <row r="976" spans="1:3">
-      <c r="A976" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B976" s="8">
+      <c r="A976" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B976" s="4">
         <f>B974-B975</f>
         <v>534</v>
       </c>
     </row>
     <row r="977" spans="1:3">
-      <c r="A977" s="7"/>
-      <c r="B977" s="8"/>
+      <c r="A977" s="3"/>
+      <c r="B977" s="4"/>
     </row>
     <row r="979" spans="1:3">
-      <c r="A979" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B979" s="3"/>
-      <c r="C979" s="3"/>
+      <c r="A979" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B979" s="5"/>
+      <c r="C979" s="5"/>
     </row>
     <row r="980" spans="1:3">
-      <c r="A980" s="4" t="s">
+      <c r="A980" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B980" s="5"/>
-      <c r="C980" s="6"/>
+      <c r="B980" s="7"/>
+      <c r="C980" s="8"/>
     </row>
     <row r="981" spans="1:3">
       <c r="A981" s="1" t="s">
@@ -7593,31 +7596,31 @@
       </c>
     </row>
     <row r="984" spans="1:3">
-      <c r="A984" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B984" s="8">
+      <c r="A984" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B984" s="4">
         <f>B982-B983</f>
         <v>59</v>
       </c>
     </row>
     <row r="985" spans="1:3">
-      <c r="A985" s="7"/>
-      <c r="B985" s="8"/>
+      <c r="A985" s="3"/>
+      <c r="B985" s="4"/>
     </row>
     <row r="987" spans="1:3">
-      <c r="A987" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B987" s="3"/>
-      <c r="C987" s="3"/>
+      <c r="A987" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B987" s="5"/>
+      <c r="C987" s="5"/>
     </row>
     <row r="988" spans="1:3">
-      <c r="A988" s="4" t="s">
+      <c r="A988" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B988" s="5"/>
-      <c r="C988" s="6"/>
+      <c r="B988" s="7"/>
+      <c r="C988" s="8"/>
     </row>
     <row r="989" spans="1:3">
       <c r="A989" s="1" t="s">
@@ -7650,31 +7653,31 @@
       </c>
     </row>
     <row r="992" spans="1:3">
-      <c r="A992" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B992" s="8">
+      <c r="A992" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B992" s="4">
         <f>B990-B991</f>
         <v>164</v>
       </c>
     </row>
     <row r="993" spans="1:3">
-      <c r="A993" s="7"/>
-      <c r="B993" s="8"/>
+      <c r="A993" s="3"/>
+      <c r="B993" s="4"/>
     </row>
     <row r="995" spans="1:3">
-      <c r="A995" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B995" s="3"/>
-      <c r="C995" s="3"/>
+      <c r="A995" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B995" s="5"/>
+      <c r="C995" s="5"/>
     </row>
     <row r="996" spans="1:3">
-      <c r="A996" s="4" t="s">
+      <c r="A996" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B996" s="5"/>
-      <c r="C996" s="6"/>
+      <c r="B996" s="7"/>
+      <c r="C996" s="8"/>
     </row>
     <row r="997" spans="1:3">
       <c r="A997" s="1" t="s">
@@ -7707,31 +7710,31 @@
       </c>
     </row>
     <row r="1000" spans="1:3">
-      <c r="A1000" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1000" s="8">
+      <c r="A1000" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1000" s="4">
         <f>B998-B999</f>
         <v>1579</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
-      <c r="A1001" s="7"/>
-      <c r="B1001" s="8"/>
+      <c r="A1001" s="3"/>
+      <c r="B1001" s="4"/>
     </row>
     <row r="1003" spans="1:3">
-      <c r="A1003" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1003" s="3"/>
-      <c r="C1003" s="3"/>
+      <c r="A1003" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1003" s="5"/>
+      <c r="C1003" s="5"/>
     </row>
     <row r="1004" spans="1:3">
-      <c r="A1004" s="4" t="s">
+      <c r="A1004" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1004" s="5"/>
-      <c r="C1004" s="6"/>
+      <c r="B1004" s="7"/>
+      <c r="C1004" s="8"/>
     </row>
     <row r="1005" spans="1:3">
       <c r="A1005" s="1" t="s">
@@ -7764,17 +7767,17 @@
       </c>
     </row>
     <row r="1008" spans="1:3">
-      <c r="A1008" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1008" s="8">
+      <c r="A1008" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1008" s="4">
         <f>B1006-B1007</f>
         <v>618</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
-      <c r="A1009" s="7"/>
-      <c r="B1009" s="8"/>
+      <c r="A1009" s="3"/>
+      <c r="B1009" s="4"/>
     </row>
     <row r="1010" spans="1:3">
       <c r="A1010" s="1" t="s">
@@ -7785,18 +7788,18 @@
       </c>
     </row>
     <row r="1012" spans="1:3">
-      <c r="A1012" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1012" s="3"/>
-      <c r="C1012" s="3"/>
+      <c r="A1012" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1012" s="5"/>
+      <c r="C1012" s="5"/>
     </row>
     <row r="1013" spans="1:3">
-      <c r="A1013" s="4" t="s">
+      <c r="A1013" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1013" s="5"/>
-      <c r="C1013" s="6"/>
+      <c r="B1013" s="7"/>
+      <c r="C1013" s="8"/>
     </row>
     <row r="1014" spans="1:3">
       <c r="A1014" s="1" t="s">
@@ -7829,31 +7832,31 @@
       </c>
     </row>
     <row r="1017" spans="1:3">
-      <c r="A1017" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1017" s="8">
+      <c r="A1017" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1017" s="4">
         <f>B1015-B1016</f>
         <v>166</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
-      <c r="A1018" s="7"/>
-      <c r="B1018" s="8"/>
+      <c r="A1018" s="3"/>
+      <c r="B1018" s="4"/>
     </row>
     <row r="1020" spans="1:3">
-      <c r="A1020" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1020" s="3"/>
-      <c r="C1020" s="3"/>
+      <c r="A1020" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1020" s="5"/>
+      <c r="C1020" s="5"/>
     </row>
     <row r="1021" spans="1:3">
-      <c r="A1021" s="4" t="s">
+      <c r="A1021" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1021" s="5"/>
-      <c r="C1021" s="6"/>
+      <c r="B1021" s="7"/>
+      <c r="C1021" s="8"/>
     </row>
     <row r="1022" spans="1:3">
       <c r="A1022" s="1" t="s">
@@ -7886,31 +7889,31 @@
       </c>
     </row>
     <row r="1025" spans="1:3">
-      <c r="A1025" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1025" s="8">
+      <c r="A1025" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1025" s="4">
         <f>B1023-B1024</f>
         <v>77</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
-      <c r="A1026" s="7"/>
-      <c r="B1026" s="8"/>
+      <c r="A1026" s="3"/>
+      <c r="B1026" s="4"/>
     </row>
     <row r="1028" spans="1:3">
-      <c r="A1028" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1028" s="3"/>
-      <c r="C1028" s="3"/>
+      <c r="A1028" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1028" s="5"/>
+      <c r="C1028" s="5"/>
     </row>
     <row r="1029" spans="1:3">
-      <c r="A1029" s="4" t="s">
+      <c r="A1029" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1029" s="5"/>
-      <c r="C1029" s="6"/>
+      <c r="B1029" s="7"/>
+      <c r="C1029" s="8"/>
     </row>
     <row r="1030" spans="1:3">
       <c r="A1030" s="1" t="s">
@@ -7943,31 +7946,31 @@
       </c>
     </row>
     <row r="1033" spans="1:3">
-      <c r="A1033" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1033" s="8">
+      <c r="A1033" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1033" s="4">
         <f>B1031-B1032</f>
         <v>11</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
-      <c r="A1034" s="7"/>
-      <c r="B1034" s="8"/>
+      <c r="A1034" s="3"/>
+      <c r="B1034" s="4"/>
     </row>
     <row r="1036" spans="1:3">
-      <c r="A1036" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1036" s="3"/>
-      <c r="C1036" s="3"/>
+      <c r="A1036" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1036" s="5"/>
+      <c r="C1036" s="5"/>
     </row>
     <row r="1037" spans="1:3">
-      <c r="A1037" s="4" t="s">
+      <c r="A1037" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1037" s="5"/>
-      <c r="C1037" s="6"/>
+      <c r="B1037" s="7"/>
+      <c r="C1037" s="8"/>
     </row>
     <row r="1038" spans="1:3">
       <c r="A1038" s="1" t="s">
@@ -8000,31 +8003,31 @@
       </c>
     </row>
     <row r="1041" spans="1:3">
-      <c r="A1041" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1041" s="8">
+      <c r="A1041" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1041" s="4">
         <f>B1039-B1040</f>
         <v>148</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
-      <c r="A1042" s="7"/>
-      <c r="B1042" s="8"/>
+      <c r="A1042" s="3"/>
+      <c r="B1042" s="4"/>
     </row>
     <row r="1044" spans="1:3">
-      <c r="A1044" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1044" s="3"/>
-      <c r="C1044" s="3"/>
+      <c r="A1044" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1044" s="5"/>
+      <c r="C1044" s="5"/>
     </row>
     <row r="1045" spans="1:3">
-      <c r="A1045" s="4" t="s">
+      <c r="A1045" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1045" s="5"/>
-      <c r="C1045" s="6"/>
+      <c r="B1045" s="7"/>
+      <c r="C1045" s="8"/>
     </row>
     <row r="1046" spans="1:3">
       <c r="A1046" s="1" t="s">
@@ -8057,31 +8060,31 @@
       </c>
     </row>
     <row r="1049" spans="1:3">
-      <c r="A1049" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1049" s="8">
+      <c r="A1049" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1049" s="4">
         <f>B1047-B1048</f>
         <v>1669</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
-      <c r="A1050" s="7"/>
-      <c r="B1050" s="8"/>
+      <c r="A1050" s="3"/>
+      <c r="B1050" s="4"/>
     </row>
     <row r="1052" spans="1:3">
-      <c r="A1052" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1052" s="3"/>
-      <c r="C1052" s="3"/>
+      <c r="A1052" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1052" s="5"/>
+      <c r="C1052" s="5"/>
     </row>
     <row r="1053" spans="1:3">
-      <c r="A1053" s="4" t="s">
+      <c r="A1053" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1053" s="5"/>
-      <c r="C1053" s="6"/>
+      <c r="B1053" s="7"/>
+      <c r="C1053" s="8"/>
     </row>
     <row r="1054" spans="1:3">
       <c r="A1054" s="1" t="s">
@@ -8114,31 +8117,31 @@
       </c>
     </row>
     <row r="1057" spans="1:3">
-      <c r="A1057" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1057" s="8">
+      <c r="A1057" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1057" s="4">
         <f>B1055-B1056</f>
         <v>675</v>
       </c>
     </row>
     <row r="1058" spans="1:3">
-      <c r="A1058" s="7"/>
-      <c r="B1058" s="8"/>
+      <c r="A1058" s="3"/>
+      <c r="B1058" s="4"/>
     </row>
     <row r="1060" spans="1:3">
-      <c r="A1060" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1060" s="3"/>
-      <c r="C1060" s="3"/>
+      <c r="A1060" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1060" s="5"/>
+      <c r="C1060" s="5"/>
     </row>
     <row r="1061" spans="1:3">
-      <c r="A1061" s="4" t="s">
+      <c r="A1061" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1061" s="5"/>
-      <c r="C1061" s="6"/>
+      <c r="B1061" s="7"/>
+      <c r="C1061" s="8"/>
     </row>
     <row r="1062" spans="1:3">
       <c r="A1062" s="1" t="s">
@@ -8171,31 +8174,31 @@
       </c>
     </row>
     <row r="1065" spans="1:3">
-      <c r="A1065" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1065" s="8">
+      <c r="A1065" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1065" s="4">
         <f>B1063-B1064</f>
         <v>100</v>
       </c>
     </row>
     <row r="1066" spans="1:3">
-      <c r="A1066" s="7"/>
-      <c r="B1066" s="8"/>
+      <c r="A1066" s="3"/>
+      <c r="B1066" s="4"/>
     </row>
     <row r="1068" spans="1:3">
-      <c r="A1068" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1068" s="3"/>
-      <c r="C1068" s="3"/>
+      <c r="A1068" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1068" s="5"/>
+      <c r="C1068" s="5"/>
     </row>
     <row r="1069" spans="1:3">
-      <c r="A1069" s="4" t="s">
+      <c r="A1069" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1069" s="5"/>
-      <c r="C1069" s="6"/>
+      <c r="B1069" s="7"/>
+      <c r="C1069" s="8"/>
     </row>
     <row r="1070" spans="1:3">
       <c r="A1070" s="1" t="s">
@@ -8228,17 +8231,17 @@
       </c>
     </row>
     <row r="1073" spans="1:3">
-      <c r="A1073" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1073" s="8">
+      <c r="A1073" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1073" s="4">
         <f>B1071-B1072</f>
         <v>147</v>
       </c>
     </row>
     <row r="1074" spans="1:3">
-      <c r="A1074" s="7"/>
-      <c r="B1074" s="8"/>
+      <c r="A1074" s="3"/>
+      <c r="B1074" s="4"/>
     </row>
     <row r="1075" spans="1:3">
       <c r="A1075" s="1" t="s">
@@ -8249,18 +8252,18 @@
       </c>
     </row>
     <row r="1077" spans="1:3">
-      <c r="A1077" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1077" s="3"/>
-      <c r="C1077" s="3"/>
+      <c r="A1077" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1077" s="5"/>
+      <c r="C1077" s="5"/>
     </row>
     <row r="1078" spans="1:3">
-      <c r="A1078" s="4" t="s">
+      <c r="A1078" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1078" s="5"/>
-      <c r="C1078" s="6"/>
+      <c r="B1078" s="7"/>
+      <c r="C1078" s="8"/>
     </row>
     <row r="1079" spans="1:3">
       <c r="A1079" s="1" t="s">
@@ -8293,31 +8296,31 @@
       </c>
     </row>
     <row r="1082" spans="1:3">
-      <c r="A1082" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1082" s="8">
+      <c r="A1082" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1082" s="4">
         <f>B1080-B1081</f>
         <v>90</v>
       </c>
     </row>
     <row r="1083" spans="1:3">
-      <c r="A1083" s="7"/>
-      <c r="B1083" s="8"/>
+      <c r="A1083" s="3"/>
+      <c r="B1083" s="4"/>
     </row>
     <row r="1085" spans="1:3">
-      <c r="A1085" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1085" s="3"/>
-      <c r="C1085" s="3"/>
+      <c r="A1085" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1085" s="5"/>
+      <c r="C1085" s="5"/>
     </row>
     <row r="1086" spans="1:3">
-      <c r="A1086" s="4" t="s">
+      <c r="A1086" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1086" s="5"/>
-      <c r="C1086" s="6"/>
+      <c r="B1086" s="7"/>
+      <c r="C1086" s="8"/>
     </row>
     <row r="1087" spans="1:3">
       <c r="A1087" s="1" t="s">
@@ -8350,31 +8353,31 @@
       </c>
     </row>
     <row r="1090" spans="1:3">
-      <c r="A1090" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1090" s="8">
+      <c r="A1090" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1090" s="4">
         <f>B1088-B1089</f>
         <v>262</v>
       </c>
     </row>
     <row r="1091" spans="1:3">
-      <c r="A1091" s="7"/>
-      <c r="B1091" s="8"/>
+      <c r="A1091" s="3"/>
+      <c r="B1091" s="4"/>
     </row>
     <row r="1093" spans="1:3">
-      <c r="A1093" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1093" s="3"/>
-      <c r="C1093" s="3"/>
+      <c r="A1093" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1093" s="5"/>
+      <c r="C1093" s="5"/>
     </row>
     <row r="1094" spans="1:3">
-      <c r="A1094" s="4" t="s">
+      <c r="A1094" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1094" s="5"/>
-      <c r="C1094" s="6"/>
+      <c r="B1094" s="7"/>
+      <c r="C1094" s="8"/>
     </row>
     <row r="1095" spans="1:3">
       <c r="A1095" s="1" t="s">
@@ -8407,31 +8410,31 @@
       </c>
     </row>
     <row r="1098" spans="1:3">
-      <c r="A1098" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1098" s="8">
+      <c r="A1098" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1098" s="4">
         <f>B1096-B1097</f>
         <v>43</v>
       </c>
     </row>
     <row r="1099" spans="1:3">
-      <c r="A1099" s="7"/>
-      <c r="B1099" s="8"/>
+      <c r="A1099" s="3"/>
+      <c r="B1099" s="4"/>
     </row>
     <row r="1101" spans="1:3">
-      <c r="A1101" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1101" s="3"/>
-      <c r="C1101" s="3"/>
+      <c r="A1101" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1101" s="5"/>
+      <c r="C1101" s="5"/>
     </row>
     <row r="1102" spans="1:3">
-      <c r="A1102" s="4" t="s">
+      <c r="A1102" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1102" s="5"/>
-      <c r="C1102" s="6"/>
+      <c r="B1102" s="7"/>
+      <c r="C1102" s="8"/>
     </row>
     <row r="1103" spans="1:3">
       <c r="A1103" s="1" t="s">
@@ -8464,31 +8467,31 @@
       </c>
     </row>
     <row r="1106" spans="1:3">
-      <c r="A1106" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1106" s="8">
+      <c r="A1106" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1106" s="4">
         <f>B1104-B1105</f>
         <v>262</v>
       </c>
     </row>
     <row r="1107" spans="1:3">
-      <c r="A1107" s="7"/>
-      <c r="B1107" s="8"/>
+      <c r="A1107" s="3"/>
+      <c r="B1107" s="4"/>
     </row>
     <row r="1109" spans="1:3">
-      <c r="A1109" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1109" s="3"/>
-      <c r="C1109" s="3"/>
+      <c r="A1109" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1109" s="5"/>
+      <c r="C1109" s="5"/>
     </row>
     <row r="1110" spans="1:3">
-      <c r="A1110" s="4" t="s">
+      <c r="A1110" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1110" s="5"/>
-      <c r="C1110" s="6"/>
+      <c r="B1110" s="7"/>
+      <c r="C1110" s="8"/>
     </row>
     <row r="1111" spans="1:3">
       <c r="A1111" s="1" t="s">
@@ -8521,145 +8524,915 @@
       </c>
     </row>
     <row r="1114" spans="1:3">
-      <c r="A1114" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1114" s="8">
+      <c r="A1114" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1114" s="4">
         <f>B1112-B1113</f>
         <v>61</v>
       </c>
     </row>
     <row r="1115" spans="1:3">
-      <c r="A1115" s="7"/>
-      <c r="B1115" s="8"/>
+      <c r="A1115" s="3"/>
+      <c r="B1115" s="4"/>
+    </row>
+    <row r="1117" spans="1:3">
+      <c r="A1117" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1117" s="5"/>
+      <c r="C1117" s="5"/>
+    </row>
+    <row r="1118" spans="1:3">
+      <c r="A1118" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1118" s="7"/>
+      <c r="C1118" s="8"/>
+    </row>
+    <row r="1119" spans="1:3">
+      <c r="A1119" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1119" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:3">
+      <c r="A1120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1120" s="2">
+        <v>1158</v>
+      </c>
+      <c r="C1120" s="2">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:3">
+      <c r="A1121" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1121" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:3">
+      <c r="A1122" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1122" s="4">
+        <f>B1120-B1121</f>
+        <v>524</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3">
+      <c r="A1123" s="3"/>
+      <c r="B1123" s="4"/>
+    </row>
+    <row r="1124" spans="1:3">
+      <c r="A1124" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1124" s="2">
+        <v>52265</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:3">
+      <c r="A1126" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1126" s="5"/>
+      <c r="C1126" s="5"/>
+    </row>
+    <row r="1127" spans="1:3">
+      <c r="A1127" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1127" s="7"/>
+      <c r="C1127" s="8"/>
+    </row>
+    <row r="1128" spans="1:3">
+      <c r="A1128" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1128" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:3">
+      <c r="A1129" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1129" s="2">
+        <v>1097</v>
+      </c>
+      <c r="C1129" s="2">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3">
+      <c r="A1130" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1130" s="2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:3">
+      <c r="A1131" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1131" s="4">
+        <f>B1129-B1130</f>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:3">
+      <c r="A1132" s="3"/>
+      <c r="B1132" s="4"/>
+    </row>
+    <row r="1134" spans="1:3">
+      <c r="A1134" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1134" s="5"/>
+      <c r="C1134" s="5"/>
+    </row>
+    <row r="1135" spans="1:3">
+      <c r="A1135" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1135" s="7"/>
+      <c r="C1135" s="8"/>
+    </row>
+    <row r="1136" spans="1:3">
+      <c r="A1136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1136" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:3">
+      <c r="A1137" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1137" s="2">
+        <v>67</v>
+      </c>
+      <c r="C1137" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3">
+      <c r="A1138" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1138" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:3">
+      <c r="A1139" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1139" s="4">
+        <f>B1137-B1138</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3">
+      <c r="A1140" s="3"/>
+      <c r="B1140" s="4"/>
+    </row>
+    <row r="1142" spans="1:3">
+      <c r="A1142" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1142" s="5"/>
+      <c r="C1142" s="5"/>
+    </row>
+    <row r="1143" spans="1:3">
+      <c r="A1143" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1143" s="7"/>
+      <c r="C1143" s="8"/>
+    </row>
+    <row r="1144" spans="1:3">
+      <c r="A1144" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1144" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1144" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:3">
+      <c r="A1145" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1145" s="2">
+        <v>103</v>
+      </c>
+      <c r="C1145" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:3">
+      <c r="A1146" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1146" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:3">
+      <c r="A1147" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1147" s="4">
+        <f>B1145-B1146</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:3">
+      <c r="A1148" s="3"/>
+      <c r="B1148" s="4"/>
+    </row>
+    <row r="1150" spans="1:3">
+      <c r="A1150" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1150" s="5"/>
+      <c r="C1150" s="5"/>
+    </row>
+    <row r="1151" spans="1:3">
+      <c r="A1151" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1151" s="7"/>
+      <c r="C1151" s="8"/>
+    </row>
+    <row r="1152" spans="1:3">
+      <c r="A1152" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1152" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1152" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:3">
+      <c r="A1153" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1153" s="2">
+        <v>318</v>
+      </c>
+      <c r="C1153" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:3">
+      <c r="A1154" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1154" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3">
+      <c r="A1155" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1155" s="4">
+        <f>B1153-B1154</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:3">
+      <c r="A1156" s="3"/>
+      <c r="B1156" s="4"/>
+    </row>
+    <row r="1158" spans="1:3">
+      <c r="A1158" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1158" s="5"/>
+      <c r="C1158" s="5"/>
+    </row>
+    <row r="1159" spans="1:3">
+      <c r="A1159" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1159" s="7"/>
+      <c r="C1159" s="8"/>
+    </row>
+    <row r="1160" spans="1:3">
+      <c r="A1160" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1160" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1160" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3">
+      <c r="A1161" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1161" s="2">
+        <v>610</v>
+      </c>
+      <c r="C1161" s="2">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:3">
+      <c r="A1162" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1162" s="2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:3">
+      <c r="A1163" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1163" s="4">
+        <f>B1161-B1162</f>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:3">
+      <c r="A1164" s="3"/>
+      <c r="B1164" s="4"/>
+    </row>
+    <row r="1166" spans="1:3">
+      <c r="A1166" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1166" s="5"/>
+      <c r="C1166" s="5"/>
+    </row>
+    <row r="1167" spans="1:3">
+      <c r="A1167" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1167" s="7"/>
+      <c r="C1167" s="8"/>
+    </row>
+    <row r="1168" spans="1:3">
+      <c r="A1168" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1168" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1168" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:3">
+      <c r="A1169" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1169" s="2">
+        <v>247</v>
+      </c>
+      <c r="C1169" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:3">
+      <c r="A1170" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1170" s="2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:3">
+      <c r="A1171" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1171" s="4">
+        <f>B1169-B1170</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:3">
+      <c r="A1172" s="3"/>
+      <c r="B1172" s="4"/>
+    </row>
+    <row r="1174" spans="1:3">
+      <c r="A1174" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1174" s="5"/>
+      <c r="C1174" s="5"/>
+    </row>
+    <row r="1175" spans="1:3">
+      <c r="A1175" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1175" s="7"/>
+      <c r="C1175" s="8"/>
+    </row>
+    <row r="1176" spans="1:3">
+      <c r="A1176" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1176" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1176" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:3">
+      <c r="A1177" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1177" s="2">
+        <v>220</v>
+      </c>
+      <c r="C1177" s="2">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:3">
+      <c r="A1178" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1178" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:3">
+      <c r="A1179" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1179" s="4">
+        <f>B1177-B1178</f>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:3">
+      <c r="A1180" s="3"/>
+      <c r="B1180" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="548">
-    <mergeCell ref="A1106:A1107"/>
-    <mergeCell ref="B1106:B1107"/>
-    <mergeCell ref="A1109:C1109"/>
-    <mergeCell ref="A1110:C1110"/>
-    <mergeCell ref="A1114:A1115"/>
-    <mergeCell ref="B1114:B1115"/>
-    <mergeCell ref="A1086:C1086"/>
-    <mergeCell ref="A1090:A1091"/>
-    <mergeCell ref="B1090:B1091"/>
-    <mergeCell ref="A1093:C1093"/>
-    <mergeCell ref="A1094:C1094"/>
-    <mergeCell ref="A1098:A1099"/>
-    <mergeCell ref="B1098:B1099"/>
-    <mergeCell ref="A1101:C1101"/>
-    <mergeCell ref="A1102:C1102"/>
-    <mergeCell ref="A1068:C1068"/>
-    <mergeCell ref="A1069:C1069"/>
-    <mergeCell ref="A1073:A1074"/>
-    <mergeCell ref="B1073:B1074"/>
-    <mergeCell ref="A1077:C1077"/>
-    <mergeCell ref="A1078:C1078"/>
-    <mergeCell ref="A1082:A1083"/>
-    <mergeCell ref="B1082:B1083"/>
-    <mergeCell ref="A1085:C1085"/>
-    <mergeCell ref="A927:A928"/>
-    <mergeCell ref="B927:B928"/>
-    <mergeCell ref="A930:C930"/>
-    <mergeCell ref="A931:C931"/>
-    <mergeCell ref="A935:A936"/>
-    <mergeCell ref="B935:B936"/>
-    <mergeCell ref="A907:C907"/>
-    <mergeCell ref="A911:A912"/>
-    <mergeCell ref="B911:B912"/>
-    <mergeCell ref="A914:C914"/>
-    <mergeCell ref="A915:C915"/>
-    <mergeCell ref="A919:A920"/>
-    <mergeCell ref="B919:B920"/>
-    <mergeCell ref="A922:C922"/>
-    <mergeCell ref="A923:C923"/>
-    <mergeCell ref="A889:C889"/>
-    <mergeCell ref="A890:C890"/>
-    <mergeCell ref="A894:A895"/>
-    <mergeCell ref="B894:B895"/>
-    <mergeCell ref="A898:C898"/>
-    <mergeCell ref="A899:C899"/>
-    <mergeCell ref="A903:A904"/>
-    <mergeCell ref="B903:B904"/>
-    <mergeCell ref="A906:C906"/>
-    <mergeCell ref="A824:C824"/>
-    <mergeCell ref="A825:C825"/>
-    <mergeCell ref="A829:A830"/>
-    <mergeCell ref="B829:B830"/>
-    <mergeCell ref="A805:A806"/>
-    <mergeCell ref="B805:B806"/>
-    <mergeCell ref="A808:C808"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="A813:A814"/>
-    <mergeCell ref="B813:B814"/>
-    <mergeCell ref="A816:C816"/>
-    <mergeCell ref="A817:C817"/>
-    <mergeCell ref="A821:A822"/>
-    <mergeCell ref="B821:B822"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="A789:A790"/>
-    <mergeCell ref="B789:B790"/>
-    <mergeCell ref="A792:C792"/>
-    <mergeCell ref="A793:C793"/>
-    <mergeCell ref="A797:A798"/>
-    <mergeCell ref="B797:B798"/>
-    <mergeCell ref="A800:C800"/>
-    <mergeCell ref="A801:C801"/>
-    <mergeCell ref="A767:C767"/>
-    <mergeCell ref="A768:C768"/>
-    <mergeCell ref="A772:A773"/>
-    <mergeCell ref="B772:B773"/>
-    <mergeCell ref="A776:C776"/>
-    <mergeCell ref="A777:C777"/>
-    <mergeCell ref="A781:A782"/>
-    <mergeCell ref="B781:B782"/>
-    <mergeCell ref="A784:C784"/>
-    <mergeCell ref="A605:C605"/>
-    <mergeCell ref="A606:C606"/>
-    <mergeCell ref="A610:A611"/>
-    <mergeCell ref="B610:B611"/>
-    <mergeCell ref="A630:C630"/>
-    <mergeCell ref="A634:A635"/>
-    <mergeCell ref="B634:B635"/>
-    <mergeCell ref="A613:C613"/>
-    <mergeCell ref="A614:C614"/>
-    <mergeCell ref="A618:A619"/>
-    <mergeCell ref="B618:B619"/>
-    <mergeCell ref="A621:C621"/>
-    <mergeCell ref="A622:C622"/>
-    <mergeCell ref="A626:A627"/>
-    <mergeCell ref="B626:B627"/>
-    <mergeCell ref="A629:C629"/>
-    <mergeCell ref="A589:C589"/>
-    <mergeCell ref="A590:C590"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="B577:B578"/>
-    <mergeCell ref="A594:A595"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="A597:C597"/>
-    <mergeCell ref="A598:C598"/>
-    <mergeCell ref="A602:A603"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="A536:A537"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="A539:C539"/>
-    <mergeCell ref="A540:C540"/>
-    <mergeCell ref="A544:A545"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A581:C581"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="B585:B586"/>
-    <mergeCell ref="A516:C516"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A523:C523"/>
-    <mergeCell ref="A524:C524"/>
-    <mergeCell ref="A528:A529"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="A532:C532"/>
+  <mergeCells count="580">
+    <mergeCell ref="A1174:C1174"/>
+    <mergeCell ref="A1175:C1175"/>
+    <mergeCell ref="A1179:A1180"/>
+    <mergeCell ref="B1179:B1180"/>
+    <mergeCell ref="A1155:A1156"/>
+    <mergeCell ref="B1155:B1156"/>
+    <mergeCell ref="A1158:C1158"/>
+    <mergeCell ref="A1159:C1159"/>
+    <mergeCell ref="A1163:A1164"/>
+    <mergeCell ref="B1163:B1164"/>
+    <mergeCell ref="A1166:C1166"/>
+    <mergeCell ref="A1167:C1167"/>
+    <mergeCell ref="A1171:A1172"/>
+    <mergeCell ref="B1171:B1172"/>
+    <mergeCell ref="A1135:C1135"/>
+    <mergeCell ref="A1139:A1140"/>
+    <mergeCell ref="B1139:B1140"/>
+    <mergeCell ref="A1142:C1142"/>
+    <mergeCell ref="A1143:C1143"/>
+    <mergeCell ref="A1147:A1148"/>
+    <mergeCell ref="B1147:B1148"/>
+    <mergeCell ref="A1150:C1150"/>
+    <mergeCell ref="A1151:C1151"/>
+    <mergeCell ref="A1117:C1117"/>
+    <mergeCell ref="A1118:C1118"/>
+    <mergeCell ref="A1122:A1123"/>
+    <mergeCell ref="B1122:B1123"/>
+    <mergeCell ref="A1126:C1126"/>
+    <mergeCell ref="A1127:C1127"/>
+    <mergeCell ref="A1131:A1132"/>
+    <mergeCell ref="B1131:B1132"/>
+    <mergeCell ref="A1134:C1134"/>
+    <mergeCell ref="A1060:C1060"/>
+    <mergeCell ref="A1061:C1061"/>
+    <mergeCell ref="A1065:A1066"/>
+    <mergeCell ref="B1065:B1066"/>
+    <mergeCell ref="A1041:A1042"/>
+    <mergeCell ref="B1041:B1042"/>
+    <mergeCell ref="A1044:C1044"/>
+    <mergeCell ref="A1045:C1045"/>
+    <mergeCell ref="A1049:A1050"/>
+    <mergeCell ref="B1049:B1050"/>
+    <mergeCell ref="A1052:C1052"/>
+    <mergeCell ref="A1053:C1053"/>
+    <mergeCell ref="A1057:A1058"/>
+    <mergeCell ref="B1057:B1058"/>
+    <mergeCell ref="A1021:C1021"/>
+    <mergeCell ref="A1025:A1026"/>
+    <mergeCell ref="B1025:B1026"/>
+    <mergeCell ref="A1028:C1028"/>
+    <mergeCell ref="A1029:C1029"/>
+    <mergeCell ref="A1033:A1034"/>
+    <mergeCell ref="B1033:B1034"/>
+    <mergeCell ref="A1036:C1036"/>
+    <mergeCell ref="A1037:C1037"/>
+    <mergeCell ref="A1003:C1003"/>
+    <mergeCell ref="A1004:C1004"/>
+    <mergeCell ref="A1008:A1009"/>
+    <mergeCell ref="B1008:B1009"/>
+    <mergeCell ref="A1012:C1012"/>
+    <mergeCell ref="A1013:C1013"/>
+    <mergeCell ref="A1017:A1018"/>
+    <mergeCell ref="B1017:B1018"/>
+    <mergeCell ref="A1020:C1020"/>
+    <mergeCell ref="A995:C995"/>
+    <mergeCell ref="A996:C996"/>
+    <mergeCell ref="A1000:A1001"/>
+    <mergeCell ref="B1000:B1001"/>
+    <mergeCell ref="A976:A977"/>
+    <mergeCell ref="B976:B977"/>
+    <mergeCell ref="A979:C979"/>
+    <mergeCell ref="A980:C980"/>
+    <mergeCell ref="A984:A985"/>
+    <mergeCell ref="B984:B985"/>
+    <mergeCell ref="A987:C987"/>
+    <mergeCell ref="A988:C988"/>
+    <mergeCell ref="A992:A993"/>
+    <mergeCell ref="B992:B993"/>
+    <mergeCell ref="A956:C956"/>
+    <mergeCell ref="A960:A961"/>
+    <mergeCell ref="B960:B961"/>
+    <mergeCell ref="A963:C963"/>
+    <mergeCell ref="A964:C964"/>
+    <mergeCell ref="A968:A969"/>
+    <mergeCell ref="B968:B969"/>
+    <mergeCell ref="A971:C971"/>
+    <mergeCell ref="A972:C972"/>
+    <mergeCell ref="A938:C938"/>
+    <mergeCell ref="A939:C939"/>
+    <mergeCell ref="A943:A944"/>
+    <mergeCell ref="B943:B944"/>
+    <mergeCell ref="A947:C947"/>
+    <mergeCell ref="A948:C948"/>
+    <mergeCell ref="A952:A953"/>
+    <mergeCell ref="B952:B953"/>
+    <mergeCell ref="A955:C955"/>
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="B870:B871"/>
+    <mergeCell ref="A873:C873"/>
+    <mergeCell ref="A874:C874"/>
+    <mergeCell ref="A878:A879"/>
+    <mergeCell ref="B878:B879"/>
+    <mergeCell ref="A881:C881"/>
+    <mergeCell ref="A882:C882"/>
+    <mergeCell ref="A886:A887"/>
+    <mergeCell ref="B886:B887"/>
+    <mergeCell ref="A850:C850"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="B854:B855"/>
+    <mergeCell ref="A857:C857"/>
+    <mergeCell ref="A858:C858"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="B862:B863"/>
+    <mergeCell ref="A865:C865"/>
+    <mergeCell ref="A866:C866"/>
+    <mergeCell ref="A832:C832"/>
+    <mergeCell ref="A833:C833"/>
+    <mergeCell ref="A837:A838"/>
+    <mergeCell ref="B837:B838"/>
+    <mergeCell ref="A841:C841"/>
+    <mergeCell ref="A842:C842"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="B846:B847"/>
+    <mergeCell ref="A849:C849"/>
+    <mergeCell ref="A759:C759"/>
+    <mergeCell ref="A760:C760"/>
+    <mergeCell ref="A764:A765"/>
+    <mergeCell ref="B764:B765"/>
+    <mergeCell ref="A740:A741"/>
+    <mergeCell ref="B740:B741"/>
+    <mergeCell ref="A743:C743"/>
+    <mergeCell ref="A744:C744"/>
+    <mergeCell ref="A748:A749"/>
+    <mergeCell ref="B748:B749"/>
+    <mergeCell ref="A751:C751"/>
+    <mergeCell ref="A752:C752"/>
+    <mergeCell ref="A756:A757"/>
+    <mergeCell ref="B756:B757"/>
+    <mergeCell ref="A720:C720"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="B724:B725"/>
+    <mergeCell ref="A727:C727"/>
+    <mergeCell ref="A728:C728"/>
+    <mergeCell ref="A732:A733"/>
+    <mergeCell ref="B732:B733"/>
+    <mergeCell ref="A735:C735"/>
+    <mergeCell ref="A736:C736"/>
+    <mergeCell ref="A702:C702"/>
+    <mergeCell ref="A703:C703"/>
+    <mergeCell ref="A707:A708"/>
+    <mergeCell ref="B707:B708"/>
+    <mergeCell ref="A711:C711"/>
+    <mergeCell ref="A712:C712"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="B716:B717"/>
+    <mergeCell ref="A719:C719"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="A699:A700"/>
+    <mergeCell ref="B699:B700"/>
+    <mergeCell ref="A675:A676"/>
+    <mergeCell ref="B675:B676"/>
+    <mergeCell ref="A678:C678"/>
+    <mergeCell ref="A679:C679"/>
+    <mergeCell ref="A683:A684"/>
+    <mergeCell ref="B683:B684"/>
+    <mergeCell ref="A686:C686"/>
+    <mergeCell ref="A687:C687"/>
+    <mergeCell ref="A691:A692"/>
+    <mergeCell ref="B691:B692"/>
+    <mergeCell ref="A655:C655"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="A662:C662"/>
+    <mergeCell ref="A663:C663"/>
+    <mergeCell ref="A667:A668"/>
+    <mergeCell ref="B667:B668"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="A637:C637"/>
+    <mergeCell ref="A638:C638"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="B642:B643"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A647:C647"/>
+    <mergeCell ref="A651:A652"/>
+    <mergeCell ref="B651:B652"/>
+    <mergeCell ref="A654:C654"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A487:A488"/>
+    <mergeCell ref="B487:B488"/>
+    <mergeCell ref="A565:C565"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="B569:B570"/>
+    <mergeCell ref="A572:C572"/>
+    <mergeCell ref="A573:C573"/>
+    <mergeCell ref="A547:C547"/>
+    <mergeCell ref="A548:C548"/>
+    <mergeCell ref="A552:A553"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="A557:C557"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="B561:B562"/>
+    <mergeCell ref="A564:C564"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="A507:C507"/>
+    <mergeCell ref="A508:C508"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="B512:B513"/>
+    <mergeCell ref="A515:C515"/>
+    <mergeCell ref="A466:C466"/>
+    <mergeCell ref="A467:C467"/>
+    <mergeCell ref="A471:A472"/>
+    <mergeCell ref="B471:B472"/>
+    <mergeCell ref="A474:C474"/>
+    <mergeCell ref="A475:C475"/>
+    <mergeCell ref="A479:A480"/>
+    <mergeCell ref="B479:B480"/>
+    <mergeCell ref="A482:C482"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="B373:B374"/>
+    <mergeCell ref="A353:C353"/>
+    <mergeCell ref="A357:A358"/>
+    <mergeCell ref="B357:B358"/>
+    <mergeCell ref="A360:C360"/>
+    <mergeCell ref="A361:C361"/>
+    <mergeCell ref="A365:A366"/>
+    <mergeCell ref="B365:B366"/>
+    <mergeCell ref="A368:C368"/>
+    <mergeCell ref="A369:C369"/>
+    <mergeCell ref="A336:C336"/>
+    <mergeCell ref="A337:C337"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B341:B342"/>
+    <mergeCell ref="A344:C344"/>
+    <mergeCell ref="A345:C345"/>
+    <mergeCell ref="A349:A350"/>
+    <mergeCell ref="B349:B350"/>
+    <mergeCell ref="A352:C352"/>
+    <mergeCell ref="A288:C288"/>
+    <mergeCell ref="A295:C295"/>
+    <mergeCell ref="A296:C296"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A304:C304"/>
+    <mergeCell ref="A328:C328"/>
+    <mergeCell ref="A329:C329"/>
+    <mergeCell ref="A333:A334"/>
+    <mergeCell ref="B333:B334"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="A319:C319"/>
+    <mergeCell ref="A320:C320"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="A312:C312"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A181:C181"/>
+    <mergeCell ref="A189:C189"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A210:A211"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A251:A252"/>
+    <mergeCell ref="A259:A260"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A311:C311"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A254:C254"/>
+    <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A262:C262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A272:C272"/>
+    <mergeCell ref="A279:C279"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A280:C280"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B259:B260"/>
+    <mergeCell ref="B267:B268"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="A287:C287"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A376:C376"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="B177:B178"/>
+    <mergeCell ref="B185:B186"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="A377:C377"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="B381:B382"/>
+    <mergeCell ref="A385:C385"/>
+    <mergeCell ref="A386:C386"/>
+    <mergeCell ref="A390:A391"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A398:A399"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="A401:C401"/>
+    <mergeCell ref="A402:C402"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="A409:C409"/>
+    <mergeCell ref="A410:C410"/>
+    <mergeCell ref="A414:A415"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="A417:C417"/>
+    <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="A425:C425"/>
+    <mergeCell ref="A426:C426"/>
     <mergeCell ref="A430:A431"/>
     <mergeCell ref="B430:B431"/>
     <mergeCell ref="A490:C490"/>
@@ -8684,405 +9457,131 @@
     <mergeCell ref="A459:C459"/>
     <mergeCell ref="A463:A464"/>
     <mergeCell ref="B463:B464"/>
-    <mergeCell ref="A410:C410"/>
-    <mergeCell ref="A414:A415"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="A417:C417"/>
-    <mergeCell ref="A418:C418"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="A425:C425"/>
-    <mergeCell ref="A426:C426"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A394:C394"/>
-    <mergeCell ref="A398:A399"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="A401:C401"/>
-    <mergeCell ref="A402:C402"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="A409:C409"/>
-    <mergeCell ref="A377:C377"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="B381:B382"/>
-    <mergeCell ref="A385:C385"/>
-    <mergeCell ref="A386:C386"/>
-    <mergeCell ref="A390:A391"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B251:B252"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A376:C376"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="B169:B170"/>
-    <mergeCell ref="B177:B178"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A242:A243"/>
-    <mergeCell ref="A251:A252"/>
-    <mergeCell ref="A259:A260"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A311:C311"/>
-    <mergeCell ref="A246:C246"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A254:C254"/>
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A262:C262"/>
-    <mergeCell ref="A263:C263"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A280:C280"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B259:B260"/>
-    <mergeCell ref="B267:B268"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="A287:C287"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A238:C238"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A237:C237"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A190:C190"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A198:C198"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="B145:B146"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A210:A211"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A137:A138"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="A288:C288"/>
-    <mergeCell ref="A295:C295"/>
-    <mergeCell ref="A296:C296"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="A328:C328"/>
-    <mergeCell ref="A329:C329"/>
-    <mergeCell ref="A333:A334"/>
-    <mergeCell ref="B333:B334"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="A319:C319"/>
-    <mergeCell ref="A320:C320"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="A312:C312"/>
-    <mergeCell ref="A336:C336"/>
-    <mergeCell ref="A337:C337"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B341:B342"/>
-    <mergeCell ref="A344:C344"/>
-    <mergeCell ref="A345:C345"/>
-    <mergeCell ref="A349:A350"/>
-    <mergeCell ref="B349:B350"/>
-    <mergeCell ref="A352:C352"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="B373:B374"/>
-    <mergeCell ref="A353:C353"/>
-    <mergeCell ref="A357:A358"/>
-    <mergeCell ref="B357:B358"/>
-    <mergeCell ref="A360:C360"/>
-    <mergeCell ref="A361:C361"/>
-    <mergeCell ref="A365:A366"/>
-    <mergeCell ref="B365:B366"/>
-    <mergeCell ref="A368:C368"/>
-    <mergeCell ref="A369:C369"/>
-    <mergeCell ref="A466:C466"/>
-    <mergeCell ref="A467:C467"/>
-    <mergeCell ref="A471:A472"/>
-    <mergeCell ref="B471:B472"/>
-    <mergeCell ref="A474:C474"/>
-    <mergeCell ref="A475:C475"/>
-    <mergeCell ref="A479:A480"/>
-    <mergeCell ref="B479:B480"/>
-    <mergeCell ref="A482:C482"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A487:A488"/>
-    <mergeCell ref="B487:B488"/>
-    <mergeCell ref="A565:C565"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="B569:B570"/>
-    <mergeCell ref="A572:C572"/>
-    <mergeCell ref="A573:C573"/>
-    <mergeCell ref="A547:C547"/>
-    <mergeCell ref="A548:C548"/>
-    <mergeCell ref="A552:A553"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="A557:C557"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="B561:B562"/>
-    <mergeCell ref="A564:C564"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="A507:C507"/>
-    <mergeCell ref="A508:C508"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="A515:C515"/>
-    <mergeCell ref="A637:C637"/>
-    <mergeCell ref="A638:C638"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="B642:B643"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A647:C647"/>
-    <mergeCell ref="A651:A652"/>
-    <mergeCell ref="B651:B652"/>
-    <mergeCell ref="A654:C654"/>
-    <mergeCell ref="A655:C655"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="A662:C662"/>
-    <mergeCell ref="A663:C663"/>
-    <mergeCell ref="A667:A668"/>
-    <mergeCell ref="B667:B668"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="A699:A700"/>
-    <mergeCell ref="B699:B700"/>
-    <mergeCell ref="A675:A676"/>
-    <mergeCell ref="B675:B676"/>
-    <mergeCell ref="A678:C678"/>
-    <mergeCell ref="A679:C679"/>
-    <mergeCell ref="A683:A684"/>
-    <mergeCell ref="B683:B684"/>
-    <mergeCell ref="A686:C686"/>
-    <mergeCell ref="A687:C687"/>
-    <mergeCell ref="A691:A692"/>
-    <mergeCell ref="B691:B692"/>
-    <mergeCell ref="A702:C702"/>
-    <mergeCell ref="A703:C703"/>
-    <mergeCell ref="A707:A708"/>
-    <mergeCell ref="B707:B708"/>
-    <mergeCell ref="A711:C711"/>
-    <mergeCell ref="A712:C712"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="B716:B717"/>
-    <mergeCell ref="A719:C719"/>
-    <mergeCell ref="A720:C720"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="B724:B725"/>
-    <mergeCell ref="A727:C727"/>
-    <mergeCell ref="A728:C728"/>
-    <mergeCell ref="A732:A733"/>
-    <mergeCell ref="B732:B733"/>
-    <mergeCell ref="A735:C735"/>
-    <mergeCell ref="A736:C736"/>
-    <mergeCell ref="A759:C759"/>
-    <mergeCell ref="A760:C760"/>
-    <mergeCell ref="A764:A765"/>
-    <mergeCell ref="B764:B765"/>
-    <mergeCell ref="A740:A741"/>
-    <mergeCell ref="B740:B741"/>
-    <mergeCell ref="A743:C743"/>
-    <mergeCell ref="A744:C744"/>
-    <mergeCell ref="A748:A749"/>
-    <mergeCell ref="B748:B749"/>
-    <mergeCell ref="A751:C751"/>
-    <mergeCell ref="A752:C752"/>
-    <mergeCell ref="A756:A757"/>
-    <mergeCell ref="B756:B757"/>
-    <mergeCell ref="A832:C832"/>
-    <mergeCell ref="A833:C833"/>
-    <mergeCell ref="A837:A838"/>
-    <mergeCell ref="B837:B838"/>
-    <mergeCell ref="A841:C841"/>
-    <mergeCell ref="A842:C842"/>
-    <mergeCell ref="A846:A847"/>
-    <mergeCell ref="B846:B847"/>
-    <mergeCell ref="A849:C849"/>
-    <mergeCell ref="A850:C850"/>
-    <mergeCell ref="A854:A855"/>
-    <mergeCell ref="B854:B855"/>
-    <mergeCell ref="A857:C857"/>
-    <mergeCell ref="A858:C858"/>
-    <mergeCell ref="A862:A863"/>
-    <mergeCell ref="B862:B863"/>
-    <mergeCell ref="A865:C865"/>
-    <mergeCell ref="A866:C866"/>
-    <mergeCell ref="A870:A871"/>
-    <mergeCell ref="B870:B871"/>
-    <mergeCell ref="A873:C873"/>
-    <mergeCell ref="A874:C874"/>
-    <mergeCell ref="A878:A879"/>
-    <mergeCell ref="B878:B879"/>
-    <mergeCell ref="A881:C881"/>
-    <mergeCell ref="A882:C882"/>
-    <mergeCell ref="A886:A887"/>
-    <mergeCell ref="B886:B887"/>
-    <mergeCell ref="A938:C938"/>
-    <mergeCell ref="A939:C939"/>
-    <mergeCell ref="A943:A944"/>
-    <mergeCell ref="B943:B944"/>
-    <mergeCell ref="A947:C947"/>
-    <mergeCell ref="A948:C948"/>
-    <mergeCell ref="A952:A953"/>
-    <mergeCell ref="B952:B953"/>
-    <mergeCell ref="A955:C955"/>
-    <mergeCell ref="A956:C956"/>
-    <mergeCell ref="A960:A961"/>
-    <mergeCell ref="B960:B961"/>
-    <mergeCell ref="A963:C963"/>
-    <mergeCell ref="A964:C964"/>
-    <mergeCell ref="A968:A969"/>
-    <mergeCell ref="B968:B969"/>
-    <mergeCell ref="A971:C971"/>
-    <mergeCell ref="A972:C972"/>
-    <mergeCell ref="A995:C995"/>
-    <mergeCell ref="A996:C996"/>
-    <mergeCell ref="A1000:A1001"/>
-    <mergeCell ref="B1000:B1001"/>
-    <mergeCell ref="A976:A977"/>
-    <mergeCell ref="B976:B977"/>
-    <mergeCell ref="A979:C979"/>
-    <mergeCell ref="A980:C980"/>
-    <mergeCell ref="A984:A985"/>
-    <mergeCell ref="B984:B985"/>
-    <mergeCell ref="A987:C987"/>
-    <mergeCell ref="A988:C988"/>
-    <mergeCell ref="A992:A993"/>
-    <mergeCell ref="B992:B993"/>
-    <mergeCell ref="A1003:C1003"/>
-    <mergeCell ref="A1004:C1004"/>
-    <mergeCell ref="A1008:A1009"/>
-    <mergeCell ref="B1008:B1009"/>
-    <mergeCell ref="A1012:C1012"/>
-    <mergeCell ref="A1013:C1013"/>
-    <mergeCell ref="A1017:A1018"/>
-    <mergeCell ref="B1017:B1018"/>
-    <mergeCell ref="A1020:C1020"/>
-    <mergeCell ref="A1021:C1021"/>
-    <mergeCell ref="A1025:A1026"/>
-    <mergeCell ref="B1025:B1026"/>
-    <mergeCell ref="A1028:C1028"/>
-    <mergeCell ref="A1029:C1029"/>
-    <mergeCell ref="A1033:A1034"/>
-    <mergeCell ref="B1033:B1034"/>
-    <mergeCell ref="A1036:C1036"/>
-    <mergeCell ref="A1037:C1037"/>
-    <mergeCell ref="A1060:C1060"/>
-    <mergeCell ref="A1061:C1061"/>
-    <mergeCell ref="A1065:A1066"/>
-    <mergeCell ref="B1065:B1066"/>
-    <mergeCell ref="A1041:A1042"/>
-    <mergeCell ref="B1041:B1042"/>
-    <mergeCell ref="A1044:C1044"/>
-    <mergeCell ref="A1045:C1045"/>
-    <mergeCell ref="A1049:A1050"/>
-    <mergeCell ref="B1049:B1050"/>
-    <mergeCell ref="A1052:C1052"/>
-    <mergeCell ref="A1053:C1053"/>
-    <mergeCell ref="A1057:A1058"/>
-    <mergeCell ref="B1057:B1058"/>
+    <mergeCell ref="A516:C516"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="A523:C523"/>
+    <mergeCell ref="A524:C524"/>
+    <mergeCell ref="A528:A529"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="A532:C532"/>
+    <mergeCell ref="A536:A537"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="A539:C539"/>
+    <mergeCell ref="A540:C540"/>
+    <mergeCell ref="A544:A545"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="A581:C581"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="B585:B586"/>
+    <mergeCell ref="A589:C589"/>
+    <mergeCell ref="A590:C590"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="B577:B578"/>
+    <mergeCell ref="A594:A595"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="A597:C597"/>
+    <mergeCell ref="A598:C598"/>
+    <mergeCell ref="A602:A603"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="A605:C605"/>
+    <mergeCell ref="A606:C606"/>
+    <mergeCell ref="A610:A611"/>
+    <mergeCell ref="B610:B611"/>
+    <mergeCell ref="A630:C630"/>
+    <mergeCell ref="A634:A635"/>
+    <mergeCell ref="B634:B635"/>
+    <mergeCell ref="A613:C613"/>
+    <mergeCell ref="A614:C614"/>
+    <mergeCell ref="A618:A619"/>
+    <mergeCell ref="B618:B619"/>
+    <mergeCell ref="A621:C621"/>
+    <mergeCell ref="A622:C622"/>
+    <mergeCell ref="A626:A627"/>
+    <mergeCell ref="B626:B627"/>
+    <mergeCell ref="A629:C629"/>
+    <mergeCell ref="A767:C767"/>
+    <mergeCell ref="A768:C768"/>
+    <mergeCell ref="A772:A773"/>
+    <mergeCell ref="B772:B773"/>
+    <mergeCell ref="A776:C776"/>
+    <mergeCell ref="A777:C777"/>
+    <mergeCell ref="A781:A782"/>
+    <mergeCell ref="B781:B782"/>
+    <mergeCell ref="A784:C784"/>
+    <mergeCell ref="A785:C785"/>
+    <mergeCell ref="A789:A790"/>
+    <mergeCell ref="B789:B790"/>
+    <mergeCell ref="A792:C792"/>
+    <mergeCell ref="A793:C793"/>
+    <mergeCell ref="A797:A798"/>
+    <mergeCell ref="B797:B798"/>
+    <mergeCell ref="A800:C800"/>
+    <mergeCell ref="A801:C801"/>
+    <mergeCell ref="A824:C824"/>
+    <mergeCell ref="A825:C825"/>
+    <mergeCell ref="A829:A830"/>
+    <mergeCell ref="B829:B830"/>
+    <mergeCell ref="A805:A806"/>
+    <mergeCell ref="B805:B806"/>
+    <mergeCell ref="A808:C808"/>
+    <mergeCell ref="A809:C809"/>
+    <mergeCell ref="A813:A814"/>
+    <mergeCell ref="B813:B814"/>
+    <mergeCell ref="A816:C816"/>
+    <mergeCell ref="A817:C817"/>
+    <mergeCell ref="A821:A822"/>
+    <mergeCell ref="B821:B822"/>
+    <mergeCell ref="A889:C889"/>
+    <mergeCell ref="A890:C890"/>
+    <mergeCell ref="A894:A895"/>
+    <mergeCell ref="B894:B895"/>
+    <mergeCell ref="A898:C898"/>
+    <mergeCell ref="A899:C899"/>
+    <mergeCell ref="A903:A904"/>
+    <mergeCell ref="B903:B904"/>
+    <mergeCell ref="A906:C906"/>
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="B927:B928"/>
+    <mergeCell ref="A930:C930"/>
+    <mergeCell ref="A931:C931"/>
+    <mergeCell ref="A935:A936"/>
+    <mergeCell ref="B935:B936"/>
+    <mergeCell ref="A907:C907"/>
+    <mergeCell ref="A911:A912"/>
+    <mergeCell ref="B911:B912"/>
+    <mergeCell ref="A914:C914"/>
+    <mergeCell ref="A915:C915"/>
+    <mergeCell ref="A919:A920"/>
+    <mergeCell ref="B919:B920"/>
+    <mergeCell ref="A922:C922"/>
+    <mergeCell ref="A923:C923"/>
+    <mergeCell ref="A1068:C1068"/>
+    <mergeCell ref="A1069:C1069"/>
+    <mergeCell ref="A1073:A1074"/>
+    <mergeCell ref="B1073:B1074"/>
+    <mergeCell ref="A1077:C1077"/>
+    <mergeCell ref="A1078:C1078"/>
+    <mergeCell ref="A1082:A1083"/>
+    <mergeCell ref="B1082:B1083"/>
+    <mergeCell ref="A1085:C1085"/>
+    <mergeCell ref="A1106:A1107"/>
+    <mergeCell ref="B1106:B1107"/>
+    <mergeCell ref="A1109:C1109"/>
+    <mergeCell ref="A1110:C1110"/>
+    <mergeCell ref="A1114:A1115"/>
+    <mergeCell ref="B1114:B1115"/>
+    <mergeCell ref="A1086:C1086"/>
+    <mergeCell ref="A1090:A1091"/>
+    <mergeCell ref="B1090:B1091"/>
+    <mergeCell ref="A1093:C1093"/>
+    <mergeCell ref="A1094:C1094"/>
+    <mergeCell ref="A1098:A1099"/>
+    <mergeCell ref="B1098:B1099"/>
+    <mergeCell ref="A1101:C1101"/>
+    <mergeCell ref="A1102:C1102"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
